--- a/nigeria_kidnapping_excelpivotcharts.xlsx
+++ b/nigeria_kidnapping_excelpivotcharts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\_USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\nigeriafolder\NIGERIA-KIDNAPPING-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543E2612-36D7-4B59-933F-4EB521F9CC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9B8ACF-085E-40EC-9F4B-D5DDB0A4065F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlchart.v5.1" hidden="1">'Pivot chart'!$A$19:$A$32</definedName>
     <definedName name="_xlchart.v5.2" hidden="1">'Pivot chart'!$B$18</definedName>
     <definedName name="_xlchart.v5.3" hidden="1">'Pivot chart'!$B$19:$B$32</definedName>
-    <definedName name="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_3" hidden="1">Table1_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_31" hidden="1">Table1_3[]</definedName>
     <definedName name="ExternalData_2" localSheetId="1" hidden="1">Table1_2!$A$1:$Q$201</definedName>
     <definedName name="TA">'Pivot table'!$F$54</definedName>
     <definedName name="TD">'Pivot table'!$G$54</definedName>
@@ -89,7 +89,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Table1_3" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_3"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_31"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -1059,7 +1059,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[nigeria_kidnapping_dataset grp 2.xlsx]Pivot table!PivotTable6</c:name>
+    <c:name>[nigeria_kidnapping_excelpivotcharts.xlsx]Pivot table!PivotTable6</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -2898,7 +2898,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[nigeria_kidnapping_dataset grp 2.xlsx]Pivot table!PivotTable21</c:name>
+    <c:name>[nigeria_kidnapping_excelpivotcharts.xlsx]Pivot table!PivotTable21</c:name>
     <c:fmtId val="8"/>
   </c:pivotSource>
   <c:chart>
@@ -4201,7 +4201,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[nigeria_kidnapping_dataset grp 2.xlsx]Pivot table!PivotTable3</c:name>
+    <c:name>[nigeria_kidnapping_excelpivotcharts.xlsx]Pivot table!PivotTable3</c:name>
     <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
@@ -4986,7 +4986,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[nigeria_kidnapping_dataset grp 2.xlsx]Pivot table!PivotTable4</c:name>
+    <c:name>[nigeria_kidnapping_excelpivotcharts.xlsx]Pivot table!PivotTable4</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -5621,7 +5621,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[nigeria_kidnapping_dataset grp 2.xlsx]Pivot table!PivotTable19</c:name>
+    <c:name>[nigeria_kidnapping_excelpivotcharts.xlsx]Pivot table!PivotTable19</c:name>
     <c:fmtId val="10"/>
   </c:pivotSource>
   <c:chart>
@@ -6202,7 +6202,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[nigeria_kidnapping_dataset grp 2.xlsx]Pivot table!PivotTable7</c:name>
+    <c:name>[nigeria_kidnapping_excelpivotcharts.xlsx]Pivot table!PivotTable7</c:name>
     <c:fmtId val="7"/>
   </c:pivotSource>
   <c:chart>
@@ -7344,7 +7344,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[nigeria_kidnapping_dataset grp 2.xlsx]Pivot table!PivotTable2</c:name>
+    <c:name>[nigeria_kidnapping_excelpivotcharts.xlsx]Pivot table!PivotTable2</c:name>
     <c:fmtId val="6"/>
   </c:pivotSource>
   <c:chart>
@@ -10163,781 +10163,778 @@
           <cx:layoutPr>
             <cx:geography cultureLanguage="en-US" cultureRegion="TH" attribution="Powered by Bing">
               <cx:geoCache provider="{E9337A44-BEBE-4D9F-B70C-5C5E7DAFC167}">
-                <cx:binary>3Htpb+W2kvZfCfL5lcNd1MVkgKF0Fu/dbveWL4Lb7ZCUKFESqfXXTzndndi+N3eQIAO8GQdw2ubh
-ORSLVfUs9H/cL/+4dw93w3dL49rwj/vlx+9NjN0/fvgh3JuH5i6cNPZ+8MH/HE/uffOD//lne//w
-w+fhbrat/oEgzH64N3dDfFi+/8//gHfTD/7C399F69vX48Ow3jyE0cXwb8b+5dB3d58b2xY2xMHe
-R/zj98WDi3fff/fQRhvX27V7+PH7Zy/5/rsfXr7RP33odw7WFcfPMJefcJJSJFCaffmS33/nfKu/
-DosTnEqGBbzkyxf79tFXdw1M/2U1372Jd/Hh28C/WtMvK7r7/Hl4CAGe6Jf/v5j87CFejN37sY2P
-W6hhN3/8/srqh8HCJtjg8y9DuX98mKvDL0//w/Pt/8//ePEL2I8Xv3kSoZeb9z8N/VOA/uvTWP2P
-Afrf/Pz2rvk0/I8reL5H/+6IiBOCJcVUyK9HRLw4IhmnGA7J7xyR//qynj97SF5Mf3FMXoz+rQ7K
-+V3r/13S/LFExvhEZkzSjGTPwiNPOBUQHPwtevTbZ37J4MdV/NnYPJ37IjBPh/5WUVEP7fhva9kf
-C0t6QjniKWPftv958siTNE2JTBmU3S8l/UtUflnFnw3Ls8kv4vJs7O8VGD/8pflCTrBMOc3ws3TB
-9IQiiRBl5Gu1exGYx1X86cA8nfwyME/H/laBOb/7PLZ/Yb/B6IRKwinB5Flo0hPJKSWEo6+RgUL3
-NGe+rOPPxub57BfBeT74N4tODPYvDQ854QJyhKRfIeHzBEpPBEHpE0CZvozSL+v582F6Nv2f4vRs
-9G8VqIs77cO3vfpXIPqPNR4BwF5kiGL2W7Y8Afb0hKcpQ4h9G37RgH5ZzZ8N0rPJL0L0bOxvFaBr
-PbZ/ZXyyVEqeZt+AwXPiRU8YlYDlKPmaZVALnxa7x8X82fA8nfsiOk+H/l7BWf9CLC2B8XAMjeZl
-TLhgRGYSKt6zWKx/GhFc/zb1ZSR+G/lbBeLGTg/DX1jH2Mmj/oAIYLIvX6BAPKlj4kQKxJBMv42/
-yJMvy/mzmfJ89osIPR/8WwXpp7vm57u/UiPA5ASBhIQQeRkehjPMKP7WhF6gga8L+bPxeTH9RYBe
-jP5/HaHfW9yXOvMFDjx7zR/U+bITAelDufiG2vizNEpPHgOUAiP6LcuelrhfJbffX8+/1vh+nfhs
-8f/rGt7v62u/Kl3FXbzb/aKiPpH4/v3oN23wxdSvzeBfYrYv+3X6+cfvscCCEEiFJ5F7fKNnreSX
-7XqeDS/mPtyF+OP3ICukUjCIGNRGKaWAvJofHkcegZ0AMVcKkOVSyikEuvVDNLACDLPg1ZkQVGQC
-Otn33wU/Pg5JIMMU4cf/QCmiPGO/qtivvFu1b3/dma8/f9eOzStv2xh+/J4heKjuy+selwtqMQXZ
-I0VcAEtIEROgenT3dzcglcPL8f+b1g7RhOndwpHZ1XFBl0s5VnXOp2R6reVYHdPV889skPMprRN+
-1JsbD3ool6s2ZvS2ot6e65BNr5pEBL+rWN0rthKSjy6ZXk0jFQexCXLG13kalUvYKtfLbBJ19fOK
-Svsq6XuLTN4P7ShJXm89j2qLTFdnXSq7i8GWrFahJevHNpJ+PkrcBapClbl0L6uUV7m0Al+WzcCS
-3VAzjC8c4eO1JPDQisdtfts0Y7mXkpQ7wUMosq6vPy5UJoVFoRtf2dWt99vAFqxYlphrP6TNWyzr
-yuasitSoASWLVAi29X1fY7afzdjFAmm5sHydWLWTg/N1Pgtn7ohjZirsspb7kmVL4ZM6voqTS4ci
-GT1TTWrtq4nMNk9L0uHctHY5as7YTZNtOqi6ll1TSGlcpzCryK2sShqPScbN6caXsO7jkJImJ7iu
-NzU343xIqNBajWtWP0CQxUWdirVRqU7K08nXessxp/I1a1hrlSYTPyRrl9mdJjayIs6reL2tIWnV
-MAfdKU4rfrGOlfeqT7V8mFrvP1XBmrswZutlPzOK8mrSmB8WLcLVRiYWFZlQY4tB+NnkGUmoU7qr
-w8+9MV2rliDZDeokfb/5SN6VPnO+kDSKD8Lj0KmpaebDUHOf7UdrGcrTzVdtzrNxa5Qjq7lrYbFH
-LO3wLmEovdRmIbpwBDydXDRd0pyOS5lT2rn5UFU82RRJycKKqkthX9dkvRC1aOJFstQr3fFyWdye
-zaQLqi1n8ZpBBrlcMNGIfFxQ44+xcWTO6SDNlossknWXpEG2eRWS8NOc2HnZpXPnx4IEUa0X1bqQ
-wyqq+tLxGg2HmGW1yUeMIA5zX3p8G7CBByVlNe7aKY17ZpC7S3pELpGD3zVjELMqESv3w9yLC7QE
-iKPdvD6Uk+1PqWnIO9Z78rZkvLmuCIRjnMdBXs1zM7zZ+r6mcFy0FirLmkwr37WJKRAyAd6hqZvT
-uYpcnJlxXesi8Wi1qooL7VQ6IenzNfbrfMCwPwdJWIiF2Gh8T6xIkEJDVaY57id9plc4o6qsmwXe
-1Kf7Tpft/ZB1zb1D/XbfjmFeC5tJfWq936wy9RavguH0rdQOEk2ndW4HTq6gApujbqK4zHhjY+5w
-aSHLcRMG5bZAbZGSSpaFmMbW5nrb2p8TkUC69XQry8Nik01fpqPp9at2RotTTQzTu6zu6Jno+HxN
-pmVyKqSVHfKY9WLXeDeZPVQLfmu7ub1fmMFdLtNqHY41zGiUTg2bC2x7Xyk8D/TD5DLC1Ow53YrW
-dfisamtaqeBLXee+Jlwe5SbD694tLJ7XLqy98iyukF8E0+qaym7NVOIiKTDUHp470sQtrxMmWlXR
-Db/qkjrN8rLux6CacmxaqIKyQ5eSN4Krcda4UcRzdDbhETUq2+K4KTHS5j7tJjEVwc86QuZzEHl2
-mk7LsOtYjZK8bHSLdn6FMuhJm4459yzZd6TFb7LO2zfEmSxTrpkefLdaqzbvwy2JTf+ayL7BqpMp
-sXnfB6fP4PDXY76iyYZcDFUfr6sNIXfu/Bz3sbT8iMnavpdLmf6UNTXJ9kNtM5e7x0/K8dhdz0DW
-6rxBXB/XcaDLvil5darnSVuVzWY+nRYu+r3YSlRE31dX0lbDJ9i+4dxsrvrQ0NFeyQRKzg52utpv
-eKh3VQ3/qjGaLuQ0o1OEAv2Ip1DtyTYvr8UYEFWSOXuVCBLf+G3zBfWDd6ptUbVfTRUPE5u7m9Fs
-8z560iOVDohfiLh1CdR6Mn/ii9vOQ43IDpeBXzT16ovESfHB1WlzNRuZvUPd2Gf7ElB1e0F4Mto3
-7Vb75cZkE93OcImoPoX6A8UqGYfpPpkph2PZbou/EEk5fdKwz1eQ591NlCPvcpOS7IOnlUew43P5
-eFrI7A54Gqf9KCUbVdpFdLa2k0lzR2sSrpwYGn4qoDU3cBJEj3aZKOn5yNqwqMrqJZeCjvEQMFrA
-bC6jzRGjpVYTWjXeZ1O3IpUFWr5GSdOthShlc4HTED/WcyuXwprUvZXMdPSYNM6/r6qpcvnMFn8T
-DV1+3izHeqfltp0TUoao5q50SV4Zbdcc/tl5JSwp0z3TK27Oa+ET+qHHwl8OkBtdnlaTrPKyrNeb
-evIpzoXDAEISUw7HCiBEstdsHA+VRMennvIzMHQPx3iw2nx19X/98T+vu4f2TRweHuLlXfeL1/zb
-2PMfAVV9haqPUPDZD/+ETX8HfX65WPA7g38ImhJAab9eHvgnaPrG1z6+EDqeYNPHyV+wKVByuA6B
-MxC3QOFCkgPM/IJN2QlmgAqAh4iMCJAnn2BTegJqmAA7JkNw20ASkF6+YlOArTCHokykKSYMEfpH
-sCl5XNhzbJqlKc9QCkIOJ1Rw9BybpgnvMqPJLkvQzHdsrtsjnOeLri2X9x4awbkVvb9rZ5PcJ8K2
-F/C066cZo+xqFFjmg+GZSmdXh6J0Nb4dApZnpTX9UZiG//xYbybFeI+vU4fHnKaxPBNDyc+1n9bT
-2Qu+X5Np/ZiM1OxcRclPvW99Qcrpyk/E5Yn0U1k0I/TSNRXyvOL9+nkUKOjcb7W+sZD98kz70uiC
-96F8NRCvXyODrN/N2Dim0mWZqzxFizyfm5DNReBdAkXck1LnERCT32eJrq0qezGcTaMfGPQmiUe1
-bQuWF9m8le1HKlpc5X2D+kRVGarfjzj108HGTbhc0wa9KslcLrlv2qXN0YAtIN9SxHfB43E4W/VS
-hSIdNwmYYKinW1kzkakBu/TNUAEvU9qV1VuXArLdy+DSz0m5xQwKacDjPiEbeb322s55raEn7qig
-i9m3ybIOSvZyvY209LcV9DFxPpRjyvOZNC1SVVXO9kozaIGqSm35ADU73jI57RNbL0rOrrpxiSXu
-02rSpimmdEO301q212mysZj7LsZbs+hWK5riZufreXnVl008q5fFdqptMrruBmh8h7Zm28Uyh+xy
-SsSy21g/5TGpw7XHWxl3hmTCqjox44PIbKCXJRran6dxCVDHkyzLl8SW9WHK3MSk8r3L+nY/cD6h
-h76GwKhEgjh8YGnZbXuZClb53YD7arnatm5NL0ITcLVf7GK6C0q6qskbXnfbLvAghn2kjRwue1oN
-GzwDzlJV2mZdlK6rTBcttl2vInYb1rkxsfbnTSnHZS6yzWY7Mrd+LcyylOHUDyMPp9NM2bjrVk62
-txLNRLXT1N9yr3t82toGvQ/pTP2d9V0t8mwyuC9kL/gNIwE/ENNPADmGuF5OPRKKOVQf5yzwVm1J
-zWZFnKZcLYImteqTBZGLqgnLcWlie4kHkZ6ubkgPFSCzw+xi/yGkYxrUaEb3IVnL+kOtM8ADc6wB
-qzkj9q1LyJjPdSUuQhnNNU86IIn12gebZwDhbVHx0npV405g1ZohwJky9SkdNC1iaZYhlyQAMoFW
-InbAM6pVRb2aUHQ68iIzKzsuwadWLSawN2wQ+Iw6Tz+Pw7xdW1ttZJdkfrnv4Cx/HsroKnhoPEjY
-NlNawCTEOBVL6vUOQMxacNjdPF2hahYr6hEg87QRp8008rMpxUIr7gU71Ky0H6wf6vUso6Ob8omj
-cLMy7xNFZWwzJRuTXM+p83DDASr919bzf7OpgQYisgyK+++3NPXUc/9Nqfl15pd+htkJdB7wYkBk
-JpQBrvnWzx47E1g0NAPlkzJGKDStb1oLPUlB9JTQa4TAmD7tZ+gEEYLTTIAeB6Pij7Qzjh/b1ROp
-hWRYyBTKH1jmGImMvZBaMLWaZoM4jdGGNgemiD+OwD8bNYR2uPK+AkzX9HZLzmaUxP3oMM19WstB
-VYi1U04gjcpctBZYcWayzZ0yuaVLkaRTQvfaGn61kLXPk46+GtncvKMhmSGZSrqnWxdkXuKlu629
-C5d4DbpUJib0dWcRT6CfmKy+XgBMvpnmYN2ZG5Jlu9yajowqm5LtHKpbgnO3JqK8X0c37MW4JUfb
-d6m/kIlBN7PpqVRSmJGBqLMO7dF0Myoc6AnpqR3ncJgTP+6A6Eq8873piBKlEO/HSJMu11jXN0jW
-Lbw029TQJex6KQVwbhEyonec2XiIZOivuJf4kVGpwetxR1h/qIyszlHWF9YmZFcHUaoaMvum3qY0
-nzZ2jQCF7gjGer/GDZ/aGdgyjVsRoFLlgJHrnOEYIc+zYmxDUD7KFqp6dzSg3l0kzLuLvkveMuQO
-DX/sLRxfhnHEe6eTUyDx5a5CdUFIDVPlao6ShyY3Dc2UBfnttG1Sv5syrgiOLqdTe5rJ5U6OyVkw
-c6V6QN1DnN9VcJ/inFi5Q03vd33dXk+kPwdSwxWwn4Px7nRK5FCEsDVFE1hBV9EoW9vlQ5ek67U1
-w3TapNK852tty6Kkjv9UGmROsXX157E39lOPY7KP0wpdeNym83EY9E2VcPNaOm51vsFtguRct25Y
-L1zHjFaG62RQbQrwKkmbRYGu0DQ561INdXrjVbMf2qzG+7IVw6kjbUzVCCCtzWOfpTehBKygVpe0
-B2Ta5qcETeSYTcyD2NSDwDJHfuBxDpWyj6U6qWz8gGxdvyVV7c6rpIM+UM9dvICncq+mpU6w2gZe
-daCjrTXoFpLJ/TpmxCiJNKrVUkdIqFpUzeXQWI1Uj9GI1QzoUistvFD9huZW9VK0xVri4YNwhOZy
-MMtRuDZ5GMdhvOGjH/NS2+6iK+kCRJKM03FAPuRc87FwJsJOzEA58zEEOIPAH8/bGbc30D/GC9Q1
-S6FZVxXI+/pYEu3elEnlbJEkNrmqTRduaesdgEIL7IxrefS6GWjufAkaGkcg6CybPV+WLbyCQ8TP
-N1HNyq5roki/JSqEKd2hte53bhFmjzgND3RcN8Xdkn2oGsc+V4yNw2UcSJ2aPQ4sTGpyCzSkWzSL
-CVjakqziXGSy30fbB7XRHciD1UEuS30GmqbOh67OPpRsMjl1Ls3htk+VZw1BBckYVQaQz53Nuj31
-t7aJ7LzHq9u7mgzXuvHrfumrT0O/vbFzPBuq9UB03FV2LBpgrGgYjpF1al4aoOd12h6bIfDdptMh
-3wCeX3UsHS9L6zag2/ENRH67AXBR5z1xw3mdbclunIb0oTUhO+tAKT7ycr1lYmwUNmUPuW/Gz6Jt
-51e1GfuzabC7WbZX7Tyy26mazc9IT+vDvLi04Eur85Ahfb6tRr8GpNBBPUjJRdkm6x0B6d6ptS/7
-Yz/HCjhA2xVosCTf+paeQvkczrcWEyWhqO0BihurRh/I7bYInicgXx9kic1+HZi4wFbyt3rZusta
-rNlu3Wb+viRJv+fsds7OmlG/MnjICsB76S4b3asE9M3r1Gw9vIkxF0RnPYiWaC5qTpvXwk38ao5p
-8tqTsTt6CE2u3VQeBUi+19DTLGSOG6e8TilVAMP0+yGTw3HakqlI25W9Zms7782UZtd+Y9uqSoK3
-N9WE613fGnegU4aCigSVb20HQvWwrNm+h2N2YHOl9+OmAYY1Ojkjw7Kc0TbWOa51oVufZzE1OzOL
-BooeYzk2dXLGZBTXWCT+kLTotY39ogxePo9VrNVs7DHU1QGw63Xl9G2jl0tQR6bzbSTNhbRmO1js
-+zwuBiu9BLPvUNaBcCarXcriuE8TtIBa3XW7ahsh0ZPNBpW2YT6SNQODwExr0fNa70ZdvdMlz0B1
-COnbdO3OGIckztq1iEk5eDXrx6PIiR6KdhPdfg6hqaHnJgHn7VSl580wiDJfBVrKKzvjJi081+Wg
-QPmckgKOGP7E06U5rVpbZ6fWlNy+wz3bDmPpe5lPvZ52fBzpoZ94nVfzEi6YIfIUTet2MfFl9rdL
-mthmZ7LBCVDR9aN+GFbQ61DKdXyjDfOfG1zG12Kx7maMOqZFG1Hf5HMFRA0chFjVqh67aT5umwPD
-Q1QjvZOVlJdN2zrFIk8fxFRqk28V5MKVrR97S1YLk68k9FueDTScjl1WIsX7rsUATuBvMKBmJOXZ
-sISeKUaBmKumMRtXHa55p4DX0I8TZnzYgxTa1Hvi4RwccVnpO58u0yd4qgwXNVRrrzYo9NdTI+X5
-QlB2ZBK0fUXtAkwX2/AKD9vnpK7f9EZMXU5XZj6hyYMxNI0dGw5wnuSNQ9ocV1N6aKggoBXrkg7A
-nRhq630m4goQu0LdxdJpV/hNsmLuRHpbLqHh5z6m/q5sgFqoJY6PtlTnrhYOvtLGnVYtoW2p0Gxq
-INptM+el89WRzGw9Ih2T9wAZa3BkZvNuZml4TzbbvprawZ6balt2ZCuX6zjT+A6tKKqqQ+CypLOI
-B9ssYsfXQD9XMdSn4KtBG4bXvEV1PZ4tXQuHk7PtU6aXY4JGtO98jCCj/5+hCPdP/3zk29WdX6Sr
-FASo36cHv3rXv1ED/DjjKS3APANlioJyjX61YAnwBXBTswzDve8sg5tET2nB78lc7ARstMfbRcAm
-Hn14mPVN1HtG0OAPi77+/NSCBWv5OS8AxQzcZs4EfB5GoMTB8p5asKkLhFVjqdxU2W45rGipnKLE
-o+x0c2iVVwC2wLpbJsjTyzGmMRY0uiGcVnqRNTRq0Yp8IWK4TcEtAepbz3q+zjwH+JZw2xNQcMYe
-ybMu4rbKFCOEOA8zakShtHSbUSAeJXZfk3R49HtZxfMOVV5cgog8gxStfQKIzaKRqyYmK1ZegFmd
-T0uVVlAVsG+VoJgtKoAPGtUYanrJuEl+2hILTkY/zsgpztP1koVM/wTOKq1y2pB1ylvw7+D9GlbO
-ChQ+61QtddodWRJNo1g9N1telQS8WDpX2VCsYom9MlU6A14HsADcZgJYtxPIdj5PemiuR9Yy9yFL
-a3LFoFjiXdROXw+gWd0ZLPkHr6P83JUkG/IAFgnYVEOYarUCoBcfSgIf+V7jPnJVMYAolytxWXM2
-T7WbVAvKXFqA4cLkKXPt6t/QrRKx2LptBuaRblnIU/Cttx0C/cCoio/yHZgrFL/h3ozbJa+G8QIE
-ehDWaUwcmKM2jNuZA4wRrkMokTsl1Sij6gSpzwloaVH5MC8fWg2yz77PpJmDmpa2fOdNNYEXDY51
-cwylGSjg276iu96G/tOwth6gci/TeyPa0uSIrOzd3PD4EdmY8B12dTyMsu/6HCxaeR9K74eimi3w
-tGGr+Zwj3IBf3YIZhZSUegB9kwOfxGJc+X6oRLrmNbPBKbSKKVXgodI0XzAs6wDC1jKpAXytY/RJ
-8tlMYJmqZbb2HKwUc5MAA/4ZM/Y2WrCJlQFvguQuyq5TrpL2zTj71sIG1f3eObzQPNmGIVGgxtD3
-xC81VjVDzarSlfObkU0VUVM1Ip1bwIrgJzuRJYBn5kBUXJrlw9LCPel86cf2nsQEPEEwn8Fb2wTf
-wL4THNaGsW32hHogfq6dtjqnGRoeDGnKe6DoIDpS6OwWbZXbB+2XWY1p305gUJa8hu92/klC5vcK
-yjYZDiUqxw4Qe0a9Gpd2u2OgZV9PlI9a9f2wbAq8Dgl3CEBuBjHI9H5ThtjKn5EIvVdZRMA809CR
-ZoVK6BGK2A1v4Dzp8r6ZMUsPXQPW3jmXI3j269h04Q2Y5MwUaQnQT02R1K9wxclNuXb1BU62WBZm
-qNHnvp/IBmqBWBoVpkp+qLgWr6OIYDylqWvV1OHUnnpHoz81s2uue+eBWYEjXjJIubTqAOBJ/UDC
-ikDvGnqJYHDeSB5A7m3gAgHYkvmjx/52NtpkUMrMNr6tvNMfx+oxPpmrLFNrxBIVYp2h9AGSIVg5
-sYBBZ6jsoUhh3V9msmreIgKftivBqn23rTM1gBvCIOAcirG+GRY2lAVFiaiLUm76yEDDnA9gafC4
-04NY3I5X87DmY++ZLmjiGkgoEG2Rai3YgyoDrxRuXYwgK6kkG2lXsBaD3NxNlUF7uCZjRqV9/fh0
-mU3AAGR+6uF5J3sZEhChlMciqxXeZFcWcqCl2K9pMn1MUOo/NqwH+WSeQdVUSU/0XMTF0k25Ua4V
-fNdxUSIN4tqFdv4UZBzOuwUu2Cid8TaCdNMtXREEozdwYBe8W8vGZUozZuadXXvhCsszoGQdJFyr
-KN0iYBU20hYAqqzmXQqQ2Fz/IgEM9Qj3RTaSgi/RNxOAuXIb9y3poSb3DEIggaU3qtF9aC7LTbT+
-HC5BVI3q1wpklqeEX4LInu1E2bQ/WdnDofgnws87YUThIvQ7ONaL/WgtsmMOOheSRQapdsuYiMA6
-QVg9KxuCw67WEggmsOYSrv904DADv3bjAOwLTAUVkwaM7gW7pC+c9oDufUWadzaYsi3SiDhWPXxb
-c7Sg7h2xPkvyYazh8E0WtSZ3bcM/mmhq/ZVki2ozux53Bm7ZwPX7z0tmUa+g11cf5X+Td25LcuJq
-Fn6VeQEcCASCywHyVOdyuaps3xDlQ0lIQiBOAp5+Ful22+49vSc8d3vvu+7oznA6K5H+f61vrYrK
-2Dcn6vrIuacyrvFAZ7HoyBc31OZmXFegCtiV2CnqVT0dyipQr3IO9E2Ete8x8Kr1gx6D7rPwcBbm
-S9PEX0g/emW2NL7/NDcyXbKw75pXyiNxmFfWXGqyrh8rEozXaUlsk2GshXjUWtk1hbW6AjZhG/J2
-U6+e40hyAf2jUSlW6JW9L23oGqBLwfpWAYx4Vd4wXXzbALuKDlDisRXl502PBnW1QE70SZRNXWBF
-5lvRTNkgJnKKRobvzOiAymBAdx2G8dFNIR6UKX6nuOerXHUlmzJd0gG7qOTtWNC5g+CCXca/FtqK
-z/3sqSSbbRvSPNJ6Se45UAed91Uchjc9ktw893jiFmg1Eh4NmCs1VeGLSv1B4IXrQMZLF/B6vlvX
-OpoBzcRuTK54SiZ1FXNvkrhZZizb72JdDapwiaT4Dig2l8dReZ3vspTXPjktXqT9+26xCckZ7XRd
-+CxOTaHisL1OsIzpSzMI2DdsleQzS7hzX8iycHvVaDjYBU7gGieTTseqWJwqw+2VywoJVISfuPYk
-9CsAPn2Jo4iWQ2HHqiyLdR788tSPyyie43Xw6A7IkJHvhgUgVYH9zJfHsnIcjlOMU57AC1rwwWyM
-EX7saz+VH0dK+3AHlSqlx2ZsEtZk/5f3BPbIc2sBjZEOLouSmsIcrIZyeR3S2Vc3P1tNleJNB48L
-/tIJoi9Zo90fltLqG1/vhWtHdgn7KeQ5XXnDr0B4af6p6TzIEwKIIH5MMqqHvKIl3ihk6dIdQQ3S
-cM7qmYf0y4itSl9wNS3qbnN417zDOA0jrregF8p2mWzuL/juHrX1bLy3/qpAjMi1CfNwjSvy1Ptr
-UB24ZRiFcZ9F82MySQNbJopcZTMZWMs+pI6Q93PpAb6qk7F89ccEtKGBm7TglFALFtTS92UGJKSr
-imGqx2GfWOBXRwicajn9HdoiZDB+9TBGXycb1QK1xGd7kkBU3ZOu74NDmEzpsnOmMpCCGAGnAXeT
-R8W6sirBhzY1N23Se+FuGYnf5nCSOb/y8BfTOfNCgt0Uo/YMkZvZTzgTqnEfTX2CrzrxKwrL1k3J
-7cBGPOYk0WGzoxg7LKa1Ea4XsEE77uI48V9t6CtM8GllMH+DnAx38RjYIGuMUGCnCAMYVS3ToA8Y
-EGiX2WjG81YCJcS6jnvzkaaQ8DI8qvYdyKVK7MeFDVHeOUf7vIZdEO9aVsm3bbeIVxMAcMv1tOls
-6UyXy6Eta5vBVI+GojGMgjrr+rHJehs7+MdpHScXRHDQQx3zxbNHWqhrY8yVnw9hBxvURCO87ckq
-X9yFY8fHk4maasZ4u4zNJXXaygwb/tLkq/OkOaauaVmujFwplIBRmWs7d7HIGp3YAMJgs2x+d+eJ
-3TSyqcplQ5xXeD5+ChkTsQJDACVAAKqRRhc+BPEyH2gH1V62ixlz7vqFFU4Kt2Q+7PjP8D00puhe
-NF95W+l0Z0sDYbOFNL50heUeloulr9q1WGPSN2tuGzYlQAn4EHcqa6ZhnC00BdaSaY+1I410AREn
-iMrMzKFX7pYlHAC9KsPYbYIzv7xYzSC7G9bVs3xmkZvHMjddKAGrdRj+6TuMnnKjK7t2g8l+Xxm4
-/l6e8Sv+cl5wf7Ax/6LczEaQ/L2K8N/KvfzX6VNT/9cvNRk/oTPb679pCskbzPsEawnU7hStC5va
-8A2dYW8oQjBwJgHQREkSMkA1f1iNqPAAWQ5uP45igv8F9mT/jeqmbygY7NQn0MdSANkgcX5DUthi
-Tj87jSHUCRrF+KMiiBN4B3gLPysKnreOEMqwuCMl5XYLPINxV7YNjbMWN2fyMJXluN6SsMX6PE0E
-Rpeyc3+JTWO8Aoy3fv6mCoB39IExdilwid7zLpNmGdrdzIT/gMlUyNMYBuFwAl8eftXTOvcZmTow
-Nj2e0xALSjkf0wZiWDi2us/pMnSk8Lp1uqhFiNXfh82SFty35VcaufA+aQNLAAvEyV1HN49IjMCB
-c8chmUDdjebLmIwhJkql2IARHI9OFlMQzUdgEc2+DCjBhKu77qkcja7yvuRJDI/RQHusZTfnvejm
-Jqsg499on7Rh5vNlAidU46TKsBaVNW70imAhXe1RCOIuo8YjfRGFSws2htHW4WQhA5hSD9c8tH5L
-gQ3WvrxfGYeMmLhKYzTlIz/oduFe3sYcaxbCHn1SDJVx1yxqfTiXqwXhl0y9AeZJcN8XTStmTAqJ
-vusX4gsMH256paXfv/7+I/4v+vBuxvzfP7x3aMr5+jL+7aO7vfoPOdB/E+OZICkNohS7U/Tno4sG
-joiCRcD3KUoZHtKf5MAt6r4xb4zgoSaAC/58dnEUgINDQhfUAZC4IPqdR5ewvzy7gBeiKIaxFIRp
-uOF1f6EEBs+1rK+9PZvPisTGzmRGcRFmFaIVsKui1LLLKSJRP+Sxs+q+gujXXph46b6AubXVbQww
-MykMjPaMpYbuZuxG7b7tEvuKu3B5ZGuf1gWU5uV29KVuskQaLJ3d2iTPY2LG26njD4IOWATHlX0u
-Swxju0n55KMnrbkboCNe1lSYz7IvyT0Q2P5LB8q435vYF0nuQ/wIbtxYjznSEsG4kwgylFDESmlO
-YE69+mAV3NRjCHUrOFgGKzhbF6nNKYhqRvHI8i66aDGvfZwTYsuCdOG03tB2EqeyG2h4jGC6vxU9
-0y90HugjxS76PiGgrbLKCUx80ZK4DioKtd4OFP34OLRkvWhKAtMiWkqLCdJjUDYbA60VwhB8kSwE
-dgQUGBJQdVMKBk0VXDOGr8XDnX8SS3oR1VA7MElweFalogOF+hHT8ZL44NwLLno9Yl8VafWuhv/+
-HEOK2ME36R4x2/Ue9nbnfYUhmB577uNg46XX2sKW1RpjRGxe4f5CDEOGooUP0ybJMYq0hKyhe/HI
-yYr5Eg71cAhr29b5GoyLubGJ1+70WNfpvZxn8bCqmj2WZPU+MivgFRkpGpDY4JOyZY2UyjwmBp15
-QTce6er6fITkdbuVCt16YQchs62heGQuGusuB9ib8DysiEW0JbAXvTXAvvzaAJISNl3v/RJD7o2T
-AduFIw2uTMnauODlEt/hHpxdHsPrwBctVd2nDoLbsRHtVF4tXeyFVyOLy+u1JDIEro5lOwP6Z2iR
-tNS7UgCqWeZiIH6ZSK3bsCpNbtZqcjvtw9VRuBhu8WMIx0JUWiBiIgcC0aiGU4/Jk8MAY7BvPqgl
-0Ts6hZ3BnqXFV6c7fw/FpNyxIAayiNTP+MJHWd7ajvKjWUu+U5YviKDoevyg+3IiO6xTHtkFOqje
-lvAX+pPndYO6smBM8DCW8eZArSy5/Y85qSkcjL8/qX8ptvnJsEHmAz7I9tpv53QKzpgiORcwHK9A
-txIEVr+PWMCMt3IRCp4KmbXkB82VvMH5DMWNURDKiOVHP87p+A3FSIYYP6a1AKPZ781YQfgX2wYH
-NfXjBBcG9SkY6e2N/zxkQXBWHa19hAPGZgclVV5PVdUOeQ3g4BJyFYRDGuiPkPkNhMdhTJqdx0OQ
-WingetgEXgi1BP6szcmQ1u2VENAzB2765xkJUVNo0/L+Heuj9MU3SEjlLPUkyULYQ+XJjToRmQmx
-tuxd7cGeRGQOSA5sZ3+6aKGscDzmzhBe1FO0jpnpQAO8a3Dah6/h7EYQzc3Y70SyjMcBOYXoEhkg
-tWNeWh5wWtXVcepic2Kp5u+FrhlCB5QubSZt6YIT5txyvaJTJTj0chXBkucdTU9IR+j50HuTCHYh
-kUhs8IYi6xa6eJmu0efHbA4kYJV4HMsZC6MtEz+f1Nzrj8mQVgzSz+i5u6GuZHJjYPE2MMonZN9q
-rfWRcx8kUYn7Yt5zoSIsuaaC/o4rpQ9PyDGqB9xs25Goeh7mUtmqw9HASA3fWdCnCvhObvs20O+d
-8Z0ubCpsvlQQQHcJIj5vwQaQeIdEk78UcJhYgB1yZTvdIpaDvTaYnqFv2FMdb2ZL2R6YP0RflySs
-p10pa8IymUQq3CVeBFhW4uoKstYT1cNQpd5rOHW4ELTwJ5dBJx4dwkWwXwhdAER4yky7dAjX8Hbq
-++gYbDJaGil7IpAy7gJarvs4UbbDvQ0FIQ8JkhGq4elVPVNvKeAAyWq/GA5efQBAUYy9Vm97Xc9P
-Y+/5bzuIiZ+GoKy+ICiaIvEhGvoEIZWFRYSvzL4COwAgtZQXKFtYcgBg3Z5IEn9KkQICDoMbLucB
-WeAitIB78gAJtwOu+Hvuhc2Rj4LnSvDHqFPqmJKBwwmq9Q6oFn8rLClfSWpDIMLk2dnhs/KtPkak
-E0/G1SJvhrjduS6ZclhMzcnvO7pv/IGcZCNe1AzApvQX77h2wY1vdH2XUrlA91s+pzLWD9sfmyr2
-ueXkWrX4wkvApvuuHasrrxZfyi76bGv9CA1enbq4XoukWg9dSwS2Gt2k95GTwOflsPJLvQaLPWBH
-mj+u/dwdwr6s652/2gARzqQ8QVhyz9P2RuNarhkv2XCL9Iu8UjzWR9Mn1zBQoi6btrslaMkxXZJp
-ZyD+HmiwwOFg2nbPEt4Gh6LcT5syNOZVzP1CJnQu2s7Dx6jFY91KrwgtwROdrkrdA0PxsjkyOGhW
-7nLRw2HhqQAgVYf8StfgtVQy97ej6J7rEhhS1wZLbqGsjvBqE+99yh2CMEF0Hbp02feJm3ODJeQJ
-VqvewzXdc72U7f9DT/hXWza2dgpYR//sAvtLleGPK+zP1367wBD9hkkYpUmwpb9RroBR/9sFFmMD
-CSEcsG1JD+CMYwX5QyNAJsdHIgdvIolxWwUBrpU/RILoDYPSgHsnJQEM5vC3kt+E/cP9BR4CkXQA
-09ufEp2xhJ+S31LPtRi7KK/xKPYV5LyU8qnwosF+jY1GbHTx00erB3URjM67WwXG0jSU98aIJWvb
-+B0C0zWiL7EUORVQLxFND5H+glGeybV75MbgKyhsd6Hl0oBQSNL+cgBuo7JwhLEOtXASh3Ws/Rvh
-+clDM2GJ96CuI3+IxMetN0SvsHTEJwa49oOBQZBr5AsvMeWzU6i99VgSInc9DqhdpR1GegcyEJ8l
-Vh04ODvBwJq2wAB2od9MwA0rvL3ZJP4nLkBBuCr6xKd+/UrBnu/hAcXvyNwgbLTN5gih+vPVIGP/
-ckk5P/nRHO4RqumvpnIciiECVTamvsUjpuYdfG3+QJel2YUACpEXVzHIOZhQu8bgEACGnT76NaXv
-O9kiPxRNIwzobsh8kzKAq43AcVBFpr/lJB1vK7jct6o1zYNB5OYz7ojbAZMS/nq+Rla1S0GC9H6O
-oBDcmwkXHYKLcORtHdGrsaLRnssW/+ogm2rXBSdRd/V7HgNShhhZFukwR/s6nbsr5wPkcolDhrpU
-RmWGj9MpiSZ2TGgdXeCsDJ9kEtPLIFz6RwQm6IswI5ADhI0PcekEUrSDizIiY3ERwF0r7CqWS9HE
-rcuYatbrMClVmUVeBDM8gZSygxthd37tmEHUqawOjWqDQ8hKegHkUCzXTkyI0tooft8xbj/Fc9ft
-unbPPSwKuWvXYUemQexG2apTW1X1acKEc+9PI38Yls5TRYKuOgSCxDrcJnZt92IVyXF0VuKWa6Ld
-vHj8sargqinEZfANXKPn1HPVcVhcU0yYu47ITo23xDIspsM8XDKtuy8ByLeLNeLjF8g6vckY8MV9
-bMbo2GF1ersQ4R2aUgVv/UYPx44pC0wO6Cj3IHrn8CbSfyOI65duFwzz5+aOn0RU+k8P1/+lp/gv
-r/12uMZvsBbQbSsArUQJ4P3vhyt9gygHlBgUPcc0oeEmzf55uG6CKI5j4B4h8TeZ9cfhikINFqEb
-J0ZQJKXRb2UXsXT8gwSLlQAhDxzhsGJwwv66HYTwhntqkWJCqP0mVGn6GvgLhkIEi4cpA1rukCtS
-PTZRBXQIbrdogoduJeVcqD6FeezL6X0UDNA7NbJaMEK8aPrSmEg08IX76mWCiApMCGhrfyHLeYWA
-0WsPKoNc2neDQngqKz3EIrOVDO9XlfTQWJCXfDR05FhBatfsVhtPdQ7SMFHQXOrypYJkQXaVKYcr
-HniM5WVLfOgjXQpzEpu6umomCjBBdLw1B/iB5bUHLgOXAPJuIp/7YE12ZFGwaBd0TowZJHJ4TSsa
-V06qnTykILzEv8AWEgdFXU8S3OwIcnmHIhBhcjeBED2U0apQoaA8ex9BdYPt3xsW7AMuZ3xMeADf
-B65BSIPAlST7JWg2SAHVA8iLgPEieeAN7Ve+sKnLa7M4fOTlgiXei/20IJGZcQ7a6kMfBikUYQTY
-0yw29Xj0YWzO0G6BPYHbV/BYbIy8+w5WXbjuEl6lLjcKjAn0Fu2NWR8t7y2qJmBaqdTD+jaid2ML
-jxlxaJvFawtvGWA/U7ZmuPPaV9fbqilWJ/HeccHZ8GbgiLLAuBdt3kvjn1iJH8t7vBv3tlfB+jnA
-CXw5cwsEbhp784H3AbkObNev+Tp00DRCT0zvLKQYmU08jR9aDrV+FwQt++CLdDjxEae3mEH8H0AZ
-si+y9D81pa6RT4xDV4QqJm1hYX3bfF1CxrGUDvaTQXwfi14so2vNqAKiBojy4wJdh1328P6rmx5p
-vFcVjX24b9o1Nce4R0tMvqbpSODPteWDTtYAq1vlJQNyuAL/EWYWwkYxq8H/KNqcvpleS7OCOo4i
-w2DFrbP0Mu0IIgtUYiPCZdRZkyt/gMPKt0gjXhqGT+nUD7g3QUZvOFoN+otr2BE7IubbWMbh139/
-JQYyB+wkHG9/r8P8WpX645j+86XfDtoEIfEwgt6GtHeA9nmKk+z7FOsDgd0ydRhlAc8SjKrfQ3Vb
-3i4EThGi/CiGbf3joE3RP+ZDnEkJkNetnvS3UnVh+JdU3ZZR9ylBWxJMN9wD54P4pzE2gAdr1nHZ
-W8S77lafpx8JipVI1s+JKQ+CpHFzkgR7v4ro6N1Um3AJax4a5nDWM3mNjAjdRE551jvns/YJRRg6
-KEdgdCiCTR4dYfPeUs/vN4d5PK56hY4ar1aDjDvrq3DAobWaaRgevE2A9TcpFlFk8YC1DWumpRqj
-z1m1XaE61ChCGYcDNBURFRC9xeMgEXwqKmA9x5B4GLadt0IPNsl6grLcHxm0/Zyyxa+QpvFDsY8j
-zQC7YEmfctI59l6C8TeZ8/xu3nKzmLCrJiS7ziPdVVAT/TS3tnE5ILu6h0fthTcuWgJglOXk09zv
-l9A7rZSvN3Oj9K41ODZUqaG5+y0pKtbYSwQEyZNruSOZYCzMBqcSdmRs9LKmcezB0zOrMemrqr2E
-YW4e1sDDjtAGvv4wNal6hxoCu1d+2b3103oE7TZytDA5fzpMvlr2DDrZs/Yx3WHEq1HrYiMAvr7X
-XQNsEbd1uFZ3C3DnIVvgf/c7OjINuAQPwyn0a4T6cOU/46vqXkuk5Z+rcoKOBox17+ZwebKBh0RD
-jxtj2rf1Io8rDJUX1K+sfBdCukYovdL2JoUR/wHXK4byNY5vIviPmwHK5j1YVnldWqBfHSPuc2nC
-9ZSWUj3pwURYGkjJbpUx5Z2RwVQe0PXUmwKUYJcUcAnpRUU5+wpbMn6NVi+dimZCwLpAFwuCh3oY
-5GeXunECkxh4xXbrIyDSJpA/RpniGnODTrfEWxF7LRAt+DnpCVByi0+wGoN3Uzk1dzIRfbc3wEuy
-PtTA17SY/cMAxNUcI9N27yM3+IeWaXkJgmcBaRrbOUCIOoofm5TJOScNBivgm0zugmnRqF2qU7M3
-Uq5QhQLpfSTcBx40xiEC7AoseDvN/BrRc3asVgN42Bu6Kz6U80MJumOvknR+qLwK4fLUTBECNiM3
-OZ+W+UL7CJpmGkDlHdepAAmJL7UeLYJxtV/K3ARuftHIWlyAyoJxq1ULzo1gBwzzypuabQMDjebN
-cvIygrIFH5+RrZ7CzRnhBudBgTgIu55jYp9mb6Kwo9LXtlHihZ6rpUJIkwgqniunwgQ20R5a05TB
-TnGHpZJ9m6nSi95Dy0Vf1bJVV6GfgT67rc6qPTdbpS2CQmJYDOrGttKrdK7Y1woj1iFwwIMKzF9I
-raSdGm6mGiTjYZkX+PL+ZNZrL3LixZfUv1OYEWUGzrB660lpT0jG0yt7buPyxhLNXJEs4/smRLK2
-AM6L7i6wSF4O0NDeVUk63ESDTO/Hc9eXNxnvJM8NYOmK/rFkReHTsHWDsdBiz4Sp5g5lQgGD9h1D
-kdhyLhXboKCTBWjb7fANUzf+Vj2GqoptEDg3kulzO5ljPX1LxtgdvThpsJIFEHdL/Nzu+ARYHIjB
-LPJhQdBzXcoMSGd/t0hElOW5D62LITCAbeMv7FyYZk0pEftL0Os0nSvVNl1/v5571vytcs3NKerX
-kAoG/o+zzDwONQ4IBKEGkOITrev+HalCD6YRGt0aGEFFCctpP6IhZI8iH4faKbQtgaYcx1t7roZL
-zzVxPg6wax8DjswVQGm2730f/Hx9Lpjrtq45e66da7YGupA0lbyQ52K6AMm+8LKkiZx22LoriKcl
-j74irt3cDbrSJ7zVKQWs4ANzdganqDfMo8N81NnDAIwsLWacZA2OedAEzx7n0E3LEMEzs6AvYZeg
-gGM8OpAafF8nZuaFH4kKWaokEH2u6mF6xczJxRUDm0sOok4mjX06jtjh33/m+d7biDHkn009f/2t
-AD+tlyFe+t18ChH6R5MNbH2MGGxDbL6bTzGDCYCZh2KNhDWKdfb71IM8kU8j9HNGqMxhLIJj9Yd2
-h6p86PIhsIIIPXJQ3NjvUAJBjDf2K+ETY5GNgxDzFSwt+tepp/MQ3pmi8NBICNVFiPdpUNSGGQCp
-t+ayjGfRnSpuWsSb2RwUnJdrmTFLXgSi+tidKt9/HZI17g7L2l9apreciZX2RuIK7o9jGaawW4eY
-5+k86ee5BxZ0QgRhe7xd94h+vhIsI7rbnjn3KvmQ9iHcUCRvgV6OExDJmDTeQeObucIyQq59GJrh
-OIR9pQpkcFHCgusfW6L2+qagiJgf0n6B20yjqbxmrGo1LHBPHTTHXyhr/H6+IaJqATIiiKmr2V0E
-KEwocfhP4x2jG+1HK15jswZDetNjDrrHPKELgQP7hbcyfhWyt18VOIdhD9OJ3vfan1HPRhCRxd6K
-hU4TL77vcfWSvaGROdpoESrTwxLsNCrevoR2JghkVhZ/LMIu6nGEY43DyNj5Chel3jUS/S+omqCf
-o0THzylwc5tFQU+uGuXjLxuxCuSj9kEs+gNO4alaPgKn9OfLCXkbGE6+Ku8hhiFkM66YewA2T88x
-+hY+aGxdOZGKwCFI2lctgSGggc6gpEjL29XvktuEl/VdgHjIcUW8OLMjauysmEB4e9NEb0FJxQj7
-DvU9Zp7oaJmabhGpwE8dhEf/AvFaDllcV+pRmUQ9x7yfH9MpTQ4r7aMvIVL1N5Ph0Z5GOBizaRr4
-V6yDHFmomQePOtJtmaHWMaSHFo/MY7zMyaM0bH4PSFRewYxDsAT1GyMGGFfiqjG2Fjvu9HSJFIc6
-tpAExouUWTSBarhcL0HnxHVkS3lsedze1mNHGkQWpAmzADmy58GoJId5Gd6DVk8/KUyAdG9aE3yc
-xKS+BGPlfUJAk70m6Gc8IiSC4OVK9T6pJ/LcqoSglU5QpK6b5cb1c/PBRTNC4G6F2jGF/HqYpWxy
-f5Mmcc+GyS5C2mWj2Bv3jKokQCp2IOQe0K1y0A8G+rEfPOyhMe9G9P8Z8wTrOH4iIw510fpoGJCx
-+jouesIZH8k7F8e8SBLl3jEyJG+ntg8fKR86WXgCEkYaxJcYCtuXEN0Ct5WHVS8rOQjmjHaou8lQ
-vYUmNpOUEFTuabsMN6DN0FMQ183FBKjhVqRzcoRsuZ7sNqmOlLETeAp13W9zLPxNMH2x1OxGIhOR
-CRFi4u0ne4OYEMZgv0eYamfQOvLSbHMy4qkKI/N5fJ62SRpiL92LbboukR1+RrDRvXayT5+DbQoH
-qIp5/Dyaz+cx3XoxRna9Te9ES3EbbBN9LTndD+cxX20Tf7zN/tJ2y16cF4Jm2w1crPT1MibtHXrF
-7R7AoHqHSGz9wegJiwXufPPgzutGeV49Gk+yhylBE5ZAtxk78m1LwYiMhUXzgTyJbYsJDJ4k4AX8
-1Gw7jtu2HcRzFsQTqsA7xed1aDqvRsG2JZEyxcLkzssT2faoCu0J67HaVqz/nGv3n8q6ly+//L6P
-H2rD90sbr/5+8/oUvAdKJCDDBlAYoKx+1xuSaINZk+0MjRHAxZ38/ebFLwOCEIy+io382GK+P25e
-8oYE4HA3ThdWVxL9Vlr3H7APeGYBDDqIJJvsATcOd/zP2EfLZk5jVx3gO1le2G0Ji1e2RWawmbXn
-HW3a1rWpnoMgU+ctLlpRNjyddzu1rXl4nL20aJggqqDnTbDblkIgAQjmb4tied4Z9Xl/7Fo+lwff
-LeVdCyzsVkgcwpnwnHqqtqfcbc97uj35liJWhzaG6rYKEO4CGtw8R+fzYlxKnB0xqNcUODttbsvt
-cAkMZ5cS8RgMCr0sxu0QwgadvGXbwcSphyNKKnVXzh3G3e0Aq7ajLNgOtRin+xMPcdCJ85k3bMcf
-2w5CZUqcieC9yH1yPinhhLlnjQIynXdY1Xf9EHgURbvbCTtgj7r2t2MXnyq/nLejOGDLgjQ+jmck
-0oJb8DwEURoc3qBu412ydssR5hN7HYfZ+wQeRX2RGJY+oqcW20NPSfppwPxyjwUNlUemXZ/d+d4Y
-pxR3SLNdJ0Oi1THcrpi5X+1Leb53yODXuIPQSrmHUdCJQpZr/7SOXvOYLkJ8aHkt0ZIB/RSrEyJq
-d7XEdj8kcTTnFaKfV5Bsr+p+hQGIeEHzHPYLU1iHXfowGbPiRdx216h/jiUMpA7ZVGrRpblrsGrf
-1L0LrpvE6wusQz3SjUDg0MbnLCKDHs5UwMw6eJEzM6iQq9OvBL0EhVO8ujZB5AqTLkwWa5KK13U0
-3ttEjehvRpo4cQBQVIIlDRghwd3mqyfKAH8UhPb80qzcfj7nnyLdNwOSCxp9t0U3OiBwxnnI9Qg0
-hmbf8k/Gc0wUpFlWhHNhAdyuyNni02gGnx4E+n2W3c8hqHpZp27KbEtC0M6hr8sXtsCvePoWfEo0
-+gh3yEjNEwKlP+JPVSyqcreSqX1lylWnYJjYTUBC/nmpkaDZzUk7nlASul7GSyPHwnRdJ/M5ZlVQ
-RMifBBmaUx14qJiDOgzjT8y3VfVcTjNq4BJviewxRUmTd1gV5dcQPsI7PmLnv0TR8nBMEJq9CgF7
-FKGrkdP1wEoilJTG430zOHbykGsvWiPGfDYbT6nF+rqEfvsFJZXp59EMLcqBMdp+hO4vXhIfZW8Y
-IJL0DmE5ea1wtewleqIAZ3m0ugJzufY70OpFWDLAHqUv6hOLearyuSYY4eagj9Eigwg45KVm+NLO
-vub7ylX0BlTv8IFblH/DdK9DGCpLWl1gGfQhsEF7FGdlR0u+AknfBB9iarQUbiJQG40T4jRnbajb
-ZCJoKiyrztrRuMlIYhOU/nOuNgQ1/n6j/OX3JP3jxYbXfrvY6PYLBvE7hFDoj3/wsR9+v9iCNxDX
-t9/3gD0OmyNa6P682ECKpPG2UWIbDRiBn/nnxRaDO8fvBtiE/nT7bQXxb/EgMVzRnzdKmKKowAB1
-st2sYYT21l/vtcFroZHioLCRj4jm/5B3XltyG2mXfZV5AWgBCNi5GyBdZZZ3ZPEGq8hiwXsEEMDT
-/xtJiqL0NzVLt60rSd1MZplExGfO2Qf7sLyqllpLg0HEMt829uRdRPF0iWkktoD0ev4NE6p23lpM
-/w/scfRrHFj5pT1EcjdmkIaBq/t4utBBwFBkmaaXuCMLwdp9ZIvHVMyHsuLZeOzvJ71rs3sRgQl4
-0qsV85NlkxmOY2RdFZmukkCxbVDbslpW1Tty7yN4qv5lUJ1inxR36loznOnBl55VYViVNlQuJKRz
-UIBGR+I3jWC7CqUNELvKOnm2lgSv4bSi8jcVleIN+jpW+oNev42INN2QedQ8ohLQMxZ8qVO8+117
-kk02C+D4UT8/wtbzq5ufPWDQviYvLLu2dK6hvTviehk9JUPM6XSyDe1697Fo/KzcYwd0put/z/PF
-h/rXz9epjtNf2joQQX1/vAgdZNNk+zYRnXyOKe5/f7zs34S5hqt5UFZwVZxXRN/rRlI9UWx7PnJg
-PqaOtQqxvk9siGXDvYRDZF1XuQZ/7B9NbNax0J+fL/wmPFsIC0zb5On/y/PVRssUxX2xmb1B2s+T
-nMx91kBcK2NHG7a1m0UjoMB5uSr8AT8E19R8MjUFxH+V1xSjqy6wlmlffBh4Mfz4bLqRaQZevFPO
-xhyN+nNrRfa+AY4ETb7lnTRwqDLAXVk3O10T3CBOlXW39uzUWx+nyN5otL7cpJqVXWGMxNZpA8Sb
-N+NsLBMU8R7blYHcFcdcWiEZcr3HbikhM1ldve8nd7KPPob8i65FF9tniFvZSUzeyTsLZ8eyNuaN
-ldHKbvvUMO5Tr+OppE9P8hGbRgEQf9XkUqtxMJDmlV9r/TLGD7VvxNa1exb2JmeRr0YZhOA39uJ6
-LxyzOOq5D8jETxAko/hp4uxVR0Rbh1FiaEAMclW0xr5q54rtRDqIaheLVddQ6ulnzfZcVtKLibCA
-lf2ihUa5lG8r6u0GmIfuhHaZ4PKOa4GKh7kDpnS3ysZr0SyWd0OxZx7Bdzn7Eh3vrViDTlZfDk5j
-u8OoW83jbb5GogCoEY+Wv3AwzQSm1KVrH6ZMny68eY1TaavsYK0RK8YicPf3XaVfDdlIBAuc82QF
-nudn9vl85qDDp9avijMdXVtB6YyfYab3Z356t6LUizNVPfe0iCNxjrsdxRDI9faMX68GvqPQmzG4
-7d0ErzcmXGXtldkKkP5I4MoTjlfts7Ty4WXJqgzjf1PkV/OCXkWlZtkdPXzCC1IEyohAGLHXnbSl
-1m9bPI7JnU69foqQs7Oqd/IY1xD0hznIi6EYL9CVIsRgkKlYbkX+tnB6PUVq1hh3ZC0gvKWCpE6P
-59J953ksHhq/Kk+DKmw+uhWxJKt7qdplddk4O4nmmsmC8MAZWtrovSZoyV4ytnY4RFI7e+x6SwvB
-87h3qSHyq1IpeQUAezlhGxr3BhE9zVVXzOjsRcsoJh9E+t6LfHwbYru568lBQLBdOVxRvbHc8wkW
-J5/4gh1mfO/gGFoSmI3oLtxUWn4I+qLetS3assRq9Y0sbPiQDIFvsGNBRuVTiIm/LC5LSwfjgZ3r
-K5H2ZrAu2HgXiE8Pei0+ja3Q+t1k9pScJhp6XIn6kj5VCwkEVc0psJlNNbL30nynC+0JLqaAtKDC
-HBfBsdMHaKkUzM4xyhp5Qs/S+HdDgdN6sAaT3+9iV9cMrLfaJNV+bF2RBiUVxR63fnxN9Zgjk/F0
-cCSTobRPWZ6V+Y0cVTpdF23u30YEZWhsRgbro1e4ib+PfFzKNPuYoeHCdiGAnmx4yDLDf4hX5TGj
-zvbjovfOgjUnUsOlZy3Rrp7YALqQJE///bceUwjX/Xs348/pjn+UlD9e+HtByaQDlQd8T+4vgXPx
-9xuPPQTCY64DwHkWMKCf8P3kh9kmJSO33qqeOqcq/7jxGJDA3NEtxijcVPo/mpQY65v8+cZDyYzR
-Wbct5n++7fzlxisnhQ2ky0M9MVqgM2AUAgDAyaZ2NO/JzXzrVdnRF3RJkQ+VJTVZ6nudddV7rNED
-FWsG7otM6/VgMOz3MTWar8viax5PuopI8dHyqObGmv2DzMyLed2FhVVpyflSQ3TgnxrH7nhyxRgR
-84OH54WdSA433S6iaJcWzJ0PPSKqNOzmLIpQGTFDCWYLolq/mJ0f6oVN9ZvZEyQmM/Lgr9dsILrN
-wH6oCvhB9l8IYZrfy2qQDz35HfW+1HL9wU8Gx98yF49P2NEq4ELD6ufsgV40R2IyIPVgT0rTwyQm
-MDd1urZ/WeNY3WWamQu7FwuftN2I+SHJEiAcU90lgNNcB1212xKzlEQlplCKbzRPtZoBNPn9Rrbz
-TJtvm212F6t2HKies/jDkor4TsST/amGLOUGtSWXW444kmyG2YCYaeVx9kY5PHx0wKW+eAOcq143
-RzbeWFeaICpdKMopsmFzvzjA+hPfZd3uQJ499rUze3s1WQgYq6LKn3p+2OaWPtr4JPGN57ts1vy9
-zaTlPu4W9WBGVf8c+X0yHBiZJKueK2u6EEPuggo5Ha2MBUslsExLhkLg5HqsmjbkTP5+xQiDtRFO
-E1KsdEKA4NU8MNSAU2Pl0lxOMVv1efsNIbHoc0Umj8GV9/cciSVl9IYvgzyG/a9oEnY8OtclNdbj
-N6JEy+Ae4JCqjP9ElECoDtTZlv5N9v+lSsAsIqxqcKzECcXagZRrLzJJVhybOvFoUfjs0K4oTIky
-dCxdrvdI0TJNWZsb14XGsbUbuQL6oTM/JNJQ1zhXaIrQEfUvYNiqY3FumgxGpzRQ52YK0Ip9pYER
-CJdzs2WeG6/x3IS554aMXx7N2TSomoe2nHFVNucGLjk3cwvnv0SiszZ51trvZWvn1zq1fh2LHp5n
-EdXz1l57RPPcLmI/uazXDpLlP80ku3QeLXvtMZtv7WYq7I6xjA7E24wd92vrExBlsFY6zgSQy+2/
-4tZg+s0Z+utO6eaPJNo/XRrfXvf7pYG7nHkC6mk00CjwfozXuTQQ7JnUAjqDBuAWTC6+t0k+oYMr
-J9NB0Pxt9P6jTXJ/Q3mHlBphFY5Mk3XKP2mTKNX+fGmcvybeCRoG03yTAfufxxB1Ug021OrQav38
-amFPhFgIUmOOHqpw7sA+R0d3BkcT5m3m7hx9SN/9FraTRuTWbrDNbGcDgAlrTY92fTp1IZ5DBmKR
-EV26UhVdgLAP8ruaYNwxoB86NGPk6QQGa7/D4nn9o80e+d0f2e0AmOb/rrrig5WL8uDFFaqOFPfZ
-0RhQWeVjbN+y2CzgodvNsm+8qNrBkna32VzQqWiS47Zn3EJz0KUuQWS1dVnlrnVDCa2MADya+dQN
-LcN0zZOf8366y/sujsJmspw9g1J2pnDiygd90sZ2MyZWTwZG7rTvcavXJx2L13Xu5pm7cnijZZtl
-XGfbLPKB8FkOqI5NunhOiJSw7gKfQ6AJm7akzWt8s36Zy8Y62HPaU7KpWL+sisS644GOnkfHX0Bs
-ehKbj0uY3D6D+5se+7FSaLCy5aiy3h7uFy5nymPg1hN0vQ5EQahcGvOL2iQsKlzaJlqHpHMOULrk
-+iaSyspPo2zyE76L/EvrzCkU0k7WrzHrNHEox7hnbD5awrzqGqfpkEbDNt1Q0gICwnXoelvyt5os
-cEzEkNs87U0/sHtwZhLOm5iWNyOThbzS8rEBYjyWbIudeqjvWKTkJ00rqu5i4ATzj1aDOfWDXQuz
-OMyliAJnloOzseeYEl7LVP6NcNTWffFSuzSfU+vVmE314uvcTONFhrP2JGQdhZo23AkPYdXcyea4
-LF7+0eWpuzDg0w3wAaT5Im3RY8iJJ1a+GnmPWEBHE78oH0RiRiK15WmM3wByknZi5caR4x/qAD1b
-zt0V1+2mT0gvmxM69mUe0y39ZHOhkMrfKGHXX0d7gGmkQ3y8yuXic4rW063BJYDkni9klJ0bylkl
-hykfxu0cD/hTwR4EBSSpi6b0Aa1UyvVeKjHeTal2Zbh+l8Hgc1HbL/kJ96YHjXi2j6DNDs6kmi2A
-2PpmTiYY2U5zyKZCuymKahNP2mtMntngztleh3zxzMLkrkbhgfveMZ8SYbn0T3qHYqlSj/m43vN9
-/c42Ld4smhBBNOcJhV06qt3sLC+e7pEsWfVvVqzMz9owHM5flVZZacCOMA2mDOPT5CsHeEPzvP6B
-ZJjuMs144X5Kg1QUEptO3e2iNnFBR1jZ3o0M5ziJ6nKK7e6+dXuQkbbjrHgv0PZtezcyGOwCowBk
-xRF6hZwBXmOREzuRXxdmm+zqdHyrBKq7qLbERePF1zJF7xHYlXm0BpZB9jLZKzeR5tFTRbGL0nQ8
-eQYPv9EyhBFoZl/trjReqq4d7ngy+jenNFWoSKaShQ4I2BnMr067LNsJWf390OhqH2dJdAP00Dqw
-XHoA/hEdGPp7G87xD32+ZHdUZGKTzPoz+VRXtq4O7voXxK0JPY7oz6BO4G5bcyyeuwqKlo2scP2P
-ARiOMqfsWMluCkcx6Fsg/85BJG2LHYABUmXgRHakha/YjzbKtPB/uNEbCyw+OLK4HjIfp7sWFSf0
-QfMTgmt8I6afAdKckAQ5+h2SF5rOUY93meG+zavCQKSpeCxbqd2XvV9sTOwbdKTuS9WDud2zwuTX
-Z4t4Dlb4/ligI1W5/8lpfbEpqErDsszdYP3ZZ6N1mxHZt68ofZHyzC1EsXXTg43EPkZqbLddyUxL
-xZ/YyuyMhYa6WxJlBTDjnTCFjLdhUOXtI0u7m41iOkgaF9aPU/IIoVgGJuFRxwpqLUb3xDJIkqxc
-xhG2jgG3HzeoQhw0rB02if/+GuX7Mn/dHfy6SmHW9fnrLwe662u/VSpk9qBt81ZLFko7jw3J7+0t
-YjokAgYqGJeR6rdt//dKZU1OJnqOiS6tMaplyofv3a2PAM/if/U8qhybP/SPOD2mv3avP6f5eHxJ
-vuOBEweqaDjrIPpnHUBGu5l3o3ZwM+FCeWlrIPyqOJmG6vfliOg8UCVl+ZRr+qYX8s0AW7ypTLe6
-joxSXLizsHajO4JpMKO525P4YX9oEjFcYyEoL4TFf7q9iwLfIPMEdA5b2MpgiJURAnYaCOu86HKf
-yFHXHJvnhSIZVZ/Rw+I0tOGaAMlpx4gTk1nE/gRDEjkefWnL/eLzyr6xx88uxqMuFEjdtsMI3mDu
-/PYzIQCyCJn0cL1O9W2Zup+LBAG2LIgpaLFTjIdkRdTPK6wengMBx7IdOI35IjXWvSc6CztE3usG
-+bRm+M7aa6+V3q7Spdy2eE0XBc13rLUKuQBiiC6oTX+bZBX4b5abG7vyj6PlvyGtqyApTvRFK0+/
-sKfHyFoeZptwyogpXRVnEwIqbd66uZ8yfPOacLGm9iQM8Wy7js5bJyrQoJZvphHGUSmTIeSqNPBy
-tf5eimk+lGLMDhqp0mG5AO6VCwL1Io7SMIlnjQADC/61ld3Ok6VdtwoRsJbfLGD7rGQ4euWib9IJ
-XZNhJhMFSA0qlS81f679pnlNdS9GqGwwPPObPrnW8ffR3Pql9wiyt7xsUk1uJEUYdCcCLja1ApnG
-3KHawlPogygS5tci6vuTHWn5o1KDz1xTzl9MVItb7H4t8iOdC3SWTRIIMCK3GFO/TKhEyMYeRKhn
-CuZbb/QXPfbTbdpTcM7t6F/Erez3fbzYUF+7hTjfmcwXgq4RgBDyWTxIAkTaIDVFctIsrWCmn1b6
-XZzp/KYqYT/4Oip1Cs1HQed9rGLPeFKCCKGNOTvcpfNkPs9zGV1X5OHOQZfFs0AQJ807LZ6h/BTo
-4q5IuYpPWHoeFDSHeCjKI5Te4hIXTB1OAzqaNO7ItUWeGhADMuyLbKTBTZFkBdL0IEFkC74yjRCW
-F2bxEsr36OZPCzxQBH7mROpPZSY7s42p94oIRy4//LCF5vNQLJ681uWEip0x7L5x5uZQuTW0cstJ
-wAB37NdDgyy6wzBJeQDy11yaruzva8IYj85MFEnlw3srqoQHDlryxNg+iwBAtP51NFN0pcU872Wa
-6/S/MDsKBOCh3eJjnkaLxPKcUXxZmm/sopp+rxqDuEeCwwJXSUSd81IK/eTbcqL+51tD8lhPr2QV
-ybfKF29jDymFfEDbv5yytN8JK1ucFWZe3zLQc9nl1FX1mFbZgPhDRRND4EiytJBW+Tr5TXaRC21a
-GZn4oWhkSLZVRYx1mskD8gKntXdVDd4k6mvUrCQmb0fasZO9+N6mkFp8g6vD3XeCQqfrE3wotqsp
-zClz9agjXL8wE8egaFdzsu2tqCC9DDAKSC2yodY82LuZzuwZ13R/rA3EFqRuJN2TzG31WfNKcmKR
-KjWM16AkhnprI2AReC4CfZkNzr5IUQk3yeLq+yz1AUN30rjuZdNcVlWTnlgNJg9iKNv7tjCQZ5VE
-z3zKHSjeQVbY17MqjA8WcaHQ3W1133qwvSB6s/De/Guu7dVa9+tr+6Z6+3Wm7PrSb7e2g70PidWq
-0mPOwLbzh3Ae/YPHfIBtKstYwvBWKuX3W9v9Dee1ydjZQem+Sv64TL9f2zYUKIbcZyIGlzfcjH8y
-X/iLbB6RA1e2CR0TZyK3t75e6j+ZBbXeoo7EViWHoTiCVVUHsU6bEta/7YaPuW4HEUkP+bda7ov6
-v/8544M90l+qBV66kkIZo5jIF12d2crPb1wBrerYSIUGNz7KbrxA73piOel1kSHAu0rSZWHLAvfu
-bnZaFoIVWjFwCbTbd0sM2SnoYueh03Trw2zqNYEdwDWe2RmBG84nPXvF4ANKz6mNZNoA9K7esE8D
-hE6zEYY110B9VJpHrrt0EGlsunniaGWsbsuLIR2bkzc82/mom0A02jnBseR32uWA8asP4qQg39mx
-6+qDhjb53Zuw9mymqPhoof/eC6hLdRDPFkw8Y9RxGZQx44hNQk1dBM2M+xwU2+K0oUdgGmB6i/0u
-MqzFuUFAiZfcqZsGRj4/gOdIaOreJKNebUgMYFaD60xb4N8u9RxWXkVu2zh2nslPR1J4z8YLrwBH
-viwWAYazd4kZuT00CeaepnTzUzumVh3mo5F+AAE831qycT8yQVCf83hBoyjMDGO5M8ZdurelaYBz
-SiUut7Zl0JCoFspfVY6IhHtk9D5kutsl6tx6M9gDoxAz64sm1GVUPEBRggrii0e3kfy8+1ZpON1w
-MDFDgklO/9yniThMJP3W161frT3KbGj6bmUkqrTMqy1ptSlEoSaVD5PIhuqUVXVM9pHwsseU0f+w
-ZTRM8COVIJN77ilBA790l1E5z5IEXCfFQhgleRamug0lUiSNu7K5h2jcC9Aun9O6NC401xjXCMlF
-t4KYYZoR6I9e7bY+e0Iy2vO4ZwcC8Z99iNfqZRqmwzggzxeRF+2KbKDmco3SeiF2z0dVdt6w4Jhg
-29Jxqc6Xc6uxhTFncUEbyBz4vKMpKumDwj7vblgDNl8l+xxtadns+EbOloeijI1Pi+LziigQ9kD5
-eSc0sR1y1jXR5M3ek6bj56uASM5YTav0viCa7qIHHMa6UvG4Y6RPRyoKNRcZX4eLCqJZlCwu/jXn
-+4oS+vX5fp+OX7v+l33Z+uJvJ7z72wpHZbmIpdJd//VHX4YizfcExzckP/Q0rCt/nPCwi1gnMHjG
-VgVYFdXNjxOee4GocUxWrCXRfa881n/APjZMLpifG7P1bUzgrbivXJOlxvrl/XzUKlHNzLiLcBwq
-/YGJ3fBUVql3JZAJEGKN1SAYKaL1i2+pShW2zfoyHjX9Qww5C1NpOnubX+Qr5bBEj6Zy5z78OWRJ
-zj6jPOgVzRdtjE1nZ44eGaW6tNUnimT1MFi2Fa37Nsi+0PepeVukr+OZ/Kt7SW1j/8sbiMB2Ax2Y
-pOjpSuFHSDm0tQWMs1g1nIwkLBy4LA1DOZLswVGaDjDjc5uYiwYj+kxmXJZ+jDJHvGqyI7ZnKXX4
-xu7scswlplm2oZ1w/4ZWzLoxyAAFMc+uIsJZSHEocHZpZhM4htDjCzsrhrDlvNKCqo/JIuPinpml
-jOV4CZCOoxiPmYsts/ajVxPOa7nzzYlJKommHWU7J/O9dKT8TH4c9BLDigzz2iddhIGhk1dwzVxn
-uE2nCKP7mu3CXMxOoit0BlW1h27IzaAMKJvTmT0C0wWJOKERMEmSfNEJ6stFUm4SgfEqHG0zwb9O
-EXloCsNB3sPe6nIW+vKlqeACbWtA9Q7ZcM3ifJxTCGiBGNvhWlBjP3WZ2evb2lnqODAIv7Dv68Is
-9xWii2UrWhX5ZPWUzdc0b9awq55lJ2CVVs/3OnFL6Ll10ybrFcsvapsxjDq9eV9PXXYGlnix5ZJi
-aCFGdAlMwP4annJffahAgK1X2Jr09e85n/5WZvvptXx/7V5/fUD9ENq6vzEVsleZLZhm4Xl/KAEt
-NIJMk7BfGrbp4vDhbPh9cCTYcYEf9SE5eyZ0oD8mR4ybqDspapHuYerE+PFPDii+lr8eUOxpIYea
-HFQeat//RXju8t4mZGM3NzEfrixzsK+zb/dGTB242icHXhh5T0iMArRcGN8TjMRH+loyg4mylzTn
-qPtIqYEWISBM2llqvORnM71Vuuo4ni32Edh2oteokr7maTsjjcWNHzP+fOhXh74jGAPQbLqHdvXv
-e/TWMB1WV3/S+e7Jqzzr1sfoHG8SMwOuzuQiPfgrFSDxpWmFU2/kwAJWtTnnbXq0ssIyN+SxIUf3
-qWJeiBKzGJqscvUS4bruAUcPBk93MXGepe1VayFz98+K9xz/dwBBc5NRO/fbaNXGE6uDTJ76QN/F
-ORJF0oOiW0ISap/44TR9bVaV/XAW3NtlTig1dsu3mETK94H8C4AABYkO8Ic2zarbRz0DqxJ2hwiJ
-xkbYb60af70f7EsCRYaDBYCpPEFqF7cjcatX0dki4J/tAto368DZRtCvjgK5eguM1WXgnA0HBRA8
-c8Mh1qNnG1pHhYTGas9GNsuL5WxaYCoVfzEj273GWpNe+PVQPdSm24cpMIqDLvmdb0k9Ww/kocF+
-swcY6vthZhT9fem65XvqNgA0mX3Lr6npM08HaB0NW6nl/Y1utSO0EPTRkAP9q5qJ9SV1ubanGzJn
-QoIVmdVAPgdE05O6zdKp3KYqrmIwfsPwKBJXoIueo+oG3I7+iL6ZhWoyj0vxOW1z70tiD/olpDNA
-O/UkHayIxrRO9Du/My7oDmD59ZF0ibxl2Tbs+iQW7zOYwEe/9ebHWlNzF3TeMkF3iFHnsv6P4WOC
-ojXvMrgYchdFhPMFbl+4bznMu2RH3Zg9jYjiKJR723lwczq6IO3y8dGRi4chhRSmftPVhuyOSeQM
-z/0IhG0DS2KqQs2cIhUmCP9uwXo6RSijuRr31VLlH/jhNRrDngrpYTQRI/QiBmfxLpuyMVZ87gIT
-LzJUd4y0mHASqTP32bXE/sXMJOqoQy8jPQw3be2dqpb5QsgbFxYZbijKt2xb4rshSaLbWMHG3WBC
-jL1jteTxPR/Rjugj7JdvIz3IgUVxF0ZePUZYfgxx8JTW7JDVI2oi2s65zTJl99tFm2ZGV4ti7oNX
-Lbsxl15epX4ZvWdGDhfKGlHTOl3ZP4laTul2qKNxl4i6OXWWxVjLc6tuV8Y1gz7HbL2T4C5knAjH
-IWCAaTx1bjNfzOzViMnlG3E2I7alPuA5qF/4cGXXMuEi23Azlu1mMOIl2wApGUhlWKwyjEu/Hhnp
-xnb+gIZU1fuGZ//DAugbPoKKAbVbsccrzjNGZ6nkVuRLpzNgtTGc2S5HWmaRBbXoel+HY2PHHw3X
-VEwAM9hafMtNMe0HFaHKbbTyIjcxk4WZRZwz29/x9l9zd9pUwb+u7f/f2ysDvl/fneurvy9dBJBR
-36AMNxECQsL7sXNhsWKxb0EyaFC9M8X44+rUf2O0AdEJPySn8ZkD9X16AwIVxavJKoZMlFWS+I9E
-9HQDf746UWGvuxuB5c9ioIIX88+1vV7WXcO+fk/qJunvWjIX27Fv9SOTHO/BM1y4JMuysEDwrJM7
-JNHXjhTu60oazV2L8ECyABjktirV+BE50niqC3shj3wNYYQxQnTf6FphV8rmobD9cTs4fc7OwygY
-aHaju4nttnyU/WId8qrVPrFQHvPNt3zGQpc+TlBiKXd5NduHGejxTRcjV4mHubhZGMzoe8U1+wkx
-vX4vdaW5m9ZOC/EeLUWJidwtOiCSRtYEba+p4zm8cRmA2mB0rresg+tVtm+pi97g3oj9NL5guAwR
-mOv8tJQaKw8k4+ZnX2+6rzMi7Y+kRXhPvdRQHFaYU8ptH02QiDgGr01bj1OqXuGxFkr7S2+B81pO
-KGuAirvTu1X23emnsEcwm/FXHNBOE3Slp75Y8XxR6yp9X/xUvS3wIO4Iu7MOs4Uwwy6k+MysF8D1
-OQBSKTT1O3PmgmcPZMc77l7jumNNcvTiWdJDCOPaysvuqptd82D4sfHAYctKPIX8F226yu+3eq3P
-LyyPzCRYhEpswu6t8tonV+9pGJfsHoXSNiK5qg1Nz3XRPoh2Y8damQceWU6Biwen3E1Oy7s73XQB
-Wdu6qU2PdLOeD8nGteqcKLjBUjAnNCZSpPE2exb78XM7NSSoCZE8zEU/bTtLMPEi7qnd+qpk+yId
-V/uQVxqjKGMZX6Tb+292K8WLmaYJKVSV3ZNObuHdgLtk7q3czo5LAzGRwq6Cn5p1zMgsRP+Plk63
-SJRXrjG78u27b4GUsligmHc00ZvC7boXXxQeZG2/Y6mfszNv3YlUO60YXzw/0h6+5VTWeG8/+UVn
-ACmz/Iemdm3gvJ4v+yAZq0da9YJY16iTDwXB0+nFH6GVBMKll4Xl1le+aCA5Upa0uyY21bPfN87B
-sdvp8luMJcJZc4NaZvpEXmsbQr02SeizpqNTCYxi0tS2qh4vwRfIU9ugHvkWbpkXbc8GveLbMZp8
-LzAivDkZAF/hqNdqbtwA8ch1xdrqBu4Ggl8UAx6Tw1jFr5qWtm9K5E+iTDrko9OSKdZftN4BfqyV
-4ITEeNs2624lZX5xMTDH2lDWtNUBGnxv3UJ4RJHlgkG5d8jEqC/TsdMOrR+1u3IGtvHFixrNCCOy
-v0562aAAKDtNLVfTBK2KPDPZPZCo5uY3AxuGVQi7iDtz7mMCw8uxv9IM1Ty6g+y8MJsjsbPwiQUD
-Jefz0hq3Qy9bjq3Evu4mekJ8Kcg2NlFCd3sxGxPCLQmvKQL3qJUjS7nZ7WgNJpxq1GC70hqVdrTq
-OnaZ7/ktrth14VvaufFiT+0KhGzcwbtT6ybXdvkFd2uayYbafa0N10Wwcd4Jp+t6GHrDgADJLtfN
-McKlqA1Mb8gIK+ebqS+NxKwCqRZWpwD3+/3CUuiU+nC1HhbWjM2mtMt3FFDj5xS7yrumdEqxNAUf
-ck2xpm1qrAho0qBXFkSmkJBxie6wi7cNx+ueBJmG9Fs5iG4ruwo+eocY8EJw/NqPWjUw3zXFUAVZ
-BKE3tKqVmbm4LucHgjemva1PnGwwYBriFiCjdiSFIXP1WzWvx2qlp/zQAvD79ReyDeKTlSTZBrv2
-+EElXmoQLGBr1yVRrJct6EMPAA0Zu0EP7/4enX1zcr3Wvhr7ItumnUWG/KC1W/42me0Q17lJaEjC
-cMNcsJsF3Jypp2zW7ReREtIA3a1JtoNd9/MmIyX2g9V5xqfJKdb5qVe/Gb3J7KTEJ0VNI1xrazsp
-0aZl0bhkq5D594rXxN6wR2Z2RCDcVvB0PkTrRLbUh+bOqlywAx2FYzAJvTuNdMEb6cXqw7+mFrL+
-thbafX372r0W/yd8xfrFPx+/dl061N1MCfS/UMU/6iI2VBgi6JfYTlGACudHYQSIGJEK42wwlAK6
-tPfHWsv/jVkCCSYWwhOqKXetmb4XRt5vkIFttC3WeSP0z8Qo1qo1+VmLwnoM+65h8V4UWahw/lwW
-UTZbsZ9V2w6cCU1MqhzvxmoFuiyvN8Zsx7gxL/a4I93h6NZCe6OXW6JQ6bm9HOY5sj+7isAFfO2D
-R0hPks5PDKywZRi2Ky+lbzfDQbYaORW2U/Q7WyHzx5IrhzFmg6xfdWfemVBF8ox6ez7JFYWGDqW+
-NWplfUUHlqBNS9m2BMkQW09QXpzb2jW8brcYbMK8+VImpkNaricN8qwnaGhdOClQwh2tQZTeRqOT
-Z++jFhvVidRRv+/w9IIbz8J//rH/74xAhFjC+vNvH43T9B8HbD9e+fuGFyqLTbmPogCxBmP233sE
-fOx0DPxxwstY8fI4/NwjsA9mym/gv8XQbvwx//fYGLNE4CnxcL/zFxv/aLzm/uVh4DHk61rTfyze
-iV3zX3oE1cBnVkm1SWU9fPKQWK4E+ukxQ9jzBK2PgBN76D5WycDy04HtiNIpG4mxoWBtnly9Kx7q
-xXTeo7Mv0Tx7FNnEGXcKpnEaqNXEKFY7Y3J2NpIv4I87O0KWvcFdn6zuxxGqZJ5686k5+yOj1Spp
-nl2T09lB6Z7dlNPZWakQLTEww26JDR3nJax9nK2YXL7MC+CP0zBmZLH6TesbW922RbSfzLTQQmFG
-PUJM/EQnPSWDZJsUlXpXlqrvxSwImo1XBoneGJU4ZIlbPBVYGNWGkdPw4kYeKiqtbOYNAb7RXTQ2
-JMxPOtlsO8MS+GGIMh7ScDB09crBB6c2T2MVStgrUMWdSJA/57Q60isNpWvJ+MG+KEVu9tdLNSZu
-6DXE/ErVMKu03ep/yDuz5biNdOu+ynkBODAncFuFmqs4iaQo3iAoUsSUmBIznv5fKNndbvfvjtDl
-OX3nCLskmgVkfsPea/d0RH2PvYZGcV4PdlXo64Qn6YVAW4cNKqbOh1ggHBYa1URbzAzvI6TN8PPh
-h7wXk2ZGgUlGUXRI/N4ix23OyvHBcrQu+aIRFVZgsZRQ1tt4ygNueB+ehchv0qZzX4psKvHMmM65
-zdC7SMXX4rWkrYsW1Sgi0No5wwzBYNTH87BNI1k9cKy0eJ3adEs2BHVGRX+DQJnVbBYN/Jhdo6NV
-Tr3x3uybdGvojfXNk6V+aBLVn5t6SLdWO2Zg4/R067MSMjZhnyU3ySzTF9urFNp9vf5OB5HeuLmD
-QG3k17n1hng4xEMfLWoXJz3MnbLGbd9E1Rj8zBruS6uvti3pSNupzvInZU/dELD0ju+GahKIdnyN
-4DZvkoOH+yGv4XD+h9DhQurJ58S6ae8RIZ6uMox6j2bZaxMa7r+mD+u1CMl0j1qRb4bESh77ftY0
-xjmsrkgRF3F6catFrJSBP92EAvVQlWC2CIxi1B4a0xu3wJkTzNR59dHmer7n+O4OKsQ5BGNwpvr3
-9A16JXsrfMK2rVIkARFc4XZIvf6ZlODxtiDjcydyaODDEAJ0YFf3TfRtuE2B8h5GSOjFqq7R2Vnw
-4C+x4/PQDYz4htooH4owtp7YiPk/pgbriImQj6zoLrupJ3rMxi2ad2o5/Vhdw45dbw7CQnO2BqS6
-izXYLzXGfZc0PsJ7ezCFU+BYrvsyqCiPvla9G/rHZmZtGmhjZv+ohMpID8V74F1tCKlW1qTFjXnR
-XWZk+vMHI5MsfESm703brEqIe58QoZQkcDW4Hfyw9bxN6Dn8s3V1QdRXR4R5dUdEiNhforiYxa0W
-LtaJYXFRuOyjWB+oRL53i8uiKvXs5IZuZJykNabZps8Hv1vbJSKvNVoErBrtT9+GdzVxTFdDB3x6
-p33IFp+HWhwfydX8UV6NIB4zd3T+oZ8SN1Kah6LTy3cc49oL4Xruxc7j4YlWn0kwU3IEg06pwTfF
-l5ffVKYtofDz6uaBmdj2Tdzivll1GSmrtWdM86oaB3JDGDDq8QpT6JQEcsiyS2i1zrzV49QgLS2J
-w/8CvRbkMepQ7rW/n/itFREI/3Pd6f/7xuwfn/95oVOmimVIx/iOK/NPMz+QGkt5uiDV2GLBGv1n
-aUtMkc8wi8KTV9CyWJj9o7S1f0P4xTqfcCHmhSbX/q/c50wx/rW4xRFmmo6xxHUgAQfHutz3f9Js
-6UMy+XaYBWMBhyFIa/JwutIZGYloRska2jLsEadomfE0NZl1AdCkvXJau2y/OjJzVg5uSvyzfvTK
-jM9K18j6SR/WEjXjvlViHlf2kEGizrxIVGhW2hj/VDaQupCGJuRhjkZfBZM7tkxs4Dq0ZPuw6Npa
-vVu6G1dPqpK9erTuXDdRe7uw5QtVgXnDSId8cODR0S3BFP5bTFL6Cyng3kcVYmlbN5ODyyFWDYlI
-U9fxSocmf+3XyKhbh1588f7LFkLlejLJ8DwiTJP9qmAXAXbTobM4QKJnlBUlIiG0zxiGO5/c4wgK
-VlNXAfNMQQQQ9p34zs7rAisvrjv/tppTVe2Y4sFoaIEwDkGWjjEsuaGpgzDSGkZrg9dBALEK3zn6
-g846HGf/TOgouAtzPcJYAyWGhguv5vL3ebndxGu3roh9E07W2us5ImZ07YlY/26ZnXfoJYGEK1sY
-Yxi0En7jBjlB+MGoBQE44h3trAZCzFZ9rdKUdNgWfa4zN/cphzEUbi0jV4Ib1fzGD1nMoDCp16bS
-Dj+G2uba01lYJUGFtK6kslgQQ6LQMCF5WeV4JFkMrrPjGOaPwtDVPLdFVX7zal9zNnKKcIhElUZi
-XuQPwPBNWqN6O8SkCYF8HNEhoyZJmBxDGHxyvdyyVy3u5JlYba2+CLSpGOrQUUPbZ2c7rFAxIMTt
-c9N9rK25VsiQJZspaRckpEAJD9UOfkN6MUXYpntYEwk0lGvQdX0NvYZ/7t+JyiQKG2di7q/na0y2
-WQ5zvxaJ1x+pEDGIm9dQba6YlOUaIVHWTr+Gb3Pp1Tx1sDTaA2AM8EUSTBqueZnjqCsaBiA8Q67y
-VgiXzROuHARlU1RqqPiScHBXXaXql1/vqv63BcH94WXhOPr7YxaPYfv3cCKbz/48YpE/IeJG+CmE
-C66ZCfEfPdMiSbDgMbgO7jdWJDr/5ndJAlmmBl4W6F74fl392mj9Y6+yhE7Q9AvkUiCPOH5/RTO1
-KCL+MkCAZQ0baZkewCf6a8/UDJ2FgsXHLEuAV5hxoLGwAyZpAM/ZhKaJfwzzLylm5sTybhIuvrq8
-ag5xpA8vCVT2G6uQxr1eV+Z3L+p/DKnGzjc0aStkG1afE6vHbWmkeBmp+gKXAa4GE53JYGNffHbl
-gdsbP5C23vdoa88irLo3t3MMjCL19CJmqZOf7nuvWRdi2uoip7qPe/yrWTxrO39IrXOEsmujgyPY
-TsRxxcFgDv3Oi6txHXZ6+FLYpYvhgQUJ0kg/p9vLO7AOCxrGHqANxlF9FtVwC36deOZZZRfX6y+k
-RaK5Nz6QaTLZa0d7zxlcH/Rqsve88zU16+BtKksf1mw4axAqtXxOWT3cTG6inWefUmsFc1pbqyRb
-5pgam4DJ1Q6O0X+QijdSy8e1gzeuci+taMmh60OrO4R2mxwR1lZsMOq3hniHDUDy6kmpc+rHD+Af
-7EPIiPGbC07ntRg9QTg2LreWE4MlUCPuvVhD99axrslpdh5HsxWYXJZ6aqy0MQnqCBXu0ICj0Uy9
-ODVVmxx6updvRotRhCQSe5N1rp6tsA4ogl619sJgRjnMNFtjUxhSZy/GcgBRBlmk0jxSrlc7vate
-+Y9gRBiqAzpuFpuSNICbslHNt1A1XlB3YbtqUDscxzZ/HUuvyVZQsWS+rTRo/Cjzpr0uNL7tqDID
-TxniUsI9jDdx7NMjxH1qPaVLAOdiZ2ChwZplVc/ReI6lZ9zLmGpkVVpptc9UbARyzNLnLB7nO1B2
-M4t1r7zDOlNswwyzRUiCiMflkovbNLNfrLkF28BiejNpibhxS0S/qlLJUy7S4jTm2nw3pmodRRWd
-KSv+/DjONKa1G087hNm3Fafq23/NuWlyjv39ufmt/P7j/zNvXT70+x7a/A37EiYB3B42cBZO0p8Q
-YB9KAaouAAYWYi2h/1NialgYDDgnfWzzVLMG+Jo/pq0ouNCcLqxErNTgcOxfU3D9e0kKnIB6eflJ
-FpLjXxnANKRF2UrvkAv0CatO9fJ7mSZO0NZSIvB0MA15bgssNsI1vJ1HoQQGH+J8gjkOgd4KYsr8
-SMarBHH4w9BVttpluiAqZGbaj2RywrrTOd0zGu5XDoPmzk5w6AxzTgPdci9gUvXQnzDMuUVjhLHX
-MuMQe6EY++9VM0VvYVqT4xjroK63nWE7attK3frWhqZTrQpEUhR5VhyZKxTUKF4mmrxjVRJWj5Uq
-q4wbdryajnxfaw7ukCtaV8Sx1FYUHQdrqVluOKlw/DutI34URUH0Sep5F646603HjdYE+uS3w15m
-LVnsyBzDlFjMRuXrENydCNyyk0hi6u4eFFr1YQgnar+YDcrdVVwR7BW0fZyDwZ2jLN+IyJ7Kxyzz
-lsjp0DsgYmrOiY56jM2TtRMV+58eSIy3HmdtpuUvvOS510bJQl6M+YG/wvzedNPAVmpEwr9KByMX
-wezqIz41pdxwrcivOdV0vsCQ7bSA4Tq7yHFM4l2GuGsdUvqc+amvZ3fJe+q6rTXBTU6Kxt2R9NJt
-miYaNyb+zMCJW29lW1UcJL0xvMK1ZPebYZ0sRXGPzS05mH3v7Hsn0y9xaxTHBGrNcahM9nStOy1B
-Sip7lDO0JL9URNR5bnWQIVkFhFnXUIkmg52r+gRWnJ5cn2kbKzoju0TWDGA5NEUEx5JEIWOvRR6K
-2UWNp4kThceo7vuqqC3g+hSTNldklI9385w74GLQFU1o8GSGSfQVlatZ0Qtg//zSjzr/XFVz5a0r
-zY1eGDGZ1cbkwaHmdZpYf2xyxzpY5HChMrOUvUu5+BKIExqPvc60wN7Mg16JrZ46/dGVcfk+1CJ1
-mLgxV11Jf3C/MAYzj40Ze2sZ8Syw7IvtR6WF+XmYLPo0jR3fs9nrfR6gT7ZPpU30lTNY9lMead67
-i3z3Nk+m/EE47nQIDae+Iw0CRGkZDdF24envS78f38wowV4YT2YKQxEdJS7zMrG/JqUy39n7D0cx
-1fj6ilGtyTBQVSC93t9ahGy9+P6QtxtpD9Xd2HrZkygZicrZLjbYZNgrZ2RZr1RogW0YhCm/I1iC
-WzzA3z12VmGBKU1mhnVT0QxvxFlHq8aj+7hLkrSbg4YxyKhScZZJL+ktzFq9RJAqPjxNkGFeZLoR
-4/1oJ0RrAKr5esctIPJO7GezNiMaC9ba69xwo09Z2FbBBRVHbzjnavbStiBxRoPacOOqNo3W6TjK
-b3PmWtqdga/ozhrLR0vLXKINF2NmZU7OJby6NUOzM+/rq4fTHprSCAbm/s+Rm0wzojKsn51HZ7hG
-xzU8ySz2va30E30OrMVOmmDYqXdYWvAz+Q1OVE7ovlnXoC1WOVoxZPZ61jcre3G49nPInJtQtYZe
-ONKf88UU++u36f/N3c7vvQpbxP9w5z6y3Pn+9xqw5cO/373Gbz53Lyk1ro1IGqv9Py9fg40fbQwM
-OfTT4Iz/0axwLyPKYmjIne04LF64yn9vVlyu8oUPRDYOrlYU1L8EKgbB+pdmBREYEyaU3ctr6157
-qT8PhBrmThWdE+PkHokCW5TxzmAf+UC+lfOFgXcTtCPyphVeIt6Jwe7bz7Fq6pUetsaOIzx/UAX7
-CYlpYZOULi8WWhN1LLTlz8xn95tp7dwovbXIBzxOliv3imTBYcygHrvVe+d43n2am2s/aV8mJdfu
-EO9sA9WAeEqqDIOUJ89aypygqHQ3MBiLPIDI6AOwO5zups+MXeU24FdSqGfe6VPMQOEhkZ76EafY
-r9d5pPTvLW94IpS5Q+ZpY80wuktWmDhhu7ggrLCXcYvXP7L7LwB+sktHZf2lzLX8ZiZz5140yuYH
-LEjpSL5LGASIVSvIOQnpI2uz642Vzpj5pePOX8SXRomixNfVD88vGcL7Ha7fZqi/OH6LAZ/B4D5m
-K8CV5rWoQOXc7h0rk4+ym4stpVJg514Qp7rcJ21tKJIUOfZWY8us19KB3pP33XAxTtXJiMzy7FdG
-fNcvmoW5AujhS0s/UougOr2KG4pF56AtigdWRcmXavLDDUP18ZXETycwFo2EWbvIJZi3IZ1AgeME
-XcNYKzB/iisWncW4KC4GzsZXhmbJV5A6CDLicoaBZmM5XMB+6DbkVcJhXuUcnSaIIiXhkL3PsCg+
-XLerzvRI6aZKm3EvHZTnNffLrl2EIo4mxY6ZjHxSVw1JschJRJ5Ft07WieESOYnxaS3CEwC30Slu
-2uqdHDiZEIQizcnfkHnj63fK4GpDN8/eJgBqz7Yp4yDm2akjmiKbKwqA4FUFk3sIR1D2xF2gzEQ4
-j32l2QeEhL22M65KmrpdVDX1IrDBBoHWxrvqbvCmo8GJrCjjgF+kObR3qHSiaVHspIt4p19kPCiB
-PvWrsie9qnxsVFX3PRV4diqaoniH3W18HU0A1pulYvWPYrFcgwPANTovZmxlon3ntjFY73W29ubZ
-DrNL1N9RGFB2TJsS5RUpZsJI8w2Nb497VB8YaNUFK7UtIInmo3cn476zpvydltQ4iUTL7zouv1c/
-1GdzQ2yfeI/sNr90Ct+6V3S3fSLEVzq0GdSFOULysu15urX83suDzI4B0jDX/JR9b1dbYbMRSURs
-ehQ0TZncCiKIP+puhMxYSy29T+PKADBuzLE4uUPG+motMhWx7ctI9lj1DEr5UvpZoK+QftVtCzRJ
-3YnqJh3vmjRWx15qsPtCApdfOwLpHg2/H9otpA6nxIhekEOTtTMplKxPBHaskXb8WNfCRs+srAkS
-oS+Je9MQEN1G3tTtmdWGh6YpGKqWhVZbn7nKZPcoe2fGMQGGKgrKlOGqXHl2JYu9lMAnGxzDECly
-rSTjsmnzbmtrOlHzsP2SkOwllRpYTQvoZmI0EcZbtQ+LMwnVI4ibuQgq3VFfW3zID6NRSJqZvKX0
-dEH8vlO2Ns1aYX6wtiIrfJDCVQ9fjHVwtvMaq9/ODQnsvSXfSwxmp6Q29Rcr9u4LnnDqGHyroipf
-QAOfrVm7RDa4kMhm5cMI9GKSx7maDCKbNkWT+sHc6/7OB0cdrhjKaje2IAWvR2e1HfoRqI9fO+G6
-k3IYeUes8Iuv+jnwtWzeOVMhH0TfdMfRsT1EdCWE5Nek6eajyYDkGFkd7q5OiuJAbpEqdpIIz83i
-D9mBsh2DsZrVBQZce4I7B/WNAIbxpYiAE23zJkz53SvKy3NWFvbaaySEqQyT87rqUw18o8wPBGuY
-nOS89vKC7rD+HimLSG6XRfqn5N322JlmzrfGGz4JnCcSRFJa8U209b5OHbFPW7s9wwRrwWtOzh2T
-i+l5xFx2giDfnRtsMCrAYjM0O1hqzjKdynPug3AQjKqFIXHlmOOexXaN6WCoDJrRAcNBP9Qa7IRW
-yijo9EQ8RDbhGVXEkCXwwLbA4mxj0m4TCtJAcMU8W3bRf6/brt65osMj9+s12f/SybBJXfL3E47b
-piv+ffP2R6HGR/8YDOvAaNiWLSHJ2MsMqrCfgw77N51dHCMLQf6yfQUf/HMwvDCH0Nv/MRnmQ/+o
-tSANCP6867xjEcv/ymCYPd6/1lqYaWGvusDPYX4Z7A3/oixjRClDC7FVA+/1vg0zpp12ijtedOG+
-zeZwE8km3zedECv8NjMg0Mg80yCjlMxSgktH86bCN7qSIQdIDfrj3iIhmCEGSSo+74vwt3T/GqAk
-XFMm9vbBiN5ISvLY+EZkFfej+cXO9VeCgCmCQiDuhlWTsiwRD8cZ4RAZU1juDCOwMZkEhRNTiNSE
-hmKcmfc6DtKbQnr1ulsA8HOJag0m3fzA5hB0Y9dWt4gVtrWh/cghkByxDI870iaq53DiSApTMpvX
-ywJvrYvo0WucjTnH8yEsUrT9KX46PYWVExF5sZ1nw98UZbxJByQLfY/XoJy1Zm9KIzmqZUI5LrPK
-8Tq2zJYJZrLMMpPrWLO6jjhxU4lLt8w9jWUCOiyz0HqZitpulecIEVoYC75fvrJ/046uS7vOONwL
-SoYX36zRym8ooooN/XRHEcAUdmYcmzZJvZst69j7aloqQma2YaPvrHJmHS/LxgmivuouXTWoczYp
-I1v1OPM2VC/GSiVO/02vjeQgK1s/zklhHkwxv8KIYGEfIrc/AfAtMOnFChyBrB+Twb5UcX4fDoO2
-KaIy2zH/YVlo9fw9CnfV8g3/qM3eD/xy1A0aV+Nrl8NzdytTsMibzTNusH4vlNEE8eDop7E05dm1
-p35fZXG0YVzSfSWZzgGL6Ok7yHuPIhlASjXeYySGfB9lzQNoRclcxFMgEnviP/I5oikYjHV81S6Q
-8XTT+ETgdiRPvtoRK70a5wO32isLP2OHTym5VO4QPrPfs+7lwse0bM0IGhSSe7dqe6zVrB94E0lI
-xIy9nTs72szeqBC260MwI20ExJW+dSOjMRVq1Qe0Zq7JybXctVHxMA4k/Z60wQ1f0rE+41UfP0Xd
-1MeMvKQ1GnDtoHX+dNczbt5P5disoQlxsfKSthuCnfQv18l85qnpJkKldJqZ8SP6JJKKLg3oFGBH
-Fn1M+lZCb6k0KqAWMkaK5Lm1dvQGUPsEVoyPrgpVUA4QR+tYOj/cyZcPaTPcJ0M83imKtLUmKntV
-jtEXoYmv3BfWTTRM3QP2Mfeh5fjahQ7Bm81CN+U1B3TqisG/4N8YghaZAtUMINRkQaL2THDWWDqM
-leFo2mpK5m/lmMw7HOsDzVXCwRLlGgkwhn2XTQhIOj9Ra0UOaqCGEVJWr15SdgY7nXdjFckuO8xc
-+VvVzB8ZV7PV80f7InydQu8zk4s2bUG4egvMdUrcYadlsQyqKI7XWjs0jwLEKnlWPIaMkwkmdeZi
-j+wIhArZvhtqmIJ9FdOVbGrJEe9nkLFFYd2A32iChOJ2NUMEX01sJgIYqh/2IN6rydH33dBmh8Kc
-aQalANDkGudGmz8ZiPGVjA2I/yzDhktDVVTaJ5vDG1+vezZFZgTpcTD6delyoo6Z9jjyZQZ0Is5W
-gO7+CB0vvDOyut+XjV4EujWc5jrcYnuHFatZ0baxyHQmrCFf6yaHV5FT8NYzVIGm6Kc1bsNmn5aT
-GQxkdfsUXQYcSNrGy7AIDN1J3ZVSfe0WSBXwZdpOPtT68oS8bDqqgig0RnYb4hzjIE/maP1fUw0s
-Wte/rwZu3hqmL//Bgbd8/GdFwCCF2QrCGkIQnSWjiBnLz4rA/Q1z+rJ3AJ36+xzlj4rAJ+IGwS28
-Kvx3/nVd8ntBgHAdESzqc4t2yzSQ+PxKQWAA4/jLppjYUg4QJD/IeRnqMOb58/AlMZNWc6W96ZKk
-WfOaWd87Iy2eBidRd1XX+OcyqhmuwAchCLTXKHfXU9mMFOj6lJibykm5YjWs34csY3jMK4tPtlhB
-WAwxLQ/tZB7AtlFx0/4K/ej6MnrplFscRIVRbe81uUuXNJBYeOj9Vvgn9DA0UvLaVBVC0GBZVpgy
-7q+1lohdWrAumr3XmTDbiYawokW7dmts9ejc2hJhLk6dpIF7w8TaW8+pII9PIw+oObDYTB7aEnr0
-ZkQJz9kpcxD5VT7q69nnxFfKjvZxRzlQ+Hn/ht0fY3MInR5ZvNK32IeiH05v4cyR4JA2PcuVb341
-Wt+UWkQ8sdfe8Mc7Mkj4QRnatpnVBXrcJre5rldnLTEGpBy9cWM4XXMzmI7cWF5p7rgVXOIDi+iE
-JBd2TpMm0aX0u5KA+EThFc61iv+iM7AhRfRjGyeWw43dVoUAxMMe/iTIfa0hPxvxDbms6jtME4s5
-RDFMA5ck/uMyFJUb2J1tnseUq9lFjZ+vTD8GAJw1EP52cbagnLRi8l4jvVSPBOLU+S7JPTLJvWs+
-uXKWrPKm9rvPriD9CMmTH2UAcZshCsYSF/0WNbfs9tXU1ZC7E8cq1uk1Gt3g918GMcIIP2CYxRy5
-GwlSt2cLz1XTdtGGoDo2P9zciy/BVZ2ZnITShh5PE2pQ5iBG73zHcRYlT1oS448iqnmkMLXDBVhr
-Cbu7Cak22RejgqqPiBeJ/SF+mgggg4L4llFg/sHQZ9LwX8PSXCmREh0ULylC9iz0DYhgk1yka8xQ
-Jjpl7Dq4BTzMmYfedE1RnKRvcWYsa79rYNFopqTbhoVPmK5vRv49T3Tq3fRmpw13ovUTcQrbuje+
-aL3wm21l+Ol/jxDH4iT6+wP29OP7978X4iyf/Xm6ur+BagUnx+6WRBK8yX8crhYiSCQwC4WIY41I
-lX9ZLBPbZdBzQWlDhuPSvf1+urJYRpdoLFpZB3ydjhfiF3Q4tHX/erqidQQ0wo/lCE7+f6ff1xWe
-oQiqc1hndrtr4SlW66TWive+GZxHh5MXG5jRR8fOr92NrjzKI6sfe7lyyRu6RdphHWXb9M/5oFMv
-uV1cR3fGyBl3QaCM4DmC2Giv43kuPgWE1YT6O4WDMcI6TYJWM9T93HvWD6Zl0XHUtWR53lv3QupI
-sq/d1KLFECS6ZENHbehYT8wU2xvdGH0q2PE5I3d2B3BHX9uZT51a2c78XvtV/t7GbfkeUk1uO3Q0
-u8hqeaHMmv8TQ6Uhw+fEZd8sZqv9Som2rIxp5TBFl1VxrhlksQGc6/HW6xmErLuJ64NBvRkkftij
-3uNqQUM3TYhE09ZZopA8/Ed63ES7hYiSrzAnzjekOPtsBSjo4IXXWmaRKz+pL11Wt94NNtb4bUq1
-nLF/aT7RqpjPPpBKNHSQgcDzNu65cCL3zO0bbs2cVmOFnB+le62bFxsM0Zst7XaLD7Hb6ALYPmLG
-sDQezYJzZBXbumRbnrWG2rl0pZdkIk/FaBh1nROiW84As83HrDGSfU8I4rjh52leQ9FgfGXtspz2
-WRY/mQrOxLrie0f0GJNojrq+sHaTboDYtG2yCIAxeO49NnnWmK0yJ0lxXMzg1/KhbM9dXs3npBL2
-A0yR+GW6UhcaMnJB3al6egM6gsQ2axt9XU4GTtrxSm5wrxQHbwE6aGlRbeoF8pBceQ/6T/bDlQMx
-XpkQ44KHwMa1zOOv1Ij+SpAILWiHQPSIWr8SJvwrbQIyjUuSmQBCYVqF8TSNKMJW9gKpEGjGTp1Y
-hqL+ArEoSgnPAsB6dVpsp3gzFt6FWNAXKILQIiULEGNipPJpLZAM+HwpwtuFnNEb5miukblC1DAW
-uMaU8N3A+Ae5UUadtberSa5lYenbyi7N16i34k0dhdO3EcbdFhf5dBBQAk5sUsMjUXrM2JzauE1S
-pfcrXND2p48keN80hndEK60/WmmZNnSodOFdNHrrnuPlhiHL9F0oEMYkw4Tvde0VbxU+u1MJ3fSr
-WzESHbJiP4Zj72xGIcsfmWy0Wxu/Cs08vl9tRUPcPCwRaT33pMqmY6YaPCWla+86wfYX23oHqb/s
-3cPk2kZ9YJIcmsFsKTSpoiKGTLMqcI5ugeB5nqQGE0gqZFAgb8l2qxuj+8D9O767tsQuw4B0ZtJd
-Wh+Oco2jUdn2Fz9xFrx6jAbOYDQJXqcHxTIRNkggDRYItBAy5aoPY5boymVSI+o44/eH9Tw1KtfA
-MhsmuIrhfCSBTvJQsvZZzncrfbTjWyRb7rmUIIPXYYarYDvSTD3LyK9uoznMXnJDyBedOQ9ENNnW
-Lyxf4t00TWJXOYl3kKlVXJYonT2ubd0803Br2cqSkeWsdC3DbDUQk0jBaYlsP9S6uzIba7rks+hJ
-IzAb44dX5u5D2OOFCaD7pC5yncEq34BY6l9dqlvjoOK0fiTlx1zVk2POTwM6BF6VLGJmtDDdaDtF
-1kWvFROx+TKmTt5Cv9Sict9FAuqzXedIp6GRJe94/5skyMfIsj+6se3kMcr6KbsTWud5a9W5HJbg
-J6moQ/JIkX9M4yz2Eumxu631OeOpJcyHTG5K0v7kxBb1dsOmJNlFSCxQ5SSJMz55fVp4WL0dUEdo
-6GKUd2bYOvfAreVxDuP6OIYa55Fw5xQuHGTSYtsYxddQxym+Ke1M19ZlBsZnY1ZoVTcZicts3oB+
-O++6SbWdkTpIThXCx7pHzkDh2ek5z0hiHNshMnI2D/mixy8MRZBh2OUFIs6FRSCbyPPXCdqVu1SD
-yrPKiM3ghEuAwq5DiRAoqR2XihQm0QovuJHeGg2jDb5RD4G214+EJ/S+2Z4aOTb3JXMqb6/KMAKh
-StWWLsZq49gTaj3DCKeFIhxaWS9V5RTQuLnQBqK3HIQbvRWV/z2z7QXP+PfF1jGJ/mMvy4d/VxLo
-v7GMxzaNku8qu6PL/dnLom1msgwHzTYNA9eJ4DO/y57R8TF1dpAfgCKEV+Xxr/5Zbvk2lhJ6XIFd
-FGHCr1Rby8D+z6pn8DG6wXYazAwJegQwL6roPzlL0nIZ0w7pocagtEWJT2aMqNgwM35epx65aGs3
-KgFAhJ7XB6SVWRnLWb//gBWvlUGY9v4nUzf1oDeDe2MMRbkuOd8Ohcu0iEIvPCy1wVPaDv5NpzdI
-iJ3R11fZbMyBkUc3CNYAiQwqHJqTJ/LiLor0Vu4Ua+hpxc1he0S9eNqzdPXJY4Y5TD4SQDffQoID
-j9ibmf4KZvFJGX5UrpVq6rc6r5IXjqsW/2kcWsix2ubU+WJGtNeXN4KCq9gUOsauFTLB8Q4CXf/Q
-ZQOs+rJJ+w6yQZKiTha2udYKo+R+jXBgbGaui6duXCoZz6q8D5ppbc9BWT0kGMV533sj2jIeLJ8z
-o1b6s9FbY7Md29Gzv0yQbN9oKwuyf+rY3FoKPpqJ35z1gKFcezMOXbREiI0avjfHkdNJQa7SVx3Z
-f99DMT2LYu5XPnuoZyU4KlaJqBPSQaUVDiDrLDJ1ebGTdWUbORgQ1ZdH3HMRxBDXW7DOjLezAzvE
-xLlUvWXfOfZUbLxFveWnlXzKF0VXeBV32YvOi/7V37ojWvYg91h9eIsizGGaeeTGNd/dRS+GM5c8
-Bjlin1lZV0lZpOLxjfBhdz9eJWfxoj7r7EzdMVChuHF8tGmLSq246tUW5Vq1aNi4YuylyukIx05Q
-fEZJitytXpRvbGztR+oM5HBqUca5qPKO+aKWoyEukW8T7eCwUZyKd2NR1mlOWwroa7x3mxEXhyDA
-qkWIly6aPKxIyPPaRannLpo9O62R83eG8aWqsdmiLJiw4a2V7ELzIYpVO511u4lOA8NSiMd9kT2b
-rlLGWooW7Cf6UH54PUcIu9K7QnvASRl/ltAx0kA1TMC5DdnnzsUS7Zv7P7JRFOc2lOZbx+/OWmdq
-qIfAzCyggx619apny/9ewRe8wSTapRuvVY1JqODogDuOatBA/sTOAWn+uNErGW4oD91sly0uZ57Z
-Asy7OZ+7TtRnFJOk8IRyLEh6qeY7miA5r8qIzc+Kciv6NnVa+ZSEc/PMOaRiZOZI6oh+yvaR0fWn
-/P+Rd2bLbVxZ1n6VP/o+3TmcnC66IgpAAiDAmeKkmwyKpHOe53z6/g4k2pQsynbT0e0/zKhylUUR
-IBLIc/ZZe+1vMfHJh9I3wyPiLZmKwABAFFdT+vExNtPpbhp855q5KuOaz6kgSTd2SrjXbatf+2Tf
-2qs4I1IAtF8ZXXR5YK5jQZyqkTnmk+kmLvHfDciQ3ElurUGLr0MdsjIj123z4Nrx2C6i2OrOpqQy
-t60tsgtF6621zZ1yhpdOP81ITd7VBVycPgn8LREY2Tm7l3M2Fml8NgRdfpTE2NsZlSp/Zp9XV0nq
-CwJ/LP/ejkV/2zWBWNcaPJ1FXw7+BQT+AWmsxw67Z6L249zK+AGD2GmgVBGCPZGuoI2YwDweaVpV
-C0HT5bbkpPWYx+W87jj8sEJU47EeDiRhEDHGeEdYxXTtg1y3FuEcmE/jKHTPEnhPFpkw820NN1pb
-m6FqXaRBrLDKcu3JNHYHaLa+Iy4SkgI5Tw1O+YyPwfrZTWzjYU6mdKWCULkQDOedUu7QelCsaYiW
-lL8dvImCpw0xuO7mriFHAIF+Ay56PE0CJ8P/VIqERnZUpksDrefEaSaHiRDaQMDTIxSnvJvp7gwx
-R7CwG8IExGzQbhW/cvewL8x5YWWhsmn7Rt806FVct5mu1DlsRAiwKZDFyyGKcPFOyAznIfYKfZGV
-TsDMGXOJGM0ge2vcFvyFwg5w6DANDY89EtxHedkYNcVyN5xqk6WTcYW7/ErxjcFT3Lk+TysRXYyT
-FApHo1MMzw3gbq0K9LKntgXvNJMNox23pCFz4nXt0SKomB8Jp1Z9op3qfsHa/+dXXPvmsMU+FuVU
-R0ztffOv//r/tHkvyXJvFzhH2Q+iDn7p3ds/CUZTmYNFXAcJg4v+pbqxfoI/oSK6oynBm9U1fuZL
-dWMi4h/GY9F50BjNV5xZ8yeNwAS8kgZtQyEl9j9T3mDM/Lq8oVFA88DmV2NEDArCt7C8biR2K3LM
-JVMDIPNrsETCdId1GPbOAhuXcUrQenkihqjZFmqvMf/f1+NOqHp4Z/gl5TcnngW6rX4V0EJcT0ng
-wZzc6w1B9ovCVdMj343IJWT/XPaEwq/bMEp2qErdOS8vJ7moe+Dgkd+pRJ/sgqzo16hNtlcrtb+N
-daMCHmDdFwCbF+So11tiqctbBQbPqu4VbW/ZuX5NblENGMG40TqD8izMKqLe1GzJ+H+97ckEG3HE
-p0vViQJ+y9q5r0Vo7juI9yczsbkLo/Qh1hnTmcjoPYd1GOxy8n+P6QEWXs9EqLKoi0rftmGp7C0H
-lyjHisbDChojLRjzNndK+6j0Lbxog4DQHavJvaVN4aegM38mVS47C1iQgc8rYbHWtMK56gNnPhVN
-EW5sx+dkYSJ/g6MVarMvcwOdZmrwiRGUhzeuKq8ZuuScVgwFcpQlysVsxQhFo4ZJgpH/D7Hugtww
-4gs1hJSNkVI5r1NYfb6au9eoGMp6zv3y2Yw5MVJVmuNedzeUbB85DzbN1tQ5ThIHRThmCoyVzIXa
-/mhanb4jZLLgJE40EXmCBBAPWsvU6uhDIHNp5BaM6GWzYxyXbGWPggD4W6uq+o3b5vf4x1I4G1ht
-F5QSsPIsti1cRnEOektkjwFQJHo/Q+w15jTvADu0F6kedI/qZOdrUaK64Flq176NP5x+wqLKhtPJ
-0YlZNIlxcpv41tGbbqO6/vTc6jnmpSp0l00dnarAgBajMy+LoTpO5mCNBRhMWKY0Xm324S63AxeW
-XhujtbHv6gQcO3oy/ANSx79Yj8QP+5ReTqn9pm1J/uzngx0p4qxPyOiMsqKIazLL5dcmpWZxeNNw
-DFkWY+i/LH02WrkB+4cWJq4ORmER378c7FgVJWGAeS5M5LQWtT+lo+vySV6f7Fj68C4wN26QKKOZ
-QhLBXp/sciRdcID1qkKuBleV66d5qM3nwN34dBR4KwJQOrCFkbQvijGOdgPj5ltHi/pjBVCAN/b6
-eJIbyIq0yFqpX8BcPqanUF8HglFrO9YHPvsZc07Es2hHHH9YE43E8G/pIFiLoFJEukC6CD7omY5Q
-0aeja66yKW73hLZJ+6BojUuFUylyIvp3AYT5EvcNMV+VmB/alGnVvJX0gTAmFXXtF27tLhqAjJdY
-41H2GQxdBiPmgl5aMzuYxJxH6KWusIfNR5Mvngso/ziatOiy6yrcHWnuk7s0Fl5QR/ElM114030t
-vAomZnyNJFMfg9QYENDU4cL19Ujhtgr8KyVGcUMkc+1rZ7CcDyXr75GjtuZzCLhnk1sGCWEmmK6s
-wlBA1W54QLpYbAOzLjZKZkxPFXaYD4NhExHQu83WjiKw0YM/HTWuE92RkGecAPmxb5woLM46W+0m
-vKuxc+LAKVpbVW2sIwPeQuWE1ZIUEwvJZtaugTqae4TafD3aUbEhtQD+ciqqcxy0aECV25AqRmZq
-ptvK1g+GECM1lsfFkJnhNp/qduX4HKbzCpi6luixR1p7s/XBq620kRHPOS5JwFQnRmSrgMuOgL3K
-69FadREP2PuiP2PjbbYzs7ZHs+p2JzRq29UEg/VmgvH4WGi1sWkDTayNJDIfNGNqriOWxn1lZcZN
-ovbmzjZ7e5sFXX8EQSrHeuWQkDfAU1hkTVEfhyqRXLqbkLcD8AZYgZvelSlp91HRITZw3dddMZpE
-2PTiWBlrcz33SYMwF5XhYupR8R3YqQBkmnRrxiaLMvCMDML2Y1zmxVWo0NtBacibM7sICRmac1e6
-hI2aUDsTNaCKKU6bthJ3OoX5tWhCbdtEhetViQWQMY5IIjKmiZ00Yv8tk2RkdkCtlo3pxkC3ycTB
-Q9Mcz+ZorEc3CI6a2FL35DeMx06gRhGKb8GhAP7IB6Oo87UCW/dZEjufZhBvjOZqF2Y6drj5+tBd
-o+Ukno1R6ryxonIZ2jUM/ZqYXLQBonLwwY67gAbXRa71/ScRtOrKcTMl3tNmtTyHocr1oSj8J9S/
-EiH4dv3r/SDqS/7kSy8VuyphmiANbIuZW/WX+tcE6cYf41SRWAOhSznxS/0r02MYwmW6CJyTjfPp
-9SbAGy3jYywyFuh+smr/CXlPSKTcN5sAjVS4CWxU0HIcmQX6ehNop9LPi6FfprWe7RBw5pPaHIJh
-EQ2IBCqG8OuUdO19NTwqRLWcjjYpJ5Ud0dJHiGOWV09O3JTMRMqvGrtZ5UQlEONGWq/m9n4CKJB4
-RmNed0DJeo7/ShQsoh5O+sINoKksYzfT1lGewDEnWGXa1JZVx57QnYFPbBTChS3rodvD36LMtPXm
-qmM4xpbzC/ERoGbiTRx0NS8oumlbzE52Xxgm7VV2T3dlOAplskqU+cJJknJVB5N9ZgR5vq8yjH5Z
-PU3Qfct+RbMKiTs0kViKWL3yMb7uWZhR3oM5OKYVWaoYM1O6CSxyWw4s7hpCSLogQlA78p1BZdoE
-nemWgtmWbpB2LxRDXY6MgYQElUfasytmfx1F/tgeGxE4nRUo7OouRPyHqa25V6Flpu1VNRX4P7om
-cj2zcfwdeY8xKZyZLe4UEZKSmVWJe973I0pJD7U5ORu1UfmYO+rE5LBhJfWyGPPgNKe5v2F8lN17
-Ftq4CUPbs2czPzUJiOIJUoJxOhLD3YuOaO59ynaxywuTEGfqwGY3M9M5MrGVkNSKAblezuS8MJkx
-GDW8VsCBnzR1jq5RzFxjEdjkUNEOnfxm3czIw2qsdUckEql7zcXK50dTSXCWg52xEA3dbjJN2cc4
-zphjdROCyPJ6s4iXaVrq0io8bcxm0k/9FpxG5POxyMZxm6v5U5vYRJt1c7ZqitLaRJ0NZSfNnb1o
-/PQUv0CaLERpK6BctPkMY/C1XcXH5lzBC86Fta8QJpZVm4EI5DTBS50B1jAyvvETcmh7zT0vplDl
-w+lQCJVduC2Y8zzLKYce/AhmJ1NKm7ARFxVDHNsGHCDtTTAdWZZ/1BrWVyUkLc0c2q1fqOVDGgyY
-f/WOGhum2qfQYWZTjau1mNrd1F11cWNdRaUPpwYxXKYj0N+ChmdVLk7x1Gf6s+2FdlkpBKZ13Wxc
-9ngTN5IbeZmjnZzToHSP5ywNIf/QNT9m1iW8EdCKoVFYvbMFxGSejFqSbwgaf6YzZLRwDaMPtdvo
-4B1UsURmIoC+QfUaB/jBNay/pZMm1S5ryK5zrI7+39CbJ8ziEdNEtQiFNzvRA+xVpGSXSwhHKr3P
-UD/Xh2TaGipclHoRBlkJAbmnNkDcNY50+L4r5n+jZwLQ8nVgV8aVwMB2l4nKfmSe1f2Qt820GOdJ
-nOli+hhk7VEnOJFYJQlGtmjGUyblwQC4feXcK7UzbAJ8ohQ/oH4cU3hB2GyJB/+oQh9fhOMnu2g8
-21WClUpZ8bGpy2nNvbZKy+m6VRhVGvwnBp+WeBBmz/TzNFg4XYyVvhiT1dQZ5zVQqcVkF3dYk5gb
-Z2bEow5LF4ZVM1dTz8Z5p+U/a1OLl5lajNpT6Y+CtAca2+9JXiuO6xaCfCcjkPBTgdwiV9BQHW/o
-jXOCeHYiCp9LRrkxjpIwmjZWAHSkSc5dB9FK7dvTJmmVdZgYzFRGzr5X+tzr7fRqav2jklkXtUlv
-UtK1CLggOx1fdOOa00LVagI2ivqe/mYJVsThqFyiHZJ4pcaw4dLpAv8bIBDcVdpMI1LN82UYSguw
-Y8P9CxRUNcLAtZQ+BAIC/vmFmFvc+EBolq46aossctdMnH6w82t7bK8StzGXLrAbHN/OVQeqpEuH
-tSmqGbb5fD7Vypp5qZ1BX6hLgmvUd1LbfW71mVbjCj6uu1WgRm3oOAa3emYu2mmwnxTb51FdWLjg
-+KNlUgq6RnHh1UFvf1SsAVDlEH7s8VmYi6YYi2xBVmGyD+0h2AmoTx52PUX6zX3CfytxEiSEr9Cp
-StdsjmKtZFn00BIHsMQFTjx5UaeeP7hiXZq+w27g5qtYCZ1TcPH5Qs8ryBSBNuNs1KFblibpLB3m
-PDCS3QmOaRPfTWF7owNj14znq8wHvk2I+zKjdD71U21aGaL2qtnd6pmis3w57SoggtCrUSmwtpAF
-hk1hl9cT8ga+wg0DUTib6la/NJQ83tKAJm2s7hIXunkSr+ZqUB+maBoug84xm8UAIUzBMdjPBjVo
-rx6ZDQ65BT4Md1mE3GynAbTIe8UnJydoLKa7UjchgcHJzxhqXCkI/MuungTjdW60mfA2bf455d8P
-zXTepyKf3nbTSZ3zcwUoKdbAWFSNak6e52Vt+FkGoMwjpQMIL446Gbn+q5sOXjYq5+EPX3LYf1UB
-LLxM0ptHhoiB3+7PqQCSvP1NAciQOkIDQoCmoinIAvFVf9ey24lzUr0CgPEzhKthWYPHuwn1UF0z
-IRneQKQeyBU1wmNbtx6VIrq2auuEGZptNg4nBl5ZNxfMXZrp7WRUZcL8Qdvhd0nzK9Ae+Za4o/Es
-y4lEDnHgKWHrrv3QGTy9ytQlDuKPOIG7FSa+W5qDwSqTINd6dk4AvGdeYpbhMZY8uHF5ptK90tnj
-QYkKbuMVPCixnQ32l0zFpxZNYbg2GQ7O6Tm6Ffh8GrHUAo8M9l5PaqWupxH0p+mHkKaSZD6FG9ed
-UmkGyzlyof7m1XnWUOQuYxija7ZNw9PisLumSxrsVVdhMkLVIEVM/CYQdkmkQo1bdbZgXqdKB7aK
-6cHXjBhyhgmMNi2jda9G2lXa4lIpQEdsGG6SwdV+djSIEoKVbcwbMkTkWG9jHvtdOT+afRl/oocC
-ns9MhXOsIol8pEgaub0VZcWcrUnQk2uDVRlyMo7M/gIrFQKNyWzObBX5JRVWQ1x6oW0KqLmt0O+q
-yL3AdgyyiyqKORWcecl55igVhAlOkGAxqoUSMdZYJcSNaoxdWrymJjQ+JbIQnA3RrBCQeLDUULZG
-nQTkr0UGK16tL6ycCQo1ZwDDyeC+kLBChcuwSEFH/aSb5k9EN34Kk4k0kFo/QpEl3b4aTX6Y4XR2
-pHrJHAaLn2WcEQISgelLRkL/BnxQFZNoZolbMrJjFe+dvavDErhHPmWkF0aEgvRKvLZK59lKtJs4
-za7m2XyG0KKtlcHGBjfSFSb9d1qBrT72MQiwiSuPTBUcde1wioeg91DJPvZaf1fqg7vHrQfxJMQd
-7ePEnDEPMNNXdVuzLsubsQ3ObMwKS98wPg0ivDdb414xsssM3Ac0FIxniRDdljK8XKS6FjIHP9yZ
-8MvmIgkx+GfJuiWI9kjXzbvCblRck66/CBgS5qo569ZsPzF8xyiQS/YGLGh1H/Gp3ZddHz0VwtDW
-xqD525nZMARdsGdGXFImGHWxrHQ4bUwQMmFndQ7R6Vl8gS3TvRzsrFlXIID5uEzjvRVb+oJOiLZk
-WJpqiRC3bqdnlj+tnF53jmtRKGtgEtq0xPA0xPiZQiaABRHtOnmW574J2A2rmLNIo0E/nQ9SXClV
-uZnUtqUvlbpKanbYAZDvODm2YO6lqKcdBD4wbsEH4bbIftzwFvPKpX8bdwOO00kqhPVBLCQmbljg
-wDM2ptQSyRixmOW18UrFDHRif+ia8aQ2jMBrYrM7FrY8Gkp9EgUvvlCI2yYnU+qXrMUuw01omm7k
-aqdTZlprVyocsKEtYoKk7AFSSV2RtM74bqrX2xa/R6HX8d42zIkkau6PbRBFo8dpITrNcod5SRBU
-njnGP9fVAEwoKUPy/wIs9z6Da8lwxRoxXDmVO28r1Rc3MAM5TAKH23aia1aZEInX4tLcFW0Q3sVd
-K25w1D7+c3ZdNqC3RZfFw/ScNm8DWqRZ/EV4oasIrZH/YhPnk/fLtmv+ZNiIKOBW6EuivrzKWJff
-gjLJf9gUJUCY3fKL+i5+4o/4AXiSgPnZMv9c41GC1l7vu3JomHxNIC00BzQbn9fX+66dNrqIO7YT
-PDTOMfRGsKqOkvERmbg5Lc93nR57NDCTaDt3U/vBOCSjpuok5gU9rHhaBzkp0y1BTbeKDFRFgkDH
-aZRu40Qyb1WziF7NtEljvpTDr76IInn7pDKolQlEKGJxzXnaE+Sfb3AhJ+ZleUh4xf3eqh4jPt21
-6ImAnQ9psB2wTetuGJ0K5BhW8dqbZXhs7lrFcXVIlNVkuKxdwcTErCgzZ8dD/iziZ4kfCRrGA9YR
-B6PpFPUwzmzc1t7cFvSnqra6VrqiGaCu1sCzFJndmBEvC0t4Kj8whiJDZPxxZm8nhqbZDVlowAhx
-3PBhqPKQJp1a9U9ZURKja+mtwTlejfu7tHHrx7w12N7HsNCvCBzQaNeyzfmeMAwKkoDYrH6hI1wP
-uMdd9+cwqbNTm2HLZz0cz0JSEmJPt7JYR7BqWZj8vmmZek4M44Z9XpeSyQyx36wxKhBLpITXzCYg
-YU1a3Vd7vXOD5jgPTWddV3QK7+qizJhd7sNe90xA+R52BlV5oP2sPfJuMN05iTFqt71Q7pOgrrdT
-esxE66A1vQ+dfwxX/5yVgpvzRytF9xj+oD7nhz8vFJqGlZJWG3gBpvXYEmCGv/gvbbZuUobp4KkM
-FL6K6tZAL+qS5mrQrBNk23B7f1koIIW7ZO/BHbDwc7LO/DmOonyS1wsFfUDUY1wKHB6EIWjWfb1Q
-pNEkEJaHjWPkFfO8s5rfwcIQ10FjM06BefISwcI0tkbZh0cjhsUZz4JW+yvXULuPEMIac5cljo2r
-dwKucjQN+MogOI+tvimTWi22Y0DOxcapG74baXiGsDAIvfN6kK5LkmU6/FSWirmOosDvd3z+odI0
-sw51kK6M2yzjxp28mIF3f4U4Cs8mlGgbpEeV0kTybpLIrWlPMxC2GcSo6VtRtDrZU2ZRLCw/GqzV
-hH3UR9o0XExHON2VTeUGVuD5RqMzJe4QucGp2x0+drVLjNicDoised17HT06YKzuFBpeU1ajs5X4
-gCNcRfMAV8fHd+FWQCE/4MCzIJeHM+tXbw9WD3uwgzbgm5zE8Yr7ODIzu2YIBNr4Brr4tLEG3NZL
-0AYt0pRZw1Qk623XlhXh3TiFyh3CKZMG9OqP7TqaKL9CfxQeYL3xdtKxWnoiUo2rOBtiixiFloS+
-uNWMe1fAOfRyv6f+6yHv7s1YM8/VBBv+eSK5c1OQUGTbzCsxNyQ6HFcuw5CLSPLqzLBCGiVuvH9Q
-54qILVWX49cUUIDufMm8UyT9bpAcvOKAxHMPeLzCaPynWYeZl33G50mSXgtSb+pCZrPbA2hPk8w9
-hvXA75FMNtCaklA+4O4A+hjDtmkAQO1TLLtBRUDGrVYZua1cowZDaXXwls4Hn2lKPs4SABnJc/HB
-idoPnVwsrXlWiK1wO3VB/zCZ9lJ5IvocEGCLQiOtrr6B92shpAN2lE41z5os98JCRHxwo8YSV2Y1
-Dc1azYNSvQH9V9zg3wjWWHkx2QbYS84N8Ae7pLTsJ4aiGMicpDPXOph041ErI08czLvlUMVHMHRo
-4nVcI/w60ukLAwvgo22if+Y9EXOs/riCrSaa7mLLwjSc67JidxlzJA83uqsOnuKDvbgsTGD12sF5
-XESy6XrwIyeW9CYTjaPctFloOV51cC8TW4+TGXdOft4f/M35wetMLEm7EdIErRdzC93DTt1TstT1
-a7vu/aNCGqeHIrSOMPgVywSb4WkvqvpSkVbrXHH9YqWKls0QDY0eirRlmweHdnRwa5tz7J/EMmij
-dQxz5ThByZIw1Qxb4YBzpBcOvXWwjiAzYZFTD3a5TjrniEcUT/7BTteSZiu86WCzq4aw3OGWfArH
-7LSODGMf0E/xdOnL0w8WPUe69WwSsetVDi4KM2xdFshpB3OffjD6FdLzh0yP/S/Df33DoqzRJ9Ab
-4uoOVsFMugbFwUCItUlRzkxCNedlQHJHfGUMZnibuLUqIyJ1seauGEJERKU3j0ze+1s1alFZ9aZ1
-T/u6wfKTCJAH3TCldBtSxN3YmJ/LoTbrjRqp6s+cM5XLebDyYwVXIdlIKSbFFTPY5Z0/xwErQWrl
-JBfRml5W4WSxnoaDzqC2PanRhogXfAdN2myVMdyW3EjWUnGVsqIDRUN3iWnT3RZBqDw79Vwri6Bt
-62tTDysvTSL/dmq58T8oPEDHNY+IHHMh3nV7sow6sbDCAI1fZCbu1WByd6OS8ylmhkwvvCwLsE6F
-dscUmZ5M1bAeqgwdUxgFQzCRYg/q0k2bqmL6F8gcbl1t3oVz0V2HqqgUT0zOgIQ/hGq8+MeUGXJr
-f7vM+Pen6O3TiPzRz0UGXiB2WIDMGr1bZjZMzDYvIiCuNoHMYJP2ousu2OWXNrD1k5z8MDmnwBBw
-KTR+LTIg4tNLxlKEfugIXdqE/kQbGA7Ct0WGzRHE5Hdg3pd0EeMbLxCfjzhEx1uS7mEf4Vj/EBm2
-RYZslJPpKN3fneme64XSL8cpge5iZbaXaTmjaR2eyLZru6ViEYCJJwZdCC7YBV1OFtAJXtw8E3HF
-vUKAo5Vv47iP1iTvTOtqiNaZ0babqgxPayO/Iwk2WAQAMle+gudCm+1Hk6u2bbuIEVXCK8KK/KjR
-T/STqUWY99vsUiixflFgG8ynShzhuIlPiLNQ10GMSYO7fKuyNQxDuifqAm6zQutYvgp1ZvIssXdT
-tINkEO4py7dIUNoxmsCKg8FTA+n31kzjdYM+Qv0CRNNRzP1s+upSj/Ad0v+Z145ar1GP7uehBkJX
-bXD1lwvMOAG+k/nJj+lCuZnY4QpVFzlakZcRCnvbpWp2n4STc6/pAdO3tsvsLHUaTZdobZgVGYPp
-EJ2EIpp5mmRtGTMUd1WtwRb16joyxQVGwIIdMGbIpL4FFzBsO7e5ALYX0cMAJcjsw7bD7+4JFwBJ
-gK44Kd5cCq5JIp7o8t6MzDI8RwrNWSNn4ERppwtjBoOUclTkCEXnVsvFk6qP8QXzPrqH0uuuYFIW
-i4p+Pr4Wek56UdekdomMkmOanlSMJR8dURfrTquGe7MMWPFaFcy12YIFqknLrdgc97ml3VeaYN4P
-ZWyidtNY9vXEOsEc8BRLvZk8e7KuuqY6HTk2LewgfXInET3J/xMFZDxXdt5jQ6+ro1Fp4mMX6CDT
-zWTfPE3VFH2c1Tg/JohZX0j+w8YKS3dV2HXBLM+UL+Ykwk4bohevEqm/EMkS3nVSk0HJJgFK6jSW
-VGyE1G5qqeK4Us/RpLID3Hq4YswJuSc9SD9EmSEDWQhCiTu3Xi41IleqRSIqwF1LBQlj25wsA12N
-9yOc/VoqTZjulItG2nF8acypCtipvALsOuoI/lyJyvG8JwPCU6Wtxzo4fFK8Pqo0/XTS/lN0+qcg
-YcRB4yJ/GmrMsXZL4snCTfTEc5Vc36acery66Mp1NMyK10gDbyWtvN3B1csexKYhrb6aVQa7oodS
-WeED1qUheJLWYMx47knO/MZeIQ3lfpYWYhAlmr7spbm49jnIhxYDk6UDGCJNOFYX4xX5dvWaUDv9
-upImZV/alVNpXNalhTkoObrHlMHSAQD/KvG3to7lmfY75meN+6XuzezOiRpYIS0NbELFzqFcxTt6
-FfW67ptyKW3Qq8Fq0qMMQSBA7+bS4r0uig7LLGOaVz5j8Hi1UnNZYPS6U40I27bhs7MFtlVvTaEX
-J2BSjFMYmuM67wf8IgxZeUaJHKPOrXZZ88i7LhyStaao8ZEWVATN2uZwkgWq5Ykk4gZQlWavcTD7
-kEXyTg676d5wUv2mrtvibuhBy1Zj3uNSbq151estuk6iT+vB0UiryPiHqY1PjjWOG/Cq7koTjXak
-NIZ+N1tKcxynU71jeNt5rJFBlo6qdRSeodfm9lp000prurspzx7BxUwLwu5u1N7dG3FwGrAWmv5j
-OF2MSbIo0Xa4/u0HXfQPonbsJeQCMNf6Iu7CbKn3teWZen4J58jaMzt3qo3589wV/cIeumg1tzkp
-SoUq1kWp1I9GX/yNnMJffGqrh/bBOyTXXnTP9XT53HQgHl62TPnd8yLK2w/F/+wv/fiBvmTmfpjK
-5//6j4cnsutXUdPW0WNLefCbON1vI8sOv9jht/7R46QPbdR2TzyBiTJBYxD1U8IP+UJZTIs8+PJt
-4B7MtmmW5B8evtBFKW9eXae3rsSPX+TnS/rjv/PVC3gsuryVb0UQFflXF8L+tvH6xiX45hF+vQTg
-oXhp1DIsb4cvHvDVJaAY4wvE9Mu3/68uwZufBaZi6Be/95Ng/aQzX6cxOiBfL1884KvLACrLNPA8
-YPr9/PW3uwwaTSBykwDGfF2Bv/F5+OZy/vp5sH8yTBCiTEN/vg7fXAiHdGpbpz7/3Hr4378VvvnF
-f7MmGPg/vzqC/NkLAF1et5hG0A5AVHkRvvokGD+ZiItMYr18+297Id57S0jdFpKsQy/n8xcHnVe3
-hA1XTgWX9cva+fmT9zf6REjnBwlk7/w8cBlY/Q4x0q9fvkwHkhN5hjyPHr7+j/aGN28IcrNNV3bl
-3nU7QKQCAmjKJPpv3n6Hsy/9d3p/f8/X/2VFlOCt910BjWxSGREllYBXN4CDJcliR5D9i8PX55Xn
-b3UDHBbrd75+9j7bcfAPvLzOr4skQGfoNHR3cGYdvj5rQH+vy2Aa9nvXAYcKgenaAz/z1aeA/cDC
-+IS49He7/798/vX3fv7Rz6iB6ed/eX9Vap9XF4DkXksVDAa/fP9v9/6/XIj3VgbsBCq7HRrjt1eA
-+ROaakiMn7/+xE74B26TX45eyzBKnw6Hrui5+d7Z7K2/8HLS+O33X5+pOEp89RflGezzc38usuS/
-/+ur3eZwEnr1zZeT0eF5vvz4lxf426f+6rleXtXLH26j5/qh5tB9+Mb05dc8fcg4tJ1N3xmmp+H8
-+R7/9df5zfnxl13gh48Oz+K3A6s8vCx7X45e3z2e/qGH3w9we7/3+DIWmyXkvb/+/uGpy7//BJ+L
-gfc+wZJZnj8QBH44qv/PLxM52fl33+UvFd17X8W/84fs0/feiF9Ok+99ho8P2c/ffatfrUbvfY4f
-pV6+8w34I+Fe73yKqyIp2u+8yS8XiPPLey/QIa+++e3t9vIULNTvfYpzjs7PD2/PuP8Vi8bvZ3+8
-8604y38woGlQOb33Kp1GwXP95vsgW2jvfoY/RER/53U6fgiKtz9OUnp478vYF8HbRiyZ8v3uJ/h9
-sPE7L9KemaDoe3vQl7vO+Atu7P3D97aHlyf4C27rP4IkfOd1+l0o0Dsff1Nkn57fvOfEX3BXr5+f
-KNPS/7d8KKOW//3wXNdRW9TTy8f06Om//uPLmyKRGe/97P4Bmsg7r5mXRO3b95+ke7/7NfxgpT2M
-wr/3FfyBWat3PsXqOW2/U2K+vNF/we29eM67H3x0/4L7+w+Z4995nRYPv2+rfedT/DshA+ToU5G9
-eZ+bf8F9/u+nh+xHgFbp0HnvffH75qAfXqrvHTN/6dT99vD50oH73o99fbKWf+MxfX6o//XfAAAA
-//8=</cx:binary>
+                <cx:binary>5Hvbct24kuWvVNTzUAUQ9xPndESD3Ft3yZbvfmHIsgyCBAleAN6+vlOW7ZJUPjVdnuqI8YweZG+B
+2ASRyJUrVyb/ebP848bdXg+/LI1rx3/cLP/6tQyh+8dvv4035W1zPR409mbwo/8UDm5885v/9Mne
+3P72cbiebWt+SxGmv92U10O4XX79j3/Ct5lbf+ZvroP17fN4O6xXt2N0YfyTse8O/XL9sbFtbscw
+2JuA//Xrf36I1fWvv9y2wYb15drd/uvXR5f8+stv//HP3/7tAr57k/u1fXfoj/dvr5sPw/92BY8X
+8IfH/sXBzoT4EVbPD1IsCSZcqvsf/usvzrfm27BiBEuKCbr/oV8f/uK6gen/eb+eX16E63D7deh7
++/L58a4/fhxuxxGe6vO/f5j+aCv/MHrjYxvuTGnAqv/69cKa28HCVtjRZ/dDmb97pIvD71nhD2aB
+XfkfNNTp9cfY/o12wuiAyJSRFKePDCQOJCMkTRn6Yj/11Qr3Brpfx4/a5/HsJ+Z5PPhTWUfftvFP
+j+udG//3nUgcEIaYoPT7TiQPhBCpFFQ+ts3nVfyoaR5NfmKZR2M/l2H80Pqvu/Q9HPlrhsHpAZaC
+EYUfOQ0mBwRJhAhNv3jN11veO42+W8UPG+bh5KeGeTj2Uxkmv3Xhb4QzdsBSQRBH4osBwDUehR0s
+IOhwuOS7Yefzan7UQI8mPzHQo7GfykCn13+r4+ADqagkKoV48sAw8oARDmwAf0U68thz7lbxo3Z5
+OPeJWR4O/WRWCaP9W3lAesA4gFcqvnjGY2QTBzxF4oFfiaf2+byeHzfRo+l/sNKj0Z/KUGfXxo9f
+9+r/PPBwwDeuEMH0d1r2wI3IAROCIkS/Dj9hBp9X86NGejT5iYkejf1UBro0sf077aOElEyorzj2
+OP6QA0okYB9Jv3gZkO77nO+eINwt5kfN83DuE+s8HPq5jLP+jaRNQkrKMGQ0T23COE2lkoB4j2yx
+/nDEufx96lNL/D7yUxniyk63w9+IY/TgjoahFMjy/Q/k/w9wjB9IjiiS4uv4Ez+5X86Pesrj2U8s
+9HjwpzLS++vm0/XfKeJAmoOASSOUPjUPxQpTgr8GoSds4MtCftQ+T6Y/MdCT0f+rLfTvFvdQ53t0
+zWeF6b8vEKgDDu5DGP/K2tgjNxIHdwYSkKr+7mUPIe6b1PXv1/N9fe3bxEeL/x/Xzv69rvZNisyv
+w/Xus4r6PX32u6NfFZkng4/E2EfP+TVOHH/8169YwJZ/E3XuvuJREPm2Ufc7/G3G7fUYYDI94EJg
+pghSRApg2L/+Mt/ejaQwIOGvCoP6oxSErV9/af0QSphEDoBhcNAeFIJEVqYQzkYf74boAdD3u1Cm
+hLozOsz6+nDPvFuNb7/t05fPv7SxeeZtG0aQbFO4SXd/3d1CIUkGAZAyyuF+GAkhYXndzfUVSONw
+Of5fwo0prWKh3VTZbjlc0VI5TVKP1PHm0CovOmFaq5fJ1uV5DCKEnAQ3jMeVWWSdDR1vebakfHgp
+YmvHvKtnM18qz0qjE2b71GoTeyRPuoDbSmmapqnzMKNGJMdjt5W6b1Bi93UqhupIrLRiWYcqz89p
+O84og0dOvB4sikw3IVmx9hx2KpuWSlR6SbBvNSeYLnp0vg46jjU5p6xM3m+J5Uz3cUZOMybWczoq
+876uLKky0qTrlLW86eD7GlrMms61dbqWRnRHNAllo2k9N1tWFWllMzJXashXvoRel5WYgw627Mme
+TNzzHUe281nS13w9oi11b5Wo0wtaUo93wThzOWxBXZdYsrfeBPmxK1I1ZOPKotXlME61XmPE/G2R
+wi3fGNwHpis6L835mjrVnMxT7Sbd+rQQeWSIymPq2tW/IFvFQ75125zuarGpMROdkNsOTWVR6opF
++dr7keAXzJdxO2fVEM8UL+QCNkxc12o7xu3E9UU/Xo5jgdxxWkUZdMfT+jTlZAnaj/PytjWFjPte
+yXIe9bS0xWtfVhPdzyopm6OxKAeiDe8rsuvt2H8Y1tZjvfVS3JS8LcoMpSt9PTcsvEM2JGyHXR0O
+o+y7Piu7Vt6MhfdDXs12Hg+HrWZzhnDjqW4la5CW0gynFWPJrDGPK9sPFRdrVlM7Oo1WPgkNLkBE
+tmBY1iEb+TLpoY/jUfBJ8rGcEjvrZbb2FBdjeZUEO37ClL4K1nS1LkeM0swF2XXaVdK+iLNvLWxQ
+3e+dwwvJkm0YEs23lLxJ/VJjXVPUrFqsjF1FOlWpnqqITGZLt3V6clwlukjnMdVhaZa3SwtJebb0
+sb1JQ2KHTJKAG71xtj3vHWewNoxts0+Jl6127bTVGVFouC3Tprgp5qa9FITiDxZtlduPxi+zjqJv
+p5xPBavht53fS/D8XqOI0uGwQEXstF0V8Tou7XZNE9ZdToRFo/t+WDZdT16GHA0FU1qWvd90mdrK
+n6RhIKO2KPU2M2wks0bFvCKd2g1vb11tiptmxlQcdo1P21Mmo+ng6Dbd+KI1KS1zUShr9RTS+hmu
+WHpVrF19hpMtFHk51Ohj30/ptjeWL40ep0q+rZjhzwMP6q0XwrV66rCwx96R4I/L2TWXvfOo1o1L
+CwouJ6ouU0Ga23RckdFs6CWCwXlLs7GXa6MZ8bPJimVxr+bSlAqgrNziq8o78y5Wd/ZRrrJUrwFL
+lPN1BuhbrEuxdnzxTpdE9gBS2PTnSlbNK5TC3XaFqNbX2zqT8nJqxoHDOeSxvhoWOhQ5QQmv80Ju
+5oimZT8f8pSzsDMDX9yOVfOwZrH31OQkcQ04VM8HpFtLndWqaMyo6yhUqhMVSZfTFjdN3k1VifaA
+0WXUxtd3T6ds4vOE+qmH553s+ZikhGqPuao13mRX5HIgBd+vIpneJUj4dw3t06jnOekmnfSpmfOw
+WLJpF+VawW8TFs3FyC/d2M4fRhmG024xm9NGsTboeu2WLh85JVdwYBe8W4vGKW0oLeedXXvucstU
+ivIOHK7VhGxhzgoaSZutXFbzToiuKy+LEpXHQx3rTW+pMFe2b6agl2KL+zbtAZN7CiaQq0sa3Zh+
+bM6Ljbf+NDSuanS/VibuKMSgqOuNVc1eFk1QO1407XsrezgU0ZqlzUKvxNVYJMWmWcdLnrsA8Q6O
+9WLfWYtszIaxRTJX4GovKeVh1FtB/EnRpHjc1UayKjO0K4IGNEVIQ8yIg177lEkdkiYYcFKX9Lkz
+3o7aV2nz2o5l0eYiIIZ1D7/WDC2oe51ar5JsiDUcvsmitsxc27B3ZShrkzlf2Hzg1VbuetyVncag
+9XxclEW9hlhfvZOs4Kg9pvPI5vl1wRtwaM3LAX+cQ9NexG2ztU7xJo7ZWDfTYWHT+lO1pO6CLZy9
+ShO7vXMxHW7KBLAwW73nH/EYk0KvHqHXi6/Uqsk4+E/UsPJw2YQ/dXjb3lucxnNV4N7rsvBE6a6v
+Bp/3vbN1ZnuPr9aw4TecVabUjfC10jPMflv0ZPaaqnS7qm2yfaqTMJ1gATCQDZaGw9lVW8zKSahL
+mjZ21RVCmOlpSPtSo770kw7lhI9ZFHBm4lxzgEZwGquLOE8EHGXiL2uToDqrh0JM2hU09HtamS7m
+dBnmRk+sRuel68ubcUlqqZe+IzRjzq3yuSEbdtloOSEXI7QNmCwxcl5rvVRtozDE+MmS61qhUMLE
+LeB4OqemWZ5tW8OWTqd8jvLMKDzVZ9wkUwWRZdmK9iV3NtT5LCsKZ6AWS3EU62RAs1amQfh4TZhD
+z4e1lzgTdHBNjgRXbV5z0p1L30t32oaSD1psFb4R0szzR7yupj/zrnBJDgjcADI5FW2+znVB7mau
+W+bWknwwLqnmjKC1GQuAIlqEvI+2KPJtCag4HuMayzd8CwndjcnYVi/DOrU+d0WFqqPCzoZbzQHl
+cdawFTZGhXQFs2/jVLyPlI5kh+ZW0SMfvRReT8pNVAJwOdW3+4GxCd32NcCYTiSoYIcrr5J5yyfF
+aJg1kw2VZ8qGYv0U1ILqixEAYtgH0sjh3NbGD+cFqit1XKoab2zXALdY5nxDLXL7cu6iODV1RUxG
+N+PNWTpRZz74IRlUXoYFgZkq1oTM0gIWmpaxmI+WIlKy6GYxhH6MS4juxNTTWj8TTKEtG4BOJ4ft
+2Ad0UnTr1GdohbN75Pqk5/sebbXL4Jh6kpGNW/x6RFtqD00vgArDQWbLKzlVrdQtY7PtdZX2vXin
+ZozfLkWypIeNjMUnFCXhh21d8RVQol5T3RQIVTrd4DDnYWpi2Mt+EuGodUO9HsOe1zFb0WTHjA9V
+Hy4rAB53WlZpvE2ARp/LpRDvRbsiscdyre0eD+OYHhI5qXU3t7ZNs03gYss844bl2yashE2b/EUn
+x4Ts1ohRl3nOjDlL4MFcJhKCVy2Bai966ET/ATDBxj2bRglHHSNLM0PmSV4GEcHNsXTE7yjQjh7Y
+WjQE4nvaxx3nEn3qCaqBwSvbAv+ut57seEz7VPu2rIucY7E44CBTcIdAEOige7aAvxWKAep1EDdf
+UWUV/JfQ/qWnwKb3cRWBZcM80zFrCrzwXSdsddUNa/mpTXlVZ27isdFqoetp6Iqm1yNQ6pD7VlAD
+hdkxej32fFZ6UA2XJ7g0sMWDQOWbBHeiyyI3NcoCGaoma1msgar0NSqfkTiYeNwybxegt2v0p3R2
+faXXslh9ts1J1R6p2Xciq9tqo3qKsW7P+2XgpfZO9ulprfzqYPOGpNxNUUw2qzyekzxBYAUtSl6z
+HfWbLLMavszlKPZlkQU61KOuurWNmZnHVeRzVc6rRqOab6Zkc8Cix9Lfms46teuLtq8+dK6j65D3
+JoHkYh1tt+Ubx6Pfst6LScaMmMCHWvspxKXXGxMdnvaQdijmcsFMygrdLiQpdutKQprVdSvEpQTM
+L062NlTDhRiapXoj2LzEImsHUuEuG4D805dAPSsCBGHomrBln5PmL/n8o9z0xnfrYE35panq28f/
+OP/aqfW5veb3v9/1U/z+6bK7bV+E4fY2nF93T6+8u9+3S3/v07nL2r817TxRAR43Uf2VwUf6wSMN
+65F+wDGwb0og9f4TFeF6BF1vvn4sqH0WE36ffi8pgCKUplD8loIQlqLPYve9pMAPFKEcGhOwgARG
+CAaa3hdJQR2QVKUUNAjoeFOIQvH1i6IgDgTnwHYRkZSlmEr6VxQFzEAceagopAqUCyoQdBZxkDeY
+gjU8VBRsCiked3QXLSDbWkjyIeKqfTUzOzzr4qjOvLkD4lTShugpqa0BmjIui67RatNdx6p2OUx6
+qo7rmo0lpNi2NC1wcl5sZ2QOa3rcmwGYvHGNQCdcOfM2Drw9Ft3Y2CM5Nnw1ejZtdzypINQp5M2i
+hwxvK4B3CzFjIKtF9WGMfRIOJ+vKl9Fs8v02KbnmNe2Gkwl11fKsEVUTT4NPscmq1Y5AR1WbyGyr
+hKguElB7xmPiUnsVfF3g3cJExDvpmvhOds2Csk1RsxsGao7KWBWXrWqma5lyCzQ5RcVucQPaN11q
+btlEhhZCu3S7KUz1O9Ut5N0AbCePpQwX8PXguhYW2uoy1CTmqAz2skGoO0ssnneBTPgCszhezClz
+OyJ9ejiZjmvat+ZUbvBNeqysOfcqepoXdlhG3SQdXBHxIDMzpmbHSjdf0NC1YrduuOpPBRDWXtcL
+Li8c2YYPYh1Jk5ftvM4Z4CJ/5gvR8ZxGmp4tVSp2fMGQgaWqXLpdPa5NcVjWHjA/aVf53iA/vCzR
+1DeHtpGT20kg+PhwYIkpz8ZexU+xLcwIoogy9b6w42zyxVNu9oimLh51a+yrPbMM8ovKC9q9AXVs
+9HkJFW2Vi3HoD01c4nxEN5JoPIZodrGYRNfo0Ccres6HmNpTMSQz5B9t0W9AmvDEPkDOY+yrxJZs
+hgS6XWK1p0WloiaCxotixgaoT2iq/oQ2JTAwNhWIZ1hydYmarfnomF+TrN9SyEcHUYmQlQ2yH+gm
+0M5FSJP3Tb+2IBqIOODDmFALh7mWPfbZGCG+XZfAgrp8qxXII0taDeu+aFU97VVq1HM40ZW8mNKY
+zM9EUFacFqGf8IsECPW477Cq3v51GP7ZAPauggQZ95/B63ebTe/Q9dvce2yFdjzQVpiSKWjqdwUQ
+qBh+xVbIERRVgnGAXxAUAfe+YCuUsgBT4ZvA6pgJAOdv4MoOBDTJAiYqnIIuR/4atoonai0g+13j
+kxRC3d2FfVZzH6i1lVuaMg4sa9wRGy2wIICYKU9Y6G9568xhsSL1qnehPknjnDzbyq7MFKmet225
+avD3l3TBjdXA2MuMlkD6QE4meu5AX9TVNrwybbtmfdkPJ65aPQi7Uo2nIURQKEkEPRJI1lQebrFB
+F2WC5As/eb9PICnBuitFc5kE9gky4fKDqFD9roW8KnNNnZ5u3SoAK5PtqMC42o2qH3fWgcNV85bs
+IFB1+w4S310ppvSoA/V0R5CfOj1bWN7SSvTBlCAez5Z9MNO43VJolttD6sxf4sWnO2UQyE5uQ8tZ
+qDg6BQwxx4gtZC/8NJ5NRQx5YKrKokJ91tf1sgM50Lyg6+p3hC1tqYeajyAwebXzbYePyJioV6ih
+9O1QdT5P2RRBtxsCIIQSpZa+NEZb1o6XBqt4aUEcvKy71r9ohaM3QBUvg5QUHg+5o7obFAjoI8q6
+ZICkd6pHo8UAQmbfMHoWLWV7U3XwcQa26eYhPS6boXlreFrsgMMVuQoL2zdqGc5m1FM9y9lnvKjb
+WrcmTseSTeIIwik7GXhDXleS09OUrOOrYd7oddlGUGr7mhzyYi5vFkjSmMYVL09SECXyfivX09Lz
+btai9ts5kUVdaJYw0BClT0DAVku/Q80s2nxkhT30dQdJiCjoSVu6cj2fyymc1j3jbwdh+g98GYbd
+0O1NshU4m7st7PAUyl2suvq4s7Y5nlpsnqMpmhdhHZI6l9C4bDQpt3Ap+63bl1spj+LcVzmznu2W
+NTGvrAUxovZDhBO4sTcqme1RWGefT1A9O8LCx0vci/SwD0s4Fc4NH9MlSU42ZuJH161jq0Xolz1v
+IzsaoKn9asVlcuiLOr1C3oWjQdT9ybAoILcJ5AoZpHTK6v/3oRV/IZ/oz8D1sv34pI/iIW+FqffY
+yqHSDEVlIK4YXhmg8HLAV2yldw3qAiqYHJqeUqh6QefgF2wFdsqgNq1AwIYKKCTqQCe/EFcGRTLF
+4OsAeBFcQMhfIa53ha4HhTDAe8VlCqyT35Xq4NQ8pq3JSOulrusshuBOIOlZjojh4rbEoAjnGyyC
+6QLqMPX9obiv737Jeh5W4KAj4umNJUohrmAJZT6sgDg/vnHLJB4wqTMsJkP2sunTT6ik3F64qpL4
+vLTbloCWYIbnK+9BjGtNP4BXurp6vhkKMDQY/mJIEH2zpshDOQ0w/HU6ShAD6hlV16uqQ3rIPS7n
+HOS29mOd9CDX2GoChakYsT9ZEjmGPHJIYvNhnUHYCUD743GwU3cqw2tWTwiqC1W/lkErNSRnoVHt
+qE3psNlx5ts3SVLiT3Le1iKfC/eWCiMOCQG9WpuVBpCoJ7QVIPA2TZmXGJiu7oBlBi3mjfeZnNEI
+sjG9Y4sSpIpL1fcgQXPfdaBgwwa8LkiyXIHYsy456Plu0G1VJRtkp5tfs1a2M5QOpkGmsDsxX9GK
+38EMEAs3yNa3bZVnvtv6o66c8XnXiPq0nyz1WT1h+wYS9PUZjZ14mzi5fKjNVs9QNqhEuueTGewh
+iyk+FCCUrJnre7lLyqWvddE20zGET5Axlezos60YhIcoE9pFp9XougzFwr0YBYHgo8hL0UXY77Ff
+EqbnZJENFK3qRB4loy3J0SzQ4i8gv+hBk1hxgvaxidlim7rdNYrYTYMGEF/MpArtadV602WEyOql
+FdyFXYPIBjpoUVVQchoWop3YhrOiWdc7GsutAu2vrKvMItaajJSduFPOQjEdEmAQH6xv8HEi8FRk
+vN0Q1WYaBNbopfSiVxnfKIivZgRlFvT4oshkjxqb2TCF+qgjhSz2rgrVnAvc0HcS3nQAhZyzge+L
+NGnU6YDivJ6tfSKnLF3JMVZcQYm1LjxUu6ICoWpTiQQ74+42YvYp2foRaYVrnGZBYkheelbScyjU
+pVCWGKHGlM2suOGVotezXOWrBGGTt2gqVu2hdnfl6FQej8vo6su4gLuDzGsn+WJZVlfBOkQy6m5b
+ojv+/wbfKaDhv9cmHr0T8qDL4T423M39KkwAp+GA4AKaFoAs32H1PXkW0PsNQoWCvnBoObjrNvgG
+8PIAA8JxBWQNZigoqHwDeH5AKfBpiBfQOMGYZOqvAHx6J7g8hnhJEZeMKgo5I0/vFv5QmYAqbT3Q
+Bu1wEf0Oyo/V+WRtF7JmGuwp1Hig2ga55nuojbdQrQtR+l1iSEL2SowBausJgRLD5sY+w0E13VlZ
+QhEwmHZ8s0A8aXPXdmZ8KUamrlHbNHMmVFKB2gA9FcXxHJ0sdUtA69vPTeKrowDgHXXVWjSddFCO
+ME4nM3CjvJnYFnU71C6+9JXz5BNZ5ljunI/jrpRrPAoFdAydrqGvdyJRxaH8LH1Mn1WQOz2k/CyN
+rJSuHcB2MafH7LN8Qu+1FPdZWDEDaCxOcrccjslUpjuCK4N3xtP5ruGBr9M5vHEJ0omioAFDraBY
+QGXtC4myqQbvei8/J6Tz5+Q0fE5UW2RKf9hPEyuPG+fckTEoaQ+LuZ+XvSlrBspwa6FojZNmJMcQ
+IOoXowIpYueAFJOsqns7gMAPSJLXa0lfW2ZY1o9d6t7OLZpd3quyz1YLVUOQWjp8ZQp4st2gOrTm
+0JYhUlAHNrFznewQoG06vYGiQH/c8LsOhaIDHA/sdpWkmXZF1WChK8lqspMJo7OucF+kuktK+yJY
+lXwi01D2OweyBUSEgsdZA7MH61PQE2xSt9NOBbKRy2kc2VF6V3tSrO6PMej/z1JabHsu637IGbTZ
+rRnBU7KvvVFnzUKTNYe2icru19as75LQmCWPAFhXo2uW13FM0NUAFbgPIS3sR2jtUQCIpaevofoo
+CPBiNO1t5YrLWRTVCSiEEJqGddjjCvMPkFy5s6Ktt5CZFENELrulr7JU1eUhRJXnJiH+yMTSZHVp
+XrGhro8UDgbaJxq3G6DAd1X2uPiEVU/OgZq8mftwU6MeUk48lK/buSkzH3i3mwcAdOjL8MdoHOje
+o4CPK19eg2SU6gKtydE2pBeodc0zRasVimXrjaq4e3F3W1WLm87g87qDA18phfZDF+1Z0pQfi4Hd
+9I17BYXr+hgymi2XdjscOlxOWXBePWdzhausCps5dVu69ofdsi3vt3EZDslYNM0ObX36LEyyOIZq
+zPwGiMGU8aaCIFqIcMmwqc5qw91RO8pz6Dpgg57uZLkUEj+1ymnXQsX0kKYrtAUI1w9vKmgIMFCG
+Hae7ckrMLDcoryRd8m5IYBtd+arpqiQnPQaPVltdP5/HMdELawFoNgOCGehZmVHllicNMWeuoTBN
+LuNlLIc3TVFaqMekkHpDORJSHC6Tt8rMoIKn7JzMat2Pcl6yduv9a+hPcntoNdobtxbdD4jwP5v6
+A0o4h/PxpwHs4btzvwewbzPvw9d9qx7kH9CTDM0TkFB8DV8YwzsZCiIaNMoSSlPye/iCVj0B+Qq0
+492p6Jg8aNWD925RmkKtmwMYwyj/K9ELuhOeRi/ImgThd6/yYtA0KehdD6MXJtYQNfDjAP1LoBaz
+Gr8DyRTq39DZMFx4X5Uia3q7JSczSsI+OkwyL2o5QMmdtkC9yujuCJ4FqqhKtbljKjex5ImYIMQZ
+EEAvFnCmLOnIs0jn5jVoIDO0gRTQ5bZ1o8ygJNe9rL0bz/E6mgK06IQ874BTJkCxoZh7uTg+vJjm
+0boTNyTLdr6BvA3+AJWsU1F0CQaNO+HFzQoEfs/jlhzZvhP+TCYlupqhnU5qyctInyX9OrRHZTej
+3JGKiWMboTNsTnzcjXyWeOf7sks1Lzh/EwNJusxgU18hWbdwqdrAmRJ6uRRcthn/L/LObTlSHO3a
+t/LfgCZAIASnQO6cdnpX3lSdEHZtEJLYCwG6+m+RM9PT3fPPF9Gn30SfdHS1XXY6kd53rWctjxBS
+dyyszMHQob+wNvZzSHbp0AItoWF/kCKWZy/pIbETcHRjVKRKOvqknOWZdeG9p7t2R32/3G8MxKma
+VZAGxuWj5FMGXV1loW9ABBZJPjUjhl8DkIvE3VFga73FEqRv+468hJ4+1Kzq4CP7d+M0+XtdklPv
+QeWBWpZTCi+wjVdxjNlYQ0UGhFHBATo1wC12cNfh0BqdBbY5JfHyEU/kZhSzTPtuzQczv0rMX2da
+xdBq+nbXq+be0v7s25Fhp7IH0eqTJfGQj6Or83oM82DFRF+pannvCF/vKzHYU81j8cZgNhd5EWj2
+7Yrv+JVWP2BYVp+9b8je2JVl8+TseRqG8kkSJh5jzeDjOITPyLmEwb3ewqYEAipYSbCs8aq5Jbxe
+0q4hdZ39HugZIHb7kLyj4aRpY/i/Az1gg5qDJ5r6G/EgDyYWW+WAiQIzimEHZuZRppVYwyORlXn3
+KqVeqFT6LEk3VtiBO3OL70o/2EURGKq44ToQLKtqsxXLyn6dEgpFzyvBmS3K4IFSkazvhroqvbT3
+Pfi3cwATHfNDG6W9AxuR9nHU5GvhD++RpkEWD2I5RrohP6dpmJ7Y1E5ZUVbdbVcE2MZiOtnj4LVj
+hmlmyrUweCWw8gbZNI54D8JiOjez3zwZLadbD+ZRDhZJ5l7bqmNBS/1cEKmrnJCKXJToxi9B0+qc
+9dWSxayMj21ZD8E/4CLmDc9ucdV5Wdz4gDcRO7tIzvDiV5LSHlrCOFq+81aFyWaJxN5jwfgzmFaQ
+U3pJ3mWtwx8yDKfhzgxUcbH3x3C04BoXYAtfvDmyIwAuskbnKIn7val6sFTBLmwqeYiXRd2sFpfb
+0KnkvcAilgVa84xSAFZJDVwMWkiQCvAjH7D/90H7papNeO79Ve+1osN9WbfrHvPK59C752o2N4Nc
+D7Q0O1lNeU3HizcMGJ2hDS91dSGKN8d6GNnOlXzIHKDcSxfy6a6oNO5abZ7xk3dP/hCprKd6gFEP
+wXnCfvuzEWNy04WlPLJi/RJuZIEvCjheUkw/oqaZH5SY+hvsBrs5bi7NPIVfrJzFL6+068950TyH
+clwCzfPKs1tF+Ti2YAxkxSmmL7J+UHhEOl1B1x772cidlk0H6LICttE3wQnH53B2DWalGIfaHlAR
+poCpHekXB5QrIzzuDnHhi/06hNGtX8XspVxcdwfIOMHKPLM3rNf9noVf5uSmnsoH4QORqbqe75JJ
+PxBNzT0XrscnEeIWZhKoqdmbc8WC+jHSll0wLpPHlk7dscWPJiu1LY5Rq8p73Gngt7B+2Exh00v5
+xMu3IYmHo3XE5mBSwsdwbeb9letqXehWEK++e5bWV7seuvAhsIkHQR1G50vVdX42LGuy7/E2O4Sz
+LPeTK9UpqEtyQ4dluQkaAwFMlXnZtAA8udiJOapx6IVh5gtFbsLYRPd+RNoDaTB7Q8tNhb/8mCS0
+pVlUx1HJg52De6nLL5il70hh7dlNtL6NK+EOld/2mVlgU5QLLOXOS7qsULHc8dBMe068Je2BK+7A
+quFBJw6MHwd9fqQrTINY2DXvmYKhWMpXLBxJxuXIX/ja3UDlhKnQrLkhxdDCdd7eioyWQ964qNtj
+CqwV7lwy+lljJT/XwxAVACS9pbhUs1/zvGVlMaTjvFqS4y3mfzK+1CdshSo5VaJg1avfh+4wFYDG
+MtuXdsemKcCOxVQm52W8DQWNT55d3a1ly9x+WTip6p1IBh1BNCoNBWa/JknqAf4wzyWg9B+1X5jH
+CNzr02RKw/PGeH2dzVgoZKqUkQpMamfno8OyO+aRnIKPWMbxXd00Og0N4z+BHpcCTjiehQuSAbhb
+EhWJbKVj77IEFPFp6hL47azvGh/DCSp7cGaQAhr7CAcjDEQJQKoWjqWdrxg4IFkHXy1ct2Gv4R2r
+PW3xPjj6hSw/Wr7YT3xXiY+lcEpaAIKVAYkbx+eFetCSICBUaVAtgAb9anzwB/eDKPXci8hCJ1tD
+8enZlhlwOyCP4EqT+EljUz2C72lxoVbwX9eFDzwtQq9R+yQyoKRqCX996Uqdg9sJ87mL+JdiGWt2
+bg1vPwrsw8hFwBubUt3py8JgVTmmy7ShQVOk3izUlLoGMkChse3TOVyPXmnIG0ZGdSTJLF7nkI9v
+1FXNg20gQQjplh11xXJv5sC8eqtnAAd5YW74HBn45kCi2DoGP6QZ1WltGa5h/D8vnlLTzdI1eHOy
+0H0m5XIkQMH3XWuM+y9yMTbL9j+rXLvPtlmr//eHOqLf+RjbB/99T4j/FjJYubCcE0R7wN7/QeaK
+fchYyP4mMWza31Su6G8cjsf1P0ZbLRLFZ/vNxojicFtFYDhDHEsY/yt7AqJAf94ToL954IY3YROG
+Cseu8vs9IeJmBbg55F1Ffs1TMGdDo6tXQUGUj2EpXkUFeLSJA3HLafSdtNVLNER3JcU9usx3AfiP
+pMGx2zL9tgY9EhINSLK8M7p5tv7cHElrlvu64YdBWChWwiT7QsTzjiLHk4GK+Qa6ZcpF5L9hKoKY
+VXZLPrj4bm5YvcOjLm4TUsBJbhDtkBh607Au30KMhbntovDoAm3zGmwhJhYh9sxvEQvAYIIt32Bz
+0at/FQdWr/f26yLbjBUCvLVS7tLWyXRBDhiDaJUsOW36h3r0JpZJeDh7viKf4uNyf4lLYDEePMQD
+lGM8qSu+Ehs4e8T4ChmGhz24QD1nblw/Cj+QuVjZks+6q/bWq/xnhEXirCUqOvRT4J0TVtSnOeym
+U8EDd0BAYNxDqWO3iGG478x28jPSLJgwX4GM9ZaEfevrdslHQ0iuhpI9c5XwrIKJcVclzD56gScf
+WzasCIm0zVOHIBQ46NY/tMzLTUjf+yqBgdofR9f8MLwL97RWD3VMkA1YIb7HFOAOqfQAPQFKuq/j
+NML3NAIdVkO3ZC4Ix9xnIT6ZDsgxGECmz1EVZEwO2KoaDUC28Uge15FKSeTdBpXnZ+2U8DuMiZ+x
+aD+FAjHsw6kuPNzYrl8YPpirFNvQkHWu1hAxcBs3DMLGrBZYMkgOyX4UKeso7mPwASkMk5tBdGtW
+NGudDaZC6MkSuY+6+Gek/Fep62fnoNYJrEpkBvsNG7xMYWxh4SHiFhJTnAYR+Y6F/jSZ+TLwyO7A
+UHyzvn3v6JycqxkomBQgfgrTfneWqmyM+unIhq57XUx5z4vey4og+JxD8ZWZ4CsJ6qcaEndaNy1B
+0iecjkGkEA2ivsh6Pr+zddm7VuGua3FLGXgsJwy3iK+M3klWSZGWcxHgVYv38II+XTuOe4B5Mewp
+7Z0rvGvP3WSrHy00wX0w+8XR2dnfWxp2eSA7shfB0GJUnarMw+i4d9EUZ3Vdy0db9cnTzOtx32v8
+adWsy9dIRjSFdO5n49hgULOFmG5oHRVrHlsa3w5hS/aIcEB+dAWWxQxfuNsFmzRJN5ES+aEeKiyE
+S13N9OIGCNtZFwj+5ArGswIszE0fGkRA1h6StF6lOU94GFnu19A7M9Gz8kuYmBDJGbgFYEi64k1O
+c1Kmaxn6p0HU1wGCzikJuuAAsX94gRwQ3Y4F92pE1CKE+JJpXO6GICh3IzJrtyFf3LFZZHUz9ZF8
+JJixcLu3BTnhLE7SWvjuAeywf1lrFu2Tbp3xY6iiXQIhWZ4x5Hh561v72WuKTWFdHlo6yDMPsNZm
+Pp6PY1lVyy52VXWpm9gdMRiZHVvkr6GfERZQnYgxiAIjQ2giUvMzzoj5GbEgd+y9InwN6pCdWWjJ
+cQqnMQcjonam1ctNCwfhXU4mfF0l+f5f4y0F/6u39Pt6nn8pc//EDn5nLQVQ0a6+PG5ej8e/sQOo
+reGQ+GEthRw5T0D2v126yLajYgCEQLI1qvArDvuPSxfaHFT3gG04Fxx/DmTrL8RogSL88dLdqCwf
+llIQ8K0ZJNxMrN9fugNBntWy4NBKyNB5gK+zSb1h5u8YI9tzES1iOAH866AX8IXmZVnADue9/yGg
+fY2pX3neLxO7aDisbjz3XG/Ry172F8kDMx6nIkgurjJRmSWL1W/LaBd2qpy/iMzMw4trZQG8n9XV
+W1mSSj4nYyBdhlUWaYTJIjUQ+S056BqhQxzDEIqMac3RBGOlciy1y84l9WRTSC1gKkNoNodkXHGR
+hsAd7zivOp2tHVEHXeIbSltvXC6+qDqw/dhsdLXMNxQKZJGSxU4PPNwAeICOtU1LxCouo4ybR0+t
+OhesCz/KTka/hBz7n6px2uxhKYWPo8bNmBIfO+cyUoLDxifR44gd1983IWuOPVuFSjX4353WS/gj
+6BecOGXV469F/lO9TGGMWdxr+uXWrlrvWtm5PbTb8DuLdfSWIIHVp4yO/m2rPHyzjFcIA2gPEL9n
+phko8PoNCQNvOVtEUGEneap4BOgEFXRyDGiGDO1bBAHzq0YIKfOl8qH/x90vLYc+bRVtTnOr5b3z
+hvg+Lov6gSIxeXTY19N+aqHUCQtagFgb3pfURtieTf3ogE4de67sPVKG+KlPjo8fABMl+Ie6Ui+q
+idVbVI7LSwJA+eDCkf0IIFNdbFOyfcgqZOCsNeXPYgV0kU9LSV80012RtokOwkOHR+YlWpf4RTZ8
+eUduQt7CasNQBT17SrJ1LmDWNX0tduWs7RnBRrj6sB2nm4T3HuJr8LA+6DCLO9YX8tiVUXdfT4Pf
+IsUnmwDXD1/fTKPiDNZk8IgAV/KpAImH+6Zr6DcrrPqB64x8YuPhv+JIrkfkJrHJuFADd7H+W6di
+/36Gxw8Zo10v87i0X2e2QFWZnc4WG5R3ZpEY9bwNO8tIFcQ7hgDoFuxq5zeOlyxMe+P7j8r1gDei
+xoTfMF1RSHblMB0IbZpXGMPRqz+Zfic6D5KdjNTPadV2F0smH+YoKvM4VvMX7pv4yXZj8BKWZpA5
+wBZYZzQ6J0XSfQQQ6+4rknhJWpQI9aThMEIs8GjQviEiVOwseQy71VxWuGxQs+v2xrohvBfJEh+B
+pLlTz/35+wR4/zRHnbobR77gDvMSOFRS84sEdZ0KEWAZHm1/QXI28pAHQb5410DG/2jrVR6x7wEQ
+7ijBhm2XYH0FyBfuRWGbvMAy/oas//xrkGPyRj1A9shusFMwce2yBcmNcdeTKDIpqO7qwddS3FOP
+DHe1LMO9kR1mN+WB1YvggL/JHjyy8GbPHtplKvM5UvpuneLuAb0u/X5qE/UFO2b9tdEWYGlbYUuY
+Y1V150IvvMaULPmzjXuSCi+I+LHEPoWQbwkIX5fGfxW87c+0wZMEeKAETxPZw9wqvUNidUVir6Lk
+FBXWCzPLVrqmFC/rxS+SegRa2Ldz5te+fq0gR7pjhTn8vwfZ2/yh/7zs/qGs8N/u3e1j/8ns8YiH
+G8qBXobQh8nxT08s/Btu1BjFMT6QjzgMtpKM33hohtsQRB2C7dhBgVP/btn1fPyvuMERUwFOzf4S
+swdS5M/37sZxwAwDdY3QGaDoP967AVKwY9hXWTL69SVQSfKLeiuc/JbOBpdP1c06NViCip1CSQJy
+vaKlz4PziyVXY4KYrCftO6Mm8FLddgqRL8Lsj7ZhokUCdqw+bC0CFCJAAhxvZLE4JJ1HTUhayrX7
+YhSnS1oQgkAlaLZ3p+JxTl0V9S9NOJXgRuq53bk+snUGRSZWsKzq4qOKqPB3VVOY25ISjjm783GY
+LUOyLVUyULetDcG/iaHsmgOSj8UdQQId3Pbg92K7Hl2881eFMOrKgnhKQeshVecwVZ1UZwncIhJ7
+NzjDI5rXtZXQFycovDuvqESTzRbD86FgTg0HAxjwEZsgwgvL2AB5o6Vc8DKBmX2nM5YXkHuh9vcr
+bbc4djON8NXQZoEzkZjuZ7lyO2R1s854yYvV3zGsiwl2y2YButxXX8eAJks2mqJKcCzX09FDhHNJ
+2xIFD/A3FNJkfYT44w6hxMDt4rJKIE4opOkRntCYAka2vveMOMTzVELA3EyKI9ii/UYcOiQvupys
+5nFYQ+5SYOrdr3nsqzZ3s8TXDia9Dy6mhOWXhonoslE23okX+LG846uZn0ZF3XcKaPq8lD3KPuw0
+Nl8Rh/HvaD+MLnNmQDInIMJ+6bEAyNSWSfTclUE87Cjt+FdPJOZUTgCuxQJn5IA+Ff5DFt5nW+i6
+3Q1RMOeBivwu7xHy7TO3BrwESWT6z6ZKNOicSLI7zUOFMg7UxXxbS9zj5xEDRnUZu8j/pZDrCfbA
+F5PmGI18yyMmyeQjidgVzzp2FLxNRWKTDULgDxHbgykb8RpNBypskaHa4n1r66DOMtZwhA7dIkmq
+Zx/WTiiBsZxiNvRNpjyDLGm5MurwoUHwmsDogTEGBXkr3qjRc1HqRcidL5Z7LJ7Bz/+eFQen4n8+
+a68FQf9RV9wo6L+ftciecKD5W/AEGY843paMv+NzW+djtCX+Nu0Qi2rwr7MWaEIALjpOoiiAHnmV
+A/+x44Cs21TK7Z9tL9qSeH9hxwk9fGG/x+dwlqOqmnssgr7IAfH9CUCwK+YmgkjbwjyxU3iO75C7
+RiqXWWIfy3ja2nta9iMc4vkUKMKOKJOYDuVQLJfGgICVQVudyzGxDzWJxnYnQ8zj4UpphifdPtgJ
++enIRfSGrfMmqpNwjde7xEZK/lpxdAEL6CsMpP3QTCB9MetB0neg6ORNB7PsdsAorNKxoevXxtB+
+PsY+xjgk3xLNMbxzOJBxFfl3RT2EZDeo0PdvNWXTPeRcFqXMuPmlrqdiD1K7ANYM5SLpevV1CWKS
+V97YTQ/VqtfvmOeW7Twh4r4deP3ix+gUyjCwB4iReEB7Uw/g+VuvfOQuxNShaaWMlzCDL4pzbkBL
+EdQ2LT6oDoXNq2Ut9kUIvRKKogG1pPmQE+T04FFX1YOlgPEQu4aFJppqOULhD5/qxG29IQo5Qwyt
+AscI9gX6JZZFYOAsYJ53bBnXvRk4rTPqQxxN5xorDgkigEwTkPCf+CFHtzhLEdnjJSlOFsafy3zc
+J49hDTM3xYrCDmTtkmpXItMJF2Jeo0e3jqRJh3lE8wsDm3G7TrJt4Z6V8U+UDLSfEjzzB66b9a6f
+QxTfSFv67LCU0XhxyPKblFrQwyjBaGdkkyjZ8sSdGn/1AlVAuITi8Mnr4uDNtYa+Fthh2hz9I9E7
+APYR7TrAKg+DYm2yn6oq9DKO1bfJWDJt2jBdxQeKaKoj/KDhlYQevyvFQsscXmiFyEzdkfo0LQXY
+6U7PBylxsaQUd3iYy47jdV3JehthgzG3ZFFrsAPyuGjYprSDAlvM0WOITVNnkBTqKJsWr26PKCqh
+QBGGWLgs2poUdoSP4E4kqhe+zageWnZ87toppyNWn1u5ojAA+St1B4LHwwWcAMvLJh8idDr3Ret/
+GX2Bb5QWcto1qAvYh8LTHwSYyJ0HPGBXT3CLgdeFxR4QRAQ9ecTPsXIt0l+QCE+BqOlr2Lf0pQhZ
+fS8pfhzTPA3xZZ5roAE9kkB4u5RlBJS/hlDXgskQueeJEZ+hVpCypWHRDVj7VeWkRSg3lWYJupRb
+LwYzYfp1Pvh4fQ4xDZEbiFxg3mgVEewpgyx45ve2vClXvEfTQtULPmnL911ZNN+Badbftde77xgk
+sGFXSVyeqraFSSWAK15GwQKo8xoPWslROzIweoGsKI5lbaK7BPKGybRfoAIF4944AO8fgyrnVMbg
+Si36x7LSueYXiQgetz5wRXFYUEpS3vFJ9OVDM3soJcACZF8T1QU3Ucfme2ohqKQjl2hmMkkf7epW
+W7HHacG+YHxsEJgSCATFGMAGRLkY+JCSi3DOfbSiyNSfh+DdakSvwYaywOUNqNQb2ahApmNbgA2C
+MMDiY+ziEXVPSF+dFQzOPkXnwYrni8JfuA/iDhoBaAV4tTh7WKbpFrBXJESzjkSFyQO0F57Asu4n
+JHeLqW5wCoJwvYsZJJ10mks0SlHYAzfWn6CrJs5MLo2moP7OOxvZfEQtEkpsUB6GlF0Z2GXYdaHy
+SIYGosbbtagiu0dWFTwTa0OC1bLxn5OurZ6pFvCOdW1/ItSPkJ1DodgXaur+kcZ9jdhfzGmV9UBO
+yxu8+f+/lRa6nc0eIyA7+nRt3q69Fgligcl+UBiCMr39TZk/dRABImQNao+Vx3UagmVfF0yeytmW
+KEuaxXyC7BX1+whR7txAH7vElRw+8fINZ+G0fK+DqbqAdgLGjFda7p0/qJ2Eo71XvmdvYzt7J88b
+g6/AouQe1RzLYzSNHjZ11DFdSETNc+tcmwftgDKopvHkfhUSKfFw7p4m4aA0t7T3kN7z2G1kXEdw
+1tP5ky3anUflUbDlMH5quCOAT+IInVm8vswiTl69burhlKFws7mljEzVc+NUuzyJBNbTjQ+guzzh
+/MFhRabBfidzwPC2bNzS3kagGT5LvM4XPOfdk4kn1mWCU5RmBbJFRZ43Y3JThM764NvJ7idw+lPK
+O8Ts18aCC9SBAjkDPK9mpwhXc413QtR7O5TBBecJ/tKyOTegiSKkVQ6j7y34LTCFgQcRBkWZWm8t
+/X1iO3SBQVksHj1SgzpDk1x964ON/6rmBqVyleD6JQ5FFxxJrSGISCt1NodL+2REsPxyFdDbXRk7
+d6a0AEU0d+i6yaQoqzXDv3YtamnQcbcPy9WvzypqSfDe+1F7N+DZ6EBd2FhmRaHWJzSYcT+LtI8h
+hIhiOEqMEGRfhtN0kLF3/L8/miI2gXIbbN7/eTD9429h+ZcK8NuH/tPvBg7LtmhahC3b4yGW7H9m
+opHI4xsWiwBbwuBf/6YBXJFZZIuSbaaN0B3zLw0gQQ7QQ9gjgcWIqdWL/xIYGwR/AmNhByBS4mMI
+9iiHRPFn7Z2iCKVx07rvQWg+OK9MviFrhyTZuMQNOggQN2pP0keOQLFwIhfYaO4R/TgaYam+ISot
+a2BeYeX3mWQ+NO+FTTWs0xr1a6g7G9CwSJEYvZ/QtXIfEm/MUPMyHZ12RqMVsNeop0O1A7DthosW
+mI8xz8R35Junav6ilkU8AwMHtt6HGkFaOq3NxSHFUON+w8OGjIZgec1D8WIk2MW8QrfWMfAJotsz
+cZv/HruTGPV45B0oppCvXgUgzgvEPmKao3EK0L/N/M1tkMB0GsTLvGHJ5SaHtVUb+LuB+MMt3ZSy
+5SqaoekOAlqwaWnzVVbjV4nNG9eAnFxYusuyaXDdpsapQgu4vJ2fV5tWB8bXf52vAp7YtDwzq5gf
+OZ8IslczfyZX2Q/VoJAA0VrTPDtkwKq0o57+aje1MN50Q+UVw5MHywGVc1AVq6vAaOEQ7GF3TG96
+0x8RGIYUWfdQ3lGxN9yx0Ij7etMsV3SOmnS9SpnhVdYEmwaFc9M6t0aSN7xV51+Fndq3atNEsYlj
+Et900v4qmY4QMyCfbkoq1PfmA7eqK3cB2ixAJFS6vyRow/kK5QcRbxdFF1ZyBAjMptSiUFLeoTyC
+n5CQm78XTeBOSSHVqzab143hhN+rpikeGkltccAIPzY5qvqGOOe1F95UYcl/jkUZ/WKOJDZv4Qqr
+HFcs2GFtjPw+JzOsiQS2R74JUmC8uhiI4CQTKCyz0RDsASNFpAO7C/MBJSkacirQ5Yl+sYVtH2Qs
+xmHfoOMpHQONDjktFu9g0DPZHFnTDe9sNt6h4xpWaW1W1D1G/UIzUOfRS5vAgsj8FpofOhS53FEY
+KZimkfbcI3DpkDKhknzzSw8dXVMU7EamVswAdinvJjbyY+WaEYKVGW5LUyzPBSqW9ipOlucKRSU/
+adJYhB/LqWwyMJTLjfbAiqcarYYPpU4E6gjxptZTD7a19gqZNXRePjRwqRtUoy2IC6oOZXM+Rocg
+q4htM+T5gQWQBdxA6uMG9fAa9dUrMMPmUjY4D3IQXfxuifz+dSE2zJSf/Opggn+E140hQNQJ5YHX
+TSKIXTvtF5/adNq2jLWSmMNVQdg7smFYQ9ZtIxlhYL3N25bSXReWpAPrJ8zaYIvcdplkqfjPCurf
+gc7o6MohDWJLTQZlLhbRXnZYlxVri2cbd0fYLD48GXoPCvOsTFH2Vz0RKfuTFlF421+XLDIVWLiY
+LKLHNgAcn6NTEysZCsEInBDXP1RxYi7MyORxuq5wxDbkJK+LXeKwVsYOc7zZVj4e9Nj+7LYIwnHD
+Tjhe90PALdgVt2auU4+2y2GHd5i6eNtG6WH3gEZ1XTT1demc+Rg++VM0H4E4tAj4b/spuBfxUFrs
+rF0bbpbkClYbWeC0BMr+sEqkDOR1zR0i1FWEY1B+8Ose3DeFBLm7bcf2uinDqg2BV2zr83WTnpcE
+WzXAfmzYOMuaF1PjgADLaFDXasO6Hr/4VQBUZVvU4T6IvIjWcT91TbHHfDZjm8AQjUrDabrvrxt/
+ct3+PTgQdx60N5khHa34fvQ8lNjWV91g2CSE/qomtJuwEPhtJW/kVW+ggHODcxHG0u7Q4VAhjFWU
+7KdHTPtgdKVP+FIt/D7uoaFobjYnw2y1NNHWUGPQ5ZbkC06yFsf8VmJDyhI5rALMR9qsGuZULFGW
+eZyvzTd13ACg8piogEPGVIyZqo39BTkUnTn82p8jrl06HpYAfvi/P/P8Exv4X62P88cfftXMv8ae
+33303wcfDCoh8GYA6bAq6FY+8K/BJ4YQB0Fus4830Q1a2T/Mj+0XhMEsAfu+RVq30u/fzA/MRD6N
+461FBv1dIAX+Unf3v+VZAR1sXV6Y1rb5CyUzf2ra6vhShtFcHVCn0pc5FsLkFDmOi2HjVbvrZWG3
+e8PWC6Wpul4nzEHMstdLRm33DUZIkuQtF77Kw+uVNGy3E7KOgHy3G6u4Xl76epENXbkUB29ei4du
+7eJ7IeE/p4LM6hXAXXycN6sz2UzPPkTJLsju6r6iqHr1N3+UXa3SaS1gm0Ya3xnK7cL2vth8VdqU
+/Iy6gwyMxCjzafNfcZXHT3zzZMuQwJ2VCsDSMuC527zbanNx6ebnRjC2X8sAHq+42r1mc3755gGr
+poAdPGzOcHw1iaECzW+67IH5DJgZdqOhJISQs5nLBgf6nbc5znhVy/OyudCUryvIXjjT6Kel9+CM
+fRRrwrc2BCwumrXWIzpV+K/JLOQTQVv1Q8IZ+wYdBMfYiDKMTwN04xE3BeJTTefe5qtlPtkE9nm7
+Oekm1uoYbO76Mrr+o7ha7r7xatjv2Hr2MNMGkcvCja9uIu1LAijya1fWEsQ9PAac4SisfaglxgwT
+R2zJKkr7W9gatzXoQJSAN1jEAlQLKtzLc/Jsm8bhg9AhcQd5MZLoRRnQVB322NV2Le78Sz3O9K6N
+yZjjXB7RdawQoJdb4AaQO0asbCw0/ZALb24DWic/fTDO+azK6q6hbM6bZOUyd/H/kHdmy5Eb25L9
+lf4BVAMIjGb9cpHImfNUZL3AWGQR8wwEhq+/C6CGks6V2tRvfc5byaQkqWImYsd29+Vu9DH3hXLn
+pD37QdjizkCyNnU4LYIM08jIuPeELzYqfc1ow3Mxh/XbSkM1s7bs4Bhm7FP8BnaAuikGBcpnxI3U
++6ShFvgBI18rpxlUNzLZ9Qx1m7+NslONfURWaNr+jETNp1k20qsrTXBfFmoWvNoTmt7TJwbVyfJi
+3EJMHSXpg99hqLEVxcF21mT1YadDfNQ7aV+xsQnfphye5nZ0MH1yCZ3P1lQmvV80TZNsRsuOdd+E
+RqnjAgdP2vF++t50wvpuq3Ucfw3kaMeEsiazPsCcA0Qzp0Z4yQQmbsKe4ePMIq9jfc16VZBi9cWQ
+Q+1WFJ2Uj3Ct/rbsBvuIMS7yqyKCE1HAJVGyaP6YhFq9u4rqvvVFV7F8wtXzDW0senXUrnCZGBz3
+BnRucpky8u8SMmd4eIGSXYjGmtttD5tSBDYp1kCN8qNthW66GXONTdfIApNECkB45tyye69GNQt3
+8RAbV2Otdi9hzXKZK30uEB0nNz5xKqlM+lyConXEzJJwJuG2TJ4a5t+9sUyjldlL4JrrkNos8yrD
+ne3F6xALv628iZbJ9j/naCOT+tcX+j9UdP3rwcZrPw82eDtkwpfcrMUfVIT8Xw82/Qu3fEA72OY4
+npZE628Hm/WF/3wx02HE021t4UT+amG3vqza07JxYNEpQA7/E6XJQs36WWjCOGAYLjC15WSFcGks
+F/6fKGedUnFZ40FRmyrAZstJ+stiLpXY60TYpxAiB+cYhMOFqOrQYAnkuNeMyvW0NVhDHNA61StQ
+NumF2QX9TiZssljeuxBewXtFq+Cs5v48ZliyuX9VE+O5S2LDMSHu3w1qUyd3ImBz/wgOkMhQkgz6
+RsrAuMwSdYy8kbXHuM2Lue2gcOXFiahb+7KAV9Bcw2a8UjRruHd7xyiwbfcmCT/YGJMHPCaFXYC2
+5WNgUzrSf3kZPRlzBHl4WKQYICbCusadC6mqU8t3gECKvWEwniTwKzVBBI+t7MNt6nNfJZNAfAna
+6YGcrltc/0yEJTk4YBtu6ty6Qk2wxNUsnbHfqKzG032FU7F5zio3yffAga3h6t//88U8ZlO0+3ef
+rp8r1n7/cP32wl8/Wsx8LN5ITUIswY/MLPq5LMOM6qomyRDiSAYlCe7vIi4lPqbOh4fg+eK1WDtn
+fxFxKdleil54FQMlXhf1H82M2vJN/vjZAlVoWppKgoWVnrnSqH76bOXDKCO9STdqpNXA+InyecSq
+I7+0FOfRXpA6I2wdXAxQdrIyhrgzOY1x2a4cnjFUYPJAXiJV0EHqkTHInnml95jxGKCXrVQf8pTu
+oU/047RcTzZFbvTThbKygKqVC6QKGSCogWl5wRibDj5s4iDYxRnmw0OL5QJ4/EoaSnEE595k0DTT
+znrjbtTM5DmQmAOCgR44kFlLbKiN32ESLmAGOe0bcuf0kRddf9+yKS/3uZKq927UWe4Wc2R4zh2d
+PEXatbmya4GBVycW0ugs2Ojj+DCIAfx/GS8HYUIepbmIE33GgGs0mm9WYrqPkgg4+VA2EYUy4Je8
+xK4RNKMg71nYhzUOiXKcKK5wW7+vp4mBx9Tr5DYca9nxHEnCr3MswlsRDua3ksYNGy2on2/YtqEZ
+dZNGDtFIw+SdB0P3bBFCfXE6coGtqkuWENBJKi/IbbLpMVxAfT/jHPAi12YDYpHnPbWlNTn7cTCw
+OxVZkT62/GXrWyYK7VvvNG66SybF3ZvMnHdwdMd7PSjap8Bto+7A8Bgt7o+kajZ0Bc1opjGqNUaq
+QuQgIBmPqdlpa3y05BH5+iPDHN5hYCLoxSpyGxz/e8Y7+P1G2uvzOWTRMW0/0dqzOhWoX5oeEAL9
+O772HHMJAb2hEST9K8q2GUrrKtel9vBJ2q5xb1LEMBba/0TahkRJVN7s3euk+r/RtlWTxhKvs4zI
+2ojlWQxey7oeenyufhk5PKx57/DgHtM67NGCSTuNRORr5srlMW/b0uq3ZtXzhpzJvN9HvTZetevx
+wGq3fbFGWZyy9figK9fmKFmPFQD05qUiKKOZ12NHX48guR5H9no08cvjmBq6seRDm0+gFSrL4iiL
+1mNt5trbszVdjjtjOfmS5QysrVK9CkVLSjILymlrLqelvh6cEEYuyuUsZR/Dscp6g4+WuZy21efB
+GwuzYUBd0Ah6CAuvdpFiNbzFp4m6+X77H3FqsAf4W/bIT0WRfzg0Pl/366FhQkSkxo0FJ4AR+Pk/
+HRpoKGSWcN5wagAY+W0ec7H34O/B+MM+YV1C/DaP2V8QQzBesusmcwhZ8R+5LAHH/fHQWH8mvhPe
+H/YaOquGPw5kZVR0JiyAjVG76eXMMp79LQ1WKSvqzLolTB+c7AlM/yatE3tnqV384dZ0XiiI28Sg
+dMDNBLYwA6vBro2HZgNWiqtBoAUXdg8Hm7BVCE9jHOj+YVXRNazxy5RNL97vw+w47QN0ifzDlSga
+xPb510WTfTVSkR/I8rFoiwEMnbSOxXcqQ/MGd3sGZcKs5n3lBMWOhL69Taas3Aul53HbMngiozex
+jeRfGhdFahvXQgux9VAboz82Xc1aQXH672k73KZtEwabajCsPVdGjPP05+T36qDI2peR0WpekVr1
+R1ir5VmtsC2ndprYS7o5mLdJwnG2TQIXf4dhTV3lx7NjAVmJysZzeQhUm6rOYQ9Url6+THllHExY
+4zHg7VC9KLLIuOUDHTxJy52pHnN6OL42to19Qpo6PrUS3CAoyPk0Jq3Z3c0czuLsggwYNn1NsA+7
+KGlRcSx1ZFmCelWwXBenlJh+zvGN+GukZ9lX6RmwavpWWxNGmbHpy9cQT7U45DJsWSBI8PaXTWVV
+DcYnOt+AiIOn8gBL2QARM6dKPGxjYFLSuNVdz2wTVe3pvxHD/K4lfdZfKqmsiIbLnMiAVXblLSul
+9KwoWdEcO55g7smo4I99NUuhZ4cpF4FnTX1n+eYEFtxUkjH9bH6oyzZ7KW2AYkPtlPDE1OzHVA3y
+mABPO4u+DDaK0t0Kh1331PTVaZ6d9NnmU3fUEnwVtEb1+ksP9QLibjjg+1dwVkH5kjpIMN6IBF6D
+ccunMXynqCz28alpJx7/5XaCAJ5ydoVl7bcRPoEpqsr9PMl4O2V9dRwx1l6Pwix/SLOj60GVnX6Z
+9rPLU7QcbjQOAQy6/CCyb+wNMMvoMKSd3E5hB4KMyBvgxkA/VrkL4qQYbeelEPJ2iJVLjeBcQjeR
+jTd3Ts8Auhwy3pN5msfuYA0Q1ycjKa+naIA8YFWHZMiU6ywr/HBQXnFEXXXEX/fEhrUnVke3JTGf
+YpNb+mMkDNvTK7XZquxAHlK5nPNt+cFeMfRnhUxhMKURg10sx91kzS+O6uDhKtp3Ixz170rXHdaf
+SimM2GNbGntDAtl4cEfLE2n1tPwHUTfcJor2wvkUg7TJeji8ZbML6sg+Bo2R7O1As06DKC6G0Gzu
+arsND4ZpWUvtCcCQur6VXJEagqwUfPAIvSTTQo9VlgLzSa8yvY52ZSzfC4EQEhCsPFZOeNXHhH48
+s9BPAAvGjQkwY+FXauLsjFkGYT6WZ0fjw6/VLDQEMuar2eTaS9HUHVlLrX23cn3cjFF96DOVgkSr
+039Y9TxvB2yOd12ljvswiYJryqCMA2u2e81sgwPrD8fnOf61TefklolMkB5Wn/RAXprqeLCXLxDW
+Oq06mOy8MoJmYEyheGoK2kVMlJ7lH7qkgMU0JKeib4aNFJ26BZ1iHURU15iHE+CAGplNqzdAx7mB
+P+r46iI7eGeVxxunz66Qg4AZKkF2JiQ2PaKB4zLX3YSCsQGriKXeknuKvVyq4S7R7PdpiZmIOBYP
+ed0rd3nrZr6O2XuP8f+laKno2bPM5ddninDyFqSJzJD2xtT9ZtWu8DOmUmKqqY0hKLxKpHFDFJTO
+HUZf8lzTQjVddl6Yzs1TMMp62+STj2z4jf3UTptrEr1zNBoeJA5rE7dmS4STKTYwlNtJy4ZDz8WF
+RewQPdDc2Ht6asyngjY/ouGRoeHZKuxdgv8JxlorSRvzq88oVyn+c/IgC5T+rzdHf6xE/n1Q+UUT
+WV78OarYX8hMojswXrB65o+/3W9ZArkO1efAPKEo80DiNb9oIlDwmVuZcAhxWkR6f9JEWEXhKcXD
+wf0XqYVL8z9ZHRFI+fOoghBmo3aZhq0zPS8/3s+7o1EUsE7MbCO7Qr3naOge8yJ2LkWSxI+ZTbDJ
+k7o6qkcq5fC4Fki25UUoFfVrCIUPQTmeHP8vCk4Xk+VJH+nB2PzccoqbljODUEX1hvFMt3a6dECM
+wR0Yv3EPGu87cBLBcrFTI5/6q/wmrNk2Y9QzDF8lTG8i/aWVCsqpUnXaCKEwjLU+xXCZlRl3l1jW
+prz3DdR3bqebXtpwhiaIZthEU5OeuQoTygTyJYmfA4z5rzjIQBrMuSqdjT2x99hFup7XGzPCRbMx
+Qu61XhImSKiEUGhHpEYtI0eq6JVnaUINj2aSdZsaJLHiFW0ISoSV4cSHVubygtw4BCwSrTaSbOkG
+rzpG53zn6gNHNhnzpvEC4Mt3vdX338G/EKrRjEDTr1zq/TiZrLSACWdb3U08BJhclnJFHsBmFFx2
+nVEUe0iphF9GrUsvhjUSQ9QIVYbWNqIy+ERVODspNlc/EsQ8CYbpkcFmy8kPVaZZBCG4IF2wCJ/f
+qgLC/LakKcoC7VLN1vMUQ1P0hKy7KxHJ/rFJ9Bb7o4V91tNonzPvSryX+0IfJTn5egxcyjLz6kec
+VkvbbMutmrxPraZ71aoTJBRVN0G1IffXQSY3QaNWHwtYmeHUEC9mP8fE56CAYTOmWUvBT+KOXwvN
+dRZK9VK1++9/h/r1EfO3m+0/NYL/6wPqt922/YVAmLlstkE4ip9TFBTSL+41wt6aibudRfZvDyhE
+W4y1bJ0FjfQ6oTVuOL8nxXE9ItWZbL1tE631nzyg+Fn+/IBiIQCFWOeBR9mPpf/pAdU1aWvScreb
+cES77JYtrCssdhyJjoqjZbBonqBwtYd0MK6mlwgTwSlfnDBOkRq9F+st/piAztFYQKs1k1h7SVcj
+jZHb40mu9pqgcSXdx4DQf6RxPbGNxokTcs7et4s7B5tnu8+Fah/qxbvjEK7UvGhx9ESNa5+dwjFu
+XEwOoR/pSbkLQpdmJXdxBEVurxubodVSjEKLwMPzNj4ZSWboPgRHFCAXUPkLXb7GVb0qRDlaEQEW
+hqzOUW0i46uaVNQGypK7ikwp3g8PGq+fcAVtt8EiR9FriTIFAlzdhamRXAK5DG5oKStd6IFx/Fot
+wla3alxmnsKUJNz9HgKU+ugooMMMlFGpRizOrxapjDUt3Ft8e2ID2RItzVhkNbXtzAsa/bqDQS4w
+P1PCLm5AaESXwarKuatCp3yqdaty1y4iXr/Iedoi7Fmrxpdh59f9pSEKxF1XW+MGcIfypCVTf5xX
+nVAskiG+bvsKNTs+umVX3FNK1W5ijGgHted3vqV2eHkgd0RZ0j3wYdfdJFrW3uW2nX/EdgWMlyGr
+/xHrLoNbpc1Bt+2VtL1WjVriFESSoIPGvSwZjS6EUJQ9YFLSCBlzG895riLoFMN4k8RDvo1HEDgU
+wnTdA7APgRQxBcU1KTD1AUmBm3s0yTn7Htep8xaZnXpBZwb5r3LoLYLP2rCMjo3baEcKAEaqfIPe
+hljHra7btVEoPiYKZx7c2pkeSmWcGq9x5gFnV4h5kz1TCGsXrLV+m+CJ63dBQDu2Z7eZ/Z7SnhLt
+WCInj3LQuQVDr7TA4xAB9eImlQ9QQ0F9TdSgtn5Tan1zigKre2oldR4+PrKh2GCDDsZNJHL1BkSw
+lW36ABP0vpiL9Ct/eVi2cdXDDw4GkHsvREtm56LKK21Bcc+wycCcNqdACWkH7NXKKXdkKYJwo9Zl
+0LCY7R007rp0zkVtyWTDN84MSpQRcbaM9eFtF0XBTTjSWeYTeQ6dEzbv8I63aEP3KBbCd8l1+cBG
+otkETikDVHZNHJxRqXYoWTDx6Za2bpJkNNvtrAyTTrfUSF8X9pDkWp/bHkZQHnwkWkpc0ZCp9HB1
+t4+i7IcYDkkgIciU1bkxDFqwHbtodnlYEsWw9No5Q1HJH8YRD5eXz6r22NjVdJy4wBGN4n/E8iVO
+gdbjc1C+8OZKrvqIg8znZMxrv9PCOfExKHabIZyNfBPmbik38xia6T21hWO5r/jsk9yJKrxRY3gw
+ayN0eAVYyI1hzUW/FencqJsoNPF4ALoDK2dQxjrjyS83sjLDZ21N48SfyZw1pdOR1zHX5E66pngS
+AxojawZ58+9/duL9QS1lBv7ryf480Cv4r+nD3175OdYjM6kM4JyJTM+OyfT8+waSIAFeJ9D8qFmf
+NYa/jPVAVGASM7xrYPuRhrXfrU4OHm/uBkBZHHRkvrD2j05Ne7Ey/dTOgsGbn2spCDD4Tpa2nqo/
+yVZjRRp4jAo/7svum8MVfakoGh7APQaPGPBgoJtd81xEHbUlxLdCFlEEzwiqcS99tNUmI9ehWx8B
+rffORo9rPv90aGi3IwlaKH7Yb7c0GoxvUTYRaKaAypU7M2Ct56NTR5RS07JORBb01LmysSTeBnOp
+3tAM6DTnIcTS4NngTOfzEOt5cxpnIuhulaWXCLpJzGd36l4WkeRtmrHQnDuZ0HFKuNDVtqppimA/
+6DFJCLGmIqIlIKGuWYkoK8aPcQlQiElQ4Apat/yqVlohDuCes8dszV1wknQv9hrGWHMZFOMGt8Ga
+1hjW5Ia2pjioCCbR0S3hDqYnrOdUL46bHhcTGfYlCCLXTIi95kPyNSuSr7mRec2QOEucpB8rRhDT
+LuQO/L1EniHgPZPxqAp1A/nUfaYolnSKCmv/johKfGUv4ZVuzbGErMZI++HEeSvWpIu+pl7iNQFT
+rmkYsSZjqKklJZMbGZn+Lppyf1wSNGwX8quk7a3nYsnX4NQ1L7olc5M1/FqcjhZze43kKGptXuC+
+QaCSS2YnCbPqbl5yPLNFFIjyMMI91ZLzmRVKVdJw4MdcY0BB4oy3+pIN0paUkEP5/LGNG0lD4ZDs
+RDemsGcIBblrxCiQaXwVL7kjY0kgqZVaf2+XVJKVA2ob1qiSs6SWojXAxDIkOc5rrEkSn4Qot3b4
+ylLIateBsNpNdZo/NsbUDz51NdHNUE02HBtXIY9ARfrgsD3Pa6y1f1PmW2Rq/DFxizw4VHPD80To
+fdBLqUzsAP/c6qvWdkBXetjZ+XaIRfwgAbwqPKW5kdLObUfJpVWVwytgbQoXAhtcShWzrPe1YlTu
+Wt0Zd+QtYtx2efXe5Wp+oE6sPzYByhOgohk8m6NuEaOMne1SYi1KO/Zp6Qh2Q+LIJ9p3x+si0I29
+nZNgGoYAawRX8BdbdsEuwWd/HMndw1uu9YSlf99eRqbLm27g5B6oULwrgkg8ctF1f0zQuEl0KQEd
+zH16VU964FNM377FZqKePkuELWf2g0Ixdxq4G8D6xnPtdL3lBxmluBLW0eSbwrKehyaESUhwLnBP
+LYlk1SfuaPyo7CY9m8vu2lnX2IlSQjs1x7zoL2fWvPO76Vhp8MCa15l2aRVD8J5AD5aUdLRsy92g
+c5xt4Jj8Waxb9HrdqOvrdj1kCfocRsVsXyvBsnofli28xTWTW0ETZ2/9sqWvSjU9Az4PtXMmxiTd
+ynxw+41RFouJZF31d597f2cVAaZVEICGgDiQLjpBsygG8SoelKuQ4DBKsycO3GQHllA/Fr0KKi8p
+lGcTG/olrZfDo5lHDHgMv2rjmaWCZRldN7+qdEAMW5OPbu7rsWFcRR3qjden2nCuHQ2kdDUOFMsx
+N6iRh6lgiv1sSNNLcsrmvFMjus9bmM2B/59wlGOsIgr1N0f5pgG48b/WVd3/dKD/8vrPA939Ytho
+MosxmCOTE/zX89z+AtR8mRqQDKnc4WT/7RZMj6XL7RRbMx9BQXU7L/rlFmx8QaBkS6dahKwoNUCh
+/AcsATZ8fz7PhU6NgVg0SiRqdfGS/bymU4d4co0g9cfCLhI/qSlM7EtzpPtF0Uq2S0IzRpwGZcq7
+qU3FJVZH5RtPa4tLbU+pomeixuO/cMNvRANEsmEtPEnsjc2Me6Ox59EzhpRwSepQmEHbVBehv6UD
+jI8k0AkT8Gh0G3+yxg5VLbEH8P2ww4kaSSjvW0uNK8iivM97y4qbg1EY2TNTgX5lwE+mfS3Mwmsw
+KO5rRAP5M+3aznvFfr2hv9ZkSx41LZWZE4x/6znQ+bZfQ63uIPjz2acevgNzBSs5c/MTlXKZ9Kgo
+Xtp+TbxDR8JlzXAMYzum10cbhhsXfmuIn7StKz+JLZuOSOSf6MbI6wIrCKqte13NSVPtm9yxJo+y
+2hDMdzJGuLKHtvaDUKEEAKW/H7auKFzz5A4qWy5qR+YcJAnoH6AyqM+bkfY1tP7l+zm50UYbq65o
+hrHNtDM2M43eGUHoSP0u9N45yozOIs+wtTEAJAoEasuWMHh3ggoBl2CgctEM9Jx4sm6SZF/zJe40
+c25vMZdQS5QqKRQTTlT9hR+ymOFpMa9NpRG8D7XBsadyD439Cg9cyWSxmPVsqOow5glhO3BTBsvc
+8xjmSyEItk9dUZUvUBoVc5tNIQpDWCmU6oTusGCjoOHVwBiom4QbNTZsKVwzJuyMV//RcnJh4C3s
+1XlLS1l9aU9ajCA7zyEBOlYxg8dy0oZPm+vWA7HyutnpdcaFMzMKeDwEfwKaZ6IsudTtoEsOhdXH
+0ot7CAWb2pBoeUSa3Bu70mttUbZzdzPTEeD6ejnMcmPHjjwxIWIw0vsqQ+wsO5A9DV1DYq/KRnNO
+HHo17zqhiw7IKBiAY4bh2IEom6PIFm3EpbgorcbxuiTRz6g6VMFNYanQvxfDLfD6qqmf//0fsr/u
+Gnnc/PWN6aX8/gO5o+jibvoJAK3zos9nK1xJczHp8cClZl1dutQ/LX4uLEqWjhg5gEKzq/pdAVlS
+IQ4PT5KHXNRdDRvfr4/WBUVpLTisX2yBxj9bMP7roxWTBs/95SdZvL1/ToUwWBVllzlUeXB99vpG
+Zt/LJDb9rs4y9AdTqy4cC8A5saUy3c2j3dieDZmODuoFh97ZwJ3cMIuoBoGTPvQLMj1dGKnIzwUV
+IPBWqw2u1qfKFt8Co2tvjBjy+jDnDIIdmgxiHWT2gkvJNSswBE6hR4HmQx+U36t2Cl+DpJb2IVLh
+vu16zQD5DoVRvHSBDgi+WKHw5gqIb1dY/LRw46sVIU87eqVd5WxLVK+alPZowbRgBEO74RnBh+co
+ls/elb3i6c2FVF8szHp3oddTrSNe1RVpr05uNxyydEHds4UHe89atsk3gaWAw7fKPmNjU/e3FKhX
+75q9gPP1FmHJi1agfiejnGAEHQb51g6NqXyAxTJfGDJwjuzY2otYZblJFl3s7YqmMbnC+8dZmRld
+Cyd+ksqYEdZZSP98C50u+mlQ/HKkRJLO4KUWYLaWigACBdQFNEQrzzUTHPEYA7TEply6BaylZQC+
+TGfCNjPnR1nP4JpBYPc7MZGkiYvW2hNCpDOnDeHKa530zahzgO9XkR9LbfiG09mrofBQDmMXt7Fa
+EHGQ0jzQLaBeRp1WnGLce6eh0mM/7CwKRMqySR+yGdeoWzaAvRyrOmYB4E5626BGQ+f2laT5IL6S
+UA8CeWDOSi29DGFYZAjQdoizmbCrdlBCB0FnWRYr9hn369jcyqqoxave8FAEt6+H+Xgzz7mJq5q1
+FxBofC652X9DhNErzrQ8hiw4qvy5qmZu9ZVihc9clfRqq/PG4dlttpH60OamOAoi4ixBRWPsk9kt
+gUkUCm97lanX2M6DWtk7NTHlCSxP+TbUdmJyc2Q/4GXuYN1zndNPrR45myzkvYCrLzIeGiDmF8Mk
+mDcU8BhPulRl7iOfGefSIJUNh8t4pODCebNQl67zeMrvgNFOx0Az6xvQqJjWy3AIdwtckgIOOb7q
+YUxwK5r0BGg1a37U9jI2vsZlo79RFTRgsqrBfxRjswHo2VR+5kh3J8h/P7vukHfbDEzFzdg56aNd
+crXPZqMA5t4aN2VKbZvXBAL7ymDr2Xf2aSRZaOKYT70oBMb1eObSOVF68UpzW+i1DqfoTRwnPT1H
+jPMjkaaLLJYZZ6ReN88hjp13R7Gp6ytSVYtAT3cTO1UiS/x6xx3RtN4+zHqthxyQIa7GXLPCj6ww
+RAHfMgpf54m2PY8EHmFIBffKldV0SbhJIO68zKkllButCa0bMZYPEKotgHB1HJ7xV5mXQTiBEw/0
+Xr+tk3ASWHLaUvMH9ldPoRVPMztPR3vsaT6JN6wZh8csjVxnl7mxOoPZJmG20NbrPaWqMSpEq7VH
+ntCy3dRYfICojyUqsJrK1jMCJX2Qc8C+hrx/y0wXqk85nSL/D1eWy/iNCb/86P7P/6Y/+K2spiZm
+ploH7d//6f+3frZfzlzzb7eU//X+mr8O/8Oe8qdX/3L4UrjGAYpVQMcV/9PFZiGhsSXEmiDoUVjK
+lH+72HDE4pHkXOY2hGK0cip+udgAXQMErbvczPliGBz/EQgax8IfLzZ0+iyMNkES0HBUnYjmny42
+edlUmNf2Yk4omFKiKdvKtlZPIhmde0ezyU3P83ySXNvOdhcFPxqKfq6KXqtua+73jKRdB/gpH+Uz
+3lx5LjNzpvKI0hmKiWJrN0nb2DR5X91npiu3ndWmIC60LNq2jbT90Kzzh76djUNa1Mo33FUy9dWA
+DJ2Xqb3LmWOoOau7yTxMlDxeNyHezbCbsuuZfmh1PyIFfsvjQr3r1VGx/dqMM/ERzFkOVtfOGirT
+Neqz6lYZT8TT9Lu5I3QP+rXc4o0qyy2/gvHYamhb7IXCY0YuertIjucZ6Ju6gdKif3fVqvkxsTt9
+rovQeWx7Bft9QWYl37bBACkBqeZKN9UwRpkXzqbN4/bCmbv0lA/YTClRtYcPI2+bc0eRQIXo5oQ/
+KE4Nf8CEtSqPa9D4BkPmWKpj/DG78fjOso9KhSgxDpOBS9HMevGd3TCFnlGIgWIc2XDs9AkRcldA
+H9qhD2pXjVsRDginHp+D0K6MNG8um8nWD5obavcIQjpxS6CZgd8UbrtVS3V6mUeC2t4sxogbV2bk
+V26vBI+dnJM77LrboBmGeqM7to0RUNQ+9Wh56jlqiwBGNCffDVbNd7e4AYLmN2AyOeGF3vIm8W2j
+TBvimsYIhVuhGDuTSbXH5RY+1UOVXrVCRPdT1g7bxhDcOTRWkVt3zKvI6y1b+ZoWCo3Y2ixfert1
+3026K170OOYJSU0DAKDaUJU3uBD63kjN5DRXwEa9iB4sahnoBfC4+fYPBv1Vo2elqXKupWveKm4v
+Kr/PZm7uDWsAH3pd8+KKzKFJ1G1wuKUYyOhNKPxUyeSL4wbKfevGSumXRHK/uVmjAVEx3PuqtE3h
+DQ5lAF4kiwfsRJnqOUHT32d028THyVbki6La5Ys2m/FFZtjlpSsqIKhIpzWAMX18csk6HSyzHi66
+McZ0QYpEZyAZh29DWdQbWj71Cys0hpNVCPJjva5sx1JeAHTuz3WFlbIagRZ6aVa32MkK/ne0Kt2L
+Ua/frWSoWWeOr9w4mRw0+6pwiBNA9KK7GvscyDfk+vCVkrb6fRTpo8ijhizFMCejR7kIIiwxrYUw
+sdQY1lXVwibDY3XsnFr1kV7r4kD77XJYc1o6nr2UIlrTbJYXsWyUQ+0G9Q5AFP2J3LDpUgyWWkV1
+bVjM17bFYW1e1KK+uZcdXqfrjv6sJRUyi1t9bWxUc9leKkuNo91BhNskS7mjsdQ8dsjiT3Ot3XRt
+TwVkRBlkA52JXkjSfqMfrH2RkzbgYu7hSQQb2Su5BHo42Q32hYHdIzrxLjfkSFlXWYY2NeNuTVi2
+ZfDIl7JKcwDcuBGV3Tm3Y+PWFF3xC25E6TBcuvmiX5Ov22ugGTIvLtVhB7ulw41r5gIMLS5eytl0
+p0sgEVI/WV5okV54/ciE6VEw3O7ntsTu6ML9uJ+HYar83Mw/sAPL7zGj+IcyqsjFnPeFc4WgzLgN
+kgyDNuDXzLMjIecLTPhNuK14vFI2oy3gxr4TzbYHOKnsG8Sxo+Dxaz4oRUfNPJdx6GxBM5sbo1hw
+s7Nt8/zA/T2DI3cTRIZOd5ZTYGBAhAyW2OrNOC2P1UKN+UvzGIDKN7qcw7MRRYlPilt+ReqItSse
+QspVznv4ogbN5PhGyDPca+n3vSN0Vp1tpzYvZZsl27gxqKnqlHrLV+sTOB6THQFTy/RgkwozwHNk
+JuNjMqnmi4hpo4I+U0XbzizbyU8yGX81Gkf7BpFyqXF3ynet1fF35c3goLsK29iaVgw6Ls8q+l1U
+JIRXlSofPxhT/G2lCLaCT+d9sBTD52pXgUi0oRE0iNveINTmLFlC+r0Tjl//Y/YP5t8mRv4rZRA6
+fi/zf13y/joN8frPachh5sFNTM/sApWgJ5283+cuwv4CfYLsoGtAfyYo8tOe1/xCYQZz0uLF1PhP
+fl7zGsu6kAmJ2gyiwf+scX2ZuP6o2mIERa5d4q2sPfhZ/jgMYV9Es4B2M1mGPrBbmxVEJBAxFrrA
+HDj3Mgj6+Vojxyt2Umo0pqb12J6ZV/oLOZrzm9ZWM6XpqVBhJGJpInmlKGenJEexHVlE3k8VROJj
+vy7G+PSKH5mcMUto69asXTdoVR6MB7ekVU2s2zVj3bQpzSxPsL1ZGqvrLi5U6+CHsdCTnXVP10eW
+c8P4xEkarZs8ZF7HBuxijmdL6wGGR2lqd3wuREdpkhHq8tClJWYpOOqzN2dN8xSQIoyXD5xjQf4u
+KLHLk+XWHDXAjFjjFVdgMCrBPXTCqdnkueV4tdSD/L/JO4/lypFs2X4RyqADmLwBjj6HWmZyAssk
+k9AyoL/+rkCJzrpm2Wb1Ztdq2F3FFEWeiB3b3ZcTJUuMLKC98RjHvL7QXAyJNjXXhB/hxoy7oTc6
+gJXa1OmURnJ3B3hp0vtFRJDIMFvxVKHfNjoQb460Te0qmw7+JultO54+12L1mrYUSuM7HWQJQ3L1
+o1Z1PDGvefmdXP2qbCiHTzvU5ee/5sOrqtt+vTx8wm3x/dfvGPXFf7xjjN98logAjVw+cz6gmT8/
+uQS7DIdSaRLCJj5Fkvp/PWRYMPKwQMVj+eg4fLTYSf7xkHHZSarAF403LlU4GKD/iUJjKUb/z59d
+9ZBB8sFBqfYPLhPj3z+7ksOl5uRB3x24ZrE1THewLeMHGFLOIwq03NLGBTY+lpxOGACG7nOqZRPo
+YWcc2EUVDy21kuccc/AuqVw2BMxL7bnU1K9ZLO5X0zq4EexTGHzn2XLzYwu9b5yoy8zd+r3nTLtP
+aSX16fSdW5i7Y3ywDW4+QaFothWGl19pKYv7stbdrYFO8UDmYdiSo2JNZfqI3m1hH4oohTPDcuIS
+s+F/SHKv/RGnvVttiqjVv3esKhLRmgfsVDYWaKO/zkrTwPoVlwABB9XVGxiRPTyS2Mqu+6YPH6tC
+K24WmnTuBb33/AFLujeS73mm6ZjCaqJQCZ0iG0p/jUBH9/3Ss7xUJiejYiry9faH51eo4n7fXRw5
+No+O35E05fw8xsj07Oa8DrcVfMGjY2X5U94v5Z6d79YuvG2c6vkx6RqjhVbI/oYGSsRXS4fnYvUj
+Z0Q81xcjMqsrvzbiu0Hdu0tNQsPPLf1M6yburvWCLtVdralbG+9G8ljPfrhD5Z7eAL5T76XuebNx
+ufIRwLj+mSKdbc9xnAIyXgcENStMamoYWfK8oWIlr2SkGCriaiHUaruVOqzU7JGvY4i5jiS9JiDR
+QxHEiDGqqcV1+/pqVJNMncrpmDs4PDlk3UOnhh1Hy8UBkSR/btc5qFQjkSjoqHWyXozXkZMYn5Ya
+nno1RsWyq99hreUJ9SbgoP0dTTa+ftca7Ojwp2Kk2MJrYTLL2Cjxs9NEebG32bWRCF8nucJj+GE6
+jfttaybCeRpqzT7xGB60g7FOg806GTZqSMRuzLzorbNjts6RkRVlbKrUeAnMkUkzmtXUmaoBdFCj
+KNPsp75Op+k6qdq8DO4HpITsUsqyfAdLYbxOJmyGnVq9+2dhOvGjz7zYUF3d8yg18ZiyNjPw2/S2
+9o0bGDERl2UUbtmfzruK1wOkMGGkxa7raOg9WPqIwtRA91XFhI38GNzZuO+tuXiXzLkXkWjFXc8W
+743K1sXcgcYT75HdFdd9Gz1SZt7fDokQrwKDZM7abSKaadP5e2v5g1dsMzsmYYTQ+JkPg13vhY1F
+IRHU0rKZlVVyK2ig+Gj6iah9k2vpfRrXBuwMY4nFxR0z/CQbQQ8iUbMMaFUwoFzyTRkW4d3asIH7
+fclc3V9Y06bTnUzj9jzkGmHskL6Ntx7o25PhDyCGM392qiDN6dIm3w8jOMDPIIg9TFOtnZtG2PgG
+W4tKQOHnINU0huDbyJv7I+JpeJISZtSmKrXG+ixa2o+f8sFZcCaTK4y2YMaLKAcUXOflMc+hCdCm
+CSdnKLQKjqTsin5v8zyNA8LaSUijUptSN1yXxFXFZGJAtRofuEIStk9klpZyW+tO+9o1SfYwGVCj
+r7yiY4fualb8zv5dyk2Lydjai6z0Q3SEgcCoq5IHnrSG/SJNlFUrf68IclySxtS/WLF3T726WshO
+dDbX1ZcuH66sRbuObKpiIxsPBpPMtQnzMpgNaOS7Ejj+dhl0/+DPOIrp72u0G1tAmht4K+zHYSKl
+5TdOCKI/Hyc+I1b46LfDsvW1bDk4c5k/iEHSPgtvgodgBbL3LZH9cjZpEjtHVk+Kos9FeaKNqC0P
+OZjMnfJhw143pu1UL+01od7uQpCYGC9soelLGZE22xcypIyZVc7gX2VVaW88mRMZzMbF3dRDqpHH
+z4sTzCiTk5yPfX7N27n5HrUWjSwuzrbPnM82KP4mc75Kb/wUVQ/tKmdHzHeio5I7dcQx7ezuipBn
+By9hdu7gm88vEyGOC3CUno5C5I4tVvYRqOWSObydOqoYA/oAFShbGDnud3M64jRrMPeOtYGqRgX0
+ZhgbWu/nLs+jba8n4iGy4ULVUaVg9pAPgSt0MUTZhM36VnDFvFg202HT9c3BFT1ZlH/NtKXgP7+e
+tg5V8f3HL59J6mv/Grbo5VN6KN1zWM5c1rK/P5NYDTN6YYxnc/wnru9PeysLZYO0u8rQO/BP/yPZ
++pQH2vy/VPyqbS9Gw38ya7FmZpb6yd3KrAVEwfXYXfuObZA24Z//5G5NC2/IWgolRWqJXdw11bbs
+pvxiGhMpjQF8bTAV0CRGJoyttPoPY6IwqzRFeRMahXUSs2XvBzFwPJnh3B6WaXFe69jqbsqhK06W
+zf8UUsDyNTQDoQZEBAHSbjikcZddOpN/p+XsbAJhDvXLgp2XF9S6uDG07gbC+Lg3161MqBY0dTXE
+rGSd/rD4fKWsHd41tOu0G4uavl031Dq5a/Y7NIL3+EVygRl3rO7Q677nMSjXPqezHM3RGI6x6que
+VXN1DoN8y+XUBYbPH1KD13ZZVMM1HxcRZKMqeZi1b1IrPDa0PRu0kSacyYt2Q6WV8P6gGbZq7tvF
+aTkGdj3pW6f0WbQjU1ENsLGXkSFLlWvnzvgU2svj7EAvD4G0lVE6bj14bDt8vwnbTK/e4OBtLuQ2
+Xmhm0fmt4ynQ2gRX58C6qejjjkW9Z+zo9PEPlCzPx8Ia0qNG7cimWEJ33y/kb3AnJ5jdZ402c5tp
+w07v5tHWCMaAE9WyW9yKOzvuzh5m/G0yAjU2zHjkTqkGusTZsLxUrKC/JboXsXkxDA29VMY3OiVW
+MFn8wntyfCru0VD7bQ87AGS9UqaqCeMIuJxyp1kVOllomT/yUMoL26AM+z8dr+j38ztBSH9Hp1VD
+dZpO7nvu2RVbCOR3syzfGVJCylM6a6OnE+92JZJJVp67RMJJmFn/niLqCA4yWhyqeVvsMrCClNNf
+6WtQ4PNHxmwqXhLTii+areVNUKMs3EcpLkKWq44aax40+AhPltEmZ7QA43myUs3ZmrNLBHwezZd5
+LpDBKUyYg3aV+jSl+mmrAJjjZL8ulCpIrPFxyklWdnlxRsfOr+BpY5vs0FNpJKb4gGrNIKQn8ZCn
+A1yWZHDmoDc97bikC+VJWlNaX/uejXAA4y97XnxKeb3CHPUAfR5poInAFORhd2z5j79pckn50uL1
+N3o/YmuqdONQu3N9LEVF7MJ2Y/sD4AulXobka7qx748sauorkxnsoSJVcnbneDmUPm/2vIz5wBVR
+M17j3gmvmCT9mxCB95Tk83zok0xHsKCyFzGFIHvTtrtxsKm0yeKZzLX5wXtQbZNrg1IHn05MMfVt
+Q0iGgBfl1NB+44G/GnWNysnrlv1H6Vsfg8xYlFDK4F+NaSL3lp1ytXoWHFsVEigA1JblU1KmHevV
+KcTzgY3Xu3V7GyHPr9NTZrHXhIUOWR3+BjbsKY+YFgHmwAd0G2ePI7U5hSxldxWVGrshLnnvLL6H
+xVeLbuFDi0Nrkc9vZQzR2hHaBOZ6Lp90ELgnkz5hWBPTjLBlh7m1qaxioH4hLF1VGHA/o968lL0j
+z3T9Jk2Q13H73GfO9J0gKEUCsEZrqFBsukjuOBAoLejNgY7ozNkXTgAc6ngR+oHKZm5qNVjLvq6v
+yrJOLq4aua2uaB6a3ICvygwCS5S0DzjN3LmZ1Yhuuw086tKZHhqPUouNBASb/H9owv9H1V4Va/z1
+tf0IvKWrfnlvqy/+/d7GkarkWsCCQgCGB5H2571t/waAw1Hsf4g0pCh/oqnhtSJ0QljE8GksUErw
+X0sSNGK+RkFzhOBqR6D9Rxf3Gtb86eJWTBxC8Do9iKRcLFftdX++uIXm1D5v6h3EzRHs1JiVRzIV
+V9Cnp9eKy+YCXL36Vo6x9g4IvLzibzt/H6EU3vQseqhsQ9YVY55JLOiZ8dRKvH509DVHNy6cT1Vz
+wmHiNMYtLCyIqKILzy5a8CWqhpmyWdfZz9owf9V6K97lqWW+NfjAt8AmbqrBzDfaGjArevLVM2PR
+JcV9+tG7ugSbplJp6E8E1KIqJKzmNDK8a1WCDeg3cu64BtvENNEaLvTJu4xAIcatdGqNY2aNxHVr
+PM5fo3Jh4/Is66vWDozRI0y3LJPhXSF/qZDdGrhrCr3RAp7j2WtviGo4JGs8L7JI6oVraK/C21Ju
+9NZIKNxac31rxA9dLZVbal5xOXI2DE/eGghsjVw8tik+PorpSAzma3iQd4L40NZIYVlKo99r5mLe
+z2voMFsDiJaLOrsv12CipzKKnRVWT6lZOe6lXZOMo1mUVAGkIcGQyKZ5h6VrEv5we9k92d6w15Js
+Ysmapw+5luCmmWNRYA8Vi/40qCCl0Ba721QqXhmvSUtLGMWuwhp21/DaOVMKgRxYFj7P9Za+HSIL
+hDanUfrXgwpyLirS2alwZ7XmPOM185mp+KfrJ9K6DvW2/Bz6SVIfo5Kik5aE2WHwc3wF9EbnflPu
+W8cZ9B8gJ7n5NA+398EWIY3IzLSgYnaou+l0syxETK5kgbK0JzMSAzs367TYoNjVyw4Oh4s5zyq8
+9rqx0nbh78DeklsDi0wQZawwtqWR1A2+v3wBxhczUFaXggfcBNRvSfwdq6KKldA0hfJUtZzXJ8RC
+siT1TM/gs6ePjF/D0Dw5VdQY4C0L/VWK0aq+JeCqXXhBxFe2XuM6D7YpqRCIm4Gmo7abr4dGV0WQ
+enYcfalYa1pG6srMI8sJYLRT7NEg+ZlXacFaaSq68tpoXXGa81YcUgqhDiO89S9SoIaz7evzL9oc
+Zl+yyKeGaOwyKqKIP+zLnIEDOmfq8hykgMLRahbsGUYsSkfJKoIHcsKkIqlcu4CgMH4HXhNnuLgj
+a9uFMV4tDyeX3NBg4+6oNwPc3EVzLLc4CZ2tH8/2cZLEYoIplvaj3brGGSaF9YEJfLnFf8U+RvOr
+6b3mZ/mjDTuiZoQucPoSygqTvbuYIE270KqiHd1JKsBi9xsxc2pCGGh0CsFE4Z7oJ3HOg8CChafM
+tQ+ZHSZfMJZl89nngT5AUdDlw4xyqwUWUSo/8IqYR7bIK7yynPTKsRT9qO5+Px3l3z1L/+t//r//
+q5caF8mvL7W7/Fv341v/61uNr/7jNar/5rLNNXySGQQuFPPkj9eo9xvRS6UJIOQhDFC1+Nfqn4cq
+/lS+SBisvrER/udWQwTkngMrAD+UK++fvUZBPv2v1yh3GTg6fkDwWKnrk9v450utY5EhFBxTQDUs
+9qb6bLBSimIrSPCKsqxz/EYQFoR3BAB3bLL7pExkfS7duf2gyqtJbl36nrxt6Y74GPzS3k2N7tT7
+uvWaT33u52exSL/Y8vibb3udKHjgravFdqm8137dN7J4jNUGEoFQvIfrWnJQG0otbcq7Tm0tCzsu
+31MZGvc0a8mPdl1vlq6OTVPXw968Gfuip/DDNvtdSj9iuNN5+pYnqqy0gjhCq1dHIp+decCe0lDb
+O7M5PJkOVTyIdVHrnGuqMt4mD119a7T4A27seqALp+1si2izbj7EUuTf7Kmzn204wF88g9M0SEZK
+hQNn9saW2L3daDu4Mf1zR2T/jHsqAtkwhxA0U00Ac6mgflH9S9sQzcIcK4y4yhFxE8aCSZfJ0gI7
+ppVNeopn/+wUDpO9iKMuY1lqd3bgtK7dXww9W7ptREtQz8ss9pOnIkvCV3qGqTvnYfwsvVpSWmyP
+2g8vNPyjjHTCCVGo1c22wQbhbljdfVZQ3bKAakawLPD9vaPj5GnGbCLj5wi7s8PyvOwOVtHU5EbW
+JqPG0+pdDrPcv8e5GT8SBRPPoao/Ek3cPUZlyjuMoAuHJl4WhSln3wVy3KRCiSe53PSmVd1SX2rc
+aiDIu2299i6NjupgIgNLH5OlqplG12zOcu1rAlTGIRirGic99KR2M6amYM1om1dlKGqXLBsJehTw
+acQnKy1+0Pys/d52RnEkmj6EV3PLlvWqF254veBns2jBw0EacLWXNlUitnaVkUAVwehyhcNWbUZ1
+bObGDe/GcZfren2VEe645dtg9duYDTTNlWlHowESDXiq1o8wlosxzr5ms5fv7MHC+lKQp/sx5q0O
+K4dCamG6cBBoTOi/RX0a3jatHR3LJYx2cEVh3ou86L/yzhxI2HmFZuzMnHqY0PKEPGlaCx2nIc/H
+hzFEzOKnk235v+ek5p3w65P6Vvblr49pvvT3Y9r5TWe5wxND1Zcp5Plfx7TNP2FjqHjNhOLBw6Dd
+/rE0JPjODg+nKcenIPChzva/FFpYqYJfb417qMXhP3l8MKD9/ZyGqMU1sR7UugtuS3WQ/HxO0ySa
+h5Ykcgb2974LM29X2yk0RtGHOBGWcBflsjjKXogAGsYCDzYyr8gH4BHKUiqFJvOm1tn65SGyQ8No
+dm9Ngq6ujmoBny278PeEHzRGK5gmZhEMoxF9ozrEI7gZVXDpJvPRLvQ3KrqQTkMazQ2rof8sxzYX
+Z9DSM4iVKE3G1h559dOpjnzZUOcD1mI56vCdbsrcazY8XozdUkmM1+m8PBAAhODZd/UtmeN9Y2g/
+Cl70Z4Be0wH8ev0SzggZYUqb2kbl8Da6iJ486ezMJV5OYclHqU2h3egpu6cIBvx+WQx/V1bxLh1J
+Hg8DLttq0eTRzI3k3C482KZG7UfYalhB1nrDJhlS6zmhmpEEK10H8c5vDXHdRzUFnUIDacE77tho
+tAfZbl0Ue8J9nMi+X70Ro9POrktaoQ8nb1uR3fhqTVZxwzOx3BEn6Clq4dW39PUbVbnNYbGs8+C3
+s9KRByz6Uj9Y1cJnPq+ks42Gur/u67G9yuYWR8gAN2eH5mkEbeIMX/XGSE45FpvzkpTmyRTLWzPH
+5G5DjKYXOM4lg2lMUarIm6dktK/ruLgPx1HblVGVHYi/kPmzBn6fFvaJ+g7/aMzB3zJw6gaDq/Ha
+FxLCSM0Bq4eLeQWrZTiKFjNKPDr6ZarM/Mq15+FYZ3FEpf3Sv+o27jASafoBAOOTSEZWtNJ7isRY
+HKNMPkDYzImFeC2kzAEefrFEWAlG+o3XCDKlJzfSp5yqj7T2zY5I5jV4ftHC3sjtGQcoIsl17Y7h
+CzE96z5XmFTL1oythPZ15MAeAJ9BUeWT6B0WUGn7pae0evGmFkunPm4XA6XK0NJv/UQyqOUK/ADa
+jbg207C9MWp+GEc6uC7a6IZf0qm5giQ3fYpGNueMApEN7kftpFFwfDdENTbqapIbtnPIcXxIux1N
+J/ojSzK+Y14730TABi7LZHa3dkNHC94OlrjwPdlCEXQKhN6hT9aNB3+U0lLPbbSzN1r5o23a0xNv
+/XZbjYBnmzh3friznz+kcrxnxJju2hgEuCZqO6im6FFo4hWVybqJxrl/YJ/sPnQcX4fQKYZAKsgt
+H3N4t64Y/Wucy+O2I4uABgoPl1br6jAQYNlgZjYCw9G0YE6Wr9WULAd4clyjecLBEhUalQiGfZfN
+bHB7n8bc1jXpaBmp1S2H9ktaefKg89ngQd5npwWhcN/K5SND0LMGfmlfhG9z6H1mOTBOZLs28BTT
+d05cuqmzOOdRFMcbrRvlk4C0S8ELP4ak6bItSmx55Jk0bmNat3Yon+VWqnBJNnc0/A1LcprK0rqh
+hkFuEyTxYAEMH8x8hLegdD/sUbzz5tSPPW+7U2kuWEhywcLTNa6ktnySB+JbMtEXrmcZkCxsGGWt
+fbJOvfH1ZghwhUQAP0djYFLiRJ0y7Wnim7nFv+DsBQT3j9Dxwjsja4ZjJfVyq1vjZWnCPVA6kMGa
+Fe2lRRs3lJBio5scXmWBTN4sMP9kOcwbWEDymFazuR1p0fORag1woJhNrkfFCWG45vHVvvZq6QuD
+G7MKX9T5+QVKxHxuS7qBSCztNA6fbZEs0eZfMw0oPe3X08ClipJfTgPqS3+fBsjNuzytfIdcJQZJ
+Xlx/Ptqc3yzT4MoHIMcSEBQOL7O/pgFOGR5lODAxZLCH/3kaAChnKb8WA4Yw+Nf+yTTAsvHv0wCJ
+T44EIv38qg46ooKS/zwNNOEyhhFkuNnreudl7EfzkNZJigGKTOOuEmk4nKhFWq5z/CNjQPfQfDG1
+iebvlNKAfBDTCcuo9u5nmkH8zEpH9OmUTuJ2crfmYFTfGzt0DrigNMSKht9JY5nRB02mV/Ve1ywA
+b26ZtnfO7KoYCGBko9YkOoIGvs2uFhjXTmi0GAqwGhBEx4sosFZZDU7YpNwXPIqf2qVYPjS7rQ5y
+FKNz9nOtObVcSa8ybWP0I1zJF2/sBIUsBYTYrZ2yHd5JLsSHxGupWqFgI4aJlYw5LdpzbL9QwAUi
+38aIfaPJZYgeKx8/140oE4fizThzwq3G82/aR5EXAQh3zfysZ74DsCe2MZF7Zh2l33R71qtNGBua
+VoDmJo19KJu5pPsy6awSlzy3Brur5LsGQRAE5YJgim80W7SNUSzFBxKwf+sOoe4SVuWC3kSVlTXn
+om9jnshlOtxY9WIjrzCVnRFr3EMR68OdRTZ/o17d0MqdttrZ5TzcZVaVXEAWWE+2v9A2A3oanVw4
+xzHVx5M3V84HodL0aA/acG8sFgk3vBc64tIQ7zLKkQly9IdsLUye1/Jktsv6db5WKmuqXZlyQ4qW
+5Vq63Kr+5Rxfh/Ul87SQnps5avdi7WmGeYnUUnb8jeDTYFw9iJjlH9CEyT4QmrDkxh3kUlzicdbg
+5mXdV8AiAJFCxUaa0VjBnZoAk7wVnjStICUEJaBK2gJfqVlRSzolbJcQWwwAJjeLFIwpBnOQ5dhb
+TtEKbDIVu2lUFKfclToHOSfhPQXtYJ6oBSMcGs2F+OTzmD/WfgmAacodfnRLqZVqN1EyGRQ1oi3U
+InpkLY+Zx9YG71usF+NX0LE57z9s9CzobQ3tVBf3zLrZdTFN/TXr6+XCUmA4GIar19dtPmcPndUg
+eWWdlXxKKxs+usip7yUBKTOg54PeIWksD/wEw2ofHXePo947uoYWB2ZttSeBswsXXGgDn2uadBvb
+RET63AENYFvWLcsW7cgKGkbCWORwkvSpVhUUP6YiNwN1Z/K7pDgV9cp6GxpLk3j0JMBDsyUlF+j6
+kjyXC7XlZaVwFFhYBuJCzPztxhmz/ALKoJk2mezkudU7fwnwM7nnMK37C5GJ2r8nXcL9Y3cm39/F
+KW+AKey0sZ/wfQoLNCA1UQfbmqIbgJBZuyk8fU6D0Zi0tzRLi+y2H6ZkvMmbzL8LbT5TQdF19hec
+ArF/CH0rPFNl4e8af9DaTZ4bafeIXch/jIhzBpneN18WXboLD+9w6q48ewn31Ui/rLDy/PLvufW4
+a/7Lrffj+/f/cu3xtX8qcPhR+H6hmNEWxI/Xn7eehW/G5VGKm9DCo+xYf4MdcA+hYnHtGboDnPGv
+NzBbTJgvhuACdWg00uHM/QOOzLr0/Nk5g5aHW4Y/loN3hqYwj33p3269WjhOxKoxpNy1O3SIxvUm
+abTyfZCj8+Ro+FMJHg/Rufcbd6e3HjOrNUwDzd18gG5rbbLOeSeHl2LUGWLdPm6iO2MC7HYN/AmY
+VIQsbW/iZSk/BTaShEdRyidpwtCR0IdotPfL4Fk/MD5G50nXkg4acOde0wiUHBs3tXj3CdqWsrFn
+YHesZ+yh3Y1uTD7Piuklox3zAKNY39iZz+Ohtgk9NH5dvHdxV72HjPh7RCcGT6vjQjEb/iZGm4b4
+iBMXBoJYrO6VuVlhDHhfk9Gs6vIKiYR/pi3NdOsNeNo2/Wz7JzzX5jbxwwEyio4imPQzxcCsrRz1
+2fbyE3xqGR0URLYIyEotNyEPFW4xpmxY/o2WWQEJx/axz5rOuyFVF3+bU63AwV1RmcGB8uKjxMMn
+AaaMB0m6V6UTuVe+bod7s+D9RygixUjC5vTahtz8zc7tbk8sqt/pLIQhcxOHMp7MkgsziG09jzdw
+Z4z24LIquE5muo4MiWvxKumb+QqYvflEb3JyHKhqm3b8eeRbKCQ5PBz0NdJQlsXPZguac8PimbZG
+PXYACxi8Eg6zbrBdtW16QpSJiGrltiZa37XmnPNiKRdrNxdj1V31Rb1cJbWwH8Cwxl9mXQdUKWny
+ZP/aNvM31DfwRVkn2eTOBsG+aYVduiv40lMMTC0t612juJjJisjUf8dlruhMwoZgNCcfoma/wjXN
+FbRJqQjQzdBykxvfg2ozSgXl9FdAJzBfl6tZwO00rdJ4nicF87QV11OYED57ofytvuJ+llWOF4Xy
+g/qiUnBw7xQiVChaaNpyxQdETJbNzJ7r01JcURPfDlAjBRsdDJNOcBBCQEgNxSOdE7439G9AKSVW
+Yh3tes43eWnp+9quzLdoQIBu2Lt+nZQoTah1PgklVNtKsmY2xC6pZOwkbVG0CWXan76SuaUSvOFQ
+6U9WWqHxSiWI99HkbQYlkrMnnb+LFp9WWs/he9N45bdayeqVEtjdGnerktyncBoc8kBoVVkutVt7
+FbCWVcxiSyEf1J0/bNJV7spaCa9PaWD9KoflShlbqsE9kVIymhOm4NDcLlarBN2ae1WzaqQ1twQm
+tczovfsob6UH81ZJcY1S5QgjTu8uUqS5w+u6YFpGv2Mxb5yN2rYf/cRR1QdK6TNwmW5ZUUCvnVcp
+UICXg8+Rp5KYkBILW5f1GavzjP9+JGHTVVZMVokxXOVGnVYwpEeAEdRgT3Z8OyltslplynCVLCde
+uC+50jGjBUWzMET+RWf5BkReKZ746OPDPM/iUDuJd8I2UF6rmqsjIVLkUrYgSKfWKqPqq6Q6MveX
+UEMESqvSXE1pzdfFIhBiLaXJelXhPoSrUOvKPnVByCgBV4yL/uqusm4bp80TDVxm0Kyy77hKwFMW
+scgzwOCzCxBZH73VrCmX6ymlmH7jjVpUHftIYG2zmwIsFQD35J0osky2xRRZ9kc/dX1+jrJhzu6E
+1nsYKnqXw7KUDcmTkNZEkCTztIhj3miNu2/0JeOnlqItmoOLSR8uTmwl0UZiek8OEdgPSDFJ4kzP
+3pCWKKyOAx2aNHJcvE1m2Dn3OPjy8xLGzXkKNc4j4S4pKH09tsu9NMrXEOcEOHk707VNlUE+3jHP
+CX2X0QtLiAJno/Oum2H6PWOMpkOutm6aAcSGSl/pBT8jiXHuxsgoMJEXinVWGi2TedgX5aaPVDQ6
+l5Hnb8g2G3cpzebs98yi44Sj19XZhHnHEd84Lrs0MM4B0VQjvTUk+ya+ox7wK2+YKDYZfLO7yHyS
+9xXLQ+/YVmGUbcpmwVZIztM4D1TvLkycRF6psG2tL3XtlFgOudBGavEcMr2DFVX/HpuyarT49bB1
+TqL/BrdQX/wfZZj9GM8a36Ahkkjnn+OWR3W4AMsHCJdwpomZ+a8lA34npAAH1RibI05mj3/0h+TA
+uMVaAPkCtQoULxmzfzJtmcxtf5+28MthtoJ6Qbuly5rr79NWWqnd+ZieGuCPe54x9DmJmrAQmsAm
+9egs3LhRhf4Vet6wpUnQysjZ+MMHhlgC/2E6+J+sQtsHXY7ujYEzZFNxvp1KlxUeg154UrPBc9qN
++KN02Y8kN3w9yBZj2RpFdFM1HmnMsQ1HefFEUd5Fkd7lh5ZE0Rxwc9geNUye9pK7+uyxWB5nHyyV
+i4Y9TjRKDGamv9FM8dzCb6g2bSubb01RJ184rjrYvnGIwm118tL7YjlZ7lDdCAauclfqQDODWs7T
+HdD+4aHPRgy5lUyHnqB1kp4cQ9jmRiuNivs1gm63W7gunvtJTTKeVXsfg4/VlIOyfkhCiwJusmHR
+np1t9ZIZTau/GIM1yf3UTZ79OKdl9W2cx5JeriY298ii08acKh3NBgsLavrYR6reb9JgiiLRztC+
+qdMOek3q30Mxv4hyGQKfSMFLKxQGIRFNwnM3t8KRpYTFkogPdrKpbaOAStAO1RkyaQTAwPW8hjxI
+zfIW41HiXNeDZd859lzuPEUU8tM6f0Yrre/CFThkK/YQ7nV/7046eMLCQ4/yMMcgl5rjmRvXfHcV
+wwjqMTatfAJNGFgr5ihq4+kb2zT3OK0YpFgRkVgRtHd4+xhuHB9ekiInlStDiRvjuVZcJa4YW005
+PRW+idO/RFhkMOkqGhPhG/uJOQNEU6toTS6kqHOhCE4E9SojGPGvO4RD5vLdULQnzekqAbCez91u
+gpAn8O90wKFSC04UmEeQUZ2iR7mKI2Wnjf+s94bxWDcgjAmJzSBON23eh+ZDFONIutJVj/nIBrva
+dkOZvZhu2xqbXHQ0pYAk4Q+vF8DZAl31okOpjT+rtSy9lcgS3IZEc1SXuq1a1bOJfvVONa33/Lez
+NlnLkmproksHscdsHQwEtt5rVdgOaKVPd17X0uNe5pNDiWhEHJDqFIQgubTTTq9zpTc3bnbIFEGa
+n1lVDU9JfN+L5gqKFw1ZYT6VtDDRJs8jSFWpryXzjFvR11k1zyeqg55ziDp6TzXTU8uWHSOjHy4F
+NF1+KEMnPhE47/0N3idq8mQdplegz+Yv8xh6zzArrWd+Tm1WQ6lXh+rRbz6HLHPENi3wTdOGUCf3
+fRk5+9RmP4DtzPlAuqerNJIQDEove3VHI32OzTyFC5p08psv0qkLktTtb+escY6dsIt7zRjcveCT
+cgvfybwpWAOe2wpMx5BF4RGff3HH7eXdTlWe3o5RX56yFFuFP8r6k3te32Z5aG94PIZfRWoPr72M
+7H1rYEMMhnoM77EZj/M2G1x9ukArfls65bG22KPCyElQUdhRQFqBbns1oSQ2GAty97XmpfVepjjw
+eh4/nBDNdIXbH7s/9X/Zsxb/D3nntRw3lm3bX+k471DAm4d7Ijq9oXci9YKgSAree3z9GRskVZRK
+VJU6+0FxixFtqkgmmEhgY+215hyzCDFgealq4vv2jMe+11UkXdgIZwnGik3pqpKyMnzZPI+9UGKV
+5dzTpHM6AoBcWz+PSPFkP9XZ+ROWNPOLE1na/RgN8UJGhXeOAkY9odxhHiSZQxfMKX+bMyXLOKwP
+dG03NhViaaYm6ywN+pPIsxOsrLke4UkK8niuGa17bFeDkGQwm1tzY1c4VZqRkVsXsgXzGxQPpPJ4
+9UZyC2dvmMCLZiZCsnXdVuq6oofGeRsZFZ4RJ6E36ziQ24suCCDLDbQZznyccuosyW0PnifMVzzD
+dbpXuC34gczyMFtCms4WZaBzH6V5pZUUy013ogymSv4cxMNLydU6JHNjeRYXenDeD5M6Q2skbel4
+YIAWWWbpj3VtYLHAAKMc1bT32PE6Vm/SeeNX/KGWH5lxO9E/qMD5qaJim7yv5haIrNcRCqQtuD2M
+PDRL1WBMvFY3JoI4R4bnRU8Ji5aq8DsvIxTjA8p5gR6mzwNtxHgTzWN8QEJnYOoSMjVd1rRfy8Y2
+RPnyRs3NCAWvvcWfZgC/EOLxb8ubpicSL7CNOSRLdZ6WUFJ0w+lWvt/a9GUd7YTJQX6sd0G1yeRW
+ga3elv1Ol1X/VqNxLBJFeAjDM7/0mOuuhshDeBbt1YrJzCxz5HjrOgGZoTw/5y1TjlXtBxGi6bQ5
+4+2l2LOaezYe6a2Mv2PnJVm7ottkLUupdDehqhWA2c27jIyrGYOBckOfNf8oEfOywDym7E0rVa8x
+Z5UrJsg3SqNRnvlJgaxMTuag1ctNS15fD6Uxnst24PFXlvZdqfvGvtFq53gk0nqm5S4ALW041RME
+AX7pe7uUbO4jBrPZsoV9JM3KrFA3tZ9Le9PG8M+2olri6g9pLWjjJrVza5u7JrbiDvSHHcrRnakM
+/mevMb6Q+JiceizICv11P1spSgYFxLOR1lWZv7Zsl52FUZBWNFN0udrnqUafZgCYsSPEEptzkV8D
+tGWflnUZ7ShTz2ejGdIo6hWUK0VuouN2iDPQQmTsqNjwxEtnZQw6zJVT55ouhrQaUzd/MkJ2jFSV
+0DxUZ03J9on9YFVtDJXtJJ43gmtjtOGnTlFanwyzUXcEwALtgCl5wsCFcPBOqSEC9y7eIofpOvOc
+62S0taOcR9mDzkTjo1kU7dqp0zuswDEZBlATZpQSecNjIuwxjIYpJCA9eYAPos9a/hnF9TDugObX
+57HqNQ/yYKUrPafrgv20XrkWzEIfIGaRdCeDrRKBauBVc6rwIyLjZi077vBUqyk+VESATH2CE6SQ
+SIvtcZ51xVE0eitoDlCLEqkC0NX6u9TyUK35dUivjeeuSvi4rUbdP6eNriOren9nt3p6fCrv43/N
+7xn08b9XT2UZ1Fk5sOZ9DxAWr/S6EGI2ZZcH8N0h0IatzR8LIUYXA7IwiSdMlVksvy6EEN1lrgMi
+VXSDldIStJ2XbZ79gQa4WAh1W3APf00ArAu36bfLIKnjOhkrzLRlSEHf6cqI4dE9J0yXZWrSYwqD
+3sSHX2gEitqV0oYr4gujeM0s3Kp3VqZJjzZ0bXfey5ExbobBNT5bbFZQcqa1jeDSD4Zr9jyuM1cM
+qzlqHCOvN00hDfI5BUK1MnqED/6sb+rWw0MmH5eWjBdc62P/hs7zsG/igOY0IEGKlV5/IsDUJ1Q1
+CC115teefh0WpXmWAQQpV6OifpHt4ajxVdMn04iuaj7rUjT/865XBvh5I/fDmduaUfillTwl3etu
+5bBpGTqSK8L/QDPx/zXUU6c/8f7NsUzZh74rrRC/+3o7QMKZ6Jw6oyRdEZyoZ3e2ycNfMelsQO00
+TRP+/dfbwWKQhOMKLyLCC8USGeevtwMlg4g2QAMBLEdTEUf+SttDFQf57oYQ0gqHuS9KUJzf390Q
+KfMO0H3lomCWw+Waqiepr4xngNhYOjPUYJ5hMPZsmfecZ30Y7Do49xtbCdojiYSCZd+q/XGq0XNH
+OoAKGZ+1Yx4xcCuvPR2rrhWqHQ+GpKoWo6crW3oDFAxapLkfGa+ZM6+QdJB47Guv1ESli9fGvWMs
+kiGs99i2BSZBr7ULiZYNvXaGQxmhbhfoBTH6Fvp4X8cmEQO1iD3wQ+K8V27mlM6sAp54gbONsZfh
+FXOvRw7V1mhBGzLO2Ky3ATs9JjPbwdWfMlJD0WAqwUXTFOjR4tTFedlnS68Mwgsg3DB4XMW/hMab
+UqYk8oMXax3dZbk7d1w1wPiVeO6lFNKOpoPsWNd2Z9pXOcXJ1pZr48ln9r5OTQ1FhcFtisLEYR5T
+aUtuUioRD/nDWkq04bFAwHfV4WpZOa1TbawgIIauc4dt5djBLR557Zh0IevGDvzstLHkZoDREdrH
+NgFJK7MotVWgwRsrbL+YZ0CJ6WeOynVZpMaeKUa66q0A6QqY/mUR68UZpBAapIVT4StG05KolrRx
+vc4HGAPaYdYlhr9Jh7Je2C6dplQIY5RIDZcIwauNy/K6UHpSj8YwJ7pZHtSZVHicdqY7i1RIa5qA
+F2xdvT2lKq02o+1L21F20BW0FBjY+/BAw2N8yLAgrGtP0VdaFBj3ijZU1wHPi31hJtpNJLfGzjJa
+a5N4TbsluipFLGrjke8IcpglVVYe+RhhV6oTuYuOpB1SEpz4No9DdRtkDZ04zvuqyXpjZTLMPJL6
+0liNbVTRtQ6whQ8tIy4bzulMc6p4Y4QGFQupHQmmu4cwT7NLX2LwSRsurU6tzCd8fUwdQUPRSmzt
+Bq2yImTnVtWFfquya73WK1/ZVEHGoD8ygSeGQUb5OQyUmQHFaR5FPYwkuZhXhhMS4tdQbmlxdTQa
+vbbqHc/bVqEp78mD7Y9sYWdgHJKxY7Z080rLynQlwcF9EnTNR9wmfFyScm7EfYP+uPWdFY3OaGkh
+7TyrzCCf+1ZJJmdJvjuNMy9HwRP1O4/p73mqtO1n3avlhe0kUriHRmsubSj4q2lt/CcYo4Qq4CeP
+gSio35caiN99fgyQEo2ckk61ZbH26RNy7PkxIJJbNZu1HvMaayN1ztfHAH1xBSfvV7k9goLXxwBJ
+sNhGqGUsHFbo9oiz+YXutyIEft89BoTggecURREiO/277WHVNRpBv86cuA30SBEBMdAOAvyuKMCW
+rqqS5y4zTL2WVTHQx3BLzn2SV1vfk7vboE60Ey2NlXP6pOpn22ufulAiGtNVBZu5dvMvA/PbVaaE
+BcLW0V+YbCgksyqBk1b6scPOZWG2ytOgyuctQqMjzJzNvdkYCgSMYri1xlgG7ufYnyKU5ybjIhRH
+fosSOvJHae10oXaEFEFeyuZgr4ZB8X1k7F27tv2c5l8ju7cpY1EGxgjD6PA4CS3OpAmYlKFv0lkw
+Rt8rjqy8Oy2jBgfRWEbHpt0em0j22kp5xG0lADm9viHTptjKOfNOMlTYf2IDW+ZAqObMxgt0QEV8
+E0aMvgYzkI7A8dPKiVKUcmUQCZSqBIx4MCW66u1jjMthBcWqMMiqz83j2qrTFekOWrN19TrYaZKe
+A1Eu7qsgaJZEC+TXZXkUOv6FmzT61gVIdgdPrvqU9raFf4vU+ZqlHQ51ZZ2z1NbXSWPmtCLT7gqR
+tgW9Q+RTwYvC2Vl4Dk3jCk2VpMrpvsrrYNuSBnen1L1CYRzpywg3dTSb5N7I7epj6s3SAKtaK8tU
+iWUgJ8zZERQMcy1Wd8Sf5WsZ5T8/RJaEUjYLT9gCsnpITrKqrO5cRssLIHP1rDIradfXTB4RVUcz
+pJ2QynJhOWiF+UAWNoRaGBLsEmsCZCFcCv7kWPCFeYEJP6mwk6OhE+aGQtgc/NhWzmNfATPJBhfa
+Zukri5gB8k3k9+NZOmYj3Wk7O4MJkuISoSmKXZlhdyQl1mkY6bfaWONtI78TU1pgnZhZ4c/KvAyu
+E+Bg+z6RxrM+LOeel/PMIwk1IQtR9RYFE5q1JOunPCjM+3/Ousk69pN18/H9pprYtD2vmuYHjElg
+iFgzLRPKqvy1qYZ/CR0w17wi1k1dFWPGl6aa9YG0TgptYrKp4NC4vy2eeUDScaPnjwlVFdXuL6ya
+usgA/W7VRJ2FD4oCn+0rmAS+/4ZtVA+5mwIRncelmuyYCo3HpdF5HQpdJg8yrsPreAiTfdE9SHJj
+nPQWafOFJQTBTPcIrVGjYyeGNkNPp8RYUNhBDqi9EiL7sb4bWLGipVYZ1w0pki03shR4M1x69L0c
+j/ireegkyipII2mcEXA/rEvTLMMleuCOJ33gw75GVNzsMb/Tu7LU6rIBnmgJvl24BUZPzLzNsG7p
+Zc2wyUY7ucs0A80Wuw5nodkSvTfZq8eZHUX5ovQG61Tz0nRfJFg6knIYIJjn7QIFDHNzHzv9LAvl
+SxeL056ClnG+N3pH6JtyGQtOjESB4nBDF9RZgYGOZ8BXlK1rdzI0QoZXH+nCWQu90eu9LmnyvAcT
+6M9zoX10hAoymASRWkD+2QLcf3HrT4pJoZ30TSOuL4sh87BcCnWlgSB0ByknhF+E5fVWehZiCk1m
+2wp5ZguZPjrthWoznQSc5STmzPrUO0mFwrObxJ6jrvRr37eWllCCGpKscAChD20mqWgjSdDdKLN3
+iE1tzpMaVbuR8JIe6zBaU3WSnY6TBDXsNOThIUmvnxWhUWUMh1zVsyrLRWM1uNWqGpk5y6HSbBVV
+kfeKg2nDDYYcGaqNcSXTKyR00KCo/+mRGn1x45NpuGyNLERImqvCFDasjWpQT9ya53Xgclmg4t2k
+cvpYR1bKWG1MFlWWm+ugQWXex6m91ys3PkGEGEdwpSyJ7C1lPMUCdm0V4ZExFjDRU93cF0w75kWd
+kOlKi5K3OpIwRjbS2o0geLWKc5YNvszFabOBzBt/g1PaO03ZRt7D/LhRoViuYQCcF0D+Nvg+czRT
+1AFJkn5SKupSyY9ErEy9cTM5v4+9DpuX2tC4IwTzs29D/JXDYgXeGMTWZRNW5mWQuzuYwSY7Srw1
+vM9oaRYOnsDYJeakbnXlopAc7appRu0CCjDdSuJ3L1IGMmeonpyjMYl9otqQ4h3BQvRvdIjsPO7M
+FrVyXxvHvRKla2sIn5CbaPVCtYKr0qlUnh+yPmd2pc3HilFa38FILwlnhQYmVO/V4C5ss0FU1LXG
+MaxWZSGzy4Y0nhyrnhGTMp/l877SZQRVvnqmdtGw0WQKr3Lme0kO5b3l+cLEWNuqMMwXo54GT1Li
+oMS3Cu1Srwf1NtEL64HgFucqrath1o+DfqrqwycvqbeNTpvTzOVsZulVfxKjwPJnTlvYd1Jpd2sP
+RxCbRrLZsBMssVVvAqX6JFeaNvP7z1ZWLS2oJwuZ7dinqsyHFffaAtLydS2BsuzcR8CYc4SN49Jw
+U7TjdhNimsz6aDE0GpAV24DHkt02FoYsQY5csn+NqZNKuIvlqJ01SvpFGWpca+xh2bNLQufe0mxr
+9607ZEdlTUpGo6uCe0/CQp3tek22oUJpZ7Zt7vTAf8rJLMIiBJsprkyPqqaKzhwbn7Lc1idVVEsr
+P9Jg7gb2HptAumyt+HKo3W0OC1Gu4pt4IJ3eSfaUuAyIHWOYyQpsFzsr7xBN5dQtNv33nIFkNCzl
+kDDPeDgPAyCeuPVWyoi6SU5TgCDC7GVbBLV6EqM6Y+cqMeIGqkKckjN9rPFdUuXOHZmSKgmcFUTi
+Kyu9tvr6MoLrMXeopvH22ZcNtVATdytDL0byG8azoZRW8DR3GmKTJvKuGem7mFm51Uf0Swv6is5G
+IuZvjYzJ+6gmxqweOtgwlsurOvQQiRwJ5lGuI0URQBSvtT5JZkeycOd/ahFvGrMq67NkFtt9tPet
+ztvpxPQto16RhLPQBZtW6MdeFEM+QUC74uGor6QkCe5rIk/m+P1kfB5lvHQ7R1/lhmvzNHDSRSj5
+9gmRGOlMTQsi2LDWL3tDJY44N/xV3HjRitzf5hhvnIGYN7OWvU1v0gjHy8QlYCDBqZfQcjhxYyww
+ml4ui9HZqImksnzZcABi11+WjD7Qy2ouRsN2l5YDM5O0G9YAM5FLl7V6oUmYRFC1qQx8msghwSEK
+F2PRyfdDMHQXXmMb1awj0lGaV0M7auzdW3lrVE5AYFxJPzfzudlOPLhgd5ILhcarTOifsRNtTTLa
+T4HeLuDSjPOmHPRdUTjBekAwvf7nlH/USu+Xf7P74Smu3keJCwDIawnI0JSNKf9BBU+Xj+LweeOM
+Nc2inMNixiSBOlB0Vr/OVUGQiP4pfXpSAk2Zb72ME/QP/Ct+ga0zme50UX9triqLEu/NQEEY1RVD
+BSdOe5dxh5CuvS0BrbhSdewoGE+K3D5io0oipy0ljRDBVqm5dB27Rf0NdjvYjM1QX2me1kkEFg36
+OGNEFw4rL030u5pYnI9SKedfKIaoKCupWduBrBpzxSzC40QZFDzNPIbVWRAwYqOFmeRPuF4J7gtL
+nuxLPWyTNSLryLjI0RZ5M8T9tbwMLau51tuiBvDQOYAB6SuYt10Pd2imoIQvl6Mmjw+pY2ZHIOFM
+2MVQ5jZWwfYfLSZyjnkfaZSKtK9y5FZwm+9RxtjoaIegJVbQQky+HOuM8VtRF9dSk1UdgZ0leXVw
+wWYwL6DW+uGQX1l6IyI7oDKmAh/ZVbuOlAJo1rbj33dF6jODlIv2MQGPFM5Mld0s/yJsb+PKKR/S
+WnPA6oIovCSrXmEaHVWgJjAN4XjwCClqZyqtR/iY2A2++FGZnFgYfMEq9ad+TJTCUjWTUKV0rmlJ
+u21V47SPNO3GF7pdireRsHejRIdBCIwEFIRUhnA5KGVb7NXG8aqj1DfsVVkwCL0tszzBL9/6rbo0
+yFhfotaQpXum68oDnwaO4kHvg3rT6tJd5JXlZoiPcFF3SgWio46wJv5zVgpuzp+tFM2D/5MOG7/8
+vFCAv5NRg1o4Tk1bYzxBC+t5obA/gGhVAe3Rd5OZSTo0v14WCpF2iqGUpDXGLTrTSW7vl4WCkaRD
+0hnNNxO5KuvMr0WXioO8XSiY5LCPRYTBVpbuH+OWbxeKOBh0trjd2tYwV5IaLqe3UJv1a2/i7KAN
+vaB0MrSNJjg8PXrMEUmGUroL9CPNJ9CnlbFLIhuAD4YzYD5Dh2xupk6QnzwqAf70E/zHLiu+G0xQ
+INBAAIJauldzZoNgg5IJIYTI2213XP/w06tRJeiTvrpTzcPKGZYhkAWXQC5BXvcFhJ1NkDwvJjJ7
+JICShS/Ykp3eK+pGF+BJZWJQmi6QVxy6PNjZZGkOmiqE/NK6cDzTW7papUImsBVd4/nvdJ8aODIu
+ppmO7V5atsuGKQt9J2fwtWWVF729EciKLaKpsYMALxidoGrG5AqBoUnoNfEh6AStzmyJ+xQEUFfA
+QJHCuwhOE6vE4wKvbE0w9bA2O8Tkc3AaNUWyURJjSrLWrs6LsoQ0G+U7tnAYKZAiHFllMADV8N1e
+X5Jl2X8cVJSkSx2a4GWYdKEJzq4mDw0gjnbn6ESLLlO3dVyKE9ndG6FinMkRLoMzMHjx3eBFEUUz
+dixsUXqDoMwpS3cWiIhIwy/YpFWc+Xt5LAg0klVh+R+mbEnXJbtBEoGTnUv0ZAYdihpeEomUmVa5
+j6NalLfJc2JlSXhlTY7K0PjwAOop21IRMZd4eEm8BIDUMVwQOZjkgpOJifXfohUB2k8yrYp6hg1l
+sUhgJnKOKvSyxSSdHScZbazK9pwuNTlf4SS0bbtGLJbmOEoLLXMaecYEKBr2ogYOeaDlUk2tKJS8
+kHlZ54G+9fNeCPGWJuC2c5PtzD2cP1O/xJ/ZVSsZP6t8Q9pmdoM8xVuhVEZD7KGeOdNAbuyi3LQe
+8XyRzjUI4bE5aZDDXsmDpT5pk/MOghS0d8YwDecIOZIQMpPWQMaqZbATS0WgF6s/omezCobb0OQp
+B/QATbTk4GjOhVC6mCTTk3o6zwxyzpVJWJ0FYmw2ya2jSXrdCxU2rmDTXhaTOJskIITaiI/Ss3aS
+b6eFkHLHnV2vdaHxVrOxhihjxc6JJDTgVtm620zowrvMN7eCIjiPUFGetHpRXkhCSZ5KjpstZL3m
+YUg1TzdHqM6NSYAeTGJ0Ywzd4zArxnltawaEZy9nSRhKvGQI/Gwh9WPn15lbMgRQAMqTGrARwsBc
+SATdSS1Yj0SZLodJRVh0fr5DDPro98lJGWja3qOzs1SF7FCdFIi2ECNaTqOWi5RgA7qpZZ5R2E/a
+RXXSMWZC0kjDAHVjgrz8hkUZv+6gVoSDTUrIRIgi9UkfiXJLkk6B5gY4xl3iUi61zvA/Rg6+XFQ7
+qr7iruh8tjNSa2wNPvuPclCz31Or2jlpywpFU6SD2Wi6IabvEbPNDLXxKe9Ko1zLgSx/KRFyXYyd
+mR5JiCZdQgvRYC58L81v3TGEehzFZrrP4aC288IfTNZTv4OIrFmDHKxNcG/cEXG1ASWwySeSmOQI
+qlg5EcbQpDqbzPPBjpVjCYFMwMgMFSxZLABlQ82NfyXxAg3nPEA04pDN0uzdqm6gsE2cM31innnQ
+z/qJg4ZFTs2WSeKhDPOtBpOcOnHTuomhpmsZHp9gYqs5cQVnLZ2Ya5XAr/kCxObLgsmmT3w2f2K1
+/WPKDPFof7/M+Pfn4P3diPjV5yLD+gAXi4GcYFowe2NY9lpkINnQ8a+IeHTSg1TsLV+LDPODMLYY
+7FNkWocUGn8UGQz/6GojCgF6aBPweqCJReVvQqXO34CdGYKw9p2ag+sj9GESzm2PEE4E+VeBZpkk
+dgYpCXpC3N4YzpmaSe28HyKIQmZiLRMlDRaI/5HWN3Uzl0ziBlE1aHODBItz+q0soAPJJuOocyFb
+rK+JmW7CsA1WhLoOq6ILVolW1+si90+AXt+Su+nNPKKcFq7E1FwZrQeDs7apmwAHbhIs/CKTt70b
+qcdDTYvArZMLXQrV8wxVZDoU+hbNRHicoxRbeSFjdu7yjcyjoevivYQwZFZLNLHFu5BHjHWRtRuC
+nWWF/p6yfEOsqnLEMHvBxuCxIlz7I6C/VaWSao4lWeBqjP1ouPJcDZBV0okCGyuXq1Zp78au3KCW
+X2NayMkjKUEJ5+OjG9IPcxJ9h+hVnqWSliwTIjg/NrGc3MEpt+8U1cNcbDlYg6nTaP8EK80oUInF
+XXDs68HIYaKVqY2EgMpyCSqrlVeBoZ+jc8x4AoZ4aMqPjhd1m8apzomFCeimEHqDtWPTIOdfQsPw
+5t74QE7Acsx1zkmkP9JvvumxajwFEm1iLcVPI9XDuTaC3orZKrKFooespPqjrPbhOXYmdamllrMg
+PSmbQbAwUCbQ/VIzsOtuqyeUHMPwKCMN+GQDKlk1StHdGbnHilfL1UI2alBUJdmkBQ/HfWoqd4UC
+DNges2igdlNY9tXIPGZM8RgGIc+8Co281lTFSc+2aWZ58aMz6MGj+D+BR6JuYaUtKvuy2PZSFR45
+xONg3oYZ8ggUP/g0ymF6lBemOgP64a1NP3cWmVVmWJUGoLhRgFrYHxj2Rk2t3+S15982GIN3qa5H
+y1ZnE24yudzoeAz2pezqNw5gxY1CxsklefLdJS4uibZa7tsec+mOGHezD79Ezlgv09QeN1B+gxM9
+yEiYH9CvIE0ao7mnyuG+Z6RYxuiUkU1JwC8QVLhCWlFkpHzxDhBcyDDp51KQ92ct4+6lLIQZ5qTR
+iFFryEK20QgBR9aon70IB4fCSf7clWh/rVptiC2P1Aj6dqpuYnY9yzJr8lXQjdKyEvrkQiiVm0m0
+zDOIh4ZQMitm7u3AYxd8usOpKvTOg1A+I6dyjlPsKXvJRBc9CoX0EKDRnLdCO126bOR9Ez9obsNv
+iSO21Vl/CYW3XBlCeV0IDbYr1NgkM+cfVaHQ9nK27iFlsJhFwFyL3I0lFN0MAtB2K9wvZWskt3ZQ
+3dtqTSu9sOszyGrhzoIKsCrbKp8LlfeiM6t4m9AQ8Ih44NQiLc+yBkUwLtRLF5c/ahuINxlSnVtZ
+C1Clay4UUs8yy42hq9lxYg7aCRPsfpW2HZMrPGQEd9KOkcdauSh55V3jd9FKkeRwq3gFsZ6W0R0n
+nmwu9SjgBpClaq+wMbtKAnEn+81wp9mxelOWdXbbQc5cFX3aIsKuQXO0KrRjVq9hJWDgSzPhvwyl
+f7TNvl8TBOYsFL1SthJIrNvRlKqjMB7KHd50+6GkDTK3ZRDikuMv69Ra6c2wUKrmdkiThzDtBxCn
+0Y3cOnst9E481kLDffCH8x66aE5vh/NfX6l6e6+XtjUHzECyvDoLGz+Zq21pLg01vYCtZe6xBp4o
+ffo0NlkLrbMJFmOd2lstk/VVBub8QWuz30gI/aI0WtzX98tJe3zePJXDxVPVQLB4neGK755lQVpf
+Zf/ZD/38hV5Uz1dD/vT//uf+EXDTIqjqMnioKQ++CqJpuNGKhFD1TbEx/VnT3/yzV4GyHNTNIy9P
+Y0IEnmKV/Z9/xVnqvf5r7QPDDkwhotKYvt7Wbz97/z9/a88n8uc/880f/pA1aS0+AI+ojLdvX7G+
+R7O889a/e4U/3jo5kPR0qWBY1KYvXvDNKaAE4wvF8+u3aQhzqt9cIO9dAj9/e798Ct69AtB5mSii
+BDTmsGtA+UDLysYnSi355gwA0tZMXRHyr+evZ4Xab3QGuEJlpM0Hvn/zg4ptEhrd6/vkBd+cBvTT
+xFPBnsM/NX39rheCkO0ddCFYH0RcsTC5v3zg354I+puU/exLnkcuv9F18HInCDXhQSeAUGcVuDCT
+oJcTwDv95kpQsDEjavzdrwQBNjzoRIh+NfYZmxnW89e3jwfrgwlg4c15er7yfqMrwgLA74hx3GGn
+QeQFENVGgfrNhQDHkk2vqhoM/Z6/pgP9Ru//9dnwvaj4nYfkd8+YPx6SJneEibNEsDlf3+mbO0L7
+QKiQAGq8fvt3XRoIKTrwUlBRAlrIplWW/zdnwPygEyStY3V9+foNb4Vp2T7w/fMUJD3K4L56eZ/f
+Lo2Q7OhUMd8CZjd9PXfBfqM7gnGcoVmH1ss2tQL26SlP/M1VwH1gInekvfabLgTqobUBHUSefCga
+Xj5fYR94cwIIGSM0XYSn/Prn/zcukq9brzlBEI/Tpit4qn60N3vvB16L8j9//82eSmwqvvlBsQd7
+Pvbzxkv88/9+s1hOG4I333zdIEzHefn1lzf450N/c6zXd/X6LzcBrtiSTff0jeHlzzy5T9i2nQ4/
+kDV/vcL/+HP+tH/8+jj86auD6/iz5ZCXF+Xf6ybsh9vTv/Xy++6+/EETnKWFvjI30KF//v7+sUl/
+fIDnmuDQA8xRFVf/ugjap/JHp0lYkinADj3KDH/VDz/ll33/oa//7/Q++fyjD+LrrurQI3y6T778
+8KN+qU7EQ/nQY9xln59eX2X7SEPjeVMsntKHvvQVf/vnH1xHr4egX3DoIS7/Rojj1PH5z++26TKt
+/nydvr4LHgyHvou/ldp14Nv467yZQw+Q/sQqolE3HHqWTgLvR+vFy+cgRmgHH+G+4pLt3r9kgbsc
+fJCjey97/3ISKT6Hvo2/DhM48KPe/zW3+dAjoE4OfvQMev20/wvPh/39jx4Prwf4L9zWf4e4eOB5
++kvm0YGvD7P/r7LtDzzCL8NLDjze3+BBHHqEv7YaH3qEn6y0kynv0Nf/nKXDT7Sc/4UH9+Iprt9f
+Z0Uj8tBVcPaUNk/vPrZFr/fgI/wdcfyBH8Xs/q9ltQce4t8RT7wtASfvnizjv/D0/vfjPZns73/k
+QqFz6Afy1+Kgn56qH20zvw6s/rz5fB1E/ejXvt1Zi594iJ/uy//9PwAAAP//</cx:binary>
               </cx:geoCache>
             </cx:geography>
           </cx:layoutPr>
@@ -20682,1350 +20679,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A32ED14D-C4B7-4A0A-B09B-9A1DE75A1CE8}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="7">
-    <chartFormat chart="6" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="15">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="16">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="17">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="18">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="19">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="6" format="20">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="22"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78102D13-0DEA-46EB-B8E2-EA9B699D30D2}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="D13:F20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Average of Ransom_Demanded_NGN" fld="1" subtotal="average" baseField="0" baseItem="1"/>
-    <dataField name="Average of Ransom_Paid_NGN" fld="2" subtotal="average" baseField="0" baseItem="1"/>
-  </dataFields>
-  <formats count="3">
-    <format dxfId="11">
-      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="10">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="9">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="5" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Average of Ransom_Demanded_NGN"/>
-    <pivotHierarchy dragToData="1" caption="Average of Ransom_Paid_NGN"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="22"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F90AD5A-9B2A-4644-85DC-FA8DE4BD73EC}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="D33:G47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="2">
-        <item x="0"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="7" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="19"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="20"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24D40726-3C6D-4A05-AD2E-119F8548D637}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A1:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item h="1" x="13"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Count of Incident_ID" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B062D374-7A13-4D9B-9989-7EB12C1EF355}" name="PivotTable23" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="J55:J56" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="2">
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFBB8FAA-77E6-4C3B-B12F-BDB7BF17E0A4}" name="PivotTable20" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="E52:I54" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Victims_Count" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="30"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C6CF286-2650-49F7-B140-A90F21B0F49D}" name="PivotTable22" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="J52:J53" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="2">
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Victims_Count" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39310B45-EBEE-48C7-BCE9-B7B36758F033}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A24:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="2">
-        <item x="0"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="2" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="31"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6CF8C2AB-E0DE-42EF-A73D-53985BFE2762}" name="PivotTable19" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="A52:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="10" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="23"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CF1B383-DC3A-430D-8403-C112D50B642C}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="D24:I30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
@@ -22261,7 +20914,538 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A32ED14D-C4B7-4A0A-B09B-9A1DE75A1CE8}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="6" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="17">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="18">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="19">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="6" format="20">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="22"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B062D374-7A13-4D9B-9989-7EB12C1EF355}" name="PivotTable23" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="J55:J56" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="2">
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24D40726-3C6D-4A05-AD2E-119F8548D637}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A1:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item h="1" x="13"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Count of Incident_ID" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFBB8FAA-77E6-4C3B-B12F-BDB7BF17E0A4}" name="PivotTable20" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="E52:I54" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Victims_Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="30"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09F515BF-FB2D-4251-AA18-55F51DD3987A}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
@@ -22416,7 +21600,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA75CDE3-3222-443A-B160-2C37DF44CBCB}" name="PivotTable21" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
   <location ref="E57:I65" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
@@ -22596,6 +21780,819 @@
   <colHierarchiesUsage count="1">
     <colHierarchyUsage hierarchyUsage="30"/>
   </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C6CF286-2650-49F7-B140-A90F21B0F49D}" name="PivotTable22" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="J52:J53" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="2">
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Victims_Count" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78102D13-0DEA-46EB-B8E2-EA9B699D30D2}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="D13:F20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Average of Ransom_Demanded_NGN" fld="1" subtotal="average" baseField="0" baseItem="1"/>
+    <dataField name="Average of Ransom_Paid_NGN" fld="2" subtotal="average" baseField="0" baseItem="1"/>
+  </dataFields>
+  <formats count="3">
+    <format dxfId="11">
+      <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="5" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Average of Ransom_Demanded_NGN"/>
+    <pivotHierarchy dragToData="1" caption="Average of Ransom_Paid_NGN"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="22"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39310B45-EBEE-48C7-BCE9-B7B36758F033}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A24:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="31"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F90AD5A-9B2A-4644-85DC-FA8DE4BD73EC}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="D33:G47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="7" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="19"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="20"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6CF8C2AB-E0DE-42EF-A73D-53985BFE2762}" name="PivotTable19" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="A52:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="10" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="23"/>
+  </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>

--- a/nigeria_kidnapping_excelpivotcharts.xlsx
+++ b/nigeria_kidnapping_excelpivotcharts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\nigeriafolder\NIGERIA-KIDNAPPING-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9B8ACF-085E-40EC-9F4B-D5DDB0A4065F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDA3C924-9FB6-41EE-BB1A-F5C2F9595A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot table" sheetId="6" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlchart.v5.1" hidden="1">'Pivot chart'!$A$19:$A$32</definedName>
     <definedName name="_xlchart.v5.2" hidden="1">'Pivot chart'!$B$18</definedName>
     <definedName name="_xlchart.v5.3" hidden="1">'Pivot chart'!$B$19:$B$32</definedName>
-    <definedName name="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_31" hidden="1">Table1_3[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_3" hidden="1">Table1_3[]</definedName>
     <definedName name="ExternalData_2" localSheetId="1" hidden="1">Table1_2!$A$1:$Q$201</definedName>
     <definedName name="TA">'Pivot table'!$F$54</definedName>
     <definedName name="TD">'Pivot table'!$G$54</definedName>
@@ -89,7 +89,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Table1_3" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_31"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_nigeria_kidnapping_datasetgrp.xlsxTable1_3"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -10163,778 +10163,775 @@
           <cx:layoutPr>
             <cx:geography cultureLanguage="en-US" cultureRegion="TH" attribution="Powered by Bing">
               <cx:geoCache provider="{E9337A44-BEBE-4D9F-B70C-5C5E7DAFC167}">
-                <cx:binary>5Hvbct24kuWvVNTzUAUQ9xPndESD3Ft3yZbvfmHIsgyCBAleAN6+vlOW7ZJUPjVdnuqI8YweZG+B
-2ASRyJUrVyb/ebP848bdXg+/LI1rx3/cLP/6tQyh+8dvv4035W1zPR409mbwo/8UDm5885v/9Mne
-3P72cbiebWt+SxGmv92U10O4XX79j3/Ct5lbf+ZvroP17fN4O6xXt2N0YfyTse8O/XL9sbFtbscw
-2JuA//Xrf36I1fWvv9y2wYb15drd/uvXR5f8+stv//HP3/7tAr57k/u1fXfoj/dvr5sPw/92BY8X
-8IfH/sXBzoT4EVbPD1IsCSZcqvsf/usvzrfm27BiBEuKCbr/oV8f/uK6gen/eb+eX16E63D7deh7
-+/L58a4/fhxuxxGe6vO/f5j+aCv/MHrjYxvuTGnAqv/69cKa28HCVtjRZ/dDmb97pIvD71nhD2aB
-XfkfNNTp9cfY/o12wuiAyJSRFKePDCQOJCMkTRn6Yj/11Qr3Brpfx4/a5/HsJ+Z5PPhTWUfftvFP
-j+udG//3nUgcEIaYoPT7TiQPhBCpFFQ+ts3nVfyoaR5NfmKZR2M/l2H80Pqvu/Q9HPlrhsHpAZaC
-EYUfOQ0mBwRJhAhNv3jN11veO42+W8UPG+bh5KeGeTj2Uxkmv3Xhb4QzdsBSQRBH4osBwDUehR0s
-IOhwuOS7Yefzan7UQI8mPzHQo7GfykCn13+r4+ADqagkKoV48sAw8oARDmwAf0U68thz7lbxo3Z5
-OPeJWR4O/WRWCaP9W3lAesA4gFcqvnjGY2QTBzxF4oFfiaf2+byeHzfRo+l/sNKj0Z/KUGfXxo9f
-9+r/PPBwwDeuEMH0d1r2wI3IAROCIkS/Dj9hBp9X86NGejT5iYkejf1UBro0sf077aOElEyorzj2
-OP6QA0okYB9Jv3gZkO77nO+eINwt5kfN83DuE+s8HPq5jLP+jaRNQkrKMGQ0T23COE2lkoB4j2yx
-/nDEufx96lNL/D7yUxniyk63w9+IY/TgjoahFMjy/Q/k/w9wjB9IjiiS4uv4Ez+5X86Pesrj2U8s
-9HjwpzLS++vm0/XfKeJAmoOASSOUPjUPxQpTgr8GoSds4MtCftQ+T6Y/MdCT0f+rLfTvFvdQ53t0
-zWeF6b8vEKgDDu5DGP/K2tgjNxIHdwYSkKr+7mUPIe6b1PXv1/N9fe3bxEeL/x/Xzv69rvZNisyv
-w/Xus4r6PX32u6NfFZkng4/E2EfP+TVOHH/8169YwJZ/E3XuvuJREPm2Ufc7/G3G7fUYYDI94EJg
-pghSRApg2L/+Mt/ejaQwIOGvCoP6oxSErV9/af0QSphEDoBhcNAeFIJEVqYQzkYf74boAdD3u1Cm
-hLozOsz6+nDPvFuNb7/t05fPv7SxeeZtG0aQbFO4SXd/3d1CIUkGAZAyyuF+GAkhYXndzfUVSONw
-Of5fwo0prWKh3VTZbjlc0VI5TVKP1PHm0CovOmFaq5fJ1uV5DCKEnAQ3jMeVWWSdDR1vebakfHgp
-YmvHvKtnM18qz0qjE2b71GoTeyRPuoDbSmmapqnzMKNGJMdjt5W6b1Bi93UqhupIrLRiWYcqz89p
-O84og0dOvB4sikw3IVmx9hx2KpuWSlR6SbBvNSeYLnp0vg46jjU5p6xM3m+J5Uz3cUZOMybWczoq
-876uLKky0qTrlLW86eD7GlrMms61dbqWRnRHNAllo2k9N1tWFWllMzJXashXvoRel5WYgw627Mme
-TNzzHUe281nS13w9oi11b5Wo0wtaUo93wThzOWxBXZdYsrfeBPmxK1I1ZOPKotXlME61XmPE/G2R
-wi3fGNwHpis6L835mjrVnMxT7Sbd+rQQeWSIymPq2tW/IFvFQ75125zuarGpMROdkNsOTWVR6opF
-+dr7keAXzJdxO2fVEM8UL+QCNkxc12o7xu3E9UU/Xo5jgdxxWkUZdMfT+jTlZAnaj/PytjWFjPte
-yXIe9bS0xWtfVhPdzyopm6OxKAeiDe8rsuvt2H8Y1tZjvfVS3JS8LcoMpSt9PTcsvEM2JGyHXR0O
-o+y7Piu7Vt6MhfdDXs12Hg+HrWZzhnDjqW4la5CW0gynFWPJrDGPK9sPFRdrVlM7Oo1WPgkNLkBE
-tmBY1iEb+TLpoY/jUfBJ8rGcEjvrZbb2FBdjeZUEO37ClL4K1nS1LkeM0swF2XXaVdK+iLNvLWxQ
-3e+dwwvJkm0YEs23lLxJ/VJjXVPUrFqsjF1FOlWpnqqITGZLt3V6clwlukjnMdVhaZa3SwtJebb0
-sb1JQ2KHTJKAG71xtj3vHWewNoxts0+Jl6127bTVGVFouC3Tprgp5qa9FITiDxZtlduPxi+zjqJv
-p5xPBavht53fS/D8XqOI0uGwQEXstF0V8Tou7XZNE9ZdToRFo/t+WDZdT16GHA0FU1qWvd90mdrK
-n6RhIKO2KPU2M2wks0bFvCKd2g1vb11tiptmxlQcdo1P21Mmo+ng6Dbd+KI1KS1zUShr9RTS+hmu
-WHpVrF19hpMtFHk51Ohj30/ptjeWL40ep0q+rZjhzwMP6q0XwrV66rCwx96R4I/L2TWXvfOo1o1L
-CwouJ6ouU0Ga23RckdFs6CWCwXlLs7GXa6MZ8bPJimVxr+bSlAqgrNziq8o78y5Wd/ZRrrJUrwFL
-lPN1BuhbrEuxdnzxTpdE9gBS2PTnSlbNK5TC3XaFqNbX2zqT8nJqxoHDOeSxvhoWOhQ5QQmv80Ju
-5oimZT8f8pSzsDMDX9yOVfOwZrH31OQkcQ04VM8HpFtLndWqaMyo6yhUqhMVSZfTFjdN3k1VifaA
-0WXUxtd3T6ds4vOE+qmH553s+ZikhGqPuao13mRX5HIgBd+vIpneJUj4dw3t06jnOekmnfSpmfOw
-WLJpF+VawW8TFs3FyC/d2M4fRhmG024xm9NGsTboeu2WLh85JVdwYBe8W4vGKW0oLeedXXvucstU
-ivIOHK7VhGxhzgoaSZutXFbzToiuKy+LEpXHQx3rTW+pMFe2b6agl2KL+zbtAZN7CiaQq0sa3Zh+
-bM6Ljbf+NDSuanS/VibuKMSgqOuNVc1eFk1QO1407XsrezgU0ZqlzUKvxNVYJMWmWcdLnrsA8Q6O
-9WLfWYtszIaxRTJX4GovKeVh1FtB/EnRpHjc1UayKjO0K4IGNEVIQ8yIg177lEkdkiYYcFKX9Lkz
-3o7aV2nz2o5l0eYiIIZ1D7/WDC2oe51ar5JsiDUcvsmitsxc27B3ZShrkzlf2Hzg1VbuetyVncag
-9XxclEW9hlhfvZOs4Kg9pvPI5vl1wRtwaM3LAX+cQ9NexG2ztU7xJo7ZWDfTYWHT+lO1pO6CLZy9
-ShO7vXMxHW7KBLAwW73nH/EYk0KvHqHXi6/Uqsk4+E/UsPJw2YQ/dXjb3lucxnNV4N7rsvBE6a6v
-Bp/3vbN1ZnuPr9aw4TecVabUjfC10jPMflv0ZPaaqnS7qm2yfaqTMJ1gATCQDZaGw9lVW8zKSahL
-mjZ21RVCmOlpSPtSo770kw7lhI9ZFHBm4lxzgEZwGquLOE8EHGXiL2uToDqrh0JM2hU09HtamS7m
-dBnmRk+sRuel68ubcUlqqZe+IzRjzq3yuSEbdtloOSEXI7QNmCwxcl5rvVRtozDE+MmS61qhUMLE
-LeB4OqemWZ5tW8OWTqd8jvLMKDzVZ9wkUwWRZdmK9iV3NtT5LCsKZ6AWS3EU62RAs1amQfh4TZhD
-z4e1lzgTdHBNjgRXbV5z0p1L30t32oaSD1psFb4R0szzR7yupj/zrnBJDgjcADI5FW2+znVB7mau
-W+bWknwwLqnmjKC1GQuAIlqEvI+2KPJtCag4HuMayzd8CwndjcnYVi/DOrU+d0WFqqPCzoZbzQHl
-cdawFTZGhXQFs2/jVLyPlI5kh+ZW0SMfvRReT8pNVAJwOdW3+4GxCd32NcCYTiSoYIcrr5J5yyfF
-aJg1kw2VZ8qGYv0U1ILqixEAYtgH0sjh3NbGD+cFqit1XKoab2zXALdY5nxDLXL7cu6iODV1RUxG
-N+PNWTpRZz74IRlUXoYFgZkq1oTM0gIWmpaxmI+WIlKy6GYxhH6MS4juxNTTWj8TTKEtG4BOJ4ft
-2Ad0UnTr1GdohbN75Pqk5/sebbXL4Jh6kpGNW/x6RFtqD00vgArDQWbLKzlVrdQtY7PtdZX2vXin
-ZozfLkWypIeNjMUnFCXhh21d8RVQol5T3RQIVTrd4DDnYWpi2Mt+EuGodUO9HsOe1zFb0WTHjA9V
-Hy4rAB53WlZpvE2ARp/LpRDvRbsiscdyre0eD+OYHhI5qXU3t7ZNs03gYss844bl2yashE2b/EUn
-x4Ts1ohRl3nOjDlL4MFcJhKCVy2Bai966ET/ATDBxj2bRglHHSNLM0PmSV4GEcHNsXTE7yjQjh7Y
-WjQE4nvaxx3nEn3qCaqBwSvbAv+ut57seEz7VPu2rIucY7E44CBTcIdAEOige7aAvxWKAep1EDdf
-UWUV/JfQ/qWnwKb3cRWBZcM80zFrCrzwXSdsddUNa/mpTXlVZ27isdFqoetp6Iqm1yNQ6pD7VlAD
-hdkxej32fFZ6UA2XJ7g0sMWDQOWbBHeiyyI3NcoCGaoma1msgar0NSqfkTiYeNwybxegt2v0p3R2
-faXXslh9ts1J1R6p2Xciq9tqo3qKsW7P+2XgpfZO9ulprfzqYPOGpNxNUUw2qzyekzxBYAUtSl6z
-HfWbLLMavszlKPZlkQU61KOuurWNmZnHVeRzVc6rRqOab6Zkc8Cix9Lfms46teuLtq8+dK6j65D3
-JoHkYh1tt+Ubx6Pfst6LScaMmMCHWvspxKXXGxMdnvaQdijmcsFMygrdLiQpdutKQprVdSvEpQTM
-L062NlTDhRiapXoj2LzEImsHUuEuG4D805dAPSsCBGHomrBln5PmL/n8o9z0xnfrYE35panq28f/
-OP/aqfW5veb3v9/1U/z+6bK7bV+E4fY2nF93T6+8u9+3S3/v07nL2r817TxRAR43Uf2VwUf6wSMN
-65F+wDGwb0og9f4TFeF6BF1vvn4sqH0WE36ffi8pgCKUplD8loIQlqLPYve9pMAPFKEcGhOwgARG
-CAaa3hdJQR2QVKUUNAjoeFOIQvH1i6IgDgTnwHYRkZSlmEr6VxQFzEAceagopAqUCyoQdBZxkDeY
-gjU8VBRsCiked3QXLSDbWkjyIeKqfTUzOzzr4qjOvLkD4lTShugpqa0BmjIui67RatNdx6p2OUx6
-qo7rmo0lpNi2NC1wcl5sZ2QOa3rcmwGYvHGNQCdcOfM2Drw9Ft3Y2CM5Nnw1ejZtdzypINQp5M2i
-hwxvK4B3CzFjIKtF9WGMfRIOJ+vKl9Fs8v02KbnmNe2Gkwl11fKsEVUTT4NPscmq1Y5AR1WbyGyr
-hKguElB7xmPiUnsVfF3g3cJExDvpmvhOds2Csk1RsxsGao7KWBWXrWqma5lyCzQ5RcVucQPaN11q
-btlEhhZCu3S7KUz1O9Ut5N0AbCePpQwX8PXguhYW2uoy1CTmqAz2skGoO0ssnneBTPgCszhezClz
-OyJ9ejiZjmvat+ZUbvBNeqysOfcqepoXdlhG3SQdXBHxIDMzpmbHSjdf0NC1YrduuOpPBRDWXtcL
-Li8c2YYPYh1Jk5ftvM4Z4CJ/5gvR8ZxGmp4tVSp2fMGQgaWqXLpdPa5NcVjWHjA/aVf53iA/vCzR
-1DeHtpGT20kg+PhwYIkpz8ZexU+xLcwIoogy9b6w42zyxVNu9oimLh51a+yrPbMM8ovKC9q9AXVs
-9HkJFW2Vi3HoD01c4nxEN5JoPIZodrGYRNfo0Ccres6HmNpTMSQz5B9t0W9AmvDEPkDOY+yrxJZs
-hgS6XWK1p0WloiaCxotixgaoT2iq/oQ2JTAwNhWIZ1hydYmarfnomF+TrN9SyEcHUYmQlQ2yH+gm
-0M5FSJP3Tb+2IBqIOODDmFALh7mWPfbZGCG+XZfAgrp8qxXII0taDeu+aFU97VVq1HM40ZW8mNKY
-zM9EUFacFqGf8IsECPW477Cq3v51GP7ZAPauggQZ95/B63ebTe/Q9dvce2yFdjzQVpiSKWjqdwUQ
-qBh+xVbIERRVgnGAXxAUAfe+YCuUsgBT4ZvA6pgJAOdv4MoOBDTJAiYqnIIuR/4atoonai0g+13j
-kxRC3d2FfVZzH6i1lVuaMg4sa9wRGy2wIICYKU9Y6G9568xhsSL1qnehPknjnDzbyq7MFKmet225
-avD3l3TBjdXA2MuMlkD6QE4meu5AX9TVNrwybbtmfdkPJ65aPQi7Uo2nIURQKEkEPRJI1lQebrFB
-F2WC5As/eb9PICnBuitFc5kE9gky4fKDqFD9roW8KnNNnZ5u3SoAK5PtqMC42o2qH3fWgcNV85bs
-IFB1+w4S310ppvSoA/V0R5CfOj1bWN7SSvTBlCAez5Z9MNO43VJolttD6sxf4sWnO2UQyE5uQ8tZ
-qDg6BQwxx4gtZC/8NJ5NRQx5YKrKokJ91tf1sgM50Lyg6+p3hC1tqYeajyAwebXzbYePyJioV6ih
-9O1QdT5P2RRBtxsCIIQSpZa+NEZb1o6XBqt4aUEcvKy71r9ohaM3QBUvg5QUHg+5o7obFAjoI8q6
-ZICkd6pHo8UAQmbfMHoWLWV7U3XwcQa26eYhPS6boXlreFrsgMMVuQoL2zdqGc5m1FM9y9lnvKjb
-WrcmTseSTeIIwik7GXhDXleS09OUrOOrYd7oddlGUGr7mhzyYi5vFkjSmMYVL09SECXyfivX09Lz
-btai9ts5kUVdaJYw0BClT0DAVku/Q80s2nxkhT30dQdJiCjoSVu6cj2fyymc1j3jbwdh+g98GYbd
-0O1NshU4m7st7PAUyl2suvq4s7Y5nlpsnqMpmhdhHZI6l9C4bDQpt3Ap+63bl1spj+LcVzmznu2W
-NTGvrAUxovZDhBO4sTcqme1RWGefT1A9O8LCx0vci/SwD0s4Fc4NH9MlSU42ZuJH161jq0Xolz1v
-IzsaoKn9asVlcuiLOr1C3oWjQdT9ybAoILcJ5AoZpHTK6v/3oRV/IZ/oz8D1sv34pI/iIW+FqffY
-yqHSDEVlIK4YXhmg8HLAV2yldw3qAiqYHJqeUqh6QefgF2wFdsqgNq1AwIYKKCTqQCe/EFcGRTLF
-4OsAeBFcQMhfIa53ha4HhTDAe8VlCqyT35Xq4NQ8pq3JSOulrusshuBOIOlZjojh4rbEoAjnGyyC
-6QLqMPX9obiv737Jeh5W4KAj4umNJUohrmAJZT6sgDg/vnHLJB4wqTMsJkP2sunTT6ik3F64qpL4
-vLTbloCWYIbnK+9BjGtNP4BXurp6vhkKMDQY/mJIEH2zpshDOQ0w/HU6ShAD6hlV16uqQ3rIPS7n
-HOS29mOd9CDX2GoChakYsT9ZEjmGPHJIYvNhnUHYCUD743GwU3cqw2tWTwiqC1W/lkErNSRnoVHt
-qE3psNlx5ts3SVLiT3Le1iKfC/eWCiMOCQG9WpuVBpCoJ7QVIPA2TZmXGJiu7oBlBi3mjfeZnNEI
-sjG9Y4sSpIpL1fcgQXPfdaBgwwa8LkiyXIHYsy456Plu0G1VJRtkp5tfs1a2M5QOpkGmsDsxX9GK
-38EMEAs3yNa3bZVnvtv6o66c8XnXiPq0nyz1WT1h+wYS9PUZjZ14mzi5fKjNVs9QNqhEuueTGewh
-iyk+FCCUrJnre7lLyqWvddE20zGET5Axlezos60YhIcoE9pFp9XougzFwr0YBYHgo8hL0UXY77Ff
-EqbnZJENFK3qRB4loy3J0SzQ4i8gv+hBk1hxgvaxidlim7rdNYrYTYMGEF/MpArtadV602WEyOql
-FdyFXYPIBjpoUVVQchoWop3YhrOiWdc7GsutAu2vrKvMItaajJSduFPOQjEdEmAQH6xv8HEi8FRk
-vN0Q1WYaBNbopfSiVxnfKIivZgRlFvT4oshkjxqb2TCF+qgjhSz2rgrVnAvc0HcS3nQAhZyzge+L
-NGnU6YDivJ6tfSKnLF3JMVZcQYm1LjxUu6ICoWpTiQQ74+42YvYp2foRaYVrnGZBYkheelbScyjU
-pVCWGKHGlM2suOGVotezXOWrBGGTt2gqVu2hdnfl6FQej8vo6su4gLuDzGsn+WJZVlfBOkQy6m5b
-ojv+/wbfKaDhv9cmHr0T8qDL4T423M39KkwAp+GA4AKaFoAs32H1PXkW0PsNQoWCvnBoObjrNvgG
-8PIAA8JxBWQNZigoqHwDeH5AKfBpiBfQOMGYZOqvAHx6J7g8hnhJEZeMKgo5I0/vFv5QmYAqbT3Q
-Bu1wEf0Oyo/V+WRtF7JmGuwp1Hig2ga55nuojbdQrQtR+l1iSEL2SowBausJgRLD5sY+w0E13VlZ
-QhEwmHZ8s0A8aXPXdmZ8KUamrlHbNHMmVFKB2gA9FcXxHJ0sdUtA69vPTeKrowDgHXXVWjSddFCO
-ME4nM3CjvJnYFnU71C6+9JXz5BNZ5ljunI/jrpRrPAoFdAydrqGvdyJRxaH8LH1Mn1WQOz2k/CyN
-rJSuHcB2MafH7LN8Qu+1FPdZWDEDaCxOcrccjslUpjuCK4N3xtP5ruGBr9M5vHEJ0omioAFDraBY
-QGXtC4myqQbvei8/J6Tz5+Q0fE5UW2RKf9hPEyuPG+fckTEoaQ+LuZ+XvSlrBspwa6FojZNmJMcQ
-IOoXowIpYueAFJOsqns7gMAPSJLXa0lfW2ZY1o9d6t7OLZpd3quyz1YLVUOQWjp8ZQp4st2gOrTm
-0JYhUlAHNrFznewQoG06vYGiQH/c8LsOhaIDHA/sdpWkmXZF1WChK8lqspMJo7OucF+kuktK+yJY
-lXwi01D2OweyBUSEgsdZA7MH61PQE2xSt9NOBbKRy2kc2VF6V3tSrO6PMej/z1JabHsu637IGbTZ
-rRnBU7KvvVFnzUKTNYe2icru19as75LQmCWPAFhXo2uW13FM0NUAFbgPIS3sR2jtUQCIpaevofoo
-CPBiNO1t5YrLWRTVCSiEEJqGddjjCvMPkFy5s6Ktt5CZFENELrulr7JU1eUhRJXnJiH+yMTSZHVp
-XrGhro8UDgbaJxq3G6DAd1X2uPiEVU/OgZq8mftwU6MeUk48lK/buSkzH3i3mwcAdOjL8MdoHOje
-o4CPK19eg2SU6gKtydE2pBeodc0zRasVimXrjaq4e3F3W1WLm87g87qDA18phfZDF+1Z0pQfi4Hd
-9I17BYXr+hgymi2XdjscOlxOWXBePWdzhausCps5dVu69ofdsi3vt3EZDslYNM0ObX36LEyyOIZq
-zPwGiMGU8aaCIFqIcMmwqc5qw91RO8pz6Dpgg57uZLkUEj+1ymnXQsX0kKYrtAUI1w9vKmgIMFCG
-Hae7ckrMLDcoryRd8m5IYBtd+arpqiQnPQaPVltdP5/HMdELawFoNgOCGehZmVHllicNMWeuoTBN
-LuNlLIc3TVFaqMekkHpDORJSHC6Tt8rMoIKn7JzMat2Pcl6yduv9a+hPcntoNdobtxbdD4jwP5v6
-A0o4h/PxpwHs4btzvwewbzPvw9d9qx7kH9CTDM0TkFB8DV8YwzsZCiIaNMoSSlPye/iCVj0B+Qq0
-492p6Jg8aNWD925RmkKtmwMYwyj/K9ELuhOeRi/ImgThd6/yYtA0KehdD6MXJtYQNfDjAP1LoBaz
-Gr8DyRTq39DZMFx4X5Uia3q7JSczSsI+OkwyL2o5QMmdtkC9yujuCJ4FqqhKtbljKjex5ImYIMQZ
-EEAvFnCmLOnIs0jn5jVoIDO0gRTQ5bZ1o8ygJNe9rL0bz/E6mgK06IQ874BTJkCxoZh7uTg+vJjm
-0boTNyTLdr6BvA3+AJWsU1F0CQaNO+HFzQoEfs/jlhzZvhP+TCYlupqhnU5qyctInyX9OrRHZTej
-3JGKiWMboTNsTnzcjXyWeOf7sks1Lzh/EwNJusxgU18hWbdwqdrAmRJ6uRRcthn/L/LObTlSHO3a
-t/LfgCZAIASnQO6cdnpX3lSdEHZtEJLYCwG6+m+RM9PT3fPPF9Gn30SfdHS1XXY6kd53rWctjxBS
-dyyszMHQob+wNvZzSHbp0AItoWF/kCKWZy/pIbETcHRjVKRKOvqknOWZdeG9p7t2R32/3G8MxKma
-VZAGxuWj5FMGXV1loW9ABBZJPjUjhl8DkIvE3VFga73FEqRv+468hJ4+1Kzq4CP7d+M0+XtdklPv
-QeWBWpZTCi+wjVdxjNlYQ0UGhFHBATo1wC12cNfh0BqdBbY5JfHyEU/kZhSzTPtuzQczv0rMX2da
-xdBq+nbXq+be0v7s25Fhp7IH0eqTJfGQj6Or83oM82DFRF+pannvCF/vKzHYU81j8cZgNhd5EWj2
-7Yrv+JVWP2BYVp+9b8je2JVl8+TseRqG8kkSJh5jzeDjOITPyLmEwb3ewqYEAipYSbCs8aq5Jbxe
-0q4hdZ39HugZIHb7kLyj4aRpY/i/Az1gg5qDJ5r6G/EgDyYWW+WAiQIzimEHZuZRppVYwyORlXn3
-KqVeqFT6LEk3VtiBO3OL70o/2EURGKq44ToQLKtqsxXLyn6dEgpFzyvBmS3K4IFSkazvhroqvbT3
-Pfi3cwATHfNDG6W9AxuR9nHU5GvhD++RpkEWD2I5RrohP6dpmJ7Y1E5ZUVbdbVcE2MZiOtnj4LVj
-hmlmyrUweCWw8gbZNI54D8JiOjez3zwZLadbD+ZRDhZJ5l7bqmNBS/1cEKmrnJCKXJToxi9B0+qc
-9dWSxayMj21ZD8E/4CLmDc9ucdV5Wdz4gDcRO7tIzvDiV5LSHlrCOFq+81aFyWaJxN5jwfgzmFaQ
-U3pJ3mWtwx8yDKfhzgxUcbH3x3C04BoXYAtfvDmyIwAuskbnKIn7val6sFTBLmwqeYiXRd2sFpfb
-0KnkvcAilgVa84xSAFZJDVwMWkiQCvAjH7D/90H7papNeO79Ve+1osN9WbfrHvPK59C752o2N4Nc
-D7Q0O1lNeU3HizcMGJ2hDS91dSGKN8d6GNnOlXzIHKDcSxfy6a6oNO5abZ7xk3dP/hCprKd6gFEP
-wXnCfvuzEWNy04WlPLJi/RJuZIEvCjheUkw/oqaZH5SY+hvsBrs5bi7NPIVfrJzFL6+068950TyH
-clwCzfPKs1tF+Ti2YAxkxSmmL7J+UHhEOl1B1x772cidlk0H6LICttE3wQnH53B2DWalGIfaHlAR
-poCpHekXB5QrIzzuDnHhi/06hNGtX8XspVxcdwfIOMHKPLM3rNf9noVf5uSmnsoH4QORqbqe75JJ
-PxBNzT0XrscnEeIWZhKoqdmbc8WC+jHSll0wLpPHlk7dscWPJiu1LY5Rq8p73Gngt7B+2Exh00v5
-xMu3IYmHo3XE5mBSwsdwbeb9letqXehWEK++e5bWV7seuvAhsIkHQR1G50vVdX42LGuy7/E2O4Sz
-LPeTK9UpqEtyQ4dluQkaAwFMlXnZtAA8udiJOapx6IVh5gtFbsLYRPd+RNoDaTB7Q8tNhb/8mCS0
-pVlUx1HJg52De6nLL5il70hh7dlNtL6NK+EOld/2mVlgU5QLLOXOS7qsULHc8dBMe068Je2BK+7A
-quFBJw6MHwd9fqQrTINY2DXvmYKhWMpXLBxJxuXIX/ja3UDlhKnQrLkhxdDCdd7eioyWQ964qNtj
-CqwV7lwy+lljJT/XwxAVACS9pbhUs1/zvGVlMaTjvFqS4y3mfzK+1CdshSo5VaJg1avfh+4wFYDG
-MtuXdsemKcCOxVQm52W8DQWNT55d3a1ly9x+WTip6p1IBh1BNCoNBWa/JknqAf4wzyWg9B+1X5jH
-CNzr02RKw/PGeH2dzVgoZKqUkQpMamfno8OyO+aRnIKPWMbxXd00Og0N4z+BHpcCTjiehQuSAbhb
-EhWJbKVj77IEFPFp6hL47azvGh/DCSp7cGaQAhr7CAcjDEQJQKoWjqWdrxg4IFkHXy1ct2Gv4R2r
-PW3xPjj6hSw/Wr7YT3xXiY+lcEpaAIKVAYkbx+eFetCSICBUaVAtgAb9anzwB/eDKPXci8hCJ1tD
-8enZlhlwOyCP4EqT+EljUz2C72lxoVbwX9eFDzwtQq9R+yQyoKRqCX996Uqdg9sJ87mL+JdiGWt2
-bg1vPwrsw8hFwBubUt3py8JgVTmmy7ShQVOk3izUlLoGMkChse3TOVyPXmnIG0ZGdSTJLF7nkI9v
-1FXNg20gQQjplh11xXJv5sC8eqtnAAd5YW74HBn45kCi2DoGP6QZ1WltGa5h/D8vnlLTzdI1eHOy
-0H0m5XIkQMH3XWuM+y9yMTbL9j+rXLvPtlmr//eHOqLf+RjbB/99T4j/FjJYubCcE0R7wN7/QeaK
-fchYyP4mMWza31Su6G8cjsf1P0ZbLRLFZ/vNxojicFtFYDhDHEsY/yt7AqJAf94ToL954IY3YROG
-Cseu8vs9IeJmBbg55F1Ffs1TMGdDo6tXQUGUj2EpXkUFeLSJA3HLafSdtNVLNER3JcU9usx3AfiP
-pMGx2zL9tgY9EhINSLK8M7p5tv7cHElrlvu64YdBWChWwiT7QsTzjiLHk4GK+Qa6ZcpF5L9hKoKY
-VXZLPrj4bm5YvcOjLm4TUsBJbhDtkBh607Au30KMhbntovDoAm3zGmwhJhYh9sxvEQvAYIIt32Bz
-0at/FQdWr/f26yLbjBUCvLVS7tLWyXRBDhiDaJUsOW36h3r0JpZJeDh7viKf4uNyf4lLYDEePMQD
-lGM8qSu+Ehs4e8T4ChmGhz24QD1nblw/Cj+QuVjZks+6q/bWq/xnhEXirCUqOvRT4J0TVtSnOeym
-U8EDd0BAYNxDqWO3iGG478x28jPSLJgwX4GM9ZaEfevrdslHQ0iuhpI9c5XwrIKJcVclzD56gScf
-WzasCIm0zVOHIBQ46NY/tMzLTUjf+yqBgdofR9f8MLwL97RWD3VMkA1YIb7HFOAOqfQAPQFKuq/j
-NML3NAIdVkO3ZC4Ix9xnIT6ZDsgxGECmz1EVZEwO2KoaDUC28Uge15FKSeTdBpXnZ+2U8DuMiZ+x
-aD+FAjHsw6kuPNzYrl8YPpirFNvQkHWu1hAxcBs3DMLGrBZYMkgOyX4UKeso7mPwASkMk5tBdGtW
-NGudDaZC6MkSuY+6+Gek/Fep62fnoNYJrEpkBvsNG7xMYWxh4SHiFhJTnAYR+Y6F/jSZ+TLwyO7A
-UHyzvn3v6JycqxkomBQgfgrTfneWqmyM+unIhq57XUx5z4vey4og+JxD8ZWZ4CsJ6qcaEndaNy1B
-0iecjkGkEA2ivsh6Pr+zddm7VuGua3FLGXgsJwy3iK+M3klWSZGWcxHgVYv38II+XTuOe4B5Mewp
-7Z0rvGvP3WSrHy00wX0w+8XR2dnfWxp2eSA7shfB0GJUnarMw+i4d9EUZ3Vdy0db9cnTzOtx32v8
-adWsy9dIRjSFdO5n49hgULOFmG5oHRVrHlsa3w5hS/aIcEB+dAWWxQxfuNsFmzRJN5ES+aEeKiyE
-S13N9OIGCNtZFwj+5ArGswIszE0fGkRA1h6StF6lOU94GFnu19A7M9Gz8kuYmBDJGbgFYEi64k1O
-c1Kmaxn6p0HU1wGCzikJuuAAsX94gRwQ3Y4F92pE1CKE+JJpXO6GICh3IzJrtyFf3LFZZHUz9ZF8
-JJixcLu3BTnhLE7SWvjuAeywf1lrFu2Tbp3xY6iiXQIhWZ4x5Hh561v72WuKTWFdHlo6yDMPsNZm
-Pp6PY1lVyy52VXWpm9gdMRiZHVvkr6GfERZQnYgxiAIjQ2giUvMzzoj5GbEgd+y9InwN6pCdWWjJ
-cQqnMQcjonam1ctNCwfhXU4mfF0l+f5f4y0F/6u39Pt6nn8pc//EDn5nLQVQ0a6+PG5ej8e/sQOo
-reGQ+GEthRw5T0D2v126yLajYgCEQLI1qvArDvuPSxfaHFT3gG04Fxx/DmTrL8RogSL88dLdqCwf
-llIQ8K0ZJNxMrN9fugNBntWy4NBKyNB5gK+zSb1h5u8YI9tzES1iOAH866AX8IXmZVnADue9/yGg
-fY2pX3neLxO7aDisbjz3XG/Ry172F8kDMx6nIkgurjJRmSWL1W/LaBd2qpy/iMzMw4trZQG8n9XV
-W1mSSj4nYyBdhlUWaYTJIjUQ+S056BqhQxzDEIqMac3RBGOlciy1y84l9WRTSC1gKkNoNodkXHGR
-hsAd7zivOp2tHVEHXeIbSltvXC6+qDqw/dhsdLXMNxQKZJGSxU4PPNwAeICOtU1LxCouo4ybR0+t
-OhesCz/KTka/hBz7n6px2uxhKYWPo8bNmBIfO+cyUoLDxifR44gd1983IWuOPVuFSjX4353WS/gj
-6BecOGXV469F/lO9TGGMWdxr+uXWrlrvWtm5PbTb8DuLdfSWIIHVp4yO/m2rPHyzjFcIA2gPEL9n
-phko8PoNCQNvOVtEUGEneap4BOgEFXRyDGiGDO1bBAHzq0YIKfOl8qH/x90vLYc+bRVtTnOr5b3z
-hvg+Lov6gSIxeXTY19N+aqHUCQtagFgb3pfURtieTf3ogE4de67sPVKG+KlPjo8fABMl+Ie6Ui+q
-idVbVI7LSwJA+eDCkf0IIFNdbFOyfcgqZOCsNeXPYgV0kU9LSV80012RtokOwkOHR+YlWpf4RTZ8
-eUduQt7CasNQBT17SrJ1LmDWNX0tduWs7RnBRrj6sB2nm4T3HuJr8LA+6DCLO9YX8tiVUXdfT4Pf
-IsUnmwDXD1/fTKPiDNZk8IgAV/KpAImH+6Zr6DcrrPqB64x8YuPhv+JIrkfkJrHJuFADd7H+W6di
-/36Gxw8Zo10v87i0X2e2QFWZnc4WG5R3ZpEY9bwNO8tIFcQ7hgDoFuxq5zeOlyxMe+P7j8r1gDei
-xoTfMF1RSHblMB0IbZpXGMPRqz+Zfic6D5KdjNTPadV2F0smH+YoKvM4VvMX7pv4yXZj8BKWZpA5
-wBZYZzQ6J0XSfQQQ6+4rknhJWpQI9aThMEIs8GjQviEiVOwseQy71VxWuGxQs+v2xrohvBfJEh+B
-pLlTz/35+wR4/zRHnbobR77gDvMSOFRS84sEdZ0KEWAZHm1/QXI28pAHQb5410DG/2jrVR6x7wEQ
-7ijBhm2XYH0FyBfuRWGbvMAy/oas//xrkGPyRj1A9shusFMwce2yBcmNcdeTKDIpqO7qwddS3FOP
-DHe1LMO9kR1mN+WB1YvggL/JHjyy8GbPHtplKvM5UvpuneLuAb0u/X5qE/UFO2b9tdEWYGlbYUuY
-Y1V150IvvMaULPmzjXuSCi+I+LHEPoWQbwkIX5fGfxW87c+0wZMEeKAETxPZw9wqvUNidUVir6Lk
-FBXWCzPLVrqmFC/rxS+SegRa2Ldz5te+fq0gR7pjhTn8vwfZ2/yh/7zs/qGs8N/u3e1j/8ns8YiH
-G8qBXobQh8nxT08s/Btu1BjFMT6QjzgMtpKM33hohtsQRB2C7dhBgVP/btn1fPyvuMERUwFOzf4S
-swdS5M/37sZxwAwDdY3QGaDoP967AVKwY9hXWTL69SVQSfKLeiuc/JbOBpdP1c06NViCip1CSQJy
-vaKlz4PziyVXY4KYrCftO6Mm8FLddgqRL8Lsj7ZhokUCdqw+bC0CFCJAAhxvZLE4JJ1HTUhayrX7
-YhSnS1oQgkAlaLZ3p+JxTl0V9S9NOJXgRuq53bk+snUGRSZWsKzq4qOKqPB3VVOY25ISjjm783GY
-LUOyLVUyULetDcG/iaHsmgOSj8UdQQId3Pbg92K7Hl2881eFMOrKgnhKQeshVecwVZ1UZwncIhJ7
-NzjDI5rXtZXQFycovDuvqESTzRbD86FgTg0HAxjwEZsgwgvL2AB5o6Vc8DKBmX2nM5YXkHuh9vcr
-bbc4djON8NXQZoEzkZjuZ7lyO2R1s854yYvV3zGsiwl2y2YButxXX8eAJks2mqJKcCzX09FDhHNJ
-2xIFD/A3FNJkfYT44w6hxMDt4rJKIE4opOkRntCYAka2vveMOMTzVELA3EyKI9ii/UYcOiQvupys
-5nFYQ+5SYOrdr3nsqzZ3s8TXDia9Dy6mhOWXhonoslE23okX+LG846uZn0ZF3XcKaPq8lD3KPuw0
-Nl8Rh/HvaD+MLnNmQDInIMJ+6bEAyNSWSfTclUE87Cjt+FdPJOZUTgCuxQJn5IA+Ff5DFt5nW+i6
-3Q1RMOeBivwu7xHy7TO3BrwESWT6z6ZKNOicSLI7zUOFMg7UxXxbS9zj5xEDRnUZu8j/pZDrCfbA
-F5PmGI18yyMmyeQjidgVzzp2FLxNRWKTDULgDxHbgykb8RpNBypskaHa4n1r66DOMtZwhA7dIkmq
-Zx/WTiiBsZxiNvRNpjyDLGm5MurwoUHwmsDogTEGBXkr3qjRc1HqRcidL5Z7LJ7Bz/+eFQen4n8+
-a68FQf9RV9wo6L+ftciecKD5W/AEGY843paMv+NzW+djtCX+Nu0Qi2rwr7MWaEIALjpOoiiAHnmV
-A/+x44Cs21TK7Z9tL9qSeH9hxwk9fGG/x+dwlqOqmnssgr7IAfH9CUCwK+YmgkjbwjyxU3iO75C7
-RiqXWWIfy3ja2nta9iMc4vkUKMKOKJOYDuVQLJfGgICVQVudyzGxDzWJxnYnQ8zj4UpphifdPtgJ
-+enIRfSGrfMmqpNwjde7xEZK/lpxdAEL6CsMpP3QTCB9MetB0neg6ORNB7PsdsAorNKxoevXxtB+
-PsY+xjgk3xLNMbxzOJBxFfl3RT2EZDeo0PdvNWXTPeRcFqXMuPmlrqdiD1K7ANYM5SLpevV1CWKS
-V97YTQ/VqtfvmOeW7Twh4r4deP3ix+gUyjCwB4iReEB7Uw/g+VuvfOQuxNShaaWMlzCDL4pzbkBL
-EdQ2LT6oDoXNq2Ut9kUIvRKKogG1pPmQE+T04FFX1YOlgPEQu4aFJppqOULhD5/qxG29IQo5Qwyt
-AscI9gX6JZZFYOAsYJ53bBnXvRk4rTPqQxxN5xorDgkigEwTkPCf+CFHtzhLEdnjJSlOFsafy3zc
-J49hDTM3xYrCDmTtkmpXItMJF2Jeo0e3jqRJh3lE8wsDm3G7TrJt4Z6V8U+UDLSfEjzzB66b9a6f
-QxTfSFv67LCU0XhxyPKblFrQwyjBaGdkkyjZ8sSdGn/1AlVAuITi8Mnr4uDNtYa+Fthh2hz9I9E7
-APYR7TrAKg+DYm2yn6oq9DKO1bfJWDJt2jBdxQeKaKoj/KDhlYQevyvFQsscXmiFyEzdkfo0LQXY
-6U7PBylxsaQUd3iYy47jdV3JehthgzG3ZFFrsAPyuGjYprSDAlvM0WOITVNnkBTqKJsWr26PKCqh
-QBGGWLgs2poUdoSP4E4kqhe+zageWnZ87toppyNWn1u5ojAA+St1B4LHwwWcAMvLJh8idDr3Ret/
-GX2Bb5QWcto1qAvYh8LTHwSYyJ0HPGBXT3CLgdeFxR4QRAQ9ecTPsXIt0l+QCE+BqOlr2Lf0pQhZ
-fS8pfhzTPA3xZZ5roAE9kkB4u5RlBJS/hlDXgskQueeJEZ+hVpCypWHRDVj7VeWkRSg3lWYJupRb
-LwYzYfp1Pvh4fQ4xDZEbiFxg3mgVEewpgyx45ve2vClXvEfTQtULPmnL911ZNN+Badbftde77xgk
-sGFXSVyeqraFSSWAK15GwQKo8xoPWslROzIweoGsKI5lbaK7BPKGybRfoAIF4944AO8fgyrnVMbg
-Si36x7LSueYXiQgetz5wRXFYUEpS3vFJ9OVDM3soJcACZF8T1QU3Ucfme2ohqKQjl2hmMkkf7epW
-W7HHacG+YHxsEJgSCATFGMAGRLkY+JCSi3DOfbSiyNSfh+DdakSvwYaywOUNqNQb2ahApmNbgA2C
-MMDiY+ziEXVPSF+dFQzOPkXnwYrni8JfuA/iDhoBaAV4tTh7WKbpFrBXJESzjkSFyQO0F57Asu4n
-JHeLqW5wCoJwvYsZJJ10mks0SlHYAzfWn6CrJs5MLo2moP7OOxvZfEQtEkpsUB6GlF0Z2GXYdaHy
-SIYGosbbtagiu0dWFTwTa0OC1bLxn5OurZ6pFvCOdW1/ItSPkJ1DodgXaur+kcZ9jdhfzGmV9UBO
-yxu8+f+/lRa6nc0eIyA7+nRt3q69Fgligcl+UBiCMr39TZk/dRABImQNao+Vx3UagmVfF0yeytmW
-KEuaxXyC7BX1+whR7txAH7vElRw+8fINZ+G0fK+DqbqAdgLGjFda7p0/qJ2Eo71XvmdvYzt7J88b
-g6/AouQe1RzLYzSNHjZ11DFdSETNc+tcmwftgDKopvHkfhUSKfFw7p4m4aA0t7T3kN7z2G1kXEdw
-1tP5ky3anUflUbDlMH5quCOAT+IInVm8vswiTl69burhlKFws7mljEzVc+NUuzyJBNbTjQ+guzzh
-/MFhRabBfidzwPC2bNzS3kagGT5LvM4XPOfdk4kn1mWCU5RmBbJFRZ43Y3JThM764NvJ7idw+lPK
-O8Ts18aCC9SBAjkDPK9mpwhXc413QtR7O5TBBecJ/tKyOTegiSKkVQ6j7y34LTCFgQcRBkWZWm8t
-/X1iO3SBQVksHj1SgzpDk1x964ON/6rmBqVyleD6JQ5FFxxJrSGISCt1NodL+2REsPxyFdDbXRk7
-d6a0AEU0d+i6yaQoqzXDv3YtamnQcbcPy9WvzypqSfDe+1F7N+DZ6EBd2FhmRaHWJzSYcT+LtI8h
-hIhiOEqMEGRfhtN0kLF3/L8/miI2gXIbbN7/eTD9429h+ZcK8NuH/tPvBg7LtmhahC3b4yGW7H9m
-opHI4xsWiwBbwuBf/6YBXJFZZIuSbaaN0B3zLw0gQQ7QQ9gjgcWIqdWL/xIYGwR/AmNhByBS4mMI
-9iiHRPFn7Z2iCKVx07rvQWg+OK9MviFrhyTZuMQNOggQN2pP0keOQLFwIhfYaO4R/TgaYam+ISot
-a2BeYeX3mWQ+NO+FTTWs0xr1a6g7G9CwSJEYvZ/QtXIfEm/MUPMyHZ12RqMVsNeop0O1A7DthosW
-mI8xz8R35Junav6ilkU8AwMHtt6HGkFaOq3NxSHFUON+w8OGjIZgec1D8WIk2MW8QrfWMfAJotsz
-cZv/HruTGPV45B0oppCvXgUgzgvEPmKao3EK0L/N/M1tkMB0GsTLvGHJ5SaHtVUb+LuB+MMt3ZSy
-5SqaoekOAlqwaWnzVVbjV4nNG9eAnFxYusuyaXDdpsapQgu4vJ2fV5tWB8bXf52vAp7YtDwzq5gf
-OZ8IslczfyZX2Q/VoJAA0VrTPDtkwKq0o57+aje1MN50Q+UVw5MHywGVc1AVq6vAaOEQ7GF3TG96
-0x8RGIYUWfdQ3lGxN9yx0Ij7etMsV3SOmnS9SpnhVdYEmwaFc9M6t0aSN7xV51+Fndq3atNEsYlj
-Et900v4qmY4QMyCfbkoq1PfmA7eqK3cB2ixAJFS6vyRow/kK5QcRbxdFF1ZyBAjMptSiUFLeoTyC
-n5CQm78XTeBOSSHVqzab143hhN+rpikeGkltccAIPzY5qvqGOOe1F95UYcl/jkUZ/WKOJDZv4Qqr
-HFcs2GFtjPw+JzOsiQS2R74JUmC8uhiI4CQTKCyz0RDsASNFpAO7C/MBJSkacirQ5Yl+sYVtH2Qs
-xmHfoOMpHQONDjktFu9g0DPZHFnTDe9sNt6h4xpWaW1W1D1G/UIzUOfRS5vAgsj8FpofOhS53FEY
-KZimkfbcI3DpkDKhknzzSw8dXVMU7EamVswAdinvJjbyY+WaEYKVGW5LUyzPBSqW9ipOlucKRSU/
-adJYhB/LqWwyMJTLjfbAiqcarYYPpU4E6gjxptZTD7a19gqZNXRePjRwqRtUoy2IC6oOZXM+Rocg
-q4htM+T5gQWQBdxA6uMG9fAa9dUrMMPmUjY4D3IQXfxuifz+dSE2zJSf/Opggn+E140hQNQJ5YHX
-TSKIXTvtF5/adNq2jLWSmMNVQdg7smFYQ9ZtIxlhYL3N25bSXReWpAPrJ8zaYIvcdplkqfjPCurf
-gc7o6MohDWJLTQZlLhbRXnZYlxVri2cbd0fYLD48GXoPCvOsTFH2Vz0RKfuTFlF421+XLDIVWLiY
-LKLHNgAcn6NTEysZCsEInBDXP1RxYi7MyORxuq5wxDbkJK+LXeKwVsYOc7zZVj4e9Nj+7LYIwnHD
-Tjhe90PALdgVt2auU4+2y2GHd5i6eNtG6WH3gEZ1XTT1demc+Rg++VM0H4E4tAj4b/spuBfxUFrs
-rF0bbpbkClYbWeC0BMr+sEqkDOR1zR0i1FWEY1B+8Ose3DeFBLm7bcf2uinDqg2BV2zr83WTnpcE
-WzXAfmzYOMuaF1PjgADLaFDXasO6Hr/4VQBUZVvU4T6IvIjWcT91TbHHfDZjm8AQjUrDabrvrxt/
-ct3+PTgQdx60N5khHa34fvQ8lNjWV91g2CSE/qomtJuwEPhtJW/kVW+ggHODcxHG0u7Q4VAhjFWU
-7KdHTPtgdKVP+FIt/D7uoaFobjYnw2y1NNHWUGPQ5ZbkC06yFsf8VmJDyhI5rALMR9qsGuZULFGW
-eZyvzTd13ACg8piogEPGVIyZqo39BTkUnTn82p8jrl06HpYAfvi/P/P8Exv4X62P88cfftXMv8ae
-33303wcfDCoh8GYA6bAq6FY+8K/BJ4YQB0Fus4830Q1a2T/Mj+0XhMEsAfu+RVq30u/fzA/MRD6N
-461FBv1dIAX+Unf3v+VZAR1sXV6Y1rb5CyUzf2ra6vhShtFcHVCn0pc5FsLkFDmOi2HjVbvrZWG3
-e8PWC6Wpul4nzEHMstdLRm33DUZIkuQtF77Kw+uVNGy3E7KOgHy3G6u4Xl76epENXbkUB29ei4du
-7eJ7IeE/p4LM6hXAXXycN6sz2UzPPkTJLsju6r6iqHr1N3+UXa3SaS1gm0Ya3xnK7cL2vth8VdqU
-/Iy6gwyMxCjzafNfcZXHT3zzZMuQwJ2VCsDSMuC527zbanNx6ebnRjC2X8sAHq+42r1mc3755gGr
-poAdPGzOcHw1iaECzW+67IH5DJgZdqOhJISQs5nLBgf6nbc5znhVy/OyudCUryvIXjjT6Kel9+CM
-fRRrwrc2BCwumrXWIzpV+K/JLOQTQVv1Q8IZ+wYdBMfYiDKMTwN04xE3BeJTTefe5qtlPtkE9nm7
-Oekm1uoYbO76Mrr+o7ha7r7xatjv2Hr2MNMGkcvCja9uIu1LAijya1fWEsQ9PAac4SisfaglxgwT
-R2zJKkr7W9gatzXoQJSAN1jEAlQLKtzLc/Jsm8bhg9AhcQd5MZLoRRnQVB322NV2Le78Sz3O9K6N
-yZjjXB7RdawQoJdb4AaQO0asbCw0/ZALb24DWic/fTDO+azK6q6hbM6bZOUyd/H/kHdmy5Eb25L9
-lf4BVAMIjGb9cpHImfNUZL3AWGQR8wwEhq+/C6CGks6V2tRvfc5byaQkqWImYsd29+Vu9DH3hXLn
-pD37QdjizkCyNnU4LYIM08jIuPeELzYqfc1ow3Mxh/XbSkM1s7bs4Bhm7FP8BnaAuikGBcpnxI3U
-+6ShFvgBI18rpxlUNzLZ9Qx1m7+NslONfURWaNr+jETNp1k20qsrTXBfFmoWvNoTmt7TJwbVyfJi
-3EJMHSXpg99hqLEVxcF21mT1YadDfNQ7aV+xsQnfphye5nZ0MH1yCZ3P1lQmvV80TZNsRsuOdd+E
-RqnjAgdP2vF++t50wvpuq3Ucfw3kaMeEsiazPsCcA0Qzp0Z4yQQmbsKe4ePMIq9jfc16VZBi9cWQ
-Q+1WFJ2Uj3Ct/rbsBvuIMS7yqyKCE1HAJVGyaP6YhFq9u4rqvvVFV7F8wtXzDW0senXUrnCZGBz3
-BnRucpky8u8SMmd4eIGSXYjGmtttD5tSBDYp1kCN8qNthW66GXONTdfIApNECkB45tyye69GNQt3
-8RAbV2Otdi9hzXKZK30uEB0nNz5xKqlM+lyConXEzJJwJuG2TJ4a5t+9sUyjldlL4JrrkNos8yrD
-ne3F6xALv628iZbJ9j/naCOT+tcX+j9UdP3rwcZrPw82eDtkwpfcrMUfVIT8Xw82/Qu3fEA72OY4
-npZE628Hm/WF/3wx02HE021t4UT+amG3vqza07JxYNEpQA7/E6XJQs36WWjCOGAYLjC15WSFcGks
-F/6fKGedUnFZ40FRmyrAZstJ+stiLpXY60TYpxAiB+cYhMOFqOrQYAnkuNeMyvW0NVhDHNA61StQ
-NumF2QX9TiZssljeuxBewXtFq+Cs5v48ZliyuX9VE+O5S2LDMSHu3w1qUyd3ImBz/wgOkMhQkgz6
-RsrAuMwSdYy8kbXHuM2Lue2gcOXFiahb+7KAV9Bcw2a8UjRruHd7xyiwbfcmCT/YGJMHPCaFXYC2
-5WNgUzrSf3kZPRlzBHl4WKQYICbCusadC6mqU8t3gECKvWEwniTwKzVBBI+t7MNt6nNfJZNAfAna
-6YGcrltc/0yEJTk4YBtu6ty6Qk2wxNUsnbHfqKzG032FU7F5zio3yffAga3h6t//88U8ZlO0+3ef
-rp8r1n7/cP32wl8/Wsx8LN5ITUIswY/MLPq5LMOM6qomyRDiSAYlCe7vIi4lPqbOh4fg+eK1WDtn
-fxFxKdleil54FQMlXhf1H82M2vJN/vjZAlVoWppKgoWVnrnSqH76bOXDKCO9STdqpNXA+InyecSq
-I7+0FOfRXpA6I2wdXAxQdrIyhrgzOY1x2a4cnjFUYPJAXiJV0EHqkTHInnml95jxGKCXrVQf8pTu
-oU/047RcTzZFbvTThbKygKqVC6QKGSCogWl5wRibDj5s4iDYxRnmw0OL5QJ4/EoaSnEE595k0DTT
-znrjbtTM5DmQmAOCgR44kFlLbKiN32ESLmAGOe0bcuf0kRddf9+yKS/3uZKq927UWe4Wc2R4zh2d
-PEXatbmya4GBVycW0ugs2Ojj+DCIAfx/GS8HYUIepbmIE33GgGs0mm9WYrqPkgg4+VA2EYUy4Je8
-xK4RNKMg71nYhzUOiXKcKK5wW7+vp4mBx9Tr5DYca9nxHEnCr3MswlsRDua3ksYNGy2on2/YtqEZ
-dZNGDtFIw+SdB0P3bBFCfXE6coGtqkuWENBJKi/IbbLpMVxAfT/jHPAi12YDYpHnPbWlNTn7cTCw
-OxVZkT62/GXrWyYK7VvvNG66SybF3ZvMnHdwdMd7PSjap8Bto+7A8Bgt7o+kajZ0Bc1opjGqNUaq
-QuQgIBmPqdlpa3y05BH5+iPDHN5hYCLoxSpyGxz/e8Y7+P1G2uvzOWTRMW0/0dqzOhWoX5oeEAL9
-O772HHMJAb2hEST9K8q2GUrrKtel9vBJ2q5xb1LEMBba/0TahkRJVN7s3euk+r/RtlWTxhKvs4zI
-2ojlWQxey7oeenyufhk5PKx57/DgHtM67NGCSTuNRORr5srlMW/b0uq3ZtXzhpzJvN9HvTZetevx
-wGq3fbFGWZyy9figK9fmKFmPFQD05qUiKKOZ12NHX48guR5H9no08cvjmBq6seRDm0+gFSrL4iiL
-1mNt5trbszVdjjtjOfmS5QysrVK9CkVLSjILymlrLqelvh6cEEYuyuUsZR/Dscp6g4+WuZy21efB
-GwuzYUBd0Ah6CAuvdpFiNbzFp4m6+X77H3FqsAf4W/bIT0WRfzg0Pl/366FhQkSkxo0FJ4AR+Pk/
-HRpoKGSWcN5wagAY+W0ec7H34O/B+MM+YV1C/DaP2V8QQzBesusmcwhZ8R+5LAHH/fHQWH8mvhPe
-H/YaOquGPw5kZVR0JiyAjVG76eXMMp79LQ1WKSvqzLolTB+c7AlM/yatE3tnqV384dZ0XiiI28Sg
-dMDNBLYwA6vBro2HZgNWiqtBoAUXdg8Hm7BVCE9jHOj+YVXRNazxy5RNL97vw+w47QN0ifzDlSga
-xPb510WTfTVSkR/I8rFoiwEMnbSOxXcqQ/MGd3sGZcKs5n3lBMWOhL69Taas3Aul53HbMngiozex
-jeRfGhdFahvXQgux9VAboz82Xc1aQXH672k73KZtEwabajCsPVdGjPP05+T36qDI2peR0WpekVr1
-R1ir5VmtsC2ndprYS7o5mLdJwnG2TQIXf4dhTV3lx7NjAVmJysZzeQhUm6rOYQ9Url6+THllHExY
-4zHg7VC9KLLIuOUDHTxJy52pHnN6OL42to19Qpo6PrUS3CAoyPk0Jq3Z3c0czuLsggwYNn1NsA+7
-KGlRcSx1ZFmCelWwXBenlJh+zvGN+GukZ9lX6RmwavpWWxNGmbHpy9cQT7U45DJsWSBI8PaXTWVV
-DcYnOt+AiIOn8gBL2QARM6dKPGxjYFLSuNVdz2wTVe3pvxHD/K4lfdZfKqmsiIbLnMiAVXblLSul
-9KwoWdEcO55g7smo4I99NUuhZ4cpF4FnTX1n+eYEFtxUkjH9bH6oyzZ7KW2AYkPtlPDE1OzHVA3y
-mABPO4u+DDaK0t0Kh1331PTVaZ6d9NnmU3fUEnwVtEb1+ksP9QLibjjg+1dwVkH5kjpIMN6IBF6D
-ccunMXynqCz28alpJx7/5XaCAJ5ydoVl7bcRPoEpqsr9PMl4O2V9dRwx1l6Pwix/SLOj60GVnX6Z
-9rPLU7QcbjQOAQy6/CCyb+wNMMvoMKSd3E5hB4KMyBvgxkA/VrkL4qQYbeelEPJ2iJVLjeBcQjeR
-jTd3Ts8Auhwy3pN5msfuYA0Q1ycjKa+naIA8YFWHZMiU6ywr/HBQXnFEXXXEX/fEhrUnVke3JTGf
-YpNb+mMkDNvTK7XZquxAHlK5nPNt+cFeMfRnhUxhMKURg10sx91kzS+O6uDhKtp3Ixz170rXHdaf
-SimM2GNbGntDAtl4cEfLE2n1tPwHUTfcJor2wvkUg7TJeji8ZbML6sg+Bo2R7O1As06DKC6G0Gzu
-arsND4ZpWUvtCcCQur6VXJEagqwUfPAIvSTTQo9VlgLzSa8yvY52ZSzfC4EQEhCsPFZOeNXHhH48
-s9BPAAvGjQkwY+FXauLsjFkGYT6WZ0fjw6/VLDQEMuar2eTaS9HUHVlLrX23cn3cjFF96DOVgkSr
-039Y9TxvB2yOd12ljvswiYJryqCMA2u2e81sgwPrD8fnOf61TefklolMkB5Wn/RAXprqeLCXLxDW
-Oq06mOy8MoJmYEyheGoK2kVMlJ7lH7qkgMU0JKeib4aNFJ26BZ1iHURU15iHE+CAGplNqzdAx7mB
-P+r46iI7eGeVxxunz66Qg4AZKkF2JiQ2PaKB4zLX3YSCsQGriKXeknuKvVyq4S7R7PdpiZmIOBYP
-ed0rd3nrZr6O2XuP8f+laKno2bPM5ddninDyFqSJzJD2xtT9ZtWu8DOmUmKqqY0hKLxKpHFDFJTO
-HUZf8lzTQjVddl6Yzs1TMMp62+STj2z4jf3UTptrEr1zNBoeJA5rE7dmS4STKTYwlNtJy4ZDz8WF
-RewQPdDc2Ht6asyngjY/ouGRoeHZKuxdgv8JxlorSRvzq88oVyn+c/IgC5T+rzdHf6xE/n1Q+UUT
-WV78OarYX8hMojswXrB65o+/3W9ZArkO1efAPKEo80DiNb9oIlDwmVuZcAhxWkR6f9JEWEXhKcXD
-wf0XqYVL8z9ZHRFI+fOoghBmo3aZhq0zPS8/3s+7o1EUsE7MbCO7Qr3naOge8yJ2LkWSxI+ZTbDJ
-k7o6qkcq5fC4Fki25UUoFfVrCIUPQTmeHP8vCk4Xk+VJH+nB2PzccoqbljODUEX1hvFMt3a6dECM
-wR0Yv3EPGu87cBLBcrFTI5/6q/wmrNk2Y9QzDF8lTG8i/aWVCsqpUnXaCKEwjLU+xXCZlRl3l1jW
-prz3DdR3bqebXtpwhiaIZthEU5OeuQoTygTyJYmfA4z5rzjIQBrMuSqdjT2x99hFup7XGzPCRbMx
-Qu61XhImSKiEUGhHpEYtI0eq6JVnaUINj2aSdZsaJLHiFW0ISoSV4cSHVubygtw4BCwSrTaSbOkG
-rzpG53zn6gNHNhnzpvEC4Mt3vdX338G/EKrRjEDTr1zq/TiZrLSACWdb3U08BJhclnJFHsBmFFx2
-nVEUe0iphF9GrUsvhjUSQ9QIVYbWNqIy+ERVODspNlc/EsQ8CYbpkcFmy8kPVaZZBCG4IF2wCJ/f
-qgLC/LakKcoC7VLN1vMUQ1P0hKy7KxHJ/rFJ9Bb7o4V91tNonzPvSryX+0IfJTn5egxcyjLz6kec
-VkvbbMutmrxPraZ71aoTJBRVN0G1IffXQSY3QaNWHwtYmeHUEC9mP8fE56CAYTOmWUvBT+KOXwvN
-dRZK9VK1++9/h/r1EfO3m+0/NYL/6wPqt922/YVAmLlstkE4ip9TFBTSL+41wt6aibudRfZvDyhE
-W4y1bJ0FjfQ6oTVuOL8nxXE9ItWZbL1tE631nzyg+Fn+/IBiIQCFWOeBR9mPpf/pAdU1aWvScreb
-cES77JYtrCssdhyJjoqjZbBonqBwtYd0MK6mlwgTwSlfnDBOkRq9F+st/piAztFYQKs1k1h7SVcj
-jZHb40mu9pqgcSXdx4DQf6RxPbGNxokTcs7et4s7B5tnu8+Fah/qxbvjEK7UvGhx9ESNa5+dwjFu
-XEwOoR/pSbkLQpdmJXdxBEVurxubodVSjEKLwMPzNj4ZSWboPgRHFCAXUPkLXb7GVb0qRDlaEQEW
-hqzOUW0i46uaVNQGypK7ikwp3g8PGq+fcAVtt8EiR9FriTIFAlzdhamRXAK5DG5oKStd6IFx/Fot
-wla3alxmnsKUJNz9HgKU+ugooMMMlFGpRizOrxapjDUt3Ft8e2ID2RItzVhkNbXtzAsa/bqDQS4w
-P1PCLm5AaESXwarKuatCp3yqdaty1y4iXr/Iedoi7Fmrxpdh59f9pSEKxF1XW+MGcIfypCVTf5xX
-nVAskiG+bvsKNTs+umVX3FNK1W5ijGgHted3vqV2eHkgd0RZ0j3wYdfdJFrW3uW2nX/EdgWMlyGr
-/xHrLoNbpc1Bt+2VtL1WjVriFESSoIPGvSwZjS6EUJQ9YFLSCBlzG895riLoFMN4k8RDvo1HEDgU
-wnTdA7APgRQxBcU1KTD1AUmBm3s0yTn7Htep8xaZnXpBZwb5r3LoLYLP2rCMjo3baEcKAEaqfIPe
-hljHra7btVEoPiYKZx7c2pkeSmWcGq9x5gFnV4h5kz1TCGsXrLV+m+CJ63dBQDu2Z7eZ/Z7SnhLt
-WCInj3LQuQVDr7TA4xAB9eImlQ9QQ0F9TdSgtn5Tan1zigKre2oldR4+PrKh2GCDDsZNJHL1BkSw
-lW36ABP0vpiL9Ct/eVi2cdXDDw4GkHsvREtm56LKK21Bcc+wycCcNqdACWkH7NXKKXdkKYJwo9Zl
-0LCY7R007rp0zkVtyWTDN84MSpQRcbaM9eFtF0XBTTjSWeYTeQ6dEzbv8I63aEP3KBbCd8l1+cBG
-otkETikDVHZNHJxRqXYoWTDx6Za2bpJkNNvtrAyTTrfUSF8X9pDkWp/bHkZQHnwkWkpc0ZCp9HB1
-t4+i7IcYDkkgIciU1bkxDFqwHbtodnlYEsWw9No5Q1HJH8YRD5eXz6r22NjVdJy4wBGN4n/E8iVO
-gdbjc1C+8OZKrvqIg8znZMxrv9PCOfExKHabIZyNfBPmbik38xia6T21hWO5r/jsk9yJKrxRY3gw
-ayN0eAVYyI1hzUW/FencqJsoNPF4ALoDK2dQxjrjyS83sjLDZ21N48SfyZw1pdOR1zHX5E66pngS
-AxojawZ58+9/duL9QS1lBv7ryf480Cv4r+nD3175OdYjM6kM4JyJTM+OyfT8+waSIAFeJ9D8qFmf
-NYa/jPVAVGASM7xrYPuRhrXfrU4OHm/uBkBZHHRkvrD2j05Ne7Ey/dTOgsGbn2spCDD4Tpa2nqo/
-yVZjRRp4jAo/7svum8MVfakoGh7APQaPGPBgoJtd81xEHbUlxLdCFlEEzwiqcS99tNUmI9ehWx8B
-rffORo9rPv90aGi3IwlaKH7Yb7c0GoxvUTYRaKaAypU7M2Ct56NTR5RS07JORBb01LmysSTeBnOp
-3tAM6DTnIcTS4NngTOfzEOt5cxpnIuhulaWXCLpJzGd36l4WkeRtmrHQnDuZ0HFKuNDVtqppimA/
-6DFJCLGmIqIlIKGuWYkoK8aPcQlQiElQ4Apat/yqVlohDuCes8dszV1wknQv9hrGWHMZFOMGt8Ga
-1hjW5Ia2pjioCCbR0S3hDqYnrOdUL46bHhcTGfYlCCLXTIi95kPyNSuSr7mRec2QOEucpB8rRhDT
-LuQO/L1EniHgPZPxqAp1A/nUfaYolnSKCmv/johKfGUv4ZVuzbGErMZI++HEeSvWpIu+pl7iNQFT
-rmkYsSZjqKklJZMbGZn+Lppyf1wSNGwX8quk7a3nYsnX4NQ1L7olc5M1/FqcjhZze43kKGptXuC+
-QaCSS2YnCbPqbl5yPLNFFIjyMMI91ZLzmRVKVdJw4MdcY0BB4oy3+pIN0paUkEP5/LGNG0lD4ZDs
-RDemsGcIBblrxCiQaXwVL7kjY0kgqZVaf2+XVJKVA2ob1qiSs6SWojXAxDIkOc5rrEkSn4Qot3b4
-ylLIateBsNpNdZo/NsbUDz51NdHNUE02HBtXIY9ARfrgsD3Pa6y1f1PmW2Rq/DFxizw4VHPD80To
-fdBLqUzsAP/c6qvWdkBXetjZ+XaIRfwgAbwqPKW5kdLObUfJpVWVwytgbQoXAhtcShWzrPe1YlTu
-Wt0Zd+QtYtx2efXe5Wp+oE6sPzYByhOgohk8m6NuEaOMne1SYi1KO/Zp6Qh2Q+LIJ9p3x+si0I29
-nZNgGoYAawRX8BdbdsEuwWd/HMndw1uu9YSlf99eRqbLm27g5B6oULwrgkg8ctF1f0zQuEl0KQEd
-zH16VU964FNM377FZqKePkuELWf2g0Ixdxq4G8D6xnPtdL3lBxmluBLW0eSbwrKehyaESUhwLnBP
-LYlk1SfuaPyo7CY9m8vu2lnX2IlSQjs1x7zoL2fWvPO76Vhp8MCa15l2aRVD8J5AD5aUdLRsy92g
-c5xt4Jj8Waxb9HrdqOvrdj1kCfocRsVsXyvBsnofli28xTWTW0ETZ2/9sqWvSjU9Az4PtXMmxiTd
-ynxw+41RFouJZF31d597f2cVAaZVEICGgDiQLjpBsygG8SoelKuQ4DBKsycO3GQHllA/Fr0KKi8p
-lGcTG/olrZfDo5lHDHgMv2rjmaWCZRldN7+qdEAMW5OPbu7rsWFcRR3qjden2nCuHQ2kdDUOFMsx
-N6iRh6lgiv1sSNNLcsrmvFMjus9bmM2B/59wlGOsIgr1N0f5pgG48b/WVd3/dKD/8vrPA939Ytho
-MosxmCOTE/zX89z+AtR8mRqQDKnc4WT/7RZMj6XL7RRbMx9BQXU7L/rlFmx8QaBkS6dahKwoNUCh
-/AcsATZ8fz7PhU6NgVg0SiRqdfGS/bymU4d4co0g9cfCLhI/qSlM7EtzpPtF0Uq2S0IzRpwGZcq7
-qU3FJVZH5RtPa4tLbU+pomeixuO/cMNvRANEsmEtPEnsjc2Me6Ox59EzhpRwSepQmEHbVBehv6UD
-jI8k0AkT8Gh0G3+yxg5VLbEH8P2ww4kaSSjvW0uNK8iivM97y4qbg1EY2TNTgX5lwE+mfS3Mwmsw
-KO5rRAP5M+3aznvFfr2hv9ZkSx41LZWZE4x/6znQ+bZfQ63uIPjz2acevgNzBSs5c/MTlXKZ9Kgo
-Xtp+TbxDR8JlzXAMYzum10cbhhsXfmuIn7StKz+JLZuOSOSf6MbI6wIrCKqte13NSVPtm9yxJo+y
-2hDMdzJGuLKHtvaDUKEEAKW/H7auKFzz5A4qWy5qR+YcJAnoH6AyqM+bkfY1tP7l+zm50UYbq65o
-hrHNtDM2M43eGUHoSP0u9N45yozOIs+wtTEAJAoEasuWMHh3ggoBl2CgctEM9Jx4sm6SZF/zJe40
-c25vMZdQS5QqKRQTTlT9hR+ymOFpMa9NpRG8D7XBsadyD439Cg9cyWSxmPVsqOow5glhO3BTBsvc
-8xjmSyEItk9dUZUvUBoVc5tNIQpDWCmU6oTusGCjoOHVwBiom4QbNTZsKVwzJuyMV//RcnJh4C3s
-1XlLS1l9aU9ajCA7zyEBOlYxg8dy0oZPm+vWA7HyutnpdcaFMzMKeDwEfwKaZ6IsudTtoEsOhdXH
-0ot7CAWb2pBoeUSa3Bu70mttUbZzdzPTEeD6ejnMcmPHjjwxIWIw0vsqQ+wsO5A9DV1DYq/KRnNO
-HHo17zqhiw7IKBiAY4bh2IEom6PIFm3EpbgorcbxuiTRz6g6VMFNYanQvxfDLfD6qqmf//0fsr/u
-Gnnc/PWN6aX8/gO5o+jibvoJAK3zos9nK1xJczHp8cClZl1dutQ/LX4uLEqWjhg5gEKzq/pdAVlS
-IQ4PT5KHXNRdDRvfr4/WBUVpLTisX2yBxj9bMP7roxWTBs/95SdZvL1/ToUwWBVllzlUeXB99vpG
-Zt/LJDb9rs4y9AdTqy4cC8A5saUy3c2j3dieDZmODuoFh97ZwJ3cMIuoBoGTPvQLMj1dGKnIzwUV
-IPBWqw2u1qfKFt8Co2tvjBjy+jDnDIIdmgxiHWT2gkvJNSswBE6hR4HmQx+U36t2Cl+DpJb2IVLh
-vu16zQD5DoVRvHSBDgi+WKHw5gqIb1dY/LRw46sVIU87eqVd5WxLVK+alPZowbRgBEO74RnBh+co
-ls/elb3i6c2FVF8szHp3oddTrSNe1RVpr05uNxyydEHds4UHe89atsk3gaWAw7fKPmNjU/e3FKhX
-75q9gPP1FmHJi1agfiejnGAEHQb51g6NqXyAxTJfGDJwjuzY2otYZblJFl3s7YqmMbnC+8dZmRld
-Cyd+ksqYEdZZSP98C50u+mlQ/HKkRJLO4KUWYLaWigACBdQFNEQrzzUTHPEYA7TEply6BaylZQC+
-TGfCNjPnR1nP4JpBYPc7MZGkiYvW2hNCpDOnDeHKa530zahzgO9XkR9LbfiG09mrofBQDmMXt7Fa
-EHGQ0jzQLaBeRp1WnGLce6eh0mM/7CwKRMqySR+yGdeoWzaAvRyrOmYB4E5626BGQ+f2laT5IL6S
-UA8CeWDOSi29DGFYZAjQdoizmbCrdlBCB0FnWRYr9hn369jcyqqoxave8FAEt6+H+Xgzz7mJq5q1
-FxBofC652X9DhNErzrQ8hiw4qvy5qmZu9ZVihc9clfRqq/PG4dlttpH60OamOAoi4ixBRWPsk9kt
-gUkUCm97lanX2M6DWtk7NTHlCSxP+TbUdmJyc2Q/4GXuYN1zndNPrR45myzkvYCrLzIeGiDmF8Mk
-mDcU8BhPulRl7iOfGefSIJUNh8t4pODCebNQl67zeMrvgNFOx0Az6xvQqJjWy3AIdwtckgIOOb7q
-YUxwK5r0BGg1a37U9jI2vsZlo79RFTRgsqrBfxRjswHo2VR+5kh3J8h/P7vukHfbDEzFzdg56aNd
-crXPZqMA5t4aN2VKbZvXBAL7ymDr2Xf2aSRZaOKYT70oBMb1eObSOVF68UpzW+i1DqfoTRwnPT1H
-jPMjkaaLLJYZZ6ReN88hjp13R7Gp6ytSVYtAT3cTO1UiS/x6xx3RtN4+zHqthxyQIa7GXLPCj6ww
-RAHfMgpf54m2PY8EHmFIBffKldV0SbhJIO68zKkllButCa0bMZYPEKotgHB1HJ7xV5mXQTiBEw/0
-Xr+tk3ASWHLaUvMH9ldPoRVPMztPR3vsaT6JN6wZh8csjVxnl7mxOoPZJmG20NbrPaWqMSpEq7VH
-ntCy3dRYfICojyUqsJrK1jMCJX2Qc8C+hrx/y0wXqk85nSL/D1eWy/iNCb/86P7P/6Y/+K2spiZm
-ploH7d//6f+3frZfzlzzb7eU//X+mr8O/8Oe8qdX/3L4UrjGAYpVQMcV/9PFZiGhsSXEmiDoUVjK
-lH+72HDE4pHkXOY2hGK0cip+udgAXQMErbvczPliGBz/EQgax8IfLzZ0+iyMNkES0HBUnYjmny42
-edlUmNf2Yk4omFKiKdvKtlZPIhmde0ezyU3P83ySXNvOdhcFPxqKfq6KXqtua+73jKRdB/gpH+Uz
-3lx5LjNzpvKI0hmKiWJrN0nb2DR5X91npiu3ndWmIC60LNq2jbT90Kzzh76djUNa1Mo33FUy9dWA
-DJ2Xqb3LmWOoOau7yTxMlDxeNyHezbCbsuuZfmh1PyIFfsvjQr3r1VGx/dqMM/ERzFkOVtfOGirT
-Neqz6lYZT8TT9Lu5I3QP+rXc4o0qyy2/gvHYamhb7IXCY0YuertIjucZ6Ju6gdKif3fVqvkxsTt9
-rovQeWx7Bft9QWYl37bBACkBqeZKN9UwRpkXzqbN4/bCmbv0lA/YTClRtYcPI2+bc0eRQIXo5oQ/
-KE4Nf8CEtSqPa9D4BkPmWKpj/DG78fjOso9KhSgxDpOBS9HMevGd3TCFnlGIgWIc2XDs9AkRcldA
-H9qhD2pXjVsRDginHp+D0K6MNG8um8nWD5obavcIQjpxS6CZgd8UbrtVS3V6mUeC2t4sxogbV2bk
-V26vBI+dnJM77LrboBmGeqM7to0RUNQ+9Wh56jlqiwBGNCffDVbNd7e4AYLmN2AyOeGF3vIm8W2j
-TBvimsYIhVuhGDuTSbXH5RY+1UOVXrVCRPdT1g7bxhDcOTRWkVt3zKvI6y1b+ZoWCo3Y2ixfert1
-3026K170OOYJSU0DAKDaUJU3uBD63kjN5DRXwEa9iB4sahnoBfC4+fYPBv1Vo2elqXKupWveKm4v
-Kr/PZm7uDWsAH3pd8+KKzKFJ1G1wuKUYyOhNKPxUyeSL4wbKfevGSumXRHK/uVmjAVEx3PuqtE3h
-DQ5lAF4kiwfsRJnqOUHT32d028THyVbki6La5Ys2m/FFZtjlpSsqIKhIpzWAMX18csk6HSyzHi66
-McZ0QYpEZyAZh29DWdQbWj71Cys0hpNVCPJjva5sx1JeAHTuz3WFlbIagRZ6aVa32MkK/ne0Kt2L
-Ua/frWSoWWeOr9w4mRw0+6pwiBNA9KK7GvscyDfk+vCVkrb6fRTpo8ijhizFMCejR7kIIiwxrYUw
-sdQY1lXVwibDY3XsnFr1kV7r4kD77XJYc1o6nr2UIlrTbJYXsWyUQ+0G9Q5AFP2J3LDpUgyWWkV1
-bVjM17bFYW1e1KK+uZcdXqfrjv6sJRUyi1t9bWxUc9leKkuNo91BhNskS7mjsdQ8dsjiT3Ot3XRt
-TwVkRBlkA52JXkjSfqMfrH2RkzbgYu7hSQQb2Su5BHo42Q32hYHdIzrxLjfkSFlXWYY2NeNuTVi2
-ZfDIl7JKcwDcuBGV3Tm3Y+PWFF3xC25E6TBcuvmiX5Ov22ugGTIvLtVhB7ulw41r5gIMLS5eytl0
-p0sgEVI/WV5okV54/ciE6VEw3O7ntsTu6ML9uJ+HYar83Mw/sAPL7zGj+IcyqsjFnPeFc4WgzLgN
-kgyDNuDXzLMjIecLTPhNuK14vFI2oy3gxr4TzbYHOKnsG8Sxo+Dxaz4oRUfNPJdx6GxBM5sbo1hw
-s7Nt8/zA/T2DI3cTRIZOd5ZTYGBAhAyW2OrNOC2P1UKN+UvzGIDKN7qcw7MRRYlPilt+ReqItSse
-QspVznv4ogbN5PhGyDPca+n3vSN0Vp1tpzYvZZsl27gxqKnqlHrLV+sTOB6THQFTy/RgkwozwHNk
-JuNjMqnmi4hpo4I+U0XbzizbyU8yGX81Gkf7BpFyqXF3ynet1fF35c3goLsK29iaVgw6Ls8q+l1U
-JIRXlSofPxhT/G2lCLaCT+d9sBTD52pXgUi0oRE0iNveINTmLFlC+r0Tjl//Y/YP5t8mRv4rZRA6
-fi/zf13y/joN8frPachh5sFNTM/sApWgJ5283+cuwv4CfYLsoGtAfyYo8tOe1/xCYQZz0uLF1PhP
-fl7zGsu6kAmJ2gyiwf+scX2ZuP6o2mIERa5d4q2sPfhZ/jgMYV9Es4B2M1mGPrBbmxVEJBAxFrrA
-HDj3Mgj6+Vojxyt2Umo0pqb12J6ZV/oLOZrzm9ZWM6XpqVBhJGJpInmlKGenJEexHVlE3k8VROJj
-vy7G+PSKH5mcMUto69asXTdoVR6MB7ekVU2s2zVj3bQpzSxPsL1ZGqvrLi5U6+CHsdCTnXVP10eW
-c8P4xEkarZs8ZF7HBuxijmdL6wGGR2lqd3wuREdpkhHq8tClJWYpOOqzN2dN8xSQIoyXD5xjQf4u
-KLHLk+XWHDXAjFjjFVdgMCrBPXTCqdnkueV4tdSD/L/JO4/lypFs2X4RyqADmLwBjj6HWmZyAssk
-k9AyoL/+rkCJzrpm2Wb1Ztdq2F3FFEWeiB3b3ZcTJUuMLKC98RjHvL7QXAyJNjXXhB/hxoy7oTc6
-gJXa1OmURnJ3B3hp0vtFRJDIMFvxVKHfNjoQb460Te0qmw7+JultO54+12L1mrYUSuM7HWQJQ3L1
-o1Z1PDGvefmdXP2qbCiHTzvU5ee/5sOrqtt+vTx8wm3x/dfvGPXFf7xjjN98logAjVw+cz6gmT8/
-uQS7DIdSaRLCJj5Fkvp/PWRYMPKwQMVj+eg4fLTYSf7xkHHZSarAF403LlU4GKD/iUJjKUb/z59d
-9ZBB8sFBqfYPLhPj3z+7ksOl5uRB3x24ZrE1THewLeMHGFLOIwq03NLGBTY+lpxOGACG7nOqZRPo
-YWcc2EUVDy21kuccc/AuqVw2BMxL7bnU1K9ZLO5X0zq4EexTGHzn2XLzYwu9b5yoy8zd+r3nTLtP
-aSX16fSdW5i7Y3ywDW4+QaFothWGl19pKYv7stbdrYFO8UDmYdiSo2JNZfqI3m1hH4oohTPDcuIS
-s+F/SHKv/RGnvVttiqjVv3esKhLRmgfsVDYWaKO/zkrTwPoVlwABB9XVGxiRPTyS2Mqu+6YPH6tC
-K24WmnTuBb33/AFLujeS73mm6ZjCaqJQCZ0iG0p/jUBH9/3Ss7xUJiejYiry9faH51eo4n7fXRw5
-No+O35E05fw8xsj07Oa8DrcVfMGjY2X5U94v5Z6d79YuvG2c6vkx6RqjhVbI/oYGSsRXS4fnYvUj
-Z0Q81xcjMqsrvzbiu0Hdu0tNQsPPLf1M6yburvWCLtVdralbG+9G8ljPfrhD5Z7eAL5T76XuebNx
-ufIRwLj+mSKdbc9xnAIyXgcENStMamoYWfK8oWIlr2SkGCriaiHUaruVOqzU7JGvY4i5jiS9JiDR
-QxHEiDGqqcV1+/pqVJNMncrpmDs4PDlk3UOnhh1Hy8UBkSR/btc5qFQjkSjoqHWyXozXkZMYn5Ya
-nno1RsWyq99hreUJ9SbgoP0dTTa+ftca7Ojwp2Kk2MJrYTLL2Cjxs9NEebG32bWRCF8nucJj+GE6
-jfttaybCeRpqzT7xGB60g7FOg806GTZqSMRuzLzorbNjts6RkRVlbKrUeAnMkUkzmtXUmaoBdFCj
-KNPsp75Op+k6qdq8DO4HpITsUsqyfAdLYbxOJmyGnVq9+2dhOvGjz7zYUF3d8yg18ZiyNjPw2/S2
-9o0bGDERl2UUbtmfzruK1wOkMGGkxa7raOg9WPqIwtRA91XFhI38GNzZuO+tuXiXzLkXkWjFXc8W
-743K1sXcgcYT75HdFdd9Gz1SZt7fDokQrwKDZM7abSKaadP5e2v5g1dsMzsmYYTQ+JkPg13vhY1F
-IRHU0rKZlVVyK2ig+Gj6iah9k2vpfRrXBuwMY4nFxR0z/CQbQQ8iUbMMaFUwoFzyTRkW4d3asIH7
-fclc3V9Y06bTnUzj9jzkGmHskL6Ntx7o25PhDyCGM392qiDN6dIm3w8jOMDPIIg9TFOtnZtG2PgG
-W4tKQOHnINU0huDbyJv7I+JpeJISZtSmKrXG+ixa2o+f8sFZcCaTK4y2YMaLKAcUXOflMc+hCdCm
-CSdnKLQKjqTsin5v8zyNA8LaSUijUptSN1yXxFXFZGJAtRofuEIStk9klpZyW+tO+9o1SfYwGVCj
-r7yiY4fualb8zv5dyk2Lydjai6z0Q3SEgcCoq5IHnrSG/SJNlFUrf68IclySxtS/WLF3T726WshO
-dDbX1ZcuH66sRbuObKpiIxsPBpPMtQnzMpgNaOS7Ejj+dhl0/+DPOIrp72u0G1tAmht4K+zHYSKl
-5TdOCKI/Hyc+I1b46LfDsvW1bDk4c5k/iEHSPgtvgodgBbL3LZH9cjZpEjtHVk+Kos9FeaKNqC0P
-OZjMnfJhw143pu1UL+01od7uQpCYGC9soelLGZE22xcypIyZVc7gX2VVaW88mRMZzMbF3dRDqpHH
-z4sTzCiTk5yPfX7N27n5HrUWjSwuzrbPnM82KP4mc75Kb/wUVQ/tKmdHzHeio5I7dcQx7ezuipBn
-By9hdu7gm88vEyGOC3CUno5C5I4tVvYRqOWSObydOqoYA/oAFShbGDnud3M64jRrMPeOtYGqRgX0
-ZhgbWu/nLs+jba8n4iGy4ULVUaVg9pAPgSt0MUTZhM36VnDFvFg202HT9c3BFT1ZlH/NtKXgP7+e
-tg5V8f3HL59J6mv/Grbo5VN6KN1zWM5c1rK/P5NYDTN6YYxnc/wnru9PeysLZYO0u8rQO/BP/yPZ
-+pQH2vy/VPyqbS9Gw38ya7FmZpb6yd3KrAVEwfXYXfuObZA24Z//5G5NC2/IWgolRWqJXdw11bbs
-pvxiGhMpjQF8bTAV0CRGJoyttPoPY6IwqzRFeRMahXUSs2XvBzFwPJnh3B6WaXFe69jqbsqhK06W
-zf8UUsDyNTQDoQZEBAHSbjikcZddOpN/p+XsbAJhDvXLgp2XF9S6uDG07gbC+Lg3161MqBY0dTXE
-rGSd/rD4fKWsHd41tOu0G4uavl031Dq5a/Y7NIL3+EVygRl3rO7Q677nMSjXPqezHM3RGI6x6que
-VXN1DoN8y+XUBYbPH1KD13ZZVMM1HxcRZKMqeZi1b1IrPDa0PRu0kSacyYt2Q6WV8P6gGbZq7tvF
-aTkGdj3pW6f0WbQjU1ENsLGXkSFLlWvnzvgU2svj7EAvD4G0lVE6bj14bDt8vwnbTK/e4OBtLuQ2
-Xmhm0fmt4ynQ2gRX58C6qejjjkW9Z+zo9PEPlCzPx8Ia0qNG7cimWEJ33y/kb3AnJ5jdZ402c5tp
-w07v5tHWCMaAE9WyW9yKOzvuzh5m/G0yAjU2zHjkTqkGusTZsLxUrKC/JboXsXkxDA29VMY3OiVW
-MFn8wntyfCru0VD7bQ87AGS9UqaqCeMIuJxyp1kVOllomT/yUMoL26AM+z8dr+j38ztBSH9Hp1VD
-dZpO7nvu2RVbCOR3syzfGVJCylM6a6OnE+92JZJJVp67RMJJmFn/niLqCA4yWhyqeVvsMrCClNNf
-6WtQ4PNHxmwqXhLTii+areVNUKMs3EcpLkKWq44aax40+AhPltEmZ7QA43myUs3ZmrNLBHwezZd5
-LpDBKUyYg3aV+jSl+mmrAJjjZL8ulCpIrPFxyklWdnlxRsfOr+BpY5vs0FNpJKb4gGrNIKQn8ZCn
-A1yWZHDmoDc97bikC+VJWlNaX/uejXAA4y97XnxKeb3CHPUAfR5poInAFORhd2z5j79pckn50uL1
-N3o/YmuqdONQu3N9LEVF7MJ2Y/sD4AulXobka7qx748sauorkxnsoSJVcnbneDmUPm/2vIz5wBVR
-M17j3gmvmCT9mxCB95Tk83zok0xHsKCyFzGFIHvTtrtxsKm0yeKZzLX5wXtQbZNrg1IHn05MMfVt
-Q0iGgBfl1NB+44G/GnWNysnrlv1H6Vsfg8xYlFDK4F+NaSL3lp1ytXoWHFsVEigA1JblU1KmHevV
-KcTzgY3Xu3V7GyHPr9NTZrHXhIUOWR3+BjbsKY+YFgHmwAd0G2ePI7U5hSxldxWVGrshLnnvLL6H
-xVeLbuFDi0Nrkc9vZQzR2hHaBOZ6Lp90ELgnkz5hWBPTjLBlh7m1qaxioH4hLF1VGHA/o968lL0j
-z3T9Jk2Q13H73GfO9J0gKEUCsEZrqFBsukjuOBAoLejNgY7ozNkXTgAc6ngR+oHKZm5qNVjLvq6v
-yrJOLq4aua2uaB6a3ICvygwCS5S0DzjN3LmZ1Yhuuw086tKZHhqPUouNBASb/H9owv9H1V4Va/z1
-tf0IvKWrfnlvqy/+/d7GkarkWsCCQgCGB5H2571t/waAw1Hsf4g0pCh/oqnhtSJ0QljE8GksUErw
-X0sSNGK+RkFzhOBqR6D9Rxf3Gtb86eJWTBxC8Do9iKRcLFftdX++uIXm1D5v6h3EzRHs1JiVRzIV
-V9Cnp9eKy+YCXL36Vo6x9g4IvLzibzt/H6EU3vQseqhsQ9YVY55JLOiZ8dRKvH509DVHNy6cT1Vz
-wmHiNMYtLCyIqKILzy5a8CWqhpmyWdfZz9owf9V6K97lqWW+NfjAt8AmbqrBzDfaGjArevLVM2PR
-JcV9+tG7ugSbplJp6E8E1KIqJKzmNDK8a1WCDeg3cu64BtvENNEaLvTJu4xAIcatdGqNY2aNxHVr
-PM5fo3Jh4/Is66vWDozRI0y3LJPhXSF/qZDdGrhrCr3RAp7j2WtviGo4JGs8L7JI6oVraK/C21Ju
-9NZIKNxac31rxA9dLZVbal5xOXI2DE/eGghsjVw8tik+PorpSAzma3iQd4L40NZIYVlKo99r5mLe
-z2voMFsDiJaLOrsv12CipzKKnRVWT6lZOe6lXZOMo1mUVAGkIcGQyKZ5h6VrEv5we9k92d6w15Js
-Ysmapw+5luCmmWNRYA8Vi/40qCCl0Ba721QqXhmvSUtLGMWuwhp21/DaOVMKgRxYFj7P9Za+HSIL
-hDanUfrXgwpyLirS2alwZ7XmPOM185mp+KfrJ9K6DvW2/Bz6SVIfo5Kik5aE2WHwc3wF9EbnflPu
-W8cZ9B8gJ7n5NA+398EWIY3IzLSgYnaou+l0syxETK5kgbK0JzMSAzs367TYoNjVyw4Oh4s5zyq8
-9rqx0nbh78DeklsDi0wQZawwtqWR1A2+v3wBxhczUFaXggfcBNRvSfwdq6KKldA0hfJUtZzXJ8RC
-siT1TM/gs6ePjF/D0Dw5VdQY4C0L/VWK0aq+JeCqXXhBxFe2XuM6D7YpqRCIm4Gmo7abr4dGV0WQ
-enYcfalYa1pG6srMI8sJYLRT7NEg+ZlXacFaaSq68tpoXXGa81YcUgqhDiO89S9SoIaz7evzL9oc
-Zl+yyKeGaOwyKqKIP+zLnIEDOmfq8hykgMLRahbsGUYsSkfJKoIHcsKkIqlcu4CgMH4HXhNnuLgj
-a9uFMV4tDyeX3NBg4+6oNwPc3EVzLLc4CZ2tH8/2cZLEYoIplvaj3brGGSaF9YEJfLnFf8U+RvOr
-6b3mZ/mjDTuiZoQucPoSygqTvbuYIE270KqiHd1JKsBi9xsxc2pCGGh0CsFE4Z7oJ3HOg8CChafM
-tQ+ZHSZfMJZl89nngT5AUdDlw4xyqwUWUSo/8IqYR7bIK7yynPTKsRT9qO5+Px3l3z1L/+t//r//
-q5caF8mvL7W7/Fv341v/61uNr/7jNar/5rLNNXySGQQuFPPkj9eo9xvRS6UJIOQhDFC1+Nfqn4cq
-/lS+SBisvrER/udWQwTkngMrAD+UK++fvUZBPv2v1yh3GTg6fkDwWKnrk9v450utY5EhFBxTQDUs
-9qb6bLBSimIrSPCKsqxz/EYQFoR3BAB3bLL7pExkfS7duf2gyqtJbl36nrxt6Y74GPzS3k2N7tT7
-uvWaT33u52exSL/Y8vibb3udKHjgravFdqm8137dN7J4jNUGEoFQvIfrWnJQG0otbcq7Tm0tCzsu
-31MZGvc0a8mPdl1vlq6OTVPXw968Gfuip/DDNvtdSj9iuNN5+pYnqqy0gjhCq1dHIp+decCe0lDb
-O7M5PJkOVTyIdVHrnGuqMt4mD119a7T4A27seqALp+1si2izbj7EUuTf7Kmzn204wF88g9M0SEZK
-hQNn9saW2L3daDu4Mf1zR2T/jHsqAtkwhxA0U00Ac6mgflH9S9sQzcIcK4y4yhFxE8aCSZfJ0gI7
-ppVNeopn/+wUDpO9iKMuY1lqd3bgtK7dXww9W7ptREtQz8ss9pOnIkvCV3qGqTvnYfwsvVpSWmyP
-2g8vNPyjjHTCCVGo1c22wQbhbljdfVZQ3bKAakawLPD9vaPj5GnGbCLj5wi7s8PyvOwOVtHU5EbW
-JqPG0+pdDrPcv8e5GT8SBRPPoao/Ek3cPUZlyjuMoAuHJl4WhSln3wVy3KRCiSe53PSmVd1SX2rc
-aiDIu2299i6NjupgIgNLH5OlqplG12zOcu1rAlTGIRirGic99KR2M6amYM1om1dlKGqXLBsJehTw
-acQnKy1+0Pys/d52RnEkmj6EV3PLlvWqF254veBns2jBw0EacLWXNlUitnaVkUAVwehyhcNWbUZ1
-bObGDe/GcZfren2VEe645dtg9duYDTTNlWlHowESDXiq1o8wlosxzr5ms5fv7MHC+lKQp/sx5q0O
-K4dCamG6cBBoTOi/RX0a3jatHR3LJYx2cEVh3ou86L/yzhxI2HmFZuzMnHqY0PKEPGlaCx2nIc/H
-hzFEzOKnk235v+ek5p3w65P6Vvblr49pvvT3Y9r5TWe5wxND1Zcp5Plfx7TNP2FjqHjNhOLBw6Dd
-/rE0JPjODg+nKcenIPChzva/FFpYqYJfb417qMXhP3l8MKD9/ZyGqMU1sR7UugtuS3WQ/HxO0ySa
-h5Ykcgb2974LM29X2yk0RtGHOBGWcBflsjjKXogAGsYCDzYyr8gH4BHKUiqFJvOm1tn65SGyQ8No
-dm9Ngq6ujmoBny278PeEHzRGK5gmZhEMoxF9ozrEI7gZVXDpJvPRLvQ3KrqQTkMazQ2rof8sxzYX
-Z9DSM4iVKE3G1h559dOpjnzZUOcD1mI56vCdbsrcazY8XozdUkmM1+m8PBAAhODZd/UtmeN9Y2g/
-Cl70Z4Be0wH8ev0SzggZYUqb2kbl8Da6iJ486ezMJV5OYclHqU2h3egpu6cIBvx+WQx/V1bxLh1J
-Hg8DLttq0eTRzI3k3C482KZG7UfYalhB1nrDJhlS6zmhmpEEK10H8c5vDXHdRzUFnUIDacE77tho
-tAfZbl0Ue8J9nMi+X70Ro9POrktaoQ8nb1uR3fhqTVZxwzOx3BEn6Clq4dW39PUbVbnNYbGs8+C3
-s9KRByz6Uj9Y1cJnPq+ks42Gur/u67G9yuYWR8gAN2eH5mkEbeIMX/XGSE45FpvzkpTmyRTLWzPH
-5G5DjKYXOM4lg2lMUarIm6dktK/ruLgPx1HblVGVHYi/kPmzBn6fFvaJ+g7/aMzB3zJw6gaDq/Ha
-FxLCSM0Bq4eLeQWrZTiKFjNKPDr6ZarM/Mq15+FYZ3FEpf3Sv+o27jASafoBAOOTSEZWtNJ7isRY
-HKNMPkDYzImFeC2kzAEefrFEWAlG+o3XCDKlJzfSp5yqj7T2zY5I5jV4ftHC3sjtGQcoIsl17Y7h
-CzE96z5XmFTL1oythPZ15MAeAJ9BUeWT6B0WUGn7pae0evGmFkunPm4XA6XK0NJv/UQyqOUK/ADa
-jbg207C9MWp+GEc6uC7a6IZf0qm5giQ3fYpGNueMApEN7kftpFFwfDdENTbqapIbtnPIcXxIux1N
-J/ojSzK+Y14730TABi7LZHa3dkNHC94OlrjwPdlCEXQKhN6hT9aNB3+U0lLPbbSzN1r5o23a0xNv
-/XZbjYBnmzh3friznz+kcrxnxJju2hgEuCZqO6im6FFo4hWVybqJxrl/YJ/sPnQcX4fQKYZAKsgt
-H3N4t64Y/Wucy+O2I4uABgoPl1br6jAQYNlgZjYCw9G0YE6Wr9WULAd4clyjecLBEhUalQiGfZfN
-bHB7n8bc1jXpaBmp1S2H9ktaefKg89ngQd5npwWhcN/K5SND0LMGfmlfhG9z6H1mOTBOZLs28BTT
-d05cuqmzOOdRFMcbrRvlk4C0S8ELP4ak6bItSmx55Jk0bmNat3Yon+VWqnBJNnc0/A1LcprK0rqh
-hkFuEyTxYAEMH8x8hLegdD/sUbzz5tSPPW+7U2kuWEhywcLTNa6ktnySB+JbMtEXrmcZkCxsGGWt
-fbJOvfH1ZghwhUQAP0djYFLiRJ0y7Wnim7nFv+DsBQT3j9Dxwjsja4ZjJfVyq1vjZWnCPVA6kMGa
-Fe2lRRs3lJBio5scXmWBTN4sMP9kOcwbWEDymFazuR1p0fORag1woJhNrkfFCWG45vHVvvZq6QuD
-G7MKX9T5+QVKxHxuS7qBSCztNA6fbZEs0eZfMw0oPe3X08ClipJfTgPqS3+fBsjNuzytfIdcJQZJ
-Xlx/Ptqc3yzT4MoHIMcSEBQOL7O/pgFOGR5lODAxZLCH/3kaAChnKb8WA4Yw+Nf+yTTAsvHv0wCJ
-T44EIv38qg46ooKS/zwNNOEyhhFkuNnreudl7EfzkNZJigGKTOOuEmk4nKhFWq5z/CNjQPfQfDG1
-iebvlNKAfBDTCcuo9u5nmkH8zEpH9OmUTuJ2crfmYFTfGzt0DrigNMSKht9JY5nRB02mV/Ve1ywA
-b26ZtnfO7KoYCGBko9YkOoIGvs2uFhjXTmi0GAqwGhBEx4sosFZZDU7YpNwXPIqf2qVYPjS7rQ5y
-FKNz9nOtObVcSa8ybWP0I1zJF2/sBIUsBYTYrZ2yHd5JLsSHxGupWqFgI4aJlYw5LdpzbL9QwAUi
-38aIfaPJZYgeKx8/140oE4fizThzwq3G82/aR5EXAQh3zfysZ74DsCe2MZF7Zh2l33R71qtNGBua
-VoDmJo19KJu5pPsy6awSlzy3Brur5LsGQRAE5YJgim80W7SNUSzFBxKwf+sOoe4SVuWC3kSVlTXn
-om9jnshlOtxY9WIjrzCVnRFr3EMR68OdRTZ/o17d0MqdttrZ5TzcZVaVXEAWWE+2v9A2A3oanVw4
-xzHVx5M3V84HodL0aA/acG8sFgk3vBc64tIQ7zLKkQly9IdsLUye1/Jktsv6db5WKmuqXZlyQ4qW
-5Vq63Kr+5Rxfh/Ul87SQnps5avdi7WmGeYnUUnb8jeDTYFw9iJjlH9CEyT4QmrDkxh3kUlzicdbg
-5mXdV8AiAJFCxUaa0VjBnZoAk7wVnjStICUEJaBK2gJfqVlRSzolbJcQWwwAJjeLFIwpBnOQ5dhb
-TtEKbDIVu2lUFKfclToHOSfhPQXtYJ6oBSMcGs2F+OTzmD/WfgmAacodfnRLqZVqN1EyGRQ1oi3U
-InpkLY+Zx9YG71usF+NX0LE57z9s9CzobQ3tVBf3zLrZdTFN/TXr6+XCUmA4GIar19dtPmcPndUg
-eWWdlXxKKxs+usip7yUBKTOg54PeIWksD/wEw2ofHXePo947uoYWB2ZttSeBswsXXGgDn2uadBvb
-RET63AENYFvWLcsW7cgKGkbCWORwkvSpVhUUP6YiNwN1Z/K7pDgV9cp6GxpLk3j0JMBDsyUlF+j6
-kjyXC7XlZaVwFFhYBuJCzPztxhmz/ALKoJk2mezkudU7fwnwM7nnMK37C5GJ2r8nXcL9Y3cm39/F
-KW+AKey0sZ/wfQoLNCA1UQfbmqIbgJBZuyk8fU6D0Zi0tzRLi+y2H6ZkvMmbzL8LbT5TQdF19hec
-ArF/CH0rPFNl4e8af9DaTZ4bafeIXch/jIhzBpneN18WXboLD+9w6q48ewn31Ui/rLDy/PLvufW4
-a/7Lrffj+/f/cu3xtX8qcPhR+H6hmNEWxI/Xn7eehW/G5VGKm9DCo+xYf4MdcA+hYnHtGboDnPGv
-NzBbTJgvhuACdWg00uHM/QOOzLr0/Nk5g5aHW4Y/loN3hqYwj33p3269WjhOxKoxpNy1O3SIxvUm
-abTyfZCj8+Ro+FMJHg/Rufcbd6e3HjOrNUwDzd18gG5rbbLOeSeHl2LUGWLdPm6iO2MC7HYN/AmY
-VIQsbW/iZSk/BTaShEdRyidpwtCR0IdotPfL4Fk/MD5G50nXkg4acOde0wiUHBs3tXj3CdqWsrFn
-YHesZ+yh3Y1uTD7Piuklox3zAKNY39iZz+Ohtgk9NH5dvHdxV72HjPh7RCcGT6vjQjEb/iZGm4b4
-iBMXBoJYrO6VuVlhDHhfk9Gs6vIKiYR/pi3NdOsNeNo2/Wz7JzzX5jbxwwEyio4imPQzxcCsrRz1
-2fbyE3xqGR0URLYIyEotNyEPFW4xpmxY/o2WWQEJx/axz5rOuyFVF3+bU63AwV1RmcGB8uKjxMMn
-AaaMB0m6V6UTuVe+bod7s+D9RygixUjC5vTahtz8zc7tbk8sqt/pLIQhcxOHMp7MkgsziG09jzdw
-Z4z24LIquE5muo4MiWvxKumb+QqYvflEb3JyHKhqm3b8eeRbKCQ5PBz0NdJQlsXPZguac8PimbZG
-PXYACxi8Eg6zbrBdtW16QpSJiGrltiZa37XmnPNiKRdrNxdj1V31Rb1cJbWwH8Cwxl9mXQdUKWny
-ZP/aNvM31DfwRVkn2eTOBsG+aYVduiv40lMMTC0t612juJjJisjUf8dlruhMwoZgNCcfoma/wjXN
-FbRJqQjQzdBykxvfg2ozSgXl9FdAJzBfl6tZwO00rdJ4nicF87QV11OYED57ofytvuJ+llWOF4Xy
-g/qiUnBw7xQiVChaaNpyxQdETJbNzJ7r01JcURPfDlAjBRsdDJNOcBBCQEgNxSOdE7439G9AKSVW
-Yh3tes43eWnp+9quzLdoQIBu2Lt+nZQoTah1PgklVNtKsmY2xC6pZOwkbVG0CWXan76SuaUSvOFQ
-6U9WWqHxSiWI99HkbQYlkrMnnb+LFp9WWs/he9N45bdayeqVEtjdGnerktyncBoc8kBoVVkutVt7
-FbCWVcxiSyEf1J0/bNJV7spaCa9PaWD9KoflShlbqsE9kVIymhOm4NDcLlarBN2ae1WzaqQ1twQm
-tczovfsob6UH81ZJcY1S5QgjTu8uUqS5w+u6YFpGv2Mxb5yN2rYf/cRR1QdK6TNwmW5ZUUCvnVcp
-UICXg8+Rp5KYkBILW5f1GavzjP9+JGHTVVZMVokxXOVGnVYwpEeAEdRgT3Z8OyltslplynCVLCde
-uC+50jGjBUWzMET+RWf5BkReKZ746OPDPM/iUDuJd8I2UF6rmqsjIVLkUrYgSKfWKqPqq6Q6MveX
-UEMESqvSXE1pzdfFIhBiLaXJelXhPoSrUOvKPnVByCgBV4yL/uqusm4bp80TDVxm0Kyy77hKwFMW
-scgzwOCzCxBZH73VrCmX6ymlmH7jjVpUHftIYG2zmwIsFQD35J0osky2xRRZ9kc/dX1+jrJhzu6E
-1nsYKnqXw7KUDcmTkNZEkCTztIhj3miNu2/0JeOnlqItmoOLSR8uTmwl0UZiek8OEdgPSDFJ4kzP
-3pCWKKyOAx2aNHJcvE1m2Dn3OPjy8xLGzXkKNc4j4S4pKH09tsu9NMrXEOcEOHk707VNlUE+3jHP
-CX2X0QtLiAJno/Oum2H6PWOMpkOutm6aAcSGSl/pBT8jiXHuxsgoMJEXinVWGi2TedgX5aaPVDQ6
-l5Hnb8g2G3cpzebs98yi44Sj19XZhHnHEd84Lrs0MM4B0VQjvTUk+ya+ox7wK2+YKDYZfLO7yHyS
-9xXLQ+/YVmGUbcpmwVZIztM4D1TvLkycRF6psG2tL3XtlFgOudBGavEcMr2DFVX/HpuyarT49bB1
-TqL/BrdQX/wfZZj9GM8a36Ahkkjnn+OWR3W4AMsHCJdwpomZ+a8lA34npAAH1RibI05mj3/0h+TA
-uMVaAPkCtQoULxmzfzJtmcxtf5+28MthtoJ6Qbuly5rr79NWWqnd+ZieGuCPe54x9DmJmrAQmsAm
-9egs3LhRhf4Vet6wpUnQysjZ+MMHhlgC/2E6+J+sQtsHXY7ujYEzZFNxvp1KlxUeg154UrPBc9qN
-+KN02Y8kN3w9yBZj2RpFdFM1HmnMsQ1HefFEUd5Fkd7lh5ZE0Rxwc9geNUye9pK7+uyxWB5nHyyV
-i4Y9TjRKDGamv9FM8dzCb6g2bSubb01RJ184rjrYvnGIwm118tL7YjlZ7lDdCAauclfqQDODWs7T
-HdD+4aHPRgy5lUyHnqB1kp4cQ9jmRiuNivs1gm63W7gunvtJTTKeVXsfg4/VlIOyfkhCiwJusmHR
-np1t9ZIZTau/GIM1yf3UTZ79OKdl9W2cx5JeriY298ii08acKh3NBgsLavrYR6reb9JgiiLRztC+
-qdMOek3q30Mxv4hyGQKfSMFLKxQGIRFNwnM3t8KRpYTFkogPdrKpbaOAStAO1RkyaQTAwPW8hjxI
-zfIW41HiXNeDZd859lzuPEUU8tM6f0Yrre/CFThkK/YQ7nV/7046eMLCQ4/yMMcgl5rjmRvXfHcV
-wwjqMTatfAJNGFgr5ihq4+kb2zT3OK0YpFgRkVgRtHd4+xhuHB9ekiInlStDiRvjuVZcJa4YW005
-PRW+idO/RFhkMOkqGhPhG/uJOQNEU6toTS6kqHOhCE4E9SojGPGvO4RD5vLdULQnzekqAbCez91u
-gpAn8O90wKFSC04UmEeQUZ2iR7mKI2Wnjf+s94bxWDcgjAmJzSBON23eh+ZDFONIutJVj/nIBrva
-dkOZvZhu2xqbXHQ0pYAk4Q+vF8DZAl31okOpjT+rtSy9lcgS3IZEc1SXuq1a1bOJfvVONa33/Lez
-NlnLkmproksHscdsHQwEtt5rVdgOaKVPd17X0uNe5pNDiWhEHJDqFIQgubTTTq9zpTc3bnbIFEGa
-n1lVDU9JfN+L5gqKFw1ZYT6VtDDRJs8jSFWpryXzjFvR11k1zyeqg55ziDp6TzXTU8uWHSOjHy4F
-NF1+KEMnPhE47/0N3idq8mQdplegz+Yv8xh6zzArrWd+Tm1WQ6lXh+rRbz6HLHPENi3wTdOGUCf3
-fRk5+9RmP4DtzPlAuqerNJIQDEove3VHI32OzTyFC5p08psv0qkLktTtb+escY6dsIt7zRjcveCT
-cgvfybwpWAOe2wpMx5BF4RGff3HH7eXdTlWe3o5RX56yFFuFP8r6k3te32Z5aG94PIZfRWoPr72M
-7H1rYEMMhnoM77EZj/M2G1x9ukArfls65bG22KPCyElQUdhRQFqBbns1oSQ2GAty97XmpfVepjjw
-eh4/nBDNdIXbH7s/9X/Zsxb/D3nntRw3lm3bX+k471DAm4d7Ijq9oXci9YKgSAree3z9GRskVZRK
-VJU6+0FxixFtqkgmmEhgY+215hyzCDFgealq4vv2jMe+11UkXdgIZwnGik3pqpKyMnzZPI+9UGKV
-5dzTpHM6AoBcWz+PSPFkP9XZ+ROWNPOLE1na/RgN8UJGhXeOAkY9odxhHiSZQxfMKX+bMyXLOKwP
-dG03NhViaaYm6ywN+pPIsxOsrLke4UkK8niuGa17bFeDkGQwm1tzY1c4VZqRkVsXsgXzGxQPpPJ4
-9UZyC2dvmMCLZiZCsnXdVuq6oofGeRsZFZ4RJ6E36ziQ24suCCDLDbQZznyccuosyW0PnifMVzzD
-dbpXuC34gczyMFtCms4WZaBzH6V5pZUUy013ogymSv4cxMNLydU6JHNjeRYXenDeD5M6Q2skbel4
-YIAWWWbpj3VtYLHAAKMc1bT32PE6Vm/SeeNX/KGWH5lxO9E/qMD5qaJim7yv5haIrNcRCqQtuD2M
-PDRL1WBMvFY3JoI4R4bnRU8Ji5aq8DsvIxTjA8p5gR6mzwNtxHgTzWN8QEJnYOoSMjVd1rRfy8Y2
-RPnyRs3NCAWvvcWfZgC/EOLxb8ubpicSL7CNOSRLdZ6WUFJ0w+lWvt/a9GUd7YTJQX6sd0G1yeRW
-ga3elv1Ol1X/VqNxLBJFeAjDM7/0mOuuhshDeBbt1YrJzCxz5HjrOgGZoTw/5y1TjlXtBxGi6bQ5
-4+2l2LOaezYe6a2Mv2PnJVm7ottkLUupdDehqhWA2c27jIyrGYOBckOfNf8oEfOywDym7E0rVa8x
-Z5UrJsg3SqNRnvlJgaxMTuag1ctNS15fD6Uxnst24PFXlvZdqfvGvtFq53gk0nqm5S4ALW041RME
-AX7pe7uUbO4jBrPZsoV9JM3KrFA3tZ9Le9PG8M+2olri6g9pLWjjJrVza5u7JrbiDvSHHcrRnakM
-/mevMb6Q+JiceizICv11P1spSgYFxLOR1lWZv7Zsl52FUZBWNFN0udrnqUafZgCYsSPEEptzkV8D
-tGWflnUZ7ShTz2ejGdIo6hWUK0VuouN2iDPQQmTsqNjwxEtnZQw6zJVT55ouhrQaUzd/MkJ2jFSV
-0DxUZ03J9on9YFVtDJXtJJ43gmtjtOGnTlFanwyzUXcEwALtgCl5wsCFcPBOqSEC9y7eIofpOvOc
-62S0taOcR9mDzkTjo1kU7dqp0zuswDEZBlATZpQSecNjIuwxjIYpJCA9eYAPos9a/hnF9TDugObX
-57HqNQ/yYKUrPafrgv20XrkWzEIfIGaRdCeDrRKBauBVc6rwIyLjZi077vBUqyk+VESATH2CE6SQ
-SIvtcZ51xVE0eitoDlCLEqkC0NX6u9TyUK35dUivjeeuSvi4rUbdP6eNriOren9nt3p6fCrv43/N
-7xn08b9XT2UZ1Fk5sOZ9DxAWr/S6EGI2ZZcH8N0h0IatzR8LIUYXA7IwiSdMlVksvy6EEN1lrgMi
-VXSDldIStJ2XbZ79gQa4WAh1W3APf00ArAu36bfLIKnjOhkrzLRlSEHf6cqI4dE9J0yXZWrSYwqD
-3sSHX2gEitqV0oYr4gujeM0s3Kp3VqZJjzZ0bXfey5ExbobBNT5bbFZQcqa1jeDSD4Zr9jyuM1cM
-qzlqHCOvN00hDfI5BUK1MnqED/6sb+rWw0MmH5eWjBdc62P/hs7zsG/igOY0IEGKlV5/IsDUJ1Q1
-CC115teefh0WpXmWAQQpV6OifpHt4ajxVdMn04iuaj7rUjT/865XBvh5I/fDmduaUfillTwl3etu
-5bBpGTqSK8L/QDPx/zXUU6c/8f7NsUzZh74rrRC/+3o7QMKZ6Jw6oyRdEZyoZ3e2ycNfMelsQO00
-TRP+/dfbwWKQhOMKLyLCC8USGeevtwMlg4g2QAMBLEdTEUf+SttDFQf57oYQ0gqHuS9KUJzf390Q
-KfMO0H3lomCWw+Waqiepr4xngNhYOjPUYJ5hMPZsmfecZ30Y7Do49xtbCdojiYSCZd+q/XGq0XNH
-OoAKGZ+1Yx4xcCuvPR2rrhWqHQ+GpKoWo6crW3oDFAxapLkfGa+ZM6+QdJB47Guv1ESli9fGvWMs
-kiGs99i2BSZBr7ULiZYNvXaGQxmhbhfoBTH6Fvp4X8cmEQO1iD3wQ+K8V27mlM6sAp54gbONsZfh
-FXOvRw7V1mhBGzLO2Ky3ATs9JjPbwdWfMlJD0WAqwUXTFOjR4tTFedlnS68Mwgsg3DB4XMW/hMab
-UqYk8oMXax3dZbk7d1w1wPiVeO6lFNKOpoPsWNd2Z9pXOcXJ1pZr48ln9r5OTQ1FhcFtisLEYR5T
-aUtuUioRD/nDWkq04bFAwHfV4WpZOa1TbawgIIauc4dt5djBLR557Zh0IevGDvzstLHkZoDREdrH
-NgFJK7MotVWgwRsrbL+YZ0CJ6WeOynVZpMaeKUa66q0A6QqY/mUR68UZpBAapIVT4StG05KolrRx
-vc4HGAPaYdYlhr9Jh7Je2C6dplQIY5RIDZcIwauNy/K6UHpSj8YwJ7pZHtSZVHicdqY7i1RIa5qA
-F2xdvT2lKq02o+1L21F20BW0FBjY+/BAw2N8yLAgrGtP0VdaFBj3ijZU1wHPi31hJtpNJLfGzjJa
-a5N4TbsluipFLGrjke8IcpglVVYe+RhhV6oTuYuOpB1SEpz4No9DdRtkDZ04zvuqyXpjZTLMPJL6
-0liNbVTRtQ6whQ8tIy4bzulMc6p4Y4QGFQupHQmmu4cwT7NLX2LwSRsurU6tzCd8fUwdQUPRSmzt
-Bq2yImTnVtWFfquya73WK1/ZVEHGoD8ygSeGQUb5OQyUmQHFaR5FPYwkuZhXhhMS4tdQbmlxdTQa
-vbbqHc/bVqEp78mD7Y9sYWdgHJKxY7Z080rLynQlwcF9EnTNR9wmfFyScm7EfYP+uPWdFY3OaGkh
-7TyrzCCf+1ZJJmdJvjuNMy9HwRP1O4/p73mqtO1n3avlhe0kUriHRmsubSj4q2lt/CcYo4Qq4CeP
-gSio35caiN99fgyQEo2ckk61ZbH26RNy7PkxIJJbNZu1HvMaayN1ztfHAH1xBSfvV7k9goLXxwBJ
-sNhGqGUsHFbo9oiz+YXutyIEft89BoTggecURREiO/277WHVNRpBv86cuA30SBEBMdAOAvyuKMCW
-rqqS5y4zTL2WVTHQx3BLzn2SV1vfk7vboE60Ey2NlXP6pOpn22ufulAiGtNVBZu5dvMvA/PbVaaE
-BcLW0V+YbCgksyqBk1b6scPOZWG2ytOgyuctQqMjzJzNvdkYCgSMYri1xlgG7ufYnyKU5ybjIhRH
-fosSOvJHae10oXaEFEFeyuZgr4ZB8X1k7F27tv2c5l8ju7cpY1EGxgjD6PA4CS3OpAmYlKFv0lkw
-Rt8rjqy8Oy2jBgfRWEbHpt0em0j22kp5xG0lADm9viHTptjKOfNOMlTYf2IDW+ZAqObMxgt0QEV8
-E0aMvgYzkI7A8dPKiVKUcmUQCZSqBIx4MCW66u1jjMthBcWqMMiqz83j2qrTFekOWrN19TrYaZKe
-A1Eu7qsgaJZEC+TXZXkUOv6FmzT61gVIdgdPrvqU9raFf4vU+ZqlHQ51ZZ2z1NbXSWPmtCLT7gqR
-tgW9Q+RTwYvC2Vl4Dk3jCk2VpMrpvsrrYNuSBnen1L1CYRzpywg3dTSb5N7I7epj6s3SAKtaK8tU
-iWUgJ8zZERQMcy1Wd8Sf5WsZ5T8/RJaEUjYLT9gCsnpITrKqrO5cRssLIHP1rDIradfXTB4RVUcz
-pJ2QynJhOWiF+UAWNoRaGBLsEmsCZCFcCv7kWPCFeYEJP6mwk6OhE+aGQtgc/NhWzmNfATPJBhfa
-Zukri5gB8k3k9+NZOmYj3Wk7O4MJkuISoSmKXZlhdyQl1mkY6bfaWONtI78TU1pgnZhZ4c/KvAyu
-E+Bg+z6RxrM+LOeel/PMIwk1IQtR9RYFE5q1JOunPCjM+3/Ousk69pN18/H9pprYtD2vmuYHjElg
-iFgzLRPKqvy1qYZ/CR0w17wi1k1dFWPGl6aa9YG0TgptYrKp4NC4vy2eeUDScaPnjwlVFdXuL6ya
-usgA/W7VRJ2FD4oCn+0rmAS+/4ZtVA+5mwIRncelmuyYCo3HpdF5HQpdJg8yrsPreAiTfdE9SHJj
-nPQWafOFJQTBTPcIrVGjYyeGNkNPp8RYUNhBDqi9EiL7sb4bWLGipVYZ1w0pki03shR4M1x69L0c
-j/ireegkyipII2mcEXA/rEvTLMMleuCOJ33gw75GVNzsMb/Tu7LU6rIBnmgJvl24BUZPzLzNsG7p
-Zc2wyUY7ucs0A80Wuw5nodkSvTfZq8eZHUX5ovQG61Tz0nRfJFg6knIYIJjn7QIFDHNzHzv9LAvl
-SxeL056ClnG+N3pH6JtyGQtOjESB4nBDF9RZgYGOZ8BXlK1rdzI0QoZXH+nCWQu90eu9LmnyvAcT
-6M9zoX10hAoymASRWkD+2QLcf3HrT4pJoZ30TSOuL4sh87BcCnWlgSB0ByknhF+E5fVWehZiCk1m
-2wp5ZguZPjrthWoznQSc5STmzPrUO0mFwrObxJ6jrvRr37eWllCCGpKscAChD20mqWgjSdDdKLN3
-iE1tzpMaVbuR8JIe6zBaU3WSnY6TBDXsNOThIUmvnxWhUWUMh1zVsyrLRWM1uNWqGpk5y6HSbBVV
-kfeKg2nDDYYcGaqNcSXTKyR00KCo/+mRGn1x45NpuGyNLERImqvCFDasjWpQT9ya53Xgclmg4t2k
-cvpYR1bKWG1MFlWWm+ugQWXex6m91ys3PkGEGEdwpSyJ7C1lPMUCdm0V4ZExFjDRU93cF0w75kWd
-kOlKi5K3OpIwRjbS2o0geLWKc5YNvszFabOBzBt/g1PaO03ZRt7D/LhRoViuYQCcF0D+Nvg+czRT
-1AFJkn5SKupSyY9ErEy9cTM5v4+9DpuX2tC4IwTzs29D/JXDYgXeGMTWZRNW5mWQuzuYwSY7Srw1
-vM9oaRYOnsDYJeakbnXlopAc7appRu0CCjDdSuJ3L1IGMmeonpyjMYl9otqQ4h3BQvRvdIjsPO7M
-FrVyXxvHvRKla2sIn5CbaPVCtYKr0qlUnh+yPmd2pc3HilFa38FILwlnhQYmVO/V4C5ss0FU1LXG
-MaxWZSGzy4Y0nhyrnhGTMp/l877SZQRVvnqmdtGw0WQKr3Lme0kO5b3l+cLEWNuqMMwXo54GT1Li
-oMS3Cu1Srwf1NtEL64HgFucqrath1o+DfqrqwycvqbeNTpvTzOVsZulVfxKjwPJnTlvYd1Jpd2sP
-RxCbRrLZsBMssVVvAqX6JFeaNvP7z1ZWLS2oJwuZ7dinqsyHFffaAtLydS2BsuzcR8CYc4SN49Jw
-U7TjdhNimsz6aDE0GpAV24DHkt02FoYsQY5csn+NqZNKuIvlqJ01SvpFGWpca+xh2bNLQufe0mxr
-9607ZEdlTUpGo6uCe0/CQp3tek22oUJpZ7Zt7vTAf8rJLMIiBJsprkyPqqaKzhwbn7Lc1idVVEsr
-P9Jg7gb2HptAumyt+HKo3W0OC1Gu4pt4IJ3eSfaUuAyIHWOYyQpsFzsr7xBN5dQtNv33nIFkNCzl
-kDDPeDgPAyCeuPVWyoi6SU5TgCDC7GVbBLV6EqM6Y+cqMeIGqkKckjN9rPFdUuXOHZmSKgmcFUTi
-Kyu9tvr6MoLrMXeopvH22ZcNtVATdytDL0byG8azoZRW8DR3GmKTJvKuGem7mFm51Uf0Swv6is5G
-IuZvjYzJ+6gmxqweOtgwlsurOvQQiRwJ5lGuI0URQBSvtT5JZkeycOd/ahFvGrMq67NkFtt9tPet
-ztvpxPQto16RhLPQBZtW6MdeFEM+QUC74uGor6QkCe5rIk/m+P1kfB5lvHQ7R1/lhmvzNHDSRSj5
-9gmRGOlMTQsi2LDWL3tDJY44N/xV3HjRitzf5hhvnIGYN7OWvU1v0gjHy8QlYCDBqZfQcjhxYyww
-ml4ui9HZqImksnzZcABi11+WjD7Qy2ouRsN2l5YDM5O0G9YAM5FLl7V6oUmYRFC1qQx8msghwSEK
-F2PRyfdDMHQXXmMb1awj0lGaV0M7auzdW3lrVE5AYFxJPzfzudlOPLhgd5ILhcarTOifsRNtTTLa
-T4HeLuDSjPOmHPRdUTjBekAwvf7nlH/USu+Xf7P74Smu3keJCwDIawnI0JSNKf9BBU+Xj+LweeOM
-Nc2inMNixiSBOlB0Vr/OVUGQiP4pfXpSAk2Zb72ME/QP/Ct+ga0zme50UX9triqLEu/NQEEY1RVD
-BSdOe5dxh5CuvS0BrbhSdewoGE+K3D5io0oipy0ljRDBVqm5dB27Rf0NdjvYjM1QX2me1kkEFg36
-OGNEFw4rL030u5pYnI9SKedfKIaoKCupWduBrBpzxSzC40QZFDzNPIbVWRAwYqOFmeRPuF4J7gtL
-nuxLPWyTNSLryLjI0RZ5M8T9tbwMLau51tuiBvDQOYAB6SuYt10Pd2imoIQvl6Mmjw+pY2ZHIOFM
-2MVQ5jZWwfYfLSZyjnkfaZSKtK9y5FZwm+9RxtjoaIegJVbQQky+HOuM8VtRF9dSk1UdgZ0leXVw
-wWYwL6DW+uGQX1l6IyI7oDKmAh/ZVbuOlAJo1rbj33dF6jODlIv2MQGPFM5Mld0s/yJsb+PKKR/S
-WnPA6oIovCSrXmEaHVWgJjAN4XjwCClqZyqtR/iY2A2++FGZnFgYfMEq9ad+TJTCUjWTUKV0rmlJ
-u21V47SPNO3GF7pdireRsHejRIdBCIwEFIRUhnA5KGVb7NXG8aqj1DfsVVkwCL0tszzBL9/6rbo0
-yFhfotaQpXum68oDnwaO4kHvg3rT6tJd5JXlZoiPcFF3SgWio46wJv5zVgpuzp+tFM2D/5MOG7/8
-vFCAv5NRg1o4Tk1bYzxBC+t5obA/gGhVAe3Rd5OZSTo0v14WCpF2iqGUpDXGLTrTSW7vl4WCkaRD
-0hnNNxO5KuvMr0WXioO8XSiY5LCPRYTBVpbuH+OWbxeKOBh0trjd2tYwV5IaLqe3UJv1a2/i7KAN
-vaB0MrSNJjg8PXrMEUmGUroL9CPNJ9CnlbFLIhuAD4YzYD5Dh2xupk6QnzwqAf70E/zHLiu+G0xQ
-INBAAIJauldzZoNgg5IJIYTI2213XP/w06tRJeiTvrpTzcPKGZYhkAWXQC5BXvcFhJ1NkDwvJjJ7
-JICShS/Ykp3eK+pGF+BJZWJQmi6QVxy6PNjZZGkOmiqE/NK6cDzTW7papUImsBVd4/nvdJ8aODIu
-ppmO7V5atsuGKQt9J2fwtWWVF729EciKLaKpsYMALxidoGrG5AqBoUnoNfEh6AStzmyJ+xQEUFfA
-QJHCuwhOE6vE4wKvbE0w9bA2O8Tkc3AaNUWyURJjSrLWrs6LsoQ0G+U7tnAYKZAiHFllMADV8N1e
-X5Jl2X8cVJSkSx2a4GWYdKEJzq4mDw0gjnbn6ESLLlO3dVyKE9ndG6FinMkRLoMzMHjx3eBFEUUz
-dixsUXqDoMwpS3cWiIhIwy/YpFWc+Xt5LAg0klVh+R+mbEnXJbtBEoGTnUv0ZAYdihpeEomUmVa5
-j6NalLfJc2JlSXhlTY7K0PjwAOop21IRMZd4eEm8BIDUMVwQOZjkgpOJifXfohUB2k8yrYp6hg1l
-sUhgJnKOKvSyxSSdHScZbazK9pwuNTlf4SS0bbtGLJbmOEoLLXMaecYEKBr2ogYOeaDlUk2tKJS8
-kHlZ54G+9fNeCPGWJuC2c5PtzD2cP1O/xJ/ZVSsZP6t8Q9pmdoM8xVuhVEZD7KGeOdNAbuyi3LQe
-8XyRzjUI4bE5aZDDXsmDpT5pk/MOghS0d8YwDecIOZIQMpPWQMaqZbATS0WgF6s/omezCobb0OQp
-B/QATbTk4GjOhVC6mCTTk3o6zwxyzpVJWJ0FYmw2ya2jSXrdCxU2rmDTXhaTOJskIITaiI/Ss3aS
-b6eFkHLHnV2vdaHxVrOxhihjxc6JJDTgVtm620zowrvMN7eCIjiPUFGetHpRXkhCSZ5KjpstZL3m
-YUg1TzdHqM6NSYAeTGJ0Ywzd4zArxnltawaEZy9nSRhKvGQI/Gwh9WPn15lbMgRQAMqTGrARwsBc
-SATdSS1Yj0SZLodJRVh0fr5DDPro98lJGWja3qOzs1SF7FCdFIi2ECNaTqOWi5RgA7qpZZ5R2E/a
-RXXSMWZC0kjDAHVjgrz8hkUZv+6gVoSDTUrIRIgi9UkfiXJLkk6B5gY4xl3iUi61zvA/Rg6+XFQ7
-qr7iruh8tjNSa2wNPvuPclCz31Or2jlpywpFU6SD2Wi6IabvEbPNDLXxKe9Ko1zLgSx/KRFyXYyd
-mR5JiCZdQgvRYC58L81v3TGEehzFZrrP4aC288IfTNZTv4OIrFmDHKxNcG/cEXG1ASWwySeSmOQI
-qlg5EcbQpDqbzPPBjpVjCYFMwMgMFSxZLABlQ82NfyXxAg3nPEA04pDN0uzdqm6gsE2cM31innnQ
-z/qJg4ZFTs2WSeKhDPOtBpOcOnHTuomhpmsZHp9gYqs5cQVnLZ2Ya5XAr/kCxObLgsmmT3w2f2K1
-/WPKDPFof7/M+Pfn4P3diPjV5yLD+gAXi4GcYFowe2NY9lpkINnQ8a+IeHTSg1TsLV+LDPODMLYY
-7FNkWocUGn8UGQz/6GojCgF6aBPweqCJReVvQqXO34CdGYKw9p2ag+sj9GESzm2PEE4E+VeBZpkk
-dgYpCXpC3N4YzpmaSe28HyKIQmZiLRMlDRaI/5HWN3Uzl0ziBlE1aHODBItz+q0soAPJJuOocyFb
-rK+JmW7CsA1WhLoOq6ILVolW1+si90+AXt+Su+nNPKKcFq7E1FwZrQeDs7apmwAHbhIs/CKTt70b
-qcdDTYvArZMLXQrV8wxVZDoU+hbNRHicoxRbeSFjdu7yjcyjoevivYQwZFZLNLHFu5BHjHWRtRuC
-nWWF/p6yfEOsqnLEMHvBxuCxIlz7I6C/VaWSao4lWeBqjP1ouPJcDZBV0okCGyuXq1Zp78au3KCW
-X2NayMkjKUEJ5+OjG9IPcxJ9h+hVnqWSliwTIjg/NrGc3MEpt+8U1cNcbDlYg6nTaP8EK80oUInF
-XXDs68HIYaKVqY2EgMpyCSqrlVeBoZ+jc8x4AoZ4aMqPjhd1m8apzomFCeimEHqDtWPTIOdfQsPw
-5t74QE7Acsx1zkmkP9JvvumxajwFEm1iLcVPI9XDuTaC3orZKrKFooespPqjrPbhOXYmdamllrMg
-PSmbQbAwUCbQ/VIzsOtuqyeUHMPwKCMN+GQDKlk1StHdGbnHilfL1UI2alBUJdmkBQ/HfWoqd4UC
-DNges2igdlNY9tXIPGZM8RgGIc+8Co281lTFSc+2aWZ58aMz6MGj+D+BR6JuYaUtKvuy2PZSFR45
-xONg3oYZ8ggUP/g0ymF6lBemOgP64a1NP3cWmVVmWJUGoLhRgFrYHxj2Rk2t3+S15982GIN3qa5H
-y1ZnE24yudzoeAz2pezqNw5gxY1CxsklefLdJS4uibZa7tsec+mOGHezD79Ezlgv09QeN1B+gxM9
-yEiYH9CvIE0ao7mnyuG+Z6RYxuiUkU1JwC8QVLhCWlFkpHzxDhBcyDDp51KQ92ct4+6lLIQZ5qTR
-iFFryEK20QgBR9aon70IB4fCSf7clWh/rVptiC2P1Aj6dqpuYnY9yzJr8lXQjdKyEvrkQiiVm0m0
-zDOIh4ZQMitm7u3AYxd8usOpKvTOg1A+I6dyjlPsKXvJRBc9CoX0EKDRnLdCO126bOR9Ez9obsNv
-iSO21Vl/CYW3XBlCeV0IDbYr1NgkM+cfVaHQ9nK27iFlsJhFwFyL3I0lFN0MAtB2K9wvZWskt3ZQ
-3dtqTSu9sOszyGrhzoIKsCrbKp8LlfeiM6t4m9AQ8Ih44NQiLc+yBkUwLtRLF5c/ahuINxlSnVtZ
-C1Clay4UUs8yy42hq9lxYg7aCRPsfpW2HZMrPGQEd9KOkcdauSh55V3jd9FKkeRwq3gFsZ6W0R0n
-nmwu9SjgBpClaq+wMbtKAnEn+81wp9mxelOWdXbbQc5cFX3aIsKuQXO0KrRjVq9hJWDgSzPhvwyl
-f7TNvl8TBOYsFL1SthJIrNvRlKqjMB7KHd50+6GkDTK3ZRDikuMv69Ra6c2wUKrmdkiThzDtBxCn
-0Y3cOnst9E481kLDffCH8x66aE5vh/NfX6l6e6+XtjUHzECyvDoLGz+Zq21pLg01vYCtZe6xBp4o
-ffo0NlkLrbMJFmOd2lstk/VVBub8QWuz30gI/aI0WtzX98tJe3zePJXDxVPVQLB4neGK755lQVpf
-Zf/ZD/38hV5Uz1dD/vT//uf+EXDTIqjqMnioKQ++CqJpuNGKhFD1TbEx/VnT3/yzV4GyHNTNIy9P
-Y0IEnmKV/Z9/xVnqvf5r7QPDDkwhotKYvt7Wbz97/z9/a88n8uc/880f/pA1aS0+AI+ojLdvX7G+
-R7O889a/e4U/3jo5kPR0qWBY1KYvXvDNKaAE4wvF8+u3aQhzqt9cIO9dAj9/e798Ct69AtB5mSii
-BDTmsGtA+UDLysYnSi355gwA0tZMXRHyr+evZ4Xab3QGuEJlpM0Hvn/zg4ptEhrd6/vkBd+cBvTT
-xFPBnsM/NX39rheCkO0ddCFYH0RcsTC5v3zg354I+puU/exLnkcuv9F18HInCDXhQSeAUGcVuDCT
-oJcTwDv95kpQsDEjavzdrwQBNjzoRIh+NfYZmxnW89e3jwfrgwlg4c15er7yfqMrwgLA74hx3GGn
-QeQFENVGgfrNhQDHkk2vqhoM/Z6/pgP9Ru//9dnwvaj4nYfkd8+YPx6SJneEibNEsDlf3+mbO0L7
-QKiQAGq8fvt3XRoIKTrwUlBRAlrIplWW/zdnwPygEyStY3V9+foNb4Vp2T7w/fMUJD3K4L56eZ/f
-Lo2Q7OhUMd8CZjd9PXfBfqM7gnGcoVmH1ss2tQL26SlP/M1VwH1gInekvfabLgTqobUBHUSefCga
-Xj5fYR94cwIIGSM0XYSn/Prn/zcukq9brzlBEI/Tpit4qn60N3vvB16L8j9//82eSmwqvvlBsQd7
-Pvbzxkv88/9+s1hOG4I333zdIEzHefn1lzf450N/c6zXd/X6LzcBrtiSTff0jeHlzzy5T9i2nQ4/
-kDV/vcL/+HP+tH/8+jj86auD6/iz5ZCXF+Xf6ybsh9vTv/Xy++6+/EETnKWFvjI30KF//v7+sUl/
-fIDnmuDQA8xRFVf/ugjap/JHp0lYkinADj3KDH/VDz/ll33/oa//7/Q++fyjD+LrrurQI3y6T778
-8KN+qU7EQ/nQY9xln59eX2X7SEPjeVMsntKHvvQVf/vnH1xHr4egX3DoIS7/Rojj1PH5z++26TKt
-/nydvr4LHgyHvou/ldp14Nv467yZQw+Q/sQqolE3HHqWTgLvR+vFy+cgRmgHH+G+4pLt3r9kgbsc
-fJCjey97/3ISKT6Hvo2/DhM48KPe/zW3+dAjoE4OfvQMev20/wvPh/39jx4Prwf4L9zWf4e4eOB5
-+kvm0YGvD7P/r7LtDzzCL8NLDjze3+BBHHqEv7YaH3qEn6y0kynv0Nf/nKXDT7Sc/4UH9+Iprt9f
-Z0Uj8tBVcPaUNk/vPrZFr/fgI/wdcfyBH8Xs/q9ltQce4t8RT7wtASfvnizjv/D0/vfjPZns73/k
-QqFz6Afy1+Kgn56qH20zvw6s/rz5fB1E/ejXvt1Zi594iJ/uy//9PwAAAP//</cx:binary>
+                <cx:binary>3HvZct04lu2vOPx8qcQMsKKyIhrkOZolT7JsvzBkSSZBggRBApy+vrc8ZErKyqpb2dkRN68eZB+B
+IEFsYO211sb5++3yt1t7fzO8WFrbjX+7XX5+WYXQ/+2nn8bb6r69GQ9aczu40X0JB7eu/cl9+WJu
+73+6G25m05U/EYTZT7fVzRDul5f/+Dvcrbx3Z+72JhjXvY73w/rmfow2jP+i7Z82vbi5a02XmzEM
+5jbgn1/q+y7ev3xx3wUT1ndrf//zyyeXvHzx0/Mb/eahLyyMK8Q76CsPKEdcMqbSbz/i5QvruvJ7
+szqQUhIlmfrxyIubFrp9HcWLt+Em/MuxfB3Jzd3dcD+O8CZf/33W+cngn7XdutiFh6krYRZ/fnlh
+yvvB3Lx8YUaXfWvK3MNLXBx+feufnk77P/7+7A8wD8/+8igyzyft3zX9NjBu6NyPWfqfBwaTA6wk
+pyl+EhBMDyhSCFFGvgfsxyO/B+ZhFH84MI87Pw/M47a/VGDyextg0fxZO4YfcCIpEkh+DwBsjUc7
+RhxgqRgWcMm3H/bj0d8C9HU0fzRATzo/C9CTtr9UgP7rc6z/bYD+F3fuf3U37efh347gKbr8K1AV
+BwQriqn456AqDlJOMSyS31ki38fzRxfJs+7Plsmz1r/UQjm9uYvdnxgnjA6oIpwSTJ7sYXmgOKWE
+cPR9i6dP9/C3cfzR+Dzt/Sw8Txv/YtEJo/lTw0MOuIBsR+R3KMXPoiQIko+AWD6P0tfx/PEwPen+
+mzg9af2LBepPJSr4QKVM0ZTALnmUCNUBpwIwDv8AQfo8PH+cqJze/Nr3N4H5tekvFZWzm9KNP6bo
+f84fBdAUkSKK2a8Y9ig69IBLyRBiP5qfEfyvo/mjW+dJ52fxedL2lwrQZRm7PzM+qVSKy/TH9nhK
+I+kBowq2FCXfsQ8y1DcG+41GPgzmj4bncd9n0Xnc9NcKzvonai8F/I1jSP/PY8IFIypVkIeexGL9
+w4rr8teuzyPxa8tfKhBvzHQ//Ik4xg4e1BQioHm//YCeeoRj4kAJxJCSP9qf7ZNvw/mjO+Vp72cR
+etr4lwrSp5v2y82fqXjArUAgiBEiz8PDcIoZxT+S0DOO9n0gfzQ+z7o/C9Cz1v+nI/R7g3vsWjy5
+5j/0+dIDAduHcvGDS/Mn20gePARIguP06y57DHG/WG+/P55/7vX90vHJ4P/Xvbzfdwt+0e35TbjZ
+fXVRH1l9/7r1h0f4rOu/spa+zdfx3c8vscCCEEbRo8g93OhpKununuWSZ13vb8bw80sBuw02Vgqp
+CDwGBm7Cyxfz/UMLe1C0EqIogPiRFK55+aJzQ6gerF7JYX+mShBYBZDGYKuOLj408QOlUg63Qwgj
+uIDSX0zsV86upet+mZjvn190sX3lTBdGuPHLF/23qx4GK0kqU6EIUUykFKWw7qD99uYN+ORwMf4/
+yciapWmaLIZgTwZaL0e0FPK+wlT5fINBcF3MU9PoRzP1Tx4LWeH5gxUiKUuxUkThVCJQHI8f3HGF
+B0ybDMuppHvVevIFVUyYC1vXCp9XZtsS3Rbl8HoV3jRZV/oB74Jt6tdbycpSD6V4OySIXa8EuUr7
+rlvfk1EZlTUzqm/WtAnkUDhczXnlpu6uSfy85aae2kIXI3YnS6LGkEfRpC4f1lkMOmDO43EwU3+q
+wnveTIh4Xfu1CjpNh+QstGk36rKyuNwJ7rrrJKnwFzVva5HPhf3AZCkPKU2Y0+XKQqPxhLZCt2Xb
+VnmFV2V1v244aDlvwmdqRmOXrcylWKtkE5ep913QwvV91DNMwPuCJssbUsV1yast2kF3dZ1sWTds
+bs061c2dnqZBEZidmK9oxR+hx6TttjG9bas6c/3mj/pqxud9K5tTPxnmsmbC5nqNeH3FYi8/JFYt
+n5tya2ZNSS3JXkzlYA55JPhQIhPXzHqvdkm1+EYXXTsdwxL0lU5Vz15txSBdHnjoFk3q0fYZioV9
+O0oaQ57Sd7KPMN+jXxKu52RRre5ik6ijZDQVPZolWtyFTztv9LTiBO1jG7PFtE23a1NqNl32Jr6d
+aR2607pzZZ9Rqup3Rgobdi2iW6unoq51WIaFaiu34axo1zVqKoVJc1tUTZ0ZxLsyo1Uv6Y5UoZgO
+aUjZZ+NafJxIPBWZ6DbEdDkNEmv0Tjnp00xsrMmachSt9mtdFJnyqDWZCVNojnpaqGJv61DPucQt
++6igaDNqJ/gg9gVJ2vR0QHFez1afqCkjKz3GqUiPWNIUTtsupnS3bmmiIM64v4+Yf0k2PyKd4gaT
+LChcSO15xc6rEZOgm1EWaTbz4lbUKbuZ1aquEoTLvENTsWrnOvPGsqk6HpfRNpdxge2ONTOTerss
+q61hHDIZdb8t0R4/LtA8gZRb16+DKavvpbFfPv7jsr/v3obh/j6c3/RfCze/tj39CNj0He8f8PTJ
+h98A/O9A+Lfq3O80/kf4TqCA9ksF7jf4/tY1Lvw+wj90/oHwCmqKOAWFCDIRKQ44/gPhMcMcrGMq
+UgJQnkIm/47wUBwCSSmgZpQiKEAACv6C8BiDHYMe4FhKTBgi/xHCk4eBPcZ4uJGUPEUS0ggnVPBn
+GC8T3qdVSXZpgma+Y3PTHZlyOeu7Yrl2dCtOjfDuppur5DYRpjuDt10/z5B8LqLAKhsqngJi2WbM
+C9vgd8OI1UlhKn8kqpZ/EVuBJs24x5fS4phRGYoTMRT8tHTTejzDntivybR+TCKtdram5JN3nctJ
+MV24idgsUW4q8jauRq9SqNOa+/UuCjSWmdua8o1BtFQnpSuqMud+LF4NxJWvUYWM2824skzLZZnr
+DLBEnc7tmM75yPtk2PWOFGUWUK/cPk3KxujCi+Fkim5gGs8KRwDJBauzdN6K7iMVHa4z3yKf6DpF
+zXXE0k2HJmzCZiVt0auCzMWSubZbugwN2CS5KUR4Pzoch5O1XOoxl3FTRtdDM71TDSRdPWAr3w41
+kBtd2qK+stKyaq9GK++SYgup7roRx31CNvJ69aWZAXMIVzsq6FLtu2RZB628Wt8FWrh3NXFcnA5F
+lDybSdshXdfFbC5K1shU19IU9yKO4R1T0z4xzaLVbOs3NjHEfl4r2bb5JDf0blqL7lImGwuZ60N4
+Vy1lVwJm4nbnmnl55Ys2nDTLYnrdAQ6vu8Gx5LBr2Ha2zGN6PiVi2W3MT1lImvHS4a0Iu4qkwugm
+qeK9SM1Izws0dF+muIxvqjRJ02xJTNEcTqmdmNLO29R3+4HzCd37BgKjEwUOyyGTRb/tlRSsdrsB
++3q52LZ+lWdjO+J6v5il6s8o6es2a3nTb7uRj2LYB9qq4dzTetjgHYBx6MK066LLpk4BJrHpPeR3
+u+Eyq6rQuNO2UHGZ83Qz6Y7MnVvzalmK8dgNkY/H00xZ3PUrJ9uVQjPR3TT5d9yVHh93pkXXo5yp
+uzGub0SWThX2ufKCv2FkxPek8lOryRDW88kjoZlFzdGcjrzTW9KwWRNbUq4XQZNG+2RB5Kxux+Vo
+aUN3jgchj1c7yMNaxupwtsF/GGWUo45VtB+StWg+NGXaX85zaN6nja3EvrMJidnc1OJsLEJ1yZN+
+irpZ/WiyVJLF5DUvjNMN7gXWXTWMsKaq5pgOJc1DUS1DpshoxiyxQeyWUdWrDuVajXlfBp6n1cqO
+ltFJo5dqZG/ZIPAJtY7exWHeLo2pN7JLUrfc9rCW74Yi2BpeGg8Kpq0qzF5spLI6FNQBcWLNmnOY
+3UyugJpAWzzyx1S24ridIj+ZJBal5k6ww4YV5oNxQ7OepDTaKZs4Gt8AYXKJpip0qVZtlVzO0jo4
++gBI/z31/KWT2hNx9sPc+qo8JGSX309nv6i7RzLnoce3HIbZwUO24Q8qgCoJxZofOYxAg4K/phhO
+nqQpeG3/NzmMHUAl6MF/A4HxoFSh14+M/WT24ejN98+PVQqIr+c5DEp8jDMBORMjSLMPOuaRTpF2
+JKyOhbZTbfrlcEVLbYGuOpQebxat6qKXZQfLczJNdR6DDCGnwQ7jcV0uqsmGXnQiW4gY3snYGVjX
+zVzOl6njVakTbjwBeI4eqZM+4K5ONSOEWAc9GkRzPPYbKIwWJWbfEDnUR3JlNc96VDtxzrpxRhkI
+s8TpwaDIdRuSFQMZBD2XTUsta70k2HVaUMwWPVrXBB3Hhp4zXiWftsQIrn2ckdWcy/WcjWn5qakN
+rTPaknXKOtH2cL+WFbOG9G2sblQpe2CToWo1a+Z2y+qC1Cajc50O+SqW4HVVyznoAIma7ukknNgJ
+ZHqXJb4R6xHrmP2QyoZcsIo5UFalLS8HSEg3FVb8gyuDuusLkg7ZuPJoNGDG1Og1Riw+FAQeeV1i
+H7iu2by05yuxaXsCQtFOuoO0K/PIEVPHzHare0u3WoR867eZ7Bq5pWMme6m2HQJwqHTNo3rv3Ejx
+W+6quJ3zeohnqSjUAjFMbN9pM8btxPrCj5fjWCB7TOqogu4FaU4JJMqg3TgvH7oSMH3vU1XNo56W
+rnjvqnpi+zlNqvZoLKqB6lL4mu68Gf3nYe0c1ptX8rYSXVFliKzs/dzy8BGZkPAdtk04jMr3Pqv6
+Tt2OhXNDXs9mHg+HreFzhnDrmO4Ub5FWqhyAvPBk1ljEle+HWsg1a5gZrUarmCRon5bKbMEwrEPI
+WsukBx/Ho+CS5K6aEjPrZTbmFBdj9SYJZvyCGbsKpuwbDToAkcwG1ffa1sq8jTOQfpigxu+txQvN
+km0YEg1QS6+JWxqsG4baVcuV8zeRTTXRUx1RmZnKbr2erEgTDYxmJKCe2uXD0kF9N1t87G5JSAxk
+BBpwqzfBt9feCg5jw9i0e0Kd6kDCTFuT0RQN9xVpi9tiboFRUIY/G7TVdj+Wbpl1lL6bcjEVvIHf
+Zv4EfgdIahQRGQ4LVMRemzWlTsel224YENXLifJYau+HZdPN5FTIEXBJQPrKu01XxNTuhISBjtog
+4kxW8pHOGhXzijQxG94+2KYsbtsZM3nYt450p1zFsoel2/bj264krMpBTBlQnIE0r3DNyZti7Zsz
+nGyhyKuhQXfeT2Tbl0YsrR6nWn2oeSleBxHSD05KC6q7x9IcO0uDO65m215661CjW0sKBltO1n2W
+BlXek3FFkMwGrxA0zhvJRuByrebUzWVWLIu9mquySgHKQOBf1c6WH2P9EJ/U1obpNWCFcrHOAH2L
+sQRrKxZndQX2DIAULv15qur2ChF42q6Q9fp+W2daXU7tOAhYhyI2b4aFDUVOUSKavFBbecSAoMyH
+oFd42JWDWOyO1/OwZtE7VuY0sS1sKGBkSHeGWaPToi1H3USZEp2kkfY56zBwyX6qK7QHL6mKunTN
+w9ulJnE5GCCTh/edzPmYEMq0wyIFN2RTfZGrgRZiv8pk+pgg6T62zBOwO2agLDrxpJzzsBi6aRvV
+WsPvMixayFFc2rGbP48qDKf9Um5WlykHt6RZ+6XPR8HoG1iwC96tRWtTXTJWzTuzemFzw1OC8h42
+XKcp3cKcFSxScF6EquedlH1fXRYVqo6HJjab3ogE0eHbKeil2OK+Ix4w2TMIgVpt0oKf48f2vNhE
+505Da+uvBkEZdwxyELCujdftXgGDTneiaLtPRnlYFBEkV5cFn8o3YwHMX/NeVCK3AfIdLOvFfDQG
+zJZsGDuk8hS22jvGRBj1BqzppGgJHndNqXidlawvggY0RUhDzoiDXj0oBh2SNpSwSW3ic1s6A3ZE
+Tdr3ZqyKLpcBcaw9/FoztKD+PTEuTbIhNrD4JoO6KrNdyz9WoWrKzLrC5IOot2rncV/1GkOB+m5J
+DfIacn39UfFCoO6YzSOf5/eFaGFDa1EN+G4ObXcRt800muBNHvOxaafDwpDmS70Qe8EXwa9IYraP
+NpLhtkoAC7PVOXGHx5gUenUIvV9cna6ajoP7wkpeHS6bdKcWb9sng0k8Twvsna4KR1Pd+3pwufcW
+PELjHX6zhg1fC16XlW6la1I9Q+8Phaez02DDbm8ak2xfmiRMJ1gCDGSDYQFodr3FrJpkeslIa1Zd
+g/3K9TQQcLqQBwdRh2rCxzxKWDNxbsAW2mDTgKaM80Rho0ziXVMmCDyjoZDgwRUs+D2ryz7mbBlm
+MKp4g84r66vbcUkapRffU5Zxa1f1uqQbttlowO29GOGsc5klpZrXRi81CDBwcprJ0JsmRaGCjlvA
+8XQmZbu82raWL70mYo7qrEzx1JyJMplqyCwLiNp3wprQ5LOqGayBRi7FEdhvA5p1WrYIH68Jt+j1
+sHqFM8kG2+ZIirTLG0H7c+W8sqddqECbya3Gt1KV83yH17X0Z84WNskBgcHeW2waTb7OTUEfeq5b
+ZteKfi5tUs8ZRWs7FgBFrAi5j6Yo8m0JqDge4xqra7GFhO3GZOzqd2GdwBgAlYzqo8LMJchJASiP
+QeitMDFpICuEfRun4lNkbKQ7NHcpO3LRKen0vxOWq6gTcICnlLMwa65aBsrfhGL9EtIFNRePdaRp
+SjeAgAXxeFylDd747rte3FCH7L6a+yhPQVvSMmNb6cozMjFbfnZDMqR5FRYEYap5GzLDChgoeLjF
+fLQUkdFFt0tJ2V1cQrQnZTOtzasH+2bLBqDToLJHH9BJ0a+Tz9AKa/fI+sSLvUdbYzNYpo5mdBMG
+vx/RRsxh6SVQYVjIfLlSU92B5uJ8NmBcE+/lx3TG+MNSJAs5bFUsvqCoqAApX4sVUKJZCZjsCNWa
+bLCY8zC1MeyVn2Q46iwIr2OY8yZmK5pAHYqh9uGyBuCxp1VN4n0CNPpcLYX8JLsVyT1Wa2P2eBhH
+ckjVlK67uTMdyTaJiy0D66Lk+bZJ8OjZNrmLXo0J+KARoz4Dm6gsz8AFNzaTCcWrVkC1Fz300n8G
+TDBxz6dRwVLHyDDwY+ZJXQYZYZtjZanbMaAdHthaBEkrC+LjTgiFvniKGmDwqemAfzebpzsRiSfa
+dVVT5ALLxQIHmYI9BILABjBdF9hvRcoB9XrIm1csNSn8lzL/zjFg0/u4ysCzYZ7ZmLUFXsSul6Z+
+0w9r9aUjom4yO4nY6nRh62noi9ZrcMx4yF0nWandMEYHjriYwRxKW6FOcFXCFA8SVdcJ7mWfRVE2
+KAt0AI+j4xGMq8k3qHpF41DG4447swC9XaM7ZbP1tV6rYnXZNid1d5TOrpdZ09VQAphibLpzvwyi
+0s4qT06h1rE+mFlDUu2mKCeT1Q7PSZ4giIKWlWjAIHSbqrIGbmZzFH1VZIENzajrfu1iVs7jKvO5
+ruZVI/Dabqdks8Cix8rdg1lv050vOl9/7m3P1iH3ZQLiYh1Nv+WbwKPbMu/kpMAnLIMYGu2mEBev
+Ny57PO1BdqTc5pKDB1bobqFJsVtXGkjWNJ2UlwowvzjZulAPF3Jol/pa8nmJBZREaI37bADyz94B
+9awpEIShb8OW/efOwPmPr5c89ba/Ctxfje+/qClOQVr/vovw+DTfIyPhe70Uun6zE9IDKr462AiB
+dwDW8y9FTwl2Age6lzImQe8C2PxqJ4DVgBiUNtOH43DgWf9a9ITTv5xRylMJx3qgjcj/xE6AGupz
+O0GAIyEIpfLhWBfjYL4/thOGBHT9xOmhq7cRVCaMs9NomOUH1dbutBBLNRybsus/CCsXkpdlAXU8
+6fFNlVRo1Ngg9CWoTQyH6zaeemkfJKiv/UUtaRiPYkHTi80EUWbpMtnrZZwWfgzqZKmyMA9Xm6sL
+gDnemuuyTEz9Nh1pvWVNXQEqxwnQU2CXHNoWxBcUIFF6GoILR4GOpsmnegbzNW3jpIGOji5nZTIc
+puOqIBfxqTiX0vQ2W/ukObQlvJB2aFwucGV6wLgRZ9Ys8wlxMAadLFN8JdkDEDBTtpMuIb1cjLXq
+XqNmtXnFe3ZT9rX4UtWjv2+6zYa9LxR7PVq0pDrBccqWkSRRW5yI1yPUvvC+Y7w78nytGm3DSnbW
+LuyO+gULXRoPjwUd3FxFMKmjRp1fzqbV2p2rwfeFIjm75cqK6xSYqNcc/NQz1yB4WS4NgKJFAGYo
+xPlwMusnQFq0nE4gxddcoqZ4TWUB+jtuHGrKNZuuRSKKjxbIWIbrBuf9oPovth68dg3poDhh68sN
+DepSlUX7ioByPNrEmoIb42rtqwnIXzJN7LIkk9hXU2hfb43nR1420yWoLYh63OR4A8dqaijctqa5
+ajrVXItyXK7SKVWHGxv5HW3CfDF1Jd8zbkALTFMo74sVqsV5XEpyZbntC+1SS9lhD1vmSqyLuqo7
+uXyA/FGfjSUFzSkEjmm2zgWvjjvfVrtyttMpCDwoR7raxpNUegQ0XjX+hgxzdc59UR/1pegv2zhg
+B2qm7qgmYDFdh65RWaVW+hqIbPq5gcoR23d9Rz5N1dTckWiSz+lcyS9K1OsR6Eex4xuzUKef8HXf
+KHw5Q3HypI1uvZjHxX2c+VKebvNms2Wi5XlY6tplCKLBssRQteMghB8IrpuvoUQimfYB49eQj6Hq
+LLrAPo0hIWDOlEM8TEjXvRdQPHuPY/C7qkc0U7Vo7uNqp52qef1qFqLMlWrmdxIH9WbqR3rFyjDU
+OVTkMwLFuNO0SPsbSoK7NEmKUl2UQG40G8Dm1lByc9dAlYrdlLxm/Rou1jKhWonWnUzbwC6rdFFH
+ZEm2Yy/xfBuZlMez6JvzcZTLPu1ROmWitvKiBrmkq4rSj9M4+QtwEASCvAg+y65DrLtx7VofNaAr
+p31PkgJB3qbre1BZbF8VU5cXTeWuwfOcvwz1mF4T1FINOYwf0yjtli2QwcadT4QI2tLNvMK2ri4J
+Sobzti7ZPtR9C24g6ptjQUO8rv2w7is0o+nQLbHMZ9HY8zWq/hUcyvP76NLmXdhM+7GzU2u0M7Z7
+O6vG9KeFXWSbuaSWbycFFbAKapryqJSSgtlRzmA8lAG/r6Tzp6SDnQSGcQkHAcR0OLvG7kC5r6Bc
+DEmORTEhBlb9SlZNYFovcJG2Yzb33s0ZbrF9b5Zk3Y4ML9pvx0r+f7Dtn5x3e2Lbf8udD/Xf30+7
+r+BboPc38enZu0fHjR56fzfy0YGg4LmnjPAUXA8OFv+3YjQc8ucMDhmAeQ55VHDxyMh/+HLNQyka
+KgBKYfrwFdLvx40UZHLw7SCPQ/0YCcL/k8SLJeT9x7VoAkuXCwV1HZrSh6r3Q636kY8fkrmXY5vs
+5fLVS3woaemuKSuqDWs8HNPgqZenE8d8DJmYffPagF3fn3RiHe7S3nlzKQK4X3knZqVl2rHdAq5G
+vwdk91+Axa5XchvTNudsWy8jqq3Tqoa0peHMjLqOqouX01C+rVgACweQ6LYoQEbtpgbhT0ntu1cB
+KgCnLau623os8Os++vFu6GQc951AlcoQ2JbkYn44qNJgRuKuBvAvwMsGdD1eS5y0h74ZkDui4EuT
+Qy9nP+ttrW13THgLyCfgUBM/6UFpfVoU9kWOBzptF6yH4xvFEBg94h6RN9Uo7Q1bArti4CJ9UBiK
+oNrMFWg1vqp5AP+T+WRnNhevQo+3E1fgkkBb4UH7JRJqEq6DKglYui1oHwrVwBmqpE6Zi6KSUA0h
+aweyaU2ArR9Xa3rCW/ApQQOUcHCpaFhg4FsKFk8xaraQl9VoIzhNVWretY0prgWYiDv4XvZwBaps
+TMBxm5N7VeD0aCwR2CplkfQ+94XZBIg79wUsJbCxBzjdVAE3UeqIc1uDIWnH6qrEGyhDYbtwSFvf
+t9lG4tpdeJX0OxvbNn1dL0v1dmtaeVXgLfkkfRXell1duQwKD0Aj1o3DIbVEVsHqhAzxiG3zmEXA
++cuHr/9dJnSAEkTfglepZx7bITMcA2GiBvtsFsSfjL6DaixqO6hdVj7dXqMC5OnFXBO5o5GRs66Q
+vcjL4r/JO7fluG0uC7/KvABSPIAEeTk89EHdOsuS7BuWZNkACRIEQfD49LMox46TTFKVmbmZ/79I
+Ko7Usrqb3Nh77W+tXsIb0IPzlIZL7+NCi6V5NZDKD63QY3FeTEj888DC4nIt3MpPiwYyWYJmR9EM
+yBQ5SyC4LMFxYm0i4m7atp21i35xnPLacfRZDmV5jbfBHzJR1kJBSrAu5N4mglJqYl5J8BhCfpQg
+ynI6+kZBIanFl6k2zg5aZ5EzLwRJgJNseOFDVVx3hvKDWguey44vTsrqZvhY98Xo5hBCiJt7tVfe
+FdgM9kdCjJXnTqIhDeIibFNcnSy6/udj1P+3AWnD1qGY/12d/oNj87cJ6cdjv1VpWPmxGwniCAAm
+yCFQQt+rdIjy7QOMxKCDXQgWgqjfvyJD4Ocd9537jEI3YB6GoO9VOviFwcaK6hq7ngODF/1nVfoP
+21bY1TfTdMQYJi2PBe/b2J+qdFXPjRhMkDb1IehLqBgx5WNGAtt9CVXN98XixB+62soLb5jIzSpw
+T8d+dauUWBKtwwc6u2gvoLiJlAqINiAG/WTS2A8m1Wo+cMCaaSc6c1FXS4vFLOA5jDgDNoz+gH0i
+RJJR7Nehca4EcaL7dmzbHYGo6CYaFMs1scFXKNnilVWO/Kigi6Z1I70TSiQ7+jVZD4XrVnkfd31e
+1hPq4bSSHCcezgk0aLlgo3fQ2H7mvtOOGhAefr1ZRc4rF1j+TmXwysd+/UJhtN9B+g4f3LkFQLUV
+NtCVzny2VeiclpjzoxPM/g6gUH8eCzCPNoirdIidLu2knHOs8/g9XZY294NZicTIsMeCqI3zVmn3
+4Pck/uA0lD6bSoOJCsYBezdjMRbFTCRRK0C6loHqr7kbD9cllnvXUqv2XgEj+gyp59pGEcXTc+qD
+1CbGArx3UsBPmJFG2fOEGSwiuyag56GkwY5XGn+coBbVk/GOojHNMw+9IocGU2SxnYNdE8/mPDkd
+TaZoatOwkEom4EvHYxSM7BDRJrgwYeM/VlFIT56/9B8AgdAXoQZsWjvp78NiEp9niKxB4lahuABz
+KbJuFctJtKGeEibb9dKPClkkAQmwA4xaVCCIsF3uNBNTWQ9YZd9KDRERA8SFErVYLieMXycMX+Gz
+Ybx7DWdjcqN3nKDKorlcbe6OVuRDhV5Yl2VzHJULTGwc+L1dDJFZBGsxICex2uuoW/VOrCI6DFNX
+ZUHZBvm8EP6hLLFMkECAcAWuwVNMpvJgl6nNMGc6B/Bgw7XbMZzqdrYnVtfmDUMCuVgDPrzVeulV
+wmw370I1BAeDc+ducQXZt4X07py2tgfDZHdh5hjiFIHWl0KSjct/gyYY+QyoN39bWlMkuvT/8W7k
++XMb/OPx3+UnyqiPMkYjtMFw5n2vrnCLUxDnMW5Zj6LQst+Qe1RX9MsYW3DDOHCUb0T6rz0w2JgI
+FRGgvuOhILph9I/Ka7Cx7T9B92A7PS+A23b7ibhuNrj/5ybYmbD0poXMZsVUlVUdbuOhDWbzv8RE
+sLRfHVy4bJ3/DzARkDEQosPS/J+hIl4EshMbT4gG6V8BI74BUnbkJUjGfeRO002s6hLcZ993OqvK
+kKFydW4kbmjTKZ0UDIfstV4ro/emiUJga5iLp0xWs3gs46nvsoKTPkiCKRqmPPZVHFzEk+M1+wIW
+AzSaC0AfKFjUdXEKkTXz+Pb3YTnUizTstOWQ6aSl6Qosuk4jJpxX3xui44h1KU8oc+ciszVG6hxG
+juItKrTFJjT2yRk7P8j9Y2eqChOBpXdusPa3FfYEGpSkHNzUztLDgqZXK9QJrrD7pMXb1FFW505R
+NyUW7Nxv05LV/pAwRZZqH0mNVW8VTmGwHxuFH9X2df9olW4/AgkAtAKLyNjlXBM+ZzyetiEc2mK3
+mwSKIArlbDjcDAFWzQH6kA9h1GBBb/3BWXPA6t0lWzCZgRRfOY5hrxywKhMFAzjaeOFD56+d2Xld
+LUhWU9UJcIOkMHtf1NWlxwpbHVQ4lGNSDuhh046O8EIMQD1vmPY6N8Fx28TpGkCIwO5wWscUy6Dx
+wl+scTNv0HWfBi3E/cTgbPP3zmjAGgcx3vLc+p5vj1VZV8OxXtoqSoK60bBE9ALErWpD0Ia2qrzT
+6HA4Ar7xWLwspjAZtOme//X7119dTfRvBf7/Ji3qJ51he+z3Eos6GWJhziAPoGPditg3nYFt9PoW
+x0EjBOtsyN6PDjb6BfoCxH+UXzwiBpXwo8aGv1Cg8rBYgxb0gmCD6P8BMOj5f2phUcWhEdKYOhRK
+//aL/1xjgTpJQxsnd4uhzcHwVJdjWWqbNqMpTwAlgKxQr/4EwEwBebFD1OaE+8Tfxay3ANSIjz39
+Wvdd6tq40WchQNJYrvqnGSVdZbXSvH9gfRC/OKppppTFpNou8LkqjtNQRyJRPhZmu6khbXWwsCwN
+SaVKZ7zQ2OlzjKkTGpSsGYN1SJSR9fAAFbf1v/rzNACUb4c+h0I7HGzh+MFpsZ3MGYlRFnXflIfR
+hOrI4po/i7phzsVCKYpB1RWTd8T+pVjPdCwFikotg17suKHxsY7Cet73ZBRe7rsVd3Pe0mmjBsNl
+vETWGuvSmGKRinGymLGqhNLvpKOc+/pTZOOSAToYyHRjm7KKrpTDRbvvxhF6dFPX9YFzh6h9Ab1j
+3nEhA6xXVQnyC5JI7x9hi5L3UGa2kR6dqZ9Wsitx5FWgzjO5CPpYBjxIu1579fOknKnOulh06VIC
+vcmjWrt3vMAzyw3kV6j9k2Uetpcry2sdaQcbVW98wma9OzbhhvkVGu4lG3xZIr8Z86JqXJZUUSD9
+PCIBGOwK0ouXaCLKe1vG5Ks/GggatXBG+KCKEHUPJQjvPl2c25JINeax9Vf/euz74OBtAEccyO7o
+Yol+49Fi3YUQ3g10J+yuU98dyU62PD43MyVLBvawKneL4rBB2AaVeYBN566vm/lx6IlzZ4CxvFqv
+KN/g4othAxItfQTCw3w0p864K6u6AOdcVBcwwsOQZRazcys3fMWEU58LBYUm5Z4LH5rQc1dBAZdi
+D4nqFvpre+ADznIp+IfAYFkQuzjUMJ/VuQElcyc6t/jqxp0P8tx9mjr7WTod5j7XiEc1NSJtbajz
+ycDGBLixPTq9obvWse6xasWLnF0vKZyFHFbjXTmqbm5iWi0gTpbPcRXW99tfG0v2WXP3Umpc8FUc
+Ozujh/JMGvFWmOBz19QfQH/JI8aKNYvKdW+0K+AtqNv4NpgquDIqu/JTvXpLt9fzOn/C1g6HTl80
+Te6snXdjx6g4AmmYnmCHgzTfVLCOFcxeBy6vzpKH9UH10SXQvcAk46aNeJi+4iUacwXsaE+9BWwd
+qzvzVIGq42CZ+nFjEoa0DLmTVRGdsTwieBlr8aHRFcn8zsUdHa9S3k499K85UCg0K59S0YPt47FY
+M9L4/FyjDUhlNPfXgzBPDfqOxGgP8y+YHswZYUSeYz7BX+UFl/4UL7s+muZUrV37CMi33oHX3fF6
+KfT/YJP9/02C+fUIC/7WmPufcnr5j+Nr2/x5Tvjp8d+OMcjbaO2Azm5mVEgoGxH//RijW7uPYwyu
+zyj6eVRArBwUvq17D0IX3/LzpEC3jhNuMOyxt7TGf3SKbVvy3w8KMOZuOhCOU9fDb4Bp5edDjJB1
+GDQFXI6siwnt2UqGvNAtDRPcBUV0PxaQsK9dXwPxHkc30gfZzf0JNOxwxsZ5/fyNXFfSd679yGBp
+ZXtCTlG7WJ3P6GXvQU+K6ji891aBw/wv9bjOWHC/N179exOmm2I+xG0xX/vvDRp9b9aIWceLRvjL
+mDrv7Rx3uuILDSb/Nnpv9QYRRjfmvQEU783gxLGZSDoWzCdsMn1Qj1IyC0wUeEcSUqxYD/DltLBP
+UhcUZm3MYzGg+0/7gkchZHM1vrKmMnPaCzO3CTpBdVU7rvYThy8jjGoNaJoE6G7RgDorXUDTcL8K
+4U6nAApDD9fJomHOYlRPoF9ca1JLgKIlQ9tRJ2GNA28x41CTo6msgU/yge8x1XOS6pBDlYJlv48y
+W6rpkgXa8bBT6FonjcZeBcnggknLoG7PoNmi+qZfXEdsTe74lRZO//Vfv//chnQU97/TTzGd/hYJ
+9Zt6+uOR327ab2YVWOaxkwI+DA/895t2s05i3PfhOkHsJvX833pPGC4Z6AEYUhg25a7/s+HS+QUF
+ALQnmJUAXw3/SesJPvf3dy2c/CE63xDbLXwtjOkfdlyuX3I/NuHRguBXaR1I9+OgAMgnYHvNFbgL
+wdKmK1dyMTnE7oba9dOWycgAOqUKbmEsxTZPMuZTNALxWh9ptLI5I2xEf8pLEVzNOAlTov2bgU7N
+I1TECSB0AZ/HqvsoBZSmH2Rb95fu0vMiEZb4txo2aALDI3DG67kOzf049WV9URsyr5dro7FaiMFy
+nWC/I2BEFoATnxd4znfhsJJD2WnWniPQL3cTDCURduVioDekW4w6CD05We1XATtiXuz3E2mHvMeC
+zs3bTmjc3UUYPg3WJzrlLpd3TiQVvjVecRISej0XYaTSsI89nge0tHvrme4qaCM3g+idGNyIuUe7
+fSWi6uTEXVaWBE6SPiwSbCm8O7mOLB1Xeu3Uus091+W7jQI+lpP0E9+uWQ8rXVqVXKbUxdLFFnE2
+qB53uAX3Q1A2BYIWzsDW63OnyQfq1PsmKGF+DNzLHpaXXc3JEUu5IofenHkeaLg2WsQhCvomFQ0w
+5BLw0lEBOM7Bl4JRhFbgj+oYR/NLNJCLXkzgSfSSGTs9VhieTl4ZQe3s2ryT6nr0upM7QqaIyLgX
+bX0cSWSyvl+brOlp5i+gjUtZzs+asOW6FGY8NiwSTwFwyyIr/Dr49A6wu2Ut34Dsla+da8nOjgts
+osM6ngZj+F1FAnEb1UHJ0xVJfuTEgXguZ4B6MEGJABRRohj8v4Q1c6IVaZr0Z6TdKICwu0KF5lh7
+yrI/I+3AkdTeEar5RBwI7PE2/BuMAxgwbLAP7NRXSbl5CUlV2menlPKDV8n6VBENo6KctD3jWdU3
+4ywJkEK0pxoM9yLbdIGst1uG2IMm7nA4LWYgNU0iw6q5NE3JnaRzHRCME+zPHM1/GybdCjo46aJQ
+ZUvhGpBcHjASI+YD9ozkyzCY4Q4H15AWvNRnXfgIEMB+bTxgdwsVggdDVguLVwIpDX469D2uQdt6
+JzW56g4Gx+Hs6AYSC9VV5rStPBSQju4LUtVlRkhJrqTQ/YOv2hqu5XJOo4BHh5Y3xv8Vrw8cc7/O
+a3ma57W/wUUUnNawmkCjLiTxcNYnfT+y3FkkxpI5FDsn8Psv/rDAO1DP8XPV1PStonQwl9Z4komd
+29N+hLNnBrj74Ezh2MPCQJbwFMZRt7NlBzeBn1NVQkeaZ3mxjOhMjZbxc4HsgNSva5ZCuazSuIFh
+Ah2Tj00oaCIAsDu/fSgbS0+du9S7WnrmmjftssOw8Wq69b6c7IWplr3HbV6VQ9Z4/ZVjDOZebFfm
+prwikqlDY/ogXzkz6Qpb2pWmbLgsyhqNcm3v8c6vd3C/yrTzagNUFSubAZEMX5To4wtNeXUIiuWB
+bmytK4oO974Y3kKlphsphu4Cg30+RepKTQN9ACQnvjp8XL5Mc80y7F44zCkOGKVF8FtYWTXqAfMw
+OpHlxQOwUGO3XXSHbrIVTOpKw3ZUAlzulH9E+TSnVWHQiVDUdsDq0cIPbe89rDAzpIRFeo/Ft9gt
+hoZnt4yCD3xe9SVsdjFSHqbgCVRctwvowxQDmeI3wgUkDkMyy+OhviG1Z68ZWhX8ECHOHo/hG5gc
+iJiB39yG9RhcYdYlty30sUOLtybl9Vgcwlbya5xpkNmgHYyphEyTwCfMn0wcmcO4kjEDlU1v6aIm
+sGtwNrQroAh4vtz1vhpdmXfYrOz9MQbRaLE1/lBq7aZmXuJdh8tsT6eK74aVwyfccHLhmXm+8JVF
+ZovkGVctLE5M5GIKGxQ9CsJOSHJBIxteuyFp90RhcMY2JBHu/DZUoAomUR56We1hrr6uav6AQfiS
+FON4WgevOUelWPel23bQRbHo4zNkC4BWOi1kVOWM2mHHiDOjg9Q6h1sDNzpZAXMx+C8P3oK1WyTG
+JesCyfOBV49QC+KUVT37wBZ9QQPcxLFaMgu9sk0mvl2KgcdNptZQ7zDCNRJnLgEfqcaKnRpjwgKN
+tzMXV+XkNixrA16YpJ+WkWS4xNzXgM3NEZKOjI+lKILy0e3ouh8K2CbSseNjHgyDD4EkkCmQzf5M
+hRcdnXFZz2MwT+3DzAhkYxGbGlwkjNZe5vZLHCcO8GfQDbBlvjVuYW9DOL/uBssty5R1uiadoAZU
+iZQWIIAc9DgdVihVfRZWg/8SVVF0CeKjTqgN2BeY77hI1wr3whW8sThbYhmCwPD6bk1j+OiOg47B
+pQWdVi6aExAdqBmkwJaqxw6Q+kiOSJBfswaJdmUAEr5qALth/jG7ul8aufNaXAcHt6j4S8tm9Oik
+jF0oOkPcwiJTWnjRoug0ew7iT6D+lYlfzrDNuGV/45r1jUh534lwRLTLQsWrM7aBBbkO9n6P6ym6
+qyEzHUC4bxxCuepsmZmBuZ86Su7i0MIn0FRgJmbN6wzkOs0mHbKHYu6b4NRa1r4UELPgDMZ2GZCq
+rq/mAMveNah5ojxfFYkDlAJJEAoaXlFDqvMmuhwcbskTWkZ5IOAgHyfK+idvLdXNqKAfimqdc2/F
+SGQn3z46i2OBxzs0s2wK7b5sYAoIlt5/q2wvj0sb4BjG93xwQAJezFrh4gSf9Brz+UBghtzp1oLK
++zfYA36XqNG2/zUMl7wsX+r+5S+n+/cPQHj5lr2F6HegZvgHMzQm6R8idfCLv+3tMcPDpI6G/afs
+re1LcQh4DtnxULFDB1P3j0Ug/tf/2NUOleH3k4IPfcEF6x5G1HdcQO142j/P9z9c7Y7T6ejM1hrb
+mog0Q58tfa/CvIgj0Amj55blYR0W++DD90ISGN7pmrhNUC07rpA+BCfF9ARbl/5qCsQk1D0Z9hGc
+U0Hqwu582biLK/e2qwMvKbFDg61ybDQ+vwFzF7JKxmHNaTU2e8AcMrjT4dqitGKB7+QVY8MHOnYW
+dBKkqQTmITd8nmZkXSRouFaTr76zflZx2J672g1t6pKoObBuhken9IF1p7P0RYMWdtFrUmoav3B3
+iMB5LOXYpFgsTW2+2pbv8Jd0HwiO1QnLHPMcE2TRJAC2PBwg1aIfGAyYJCmLeYWmzYupv4A46QOL
+jWLxMuEogyLgdONbg0iOKgk9C4WhdKrxue5j81lZP56zWbTevSwjWC4H2YOTgudgxC5exeibvKiA
+k5jKOP4qpGmuWBX6iPKYr0UNjST3ICp6sM1Zb0oKdFYCkJzvP4otIgSN4xoDlzKc5+uCCJQPHHJL
+lS+uGcHLDjHvz0oE0Q6tUuQ/m1Y3KPZArb084FOZ975xyMsKp99nvBuYDBY6l/YwUvJRcnRRS422
+IJlcON/OVs4i+9cXE75Xir9lBn73OQu/yQk/PfaboBD+wkIAA1hiYdtLXUyI3wUF+gv0AoCv+MyY
+EDCBv+mDP3CsTZUDSwBf/LbL32Kffq0TwS+Oi2+F8SWEGrGF/v0TRQE7sj/ViQ1XwM8Btxehom11
+5Ccey4eJtqcdslx6t7nytyvUQwmYsJ+dLDwbpZ6QrvJ+QUtkLMAWvF3nZnWLOZPb1Q9odHwO3m+J
++v32gO9zfGtVgJtGIyTmZXy/lTT6p/6ier/F/L4mgDq3O89KRMgkxfsNubr2eZURbtIVqVEfFB04
+NmbvN3EX4obGcYabG77n4qUEIermpSrsmXuEsbTQLjwAs4nh4gQYKc/tSOHgFoZrtYdxsrgkMLAD
+G0Pqj9hcJWuUu4uEl3UJ/GhIoNPClLfi3T1KPRKM2iRyLrA0C72saUZsjfsB7TF256VQ6TSiDdkX
+wSrN3iL87zYA5Ax/dK8QcefxasbLBHHv2ZvAnUDwRF7NbvHazc2thh6iBMIwYCUgVn/hCxtNim37
+hJe8WMBMEpwamRuoGeRUV37swaJAlrRFGcPN0AwHBw7QGQIi8iEwHEqY0boQ7skcnkZ/zSMONCFV
+EmZ84K01zDN9sDx3AeTeI2A2gm3jINmWG+QqsdftQnRGFgufLmVrAkpOfwXZULbZOlX43YHEdf6V
+5dBL4HAWOu0r5RzZVluf8dtMd7301s+oX/5p5h2yQsahVx9577mXXmf6NV2tAULqEzE+dCBfq2Tk
+cXivtxqWe55mHx0R2yMfwHuJGWPlHgcXe6sK57UFpoCUptCfMl+Grs46eIQ7UBU+AzhBbPeqyrjG
+XjKsgsuaUYksD6TNfFqA0bJTD19OedUjk+irDIbe3yGuMFaHsGebnTGOgUhIpYv7Olo9bBpLElmk
+kQl8Ea4/KFohaxCUIGl7/OYOXNoVrW0QKAbP4jpXOCknF3MxrbDAA75mOpVKx8KKyt+rdrwV8Pi9
+lkfvdd19r/H8vd67qPzhdgT829TaAGXnr7uy/3wt/7ol2x76rdQivRYfUbXl1yIznWFZ8qPUsl/c
+bVePL8E7+L6P+anU4gsu6im6OLCp6Mx+lFpkTntoniDs4gdSxKn+o1KL+/L3pRblHH0Y/BHQ8mEy
+gPPvD6W2haoAV0EawfpydJrooUSUJGSTUuVuZ0QWDUF847UEtrdF2kMYNixvXCSxQH5CDuVgh5SE
+Xb+PC8hNgV7NbWmYStRCsFxY6ZBoxnjShOpQVWO5G7RcAGSWu8a3dt9pcWV89Vxic59wsBVZQSw6
+rZV9DvCqHexQ7mkDMAhhKM5xBlZ4uVgJRcI2d5RU3m3r9Ce1dPSIzXd1CVTIAfIJkFTS/uCMfDdN
+9QkYESRQwhK6PQtn5Z+0ZBdLecFYJU7oTQ4tjJvnhlQZuqO3vl8gNNbVrveaMJGlp9CiQqoKCif1
+yo3ytRx5bY7Zje74cZ3MAfa6vekdnYSdQYafXt+KivAsbujFIiHVKeI3eYOUj6ehdpqPUizRR6CZ
+fE9ZzPcrDP6Ifih3ftCB2K+n8lJQJIFuTzTEAh56nGPyOh6RPBLQ2yXy2p2jqrcxNk8xl9NhiPvb
+GPvlJCp4kSFD4jAgQDCn8Yqt7Po5WEi+QvLE/EzfIk8+zmbpvpRkwQCqhLcjdrmF06rb1+iX0Uci
+4sFV9M3x5uqW6QDkhGJxhgV1m3Q+JNu1CoBYtaBRi5E2OzIty5vDOfsUUdPuBrebPgaad1B+nT5z
+AuviV2LtZedO80mF7sfORQpftLYSmROxG4jEk+ElKflbVSI9AaLwmvhD313N6B0Txuu3eKHl2/Yf
+JW8hHzMk7KjBdMeZ9NU5HisM1yW4wrelW8pPq1Ops+5CL6Fw1+xDoeOsZaa90XxBGp0sQxzAixCZ
+HCx9BO4mnoe2ni8UpTIfKSaRkI7kQBsaING0oI8xDoiD6xbT/RrK6V6ssGhjrBYRz/puQohFOFdf
+od3ZXKloPSBer7yiZYtxeYn7A7RJxAZxz6k21fPG1J45CA5xq1/lfFFQBLzCJTZLPAOwvdBeEFeF
+vK+bMfQlLDYi3oFgGURSE/cW7nNk4iGV9a0dvFcOrSBx8SK/TqaFEGahluFs8CRiL5V3qBHDjBRD
+AODlOwouNDl1becdBjB0BCe1aPOmLoqzG2p+gVzKDu/ucu3pAslBLXBq+PjiSzVSeiIgzT6uEbju
+pQRSnAL7NgdToPkRIWIXdLTlX0jMFu18j/g7swuY8j50I3FPBQbPrA5i/QTewBy4xvxSuf5HsOFd
+rrgsDgwJvHm7iHEXIVb2woxB8xyV/UvkWbVnXWRvxBRUFwxI886MPQhi/DTY/PoaDA4voGmUeGmh
+gLUtghy22If7IhodyBt1kLalFs8O5JcL6hfwEXEWmkNAvfayCRfYfrWdd2qc4mxDkHJfYyZ10ATd
+Gfzki0FMcucSpzoidajI0f5Olw13wpxKxKXAktifXF91D1DjcScjs/ijH9XeozG2fZ7gfdl1sxpL
++D5DZHB4iBlE9Vp2WwpnHjb4VwCVMArneT/UHnor2iOcF33V8xqS/lzVi7mA4T/6DJFZp/BJDEgi
+ErlVbEeHBcLZ8Lyo5nOl5gVCrnx0xvjkV/yKoxYiNVcst4i5TjQGXLz+9sGj4ws1EbZGlF+Fxkuq
+QTSpB6gKmqC6G+BlhhjfXLmz+rIOCH9hExJOVquio9864F+A2H/2x/b0b9Mc+H87iJ1efvcRTH8a
+xbZHf+sP4l8cyjYHDAyCsCoh8uT7KAZAO9gYCMSFY6cKFQZH86+j2PZJixjdsMbY0MItwfBHf4CN
+sOsB39jwDthZIrQO/xuu0IcFEt0GOEX8JhQk+R/Ybc1mTsOp3MNb0vGsM1F8DFe2pQFBetSTreN0
+rOIpGZvZ8xKJaUumwRoR5M5Mw5hIa6vPsCOTrQwLV2Z0JfGYmYKHX8GcQa9tHHqB3sFEWc2wP86M
+5nOxd6aluNHwzV2LigaI4yOTBOA8R4dp8yvHm3O5o0gMg0hfXpcecqtAlLRPwbvfeVhQnpIQsESM
+pA7aXhebOdpTnJ0Qtp4i6KCvsmEzUYPsjO7YZqzmFGd2VEl5U8xmzKGGyC/lZsX2NlN2CHf6I/dh
+1Bbvnm272bfZZuSWqoCnG4Y49zZ6d3rD7TI91QhOrVOD1UTeW4/QdHh3iFstxKWz2cbxqvLTvFnJ
+PbYsEGlhL0fYlncNydhFShDM54A1wjxazXKAwYR9HexMXgE8yrcKc/onxwDs2AHkjl8t8hduhdDY
+hCu9Pk3vvvdhjOGBbzc7vI1qefANLPJzv3YvBdt88651GnjoDal3qG3o9Kpi7R/XgbQfYhyQHzVv
+KixPMPGsSY/0rZumwrtjozCY09LzujOGrHPTrzD5IDmlffKRkyIx1k7x/ajUigfxzlwy6G8VTieD
+2D3aVWOVtzOrrpp+8i7biPQZByiGjg8eQShz2J1iXwFPOBiY2nupZqYQfdvEX1zI1dkkeXmpvGDK
+VLywKluhhH1dB0XuIjm0LbC8OppAOMqoTAv4LEG4j458RJcl2q3A8pNaeff5PdopqPsWrStCXQM/
+MwPU6lRNBJFFokBy8bdoJ0UmJjK3XVbkDmJov14RIYhXo7UO3QusfZf853ynZllHM2Lr7aJkAsip
+ixeGg215/JbpFNXIUc4R/zSPWCT9luxUhqIs8tUd9Vcmp/Lo2ZFdea7PPy8NwoHyOdLDMUQY2CkE
+BT5kyhhTpXPISi8LEK3jQdBH1pLF9QRbph++Mqcry6dinBFfG5El6A4xdvdkv0rKLz1EdN/wAR7T
+01h29hAhD/DsgybM/KlBBCGBmRR5S3E43LZ2YkeCyM5MK4GUerUZTmuxfl18R78hXDv+PCirJQKi
+h/ETJnXxEjkIqUUHE8U3yAGrLiWs8bsK+ADoX0LLM0ypa58Dcsr8goEmLBzRHFnIY5nOjYsIitnr
+QywXIYr+F3lnshy3sXbbJ4IDQKKdFqovFntSpCYIShTR90Ciefq7smTrSMe/fcPT45HtkCmRKiDz
+a/ZeG99Z1b/Xk55HlDCJdY3tuX+NGgEsd6wLwQhk9pOjXjj6NtPxycZOMwGMTCPK6crN05NRFtCV
+y7p9qe1BQgrK40nftSIfn/HOuavEi7t2O4Syuo2TwXz891xtnPF/3feeqij5y1UERswffa+HkM/2
+bfKZ0Qdiqv/jXmPfYKrkNw/ALbuKiyj+93uNSGcst8R92J6FlMhSZtDfR4xkxiHKY0uhZIiqmf5n
+RBx14f4sNVReKUaMfAsCwxTE+P+CxDfhMoZRl69nrx/s53EYzV1aIxQoIkfrN5WbhhJ9y7ycc7/H
+0M5rNJ9MjVG0rix+uXSnA4pJ7auPdCNapSIdb4YkjQ5FOzlrUxrVl8YK7V3NTq9bFaiW1xqY6WEF
+2Kqi0tcET7hTpu2tPTvVxsfqvzNqrSvWiWalZ5hUbP1tdBzzmqCIBSsPUjx3ZaD3RgialNgWXe+x
+XQoWivRdu250R5w+sBAPbYMwvEtRd6/qdvRO3kU5LovKmNdW6pvOpksM4z7xWhuduW3FGfaVkXIZ
+v6n1zF2iF2vL9LJrrVtk9EBaR2Rduxdle3xRuWsc0yjeIy+qdsIx86Oe+TBk/RhFPq7DOkrfdFTk
+VRDGhgY/Mpvws+zKZi6xsya9KLeRUJPSQk++aLbnMuRaTEaVDAEXDWLGUrwrhcINq1zdCewipsGI
+KoGTEK4LPECaPXkt6sXybriMzCNbZ2dXIGS/FbibINDB0SlCu4WRVs7yNhNVcoINLB5piadrbc6H
+XVW49n5M9fHgsa18p1dM9/R98s5g8pEFXVvq5z6V8Sbz9H1sDcMuyzUk7rMWh+0e7r9+zmXlGoEW
+ZvO9l0ovDTpEHRC5DKc6506liZfM08LXfpqjdsthHbqAhNBrrcqenyjwZnSbOzcGs4ftbLJ2k0l7
+HaBhWYoTsDHty2Bl/euSlinL4zrPzvPCBHxKzKI9eihUFoabHHMrYURee9KWSr9tkO7Gdzr1xCnE
+z8Hwz8kisA+AN+dVlve5PCCsZrRrwmr4OkKM2eROp+MmimrjzkgalOfccNQR0Vy4H7yP+UPtl8Wp
+n3KbR7fstFLhJ8ptWhW1sx0wHUBuER7bJEuT3luMn/U1xbOExT+x08e2s7QAMrJ7l5B9cy6maTiL
+Ql9OcB/kziBFpz63+YzRRDSgbrJeJB+dyOR7H9k1PXLF7VZjsML0ZSz3PMHi5I+2s9XH0ts7hsbw
+oBbtwU0Gyw+gjlbbpsHfGluNvh5yG1mTJcQNPA0EfTyF8BOL/KqwdAiq8Di+TfBrV0ZFNcWWfwgf
+9Ep8lo3Quu1Isk64NjGRILbVl+SpXMzxS1kpQ99sTpKBvuY7bWCPyLkwgzVTkGGjObZ6j8iPC905
+hmk9nJiQ1/5dnyO/6a3e5PNd7PIaO9pGG4dpJxtXJCtaWn8HKDG65nbLGLx7OiTY0Zi0z2mWFtnN
+IKdkvM6bzL8NLd4pgNu99eLlbuzvQh9AHM0IHDrkjG0AGzntH9LU8B8iJb0HJdW8LHpHF8q3NfVX
+nrWE24oYlm8uAqh/QUNHb4OCnbno39x5l3DnP996P770ey/nqdmsTbfEDWWyibcY234X1xOKRaum
+ZLr0Zb5tGNyGf/RySsLLTBU+jLoxjZ/W7/SGXHaCfT0keJU2/I+EukL8l1AXRy/+NIN8LfbwbP3+
+mwJngiYsWatvGxSjt4se+Z+Jq4L+2E1eGe5ig632ITUwJWW2NWjXiaKCQKzkkOkvsJCoQHZmKYJI
+eoGJTBewCLgVICMRzKx+bSr2yAD98MbS9C4AvDjsl3wBUuIsTQ4w+gIvAQwJyKSUff+gKbqJrjgn
+xG/ED3hK8MA0Vo41/oJEWbBEFUHSDv0Ow1dsryHKxE99ipZynUC73QtDA8YwaguwFQZwB7At3d4F
+nBNY7qwnCPR0EW8dO3dhwKaGIwOjhXuXIhsqSWjS20llRWD9TCphbFrNaK9MxWyaLvgm2NOgnASu
+ouvxAnhyL7AnvZuFdlisaLmeFA2KM0rusjAHaKPXxjpR1Cg0x8bzeEFJxUzxV/2Yee4efQHTt2p0
+H7QLgApYPzAqOJLlw0KMEgoAU89fpeJWEb3TUNqG7b0O/A4INHyrRB9BXdHVzFtX8a9yRcICAQAU
+q2hgwAkdUha81/imUPSs2SmZd84XqJZ1AWzRkHJi02Hh3LP9Tzyq40dIQsynRNG5WG7BNFDEruYC
+7+rYDwLyUkwvOHDlW9Ygj9sIuDAEsSR5c+3Dp3xlmQq0YXGcaxvLg/JcwAwD8Z6ewwYicquIYmEp
+loMfptlz3pf08zmBTzdZWYa3ZWrKcFdcen/g2cwBMCZYx8SK3G84IZwP+zIxqCShIuvY59LCUs1Q
+YbzMF1g74My9TB3S2uMgH9QworrMJRDRrh2tZlYBLMk/wOqv+RtUpb5URX96qf9L1Qp0qing46M/
+6CG/l3tbtQ322Ou7WrUSgG1nAOyXDgMVvPNU+cDwAnV1WFDNXdQSIP2SvUFg2pbMsgXLmplqn41I
+h5o7OGLT2dlM9SOn6DzYnbtPlhKmvta3V1EfTg8h0NNt5vnTQ6JxMpt+KckPw49RBmg6p2Ouo11f
+5XDGb6PcjwGE81DnGI3XdqGHaVCa4/SWI986AivGK5JnNfhngz5HBIkmq2AgLwne+JRKDSGLYCtR
+jU3yLBR2KCo5D9YozNzz5BjN86RJC9aT/1FXWfxm+QO6fIFvEpx3kuDOEUzvhy1GOLmijxx3c5J2
+WLxDzX7BaJpX67nqzWcyiaxPY+dZ98w8yDTwa7SHcT+XN0ixWRD7U+J+S1io78wRau4a+QtCOL/N
++mtJOp69m6eZP0yX5XLW7DF+01NLv81QBKQr8NvJvZamzYE0GOuqGbuoXmnoZcqVnYbOXSUQ66+h
+3PvJBkSvRku6NLe0pf213af+3YCWdAk0WWqH1HXg0/sLahkPKcu6J0iPm7HBEwexatzBfoSRzgrD
+LILZnrp5q1i5hwb+fLvhCcuudSs1H4lnUmvfzKuLdc7mpVuNbmfdG4Mz7jXHq0B2mDhPQz6320hW
+1gpXk4JjzmjHidNbRUjrb+cU10M6zeE2bB0ANFYnoje3JT8jaMowRUnsTZDm4qHu18p0vF2gMHxq
+dHLmVuNE7bfCaEAqBmdZ+dSzYQM36fYEKLCoKbpHIxEaRKYme4WDF69DeE7s48pw6/TL+ORFGj6r
+OByGmybDQ3blF62lbXRYeGeddXYaZOQHuNuOdZSgAjGbcd+W5vzagHiEa4sq+EoYVZIecd/zSZqI
+hcUptCiON1BZEpydYWR/wwFS3fZ5kh/4ViXkSVeH/j+WiqnXT8PINpx1Wg9d2V9PnGQVxzwGpk9a
+FGHqDAVa1nImIwguIvj6/Yg5LNoWXjlFLJviBHmmZ8ZdkBW9/EBhEMVXLsh6YxcXnqQAhDDq7v49
+nT5Gor+uen6JQ//zCJuv/V72kOuJC1eZnRz+RaWv/VH2mL9RCsGBgHLLIFrZkH6UPXCflOhQ6Q0F
+qkC0Rj+1+sTHISSiLPMJJYWU/k9G2A4zg187fdeymEDg3qf6sMmX+3XD3Ws1NxojwcbW4cyTgTCc
+y6XSklUvoiHb1PboHcJovMJVGFmBg77uhvOkmTeMKPw9Ggv9Gox0dmX34bCVaZ/Acw19wNRQjUh5
+QuhCw7xMilnBJQW0zm99ZLaeTVDI/ai3TXovQrJOnvRS6bzTdGSHJkPrnKf6FK8masNpU5SLAgBC
+vjviT+hoG9uJfV7U0rAazvjgD57FVj0Z6NmVfXJeEVKZ4RYfJb6NfNJ6LBtFFT9bSwwwfUROMxOW
+KJwbrNoAenq9egeuobkBp8csYf7oKeKbxMk//LY5DXU6i6t5CLv5EXOVX978DLLG7jF6QdE2hXMd
+I18R14v0piHQNQfmbg1YuH3Jaz8tdjDNnfH6f//9YvOCroKtzF+/XT/H2f/n5frxhX+8Wmx36E6w
+ujATE+As//NqOQDVGDGhIbcMZtj/EeohObFhyyi3oNJ4wbn86dViKUSEik7ULq+YhUL3H2yHDPWH
+/PpusXnEE6zbFsxW376k3v4k1CvGCbZCmwV6bDRkiOC/WOGFi9eVo3lProrunNhGop4izTOvEpI9
+Z6+1zt0l73OKNNbJJLySA9qTCCoTokGXRaWE2skUCmRnKj0UE4y/H1LzMKszPED/O8xX2iVztL7k
+j+pCht2qRGzzCsc6I+POZrO9TXJnyPYdUi8yLy6JphkRlMVqtgjI6haz9QM9tzkHUnskWMcMPbLy
+KqjR7bqH6U3FYnjdV9PI5o+i7IeHrveGaldomf7gx73jb4Ypik4wCsnIzXoF+ezIMKiP3kJSCthh
+GxHzKEZSS6pEjbzT2rHaqyQ1F3jZFvwXuxbzQ5zGZCqMrNzJwSLmFbtuowQvYQEplGMIJW41zeTt
++N16aOaZGsI2m/QumhrZc46k0aclEdGdiEb7c0VQkLuqrGG5pSUR9G2zgXnEyqL0nYOhf3FwDr16
+PWaOTjcllRo8CKhChYuhMAGHZu4Wh2DF2HcpEx1MWMeucmZvN40WMssyL7MnNLmduWF3YHwesFhn
+23TW/J3Nduk+apfpwQzL7jn0u7jfsyaKF0QJMIACvNALdLVEWuzhk1JQUg4swkgH6+B32phI+P0n
+1jagvsE3rNBMhDsaTPeBRQ6aFCsbzOUUUQ3Om++JAIs+l6csNxij/X0swJKwbgR2QHbmrvmLcAA7
+ks51wdz28XtAQANsmfyYqTT+r4AAAHz4G+3Bv0n/vyEBKMK0ZdU7VuwEQp3FxPg6N+MAlnpdxR6H
+Nc8OB/cEqXIIIHYNajaVN2yQ1DHvutJBLFAPKkwRo+JDPBjTNTgIrgf63+6VVK3ymF+uD4MZBFfJ
+5VohN8M+ayjyg+Vy7ZiXK0heriP3cjXx4XFNjf1U8dIWM37Y+nKVxZdrbWGmNNBaquvOUjdfqu7A
+xqn060h0WFvysJo3trotzcvFCdPhqlJ3KUUr1yo1IK+WrW7b+vvFmwi7ZRWl/KxmROZ24zvx3gAF
+fpxNWwyb//1b4w+d9t9WZZss6f96AWP9qMpAZOLzYBiF/xvkv6VWM9+HUUgIMWsrw4ewSETnMvhR
+lQEsMgyTERUTKehvtsII/b6AcX9TwxueIKSCaq0DL+6fXB1q//Pr1aGE5Ox/uMUwpzPg+rUs68ZB
+cJL7ATwrxtUZQX14NFnoGywINiGydRIKsMQ/6ebcQoRwnWHrFHV3iCN9fEnobq5FmaOKamrzixfJ
+b2OqER0bmuSi5X1Yf8xm420rI23QaS3xGkHVk0Zvka/oy85+E2prRxrfZlO/k8yhr7CBD2/OYBsb
+WTXzC94UYql63/ucDeHkBIMaSMeytvZZvGg7n8CNq8jN9I3O8bidwR7Gazo8ufMA0gThoIcvpVU5
+pCixNwC76xflqi0Grhk1/rZGNr4xqUJuPd7Qxvj7bmmzs+PJM0iYd9kZ78BsRhTWk7UnZbA56DU2
+YiBlzUrgM9/UQh8DzNYNY+Imf06zWlzPTqJdLT5ZwytyC8i6SjI7sHD4TYBJNSBJ8h366LTt+7gh
+s1HWzrl3e3ifMhTDgfim5AizqF7bUfPWMSbZYCKqn9r2KvXje64j6xDaFecNK4PP5eS5EJwL7IUg
+zgJiGdw7L9b6p2Jw8DD35fg4mZjDgmLMsvNUa0SyNhGjxrFj5K6ZenlCfZUcZNLKV6OfKIuTzNpk
+g4PXebCKFpqT1p+NqG7tdZr3xqY0cp0RpQp66oCpitw8ClytO32oP/M/cWcZ7UBwhVluKrrq66pr
+u9ewhV/RDMSHdU6nHae++DxVXpet2PzlxbbW6Gol1oK97mp82lFtEtdmuOeK3TNOz9iXDPNlKp5S
+RdkZ/TpFjtkMIOsXAqXj3DPu8tgAwlGJFBZJGxvrfMrS5yxG7EeTsVR05NXthK12G2bQpklJ6zxo
+eIV7k2bWC+FsXCNxZIOlTtxrB3oAhIA2eSrctDxNhbbcTmkbRFFtk4FHTXCcFhMVjhPPO023bmow
+cG//mnNT8YH/ut6+kDS7P8/wfz901Rd/r7nhuXE0UVkzB7uQ43/U3M5vWGaQcYN0A1RjUKv/ODg5
+bblLaYLRckPJYY394+CkPVbCauW84x9Qcv4ZUt6kev/54FR/DBA62+VwBuDjQ+/4xRwziRLTrJ0H
+si/1B8K5eOnKxDsL9m6kbZONgIGOyLvD94RYxMd5dRVJTf8UwWJiEpjM3vovsmIz6OpHc3LnLvg5
+MHYA/NuvMJjUXznMTGdrSg9WhT7Y02dqs+mht2wrVMUmBBiSxIrbqEHrIi+EGN2LK5uZTVZDjrFr
+KDJEWo/nqTGRYOO8XTjchRJtTPZoMTalYg4GSUphgO63J/8qs4nsq9kezHiH0+QlxKTwpg0tEaRL
+ocPBcWd6sW1smkUT2DHrjwBdrQMlOEqZfWHIIWiSRLqcKBrNRKVtCD062JwqQaNPRCuXXYQnlTHG
+3GxaWcgrEGegFAjFcZmlVX74ZkK+LyCNjwK4yJi23DOh0O4HZxi+4CPGf2dYoWFe+xE4tz3KsRK4
+iOv0t8kYsp1QOZXYgOFKnlncleUOXh5GoMmAOz5e7EHYA9CEjXOGbSjOFh3D9sVGCG8IS6G0zdii
+28ZpWF9Mhy1F2xUynOVrXaKM3VSEbjl4hOvFeZkvxkWhPIwilsNTm5qdvqkuJkfjYniscnCg+Azl
+shHNFPrkjuKOTLJaBfd2VPp4nxo92+nKS0kIDbbKmKt6x/paBqFyXcZ9KD9ZmSVe7WFJSOAAJ7EQ
+fqHMmgmj1E8lXO9h/T21+H//fOKgsKmn/u50upmrPx9NP77uj2EAURJMzKjncOCxEfwhFSVIigUi
+mhZW6UwDoP38OJj839jhCRpb7HTfZaQ/DiaXpSSHnHLyQWD5x1YSdcT9ejDxPfEn4XFBmWoiFv31
+YKrisrcBcwRW42fnhU0UywsClVEgV7lzB9kiPLozqXFB1qTu1tH75MNviGDUDJFue9tMtzY5bWSy
+6OG2S8aW0tBF3BUa4ZU7THm7YtEI3GYaiaJFbAp3ltojY80xSbFfPK97BPVSfPiSdR4MDX65bHMe
+U1HsvahkypyA6jsaPaqvTEb2LSFDOcgXTCu72gvLLbgMd5POOaoWbaCN7rgFEJK0iRv0fmVdlZlr
+3SC3oFrpiQ1/avsGYajmDV+ybrzLujYKg3q0nB2iP/KLiHMtHvRRk81axsi7yf1wmo+o0auTXpMe
+k7lZ6irUQLhsUs6UcpOGPrsIy4FWtk4WzwlYbVbtyqe5q4O6KZAE1b5Zvc4Fdag9Jx3r/SnSr8o8
+tu5o1MJn6fiUiLE3gKV3C9wlKWiD5NjJcmInlC7HKe3s/n5h6IKUAn7HSAhuSx5JMLmIuA6VGdcC
+CkgdKsHfnMHMKBjLnEB9ZSeJeecEJzz72jhzQlh4O1RvEdE2Yl/IqEMCKi1hntvaAVNr+USQr5E/
+kNcHotH1Nlru1cqozHKWHqcz/ZXdkTo6EMcqxuXdSId8OGuZrOE0gPoVK6fqqztEwdlJ0/KyPfR0
+pv7RqiF5frIrYeb7ueBAduahd9b2HCH30FK8FJcgwgZO8GvlIlQaG6+CzKnn3+Z6lId0LI2TGKow
+0LT+TngseuZ2qI/L4mUvLm/dwUhNAoHtdjBfBxvLy7aJRuKXtLhM4GXiYUZfy31YynDa8DZG7+Rm
+J+vUyowjbT0RI+h7sp01RhW9R7wwZYlRdy2zTDZoj+rDhFHzZhJ29U3aPdGDuuzNczYsPt1xNd4a
+NPcYPvlG5NC6wTBP8X7MermZox6YJxknq5zAx0Nd+PCGysn1Xksh78ZEO1OytClRuS5ezyU7gbr0
+AC7M9nGZsG6NU43ROq1u5ngEA+JwU425dpPn5ToatbfITK57d053WPeNZ8S/dxVpa0RtOOZTTCeJ
+1gYjEoEh02Mm1fymqz5QhkfrRYPEEs5ZzMAukdN2dpZXT/dYAZXduxVN5het7/eX70orLexFPgz4
+MQXUP/qTQ1JL/az+h7gf71LNeGXugKNH5PR7SCi2YRO75MRY6c4NDec4ivJqjOz2vnE7kp1tx1Ep
+nNB7muZOMvpuV0ZO3iRH6Lk2PGKV8wyyVnadm028rRL5Xgq2gGFliUPtRdeYz6GR2KV5hB4yoVwf
+bRVvjNDIm/J8GyaJPHkGLz++Jq5wdvhvdlsYr2Xb9He8Gd27U5hTMMXNHnMXziCnN785zbJsRkyd
+932tT7sojcMbsomtPULpB8Puwj0CVm/NOf6py5b0jkmbWMez/myG8mzrEzwBfoOoMQl5LeiDqxi0
+iDVH4rktCbu0WXOq/+jhAU7mmB6xQ+GcEvAL4Bg5exE3DWZUxIalAbbVGSwgrH64nkwL85MbviPG
+5sEZ8mt2oWCBtTA/kdU3PyEAwbVs+il51yPxfI5+R/wcAiUQ09vUcN9nwiTAmSTisWgG7b7o/ByK
+dWehXnJfy440+h09PB+fLaJ5pfhCMmevPWX+Z6fxxTpn2hgURebiGoquU2ndpktNBCwjTeUvbAj+
+VKplTMz2MZzAerd0mOzMP6Mw3hoL4qt2iSdrBRbHCRICbNeIGr1daGl3s5FjhWMgjZR+jB9FwTzL
+zKzlWBIuD0EhtoxNgfAE6ZqtQyvtJOUJH31O1me5+t+vUf5og5jw/3UP9fjWvn35a9crYVm/91C4
+UAASqvAtxwIqgsPlj+ET9QjYa8ZS7CiAi7A4/KlUcdjScc8QzGX/Ti/5j/r3Uqc4eEAJ0qT3+SfD
+J2TDv5YqyEepnlQvp6LxSA1jAvYzYKDDkFvz+m2hBOHvRFM53Ro8J/fs/e0HQnm7NdEgSpLaATkJ
+Rkv2H1PdNSs97A1Ue0tx34ImOub0BZukcgzg197QHktN/Z7F4ryaxIJE6Y1AN3WcBTjeFsUVRj/2
+i079dQDAepdCtiKP+WVuMRGO8c4y6pPrAqXK1i4Rv1daCqi+rHVnbcDlv+dVlWuuf+RDpt88mm1h
+IVYmvWWRYX+KezHcJ7nXfovTgQyjImr1L70xbTEWmjsjWyy6H2M4ZyVwldUQl4i4pOK9ISm25AOF
+RnYemJQ8VIVWXC/kcN65XWvxDeJkg6+XZ5p+KpuaGzwhkRBTjDTI/WvSl6Gu4my16EblMubS22+e
+X+mb3h/6k92NzYPt9wy+MTrtY6nN8Trx+kYlCPR7W2T5Yz4s5daEaGAV3jpOyXWBoWW0KMygcUEx
+ymCp6BhJyMkBaBrP9YnUr+rKx5B6K71o+rTUHCxESepHyE0dR7mLT6nU+/pOS8MQol+ZPNSzH260
+KZs+43u314Y7RG9m47iQG5yEEHkDWeZ66MhVWJudSe9XpF71Pjl5uB3NxvyMdAjzLtOveR1D4J42
+llMpsqqdTk+5sOG0mLj4wmDQXAz5KL/6dDv2GtWhM9RXzLzSTZ120z63K3SqRCHtemjW97aWuztC
+AfKnFlkhGW9TIpArwDmzs8Edz5GdGB8ijvEqhaDc4q6vv6KPIeKcaw1/6YYcTF+/bQ2NKjputKIl
+U8yoCEjMMBCtyiZiyGUlJsyELCTfBWUpP1vrN/Gwbs3EtR8lOMrDoE9S25E9KdoNax3EJQ2jyh0C
+xzbaeDFxWBClgVavIhFlEBwsRyOaguDP62jWeepT9NEfsgrll9IuPvRxRAae+qiKHki9Tu6kq7vZ
+qezK8itbcuPTZLIq3oxDbflH0Pjxg68n2E+XdjCuWxO1/Upn8x6g6dXewAUTnqGhoQ7XJQbVTcV0
+BHWHa6TFhkGmdHdMQklUaC6JddXQdO/SmY27QczFV0aMxslNtOJ2yIi7A/tF8h1yJvdrZBGHR7r0
+A0BMAvIS1/3ExI3UvNCc6Chgws83wpcepHYr5mIcu+Yjl9Kqt66lZ6fEBW22ruuuSm5cQBzvDXlC
+9bEhAP4ujWuDVb6xxO7JGTN6lsDN2ogKKUOVtsKvHPOhXCLGrBzf9rZ0U+R9o16n022Xxu1R5lAv
+1yHYkc8DQp1Hw5djv8382a5WxOqRTZn1CwizojIB2NsT49Vj07jWdZa0YmbT5efIYMiMqm4iBdRP
+25r0+a4k1aMqtUZ8FBf6PqA9SPwh5XC0rr4j+j2rzst9nrPc7C4Af3mB+SNNKIYtik6c9eyOkpA8
+1hb4PxwTuix3MuWuFI3PrjcJ20eu2qVc17rdfuqbJLufjDKvr7yib5vAQZb+1c70rkMoPwJwdbMS
+xL9bS/ocRw0dvE7I7dKB/5Ei/1oxwzkljam/iNi7A9EJsjObsDvX1Qty9iuxaOfIAjcWWXq8Art8
+NtEprmaDGFdI56m/XqTu73wsFCFJXI12bbmog6RIiu1IpDguxcbmvc3zceIdEeGD38pl7WvZsrPn
+Mr93ZQfBjPV3i+cdVf/npBuWo8nA+xgJOFJiyN3yQJZpW+5ypI2bCM3rDvk18CVgCGd60f5E/0v3
+ialpeikjiqRt0YUA/VgISP8qqxR9oQM8ywOyOEEtU431YF4cMKuZnOS89vm5SbrmS9QKwDROlkQf
+Oe+2t9KbzH4Fn/5BUBM2u3y0fD6JHqwjbNp92lv9Fb1Jz/p2tm+ZRM/PE/ObE1qN4aoLq6pdp2MC
+wJaezlbbhqLgPghH4LFc4fm2ROq+r6iso0AbayLqQzCCgRwbyKlzn+fRetAT9x7pbxrUEUPztYda
+jV1vH6MCTjpjXLtcMc8Cyu+Xph+aneMOsLb+PdXW3276Pr8VHxRcf54L/VGr/dj1sZuzmDqjv4IO
+LTzvP2YrtetDiA4RDvDaBe/2o9zCRAxNGG0Uaace8U8G85rfyy1DVytCrKO4oyi28P7+k3KL74Vy
+6pcAKNbWpJOYHM4e9dafUlDbrLPjsd7OdcS4MU0dVKjIDzyJrxdx6shyxl+RvWMR6HbRr8boAY+F
+ErV6ZQZEhDsMqWvoIPoWIaGfaWK8coqgibUKdzrKi1I2BPhurxp9Nr5lSTOjmUJUG9E1PHRKaOuA
+ldgVQnf3jZLhetJGkRsrcW7c+u7JKz3r1kevGK1jMwXLHvnEjvhK3Bv7g2kFY2dkaH6V4ZAJfHK0
+0twyuXaVI9Gvk+GVd8m6bi6OxQLvou6BVV/1ns6War64G8vGwunoX0yPGTLOFSkd3JSu3m1CZY9M
+Lk7JzDChmGS4wNh0hbce76lPGZMkb7UyWvYXz6VdZOCq46x5j2BVfvQlNRi0qSGIgEata2XdRExE
+HgbHkQiAZuPttJTNU+96+2pU1k8LalZxggsjbiUg1nN4cYn6F8eo9t09enGSdspUOih7KSe20mcq
+z2lO1qG5ZqzdYRnqG2cKwMlqz0Y6D4fl4lsVysJqhrZ7jbs6OfhVXz5wYXVBgqZ8rw985pthrNSI
+vq9xYO8IJfH9IDXy7r5w3eIjcWtCOmgZh2+J6Ss4Hod4vxm0rLvRrYZ9nIZwjoBI/1zR6F0JoWk7
+gBPmDD54gmadMFhBTTdOt2kyFptkisqItMa+fxQx6nkmK2F5AyNJf0T4piqoWS75l6TJvK+x3etX
+BNpBwKvGwfHBd46qEW791jjkjACLVRcOLjBcZlT9tosj8TGTBvnoN978WFGwEOnkLSMi7ci0PdQQ
+ERkcxN2Ydyny9mEbhkvvs4rO3feMaMN4i9QpfZKjyUwPBorz4GYA0lZJm8lHgORQROcF+Ou6rQwq
+rjh0+udOkrW3RhI+loFmjuEUxHirbokOcfJgCOeSW3kps0/85UH8sJwSd1c4QvN9FTApvKu6qKFK
+UPWAPYWg3h5DLcroDfTaw0dVmWEU6E0VtsiHBg/PdVN5dACOZGWKksZaeQQKwmMxq+iuZzd5G01Q
+fNbkaEfesVyy6J5HFB4Oq+HpXTL82zNfbYPQq2SI69sQe2/SavgmPODE0M7ObZpOdrdZIMqYQbNM
+xDKAuUxvzKUbzolfhB8pfQwEC4lh0WmL7klUAzDBnspzG4uqPrWWNcmV55bttoiqhVQTNAAnwXbk
+cZpY+68K2pSn1q3nw8w4CoAuP4izlt3s0jg4onrl4Uqvh5jVxppdSUGjYkQ0BXgN+mCMFqsIosKv
+ZLBMkZ09YNObql3Nu/9pIQwXmfMUEWZsRR5fgZohsJylBCySLSgY2PJSx9suR1pqzapj0rsqkLUd
+vRjw5qx1kgJE40cGAbTrpxDjY60Vh8yEJxCkFqBnhqby9l9zd4q/dWwdiv9jn/L7vam+8o9VLwNp
+trYOKkmYqUB8/xhTIE+mWVVCSfdi5DL4mt8NW/Zv8DZ8ZaZi3eFaTPp/3Jv2b+SQ22igVdb3JVXx
+n9ybzEV+vTcvCx3P5VtDcSMM4sj59Z/klcPE9C3x7ABSphmUbR1viGEBbh1Lj2msL67x5tZnrBnd
+vtIlPK5MtsBudDN+EVgz1esO+bMMzYeIbKgtNCrSu7OT2eF9XlW+nh9CP2E9YY11IPERb3sU9Ec5
+lMMtP165y4zhTaZl+aKP0joCQAfTo4A9Cl64T03R8Gw7rxUcVPimAH4UnOeTpqA/rcL/OAoEVCkk
+kDeKZ2MQTPbjomHiqwN1VhghyPeABHV2nLoCDEFK915bK7ZPg+j986JAREIhiehrbqxCrTbaODqW
+ClxUK4SRvNCMWgU26mMQR47HkMbjhtgwiQGi3YplX3q1eyAGl1ZwxFDiqQhdR4XpRoP9wXC5gOyu
+knYtLa62hlERMxN55JN3VbxzPZVjYTeUEqx49e5Ul4Io8ZlEliPzclrTpn4idC/NuSfAMFWOBbFR
+xQDbJE5B/6mdxxRW4iokLVhXscHMMTQ4UEQJh/+PvDNbjttKt/QTwY2NGR19lYkcmUwOIilKNwiS
+kjDP2Jie/nwb8rHLVa0T4b7rcNRFWbZpUcnMjf2v/1tr0Xn7nPDU3C9lWH+3U1eTASG3043hHyhN
+/DrpQ9cdbSMb5msKYbLPebjc+U3rfrUdaZzZNZEBa3fxlbUCfOko+mAopnDDKsG65DimnwviVy80
+WUwfFp7hz07TDAe/L78wvuWkw6J0bbpYryV6OX4mbUxLpBOr+KCAxtoM/HpHUuNyNh2vf8iNSH7o
+s1vurZqDm5GBwCW3bA4xKGJTjFeiydi22F5Nbmf62TM6edD9cP7eGyWzQxP7+KqTK33ypFN7yxYD
+0iVbCMI1qGtPC63btfYQn0s3ovo77tOtndmER8Cvklo2/jOMqgY5gv+TQHsz/l8HBnyqP7/y57Hn
+/GbosCh4LwBJPHul/H6igRg2CHDlXwcAJECI0/GPY4+ZAJIJjkUQ2YBzQ/xJuHj4VKmRATL0sHnw
+HxZ/59jDi/rXYw+TKt8X5y/5huxvxL+jgVPN23mKyyCRVf/VY9OiipPHJyL0w2dMRJTC2X37Wsa9
+TTIKljP2iekQoWyxXnh29Tb/VC2G8yNcrezGamuvlMN9IliT957yvVPxOH3EqxmeWmx/2Nsh29kA
+G0msDPMDZjdyk+eberXUh8pdb6xGe1qd8MO6qwF/XM34k/Ll+8qhj98Cs75Bu+cXxTB/zAtZNjf9
+kFrd1q8bX+wI7TbDw2gkubY1jbBjHwMufqMn9Lbt4rycfkzWVD2as5kQEaRidfCTluaRCp38Ocf1
+PgVcofsvbugVF3oGaVgJOzN8CIca7nHU50jsBWFnEWUlBNlse6FPb4yN2GdRDaatJE6Iw8gJzZvB
+Rm/ZuZnGwqvgOmWfCjMzuutChpu79WrkbTnVzF7EuQ17+gAH6GnyJRfk8LpEn+Od9Co9addbnRyA
+x9hlf+hSb/Delwt4SsSGE8mQSJwPwiCh1gx6HaNT4g/mcq6WrJoeTVuTySeNJ1+JKz8n6reP54Jz
+yfOJaHGLa9pJ57XM5gok2rCJgtaNXd7yY/EgDN/dnuURu6DGvjCSwI8P8TLu0yivH5c47UHZkWGp
+NEcQhZwkPVZL5KeM/OmrKzsdQS71pgdj6NK9oPLki5eTMdkBJF4I9kv3Jm21uzzX070P9CRIO8yS
+a7Lk6avl1S0rfL1576omvTqFrQfjxMvJYy4eT/E4REQqhHZ6WmRrTvsBd+IU4HEsMf5U5lCDYBa0
+IzZZ8dxasxyDemni+7GeKcKtfEQu0iHy0QOCKBrsgaQAsc4zOUOJ03WnTVu7zXul6wnaYa4nP2aA
+qqPXmCDpGT6MJ6NCaGeVK7Fls0gwycFY0rw56I0bEscX9W5BT7uZPA2UZmg8wln0IyW5cXrr1NX4
+RlkRDZShSyJDnaBfBqKctMfO8Cb2Jaxu3bKov/WFXhwBa+WpDQHDfWgi0FQP5T+kF931QzOAz0wC
+7hGI6Kk3vAxNNt1xF7EObkEk7cgFIMih0b64Qx/uU7zCp4k4XjpsGoNYC0KJb2OqcA/NyMgyNqJ6
+LMPYfIb58r/PNBztjUULD2Ums2szGyRfOmX3QeqEfq6BTH6UjrcEYanZe9EU8a05Wq/ECUoiRnM7
+xBFp051hm47zOrZREX2uByf0z90CGBiwKbC+126b0aMGguCtNEKqVTRI2FNRytuFbf3yzfacLHxi
+W+/N+6xOaEWaTY+GI1djL7Lxw97zdiEd0PxhVhiCywBghLFCEhG77NcoLhf3TgsVQTEqmMJxmhQ5
+pE3yD6lgi7pCbKZMKhI3uTmlJFQWoy+3FowvHq+V2Oh/4hveynLMK9dBSDKMR6Zwj1aBH8nKgFQr
+D4I/VbLuD/1036Afn0qpVx+EjGivNlbaW6uIx2cSV5hsmfr1dkORHLZLbBfFtTasnChoPrpFYCSW
+dY17IByC5embazxBTU89jdTdMzChxeL5mZMgV/hvaPb2stfjVHx09OCEwT9mhjF48v162/qlev/O
+pFL2ST//Syex+qKfz3Fh/GYrexfzi7CwN/3LktVxEQJVtDD6HvuVP5/iJAd6kP0Y+xme/bWi4U/R
+D3BV+S6BVjCUWX9P9PvP1ncwMCYY9Z0oV+i/JwfymS+rPvdo7mKk3ch2yN+rNLEDehlyKFFbsBRw
+6DPBFVyR6Tu5rcsugSCHYFHtJ71LHLkf5TFNYNSiqH1Re8joiukBXEoav+qZqQU/5Evtml9Dq+/u
+rYQs2JFhCdkNchYcgCKWkuflHbIUCIVpxKEISpfSlrqbo7cwbQb3GOsG1SqS4ZD5J9fNL31o2PWm
+XDtg7LUPplu7YWZVE8O2sydOmExycS1QMPRNPWvdyRmLltMBwpYHI7WRJ9OhFvwKWw9bZfcU05Sq
+osZXZTWYM8w3fW2w0We/H49I9DTbTGvLDVJpS08EIVRu4FQyR0Vp5AMBRfU3sfbkGGtnTrz25/RD
+TEaxoLKo2LmRNVdPWeapJuTQO6F7dZdER3BkPWeyYqEVeFi7eqZFWzhVSy95GbQpJ9BRFfvwWxjv
+nZxHLago26Scb1QtQIujGoEInaMdqCW54KbhcCFC0UpLkt8WqoQcA2P/GMve3mWLvTyzHndU0oeU
+e3MmbTEpO+eAx5+KvC4iF1f0A4vc3qNrp2YdPIjxKx7ZTUNs0yGu3PIh0Uti8IbBPlIlpN/GvSjP
+Cb6v81gbSRD1Dn1h7C6yp3zBb+hXLVH0nlOf8nDCT56wZtLzWQRa2v4g4jClDYwLzZJXIruNzIVY
+xtBwIzyxZEmIoxZ5YLdKwNXcG+SAqX0YalaNb0ZLXzvtOkYEHLAszGWwyAvh0LTqZIUtv4LKGnUQ
+RkXifhomgAIWggvZSbXmRNR5FEa9M3jjRMyPzFhPXWGbhKmKEmHSbK1DilUjge3TeNvrHMjWbmEH
+6O711B7OTh5XH2PjpjaXGq6um9wfnU/cNIxzZ8TeNo94L+AHi62nVguLyzibTPqsgYcXY9CHIgBy
+tm4qi9ATkuOtZ/qsvA8HBviuSObikQ30fAqF3dxHrKDuxioao71CJY6VP0xvRpQQnRHPBhv4FOkd
+nqdKrM9J1RofNAOOZ3duCDUrp3brzFNbB7k3+HuTeJVX3x+LnhXxWN9PvZc9uxW3znyxyp1fdtZ9
+lVGxvGlDE0BudI38HY2LtENW/ctZmqWJ5TlZuA/NdFy90bIcbTovn6P7JEkltYY8aaY2dS95MuTL
+DodP+xrBBH7zNJdq7ZIlb7yBhpgRPoi15Mc77Ykvle5xYYsfbT3CYIxtIRz2Z6Vlllgq4uhtmWnG
+ZufskjWgwceRj9un0TadpvzLkjmmdi/ayLk3p+rJ1Fis7/ImiW5qY7Zvw2geO3bG0nho0mg2gf66
+SgSs4YyXyEnmBR3SE8+SorOEldo0PudZ7Hv73E/0JTBTUkgpV2WEjpD32Qx0ojtxQg/dtgEiJIMZ
+twr4QzZ0GyvUsqdhCRkliNPpNrOM9JeCCrH/h6fpbfLRVtB7/f/5Xx/T//6o6rlNorhf7V5//ur/
+0y5llYD/62fuXSfLXy/c/hAOKTyhOBUNUAU2sSMTfwiHFv+ET4oyXzNCs0Xjofy7cMiY7Nt46/5w
+1/FFvz97HVoCdKhufX0CO+zd/s4EbRr/kfREtxKjPRi27gB9Kgf4vwqH2Lzy0OzabYeH96GnUG5X
+WykIritDSoeXcBflXXHspOtuWBosmDsj48KRnbKETglRmYxrjR1ik4ecpg2JNQ/m5KJn9SSC+uyo
+XX/P80jDk8rqxyg2wyiiNxJ/Pa55UQWMSA63VehfCSUCPAoJ+xNmQ+JTDgMYZ0QfZGh5cBoisFDK
+A4pZgH8aAkxQ/5ejjjHiWuZes5UqKHCpOj4L6bw8aqIC25Z9fceEQoyV9r3wivqME2Y6kKVQv4Qz
+V88wJT9qSxINCww3evIovjNI2T+FZRretSlLQT3Nmk1EoMN+WYS/K6t4l47MKcOQSR5qWnc0cpGc
+W+XympTfa1qtX5lygSXKD5as1rB6tYmxEnJvpfKOCeUiG5WfrFHOMsupi4Lpo6cK0Perr50ltLPj
+8ADBUugFFY/TL7RwFlfApZKE/1EC3uBkW7C0pV3SHBbTPBPzPysKC99b2OkHs1q4g+dVZwfRUMtb
+WY/tJZtbyp8H1os7iCGxaRN7+KI3IjnRdaqfqXEzToa7fG1mohSxrrTjDabscpOJuIUlzpunZLRu
+67h4CMdRI5i9oj0rzcjPNQd+n5YVkfoJfydY0g/8atIFR6n4LAty/5zaoLMzXKiWDJfh6Lb0ThPZ
+rt9MlZFfHGsejnUWR/TiLPIzdb82SLSnH6Bun9xkjHZD5z1F7lgco6x7BKvOeVJ7LXj0QLhFsUSA
+eKPYxuvAQlbxtfOJ45GR1n61ImvD9DNvIEm+Tm0kDixbktvaGcMXF4L3IVdsvGlpNBBgkzk6Nd1B
+FP9aRz6J3mHBY7RfpEWDlTe1YKE0UC4CzkNo6ZucuKy1oVZ/w4EPmjI7prMVNW/GkdShG210wtd0
+ai5YsKYfbtM154zc3+1MCNJJk/58P2DZIztk6rY5rw2Emev3OwKK9U+ru5Hy4/kaIU3cLPgk76yG
+aGXISG3jA3UjHnD33KDYQ/fUjQd0jv7gOY12RkfPPxFsOj05bdgGlXIbNHFuf3dmP39Mu/EhGePp
+vgWM2mpubW2qKfrkau7nyGrNazTO8pEdmPPYc3zRFVQMm045G/iYY3Jw3NG/ZfFHBjOPBwgiTBCJ
+skMM3Cm21AiJjbApSZqT5Us1JcsBI9YI0Eh/lxYVGvkmwrrPZqZG6SfttnUMopWpI4WUb19TfJcH
++k7mTZTL7LSA2ezp4vmWgcOYNL5tfDf8OofejyxXgpSyb3jKyDEnznjQsjgPEPzjrdaP3ZOLvYJc
+Zt6GDDhZAMdUHtEaxiAmZ2gHN1Ti+eV5n809mWbDgl2kLM0rmSpdkACUbRZSHjYz7s4A/8Q3a3Q/
+6tnWj3Lss1NpLACYuetsPUdcOm35wRWNH8lEiyJ9hrAEQIxlrf3AfX319YaM89KIoLxHMWwrhxN1
+yjS6LnUMxo609y5xDN9C2wvvRdYMx6rTy0A3x5ulCfe4uVS7iBntSf4v0AiXYqsbHF5lAWRGo6+x
+6cph3rIy7Y5pNRvBSG6YD+gkYMBBNW9HpSo6c3tf5e1nSa5ogaEe1JMv6v38Bk1pPlNB/uxzidxp
+HD5BkdAL8o+ZwE2ewb++Ddx8f3//tddefe1/C+rCATJWwy4hKPafg7j5G/tDHs+ALyquwTb/MomT
+PkyEkG3Tv2ezzf/jNqCkduynSr/hvuDpuPD/htWeW8e/6+kmMA/fFnVqXE7+w5jV1K5tRxgOQoK9
+KBuPHVFvk0YrP4ZutJ8o96J+vRBDdJZ+4+z01uPTaw4TTYEOsal3uLfNc953w0sx6nycHRk30b2Y
+EMRvEc0Q4SKX+sRtvCzlD5ftYcLjIYU1mYzKSgh0F+0DgUHmdwDK6DzpWtJjKOydW4JOkmPjpCZP
+QJcQmWyUHF22+Qxm2l91MfkcsNMLHTwLiWDs0FVZYc9Vxl4+Gr8uPvq4rz5CDru9xCp/iLBARBuj
+4U8i2jSER04cBnR3MfvPnCBqxuamMWIsqstLA9vIyLQ00x2FIR7G2NnyTwUCYJD44bCLuADhQ5Ez
+oXBT2tsq0dXLT1hcO/o+oI6KzUQj5DXkyAYU57zBytJoNLBX+tx+klnTe1f8SPHbnGoFJHiFY4wY
+WQq4kuaU4rSl+2fqnEtpR87F161wbxQ8CTdIzKivjW7cWpg/36zc6ve0zcqd7uID2wxNWIknoyQm
+eRPT3I68kPWiPThcmm6TmQgX0UE/XhLSYi54OYwnMvOS40AC1bTj++m+hm5H/Twkfk3lWpbFz0YL
+y7ElJJG4eT22mXoF5+Vh1gW7TsvCJgfw4BGr19bMfX1rUIkNm0S39kwTXn+RRb1cktq1HuF24td5
+JRs6qgiyDffH+Q2wJw3SrO/0bTWLSu6mlY5wVlLCU9CERgP1rlEgRbIyFfpPvmJlLaaVu5gUgiFX
+GsNYyQw8dVAaoekkV9+rqy/jSnH4K9EB/eUQyKxADypvxfO80h+WAkFchYRIV3GyvgJF6CuHGcH7
+U9/gCRvYFyimhOqVTpn+iRtIFHQyc+P/YSoQxWBouyPnBjplEAaJ89lKrQgFsMxscyvsZ2xHq0ia
+R6ue821emhTeWpXxNRrMeNfQBPdlqhx7HxG6cnLb0L5h9AzPJIKDXdqNuEvSVqcDEMPQDz/BWNR1
+wjsD8OlPZlqlHRcoLokymmhd5ni5MgPM725rFxfCaMKPpvHKt9pcwpuqDKfPTg0lO2blccJQY+8m
+N6++ZxSm3lFcXXLXtCoc0NzXukeV9DxsU4SV+Zy1HXsOttkH6TIu058qMZFVg3OaHUs0J+Di0AgW
+sy2Cwa1JU9bMOoJ2LyHyljnX4O5ysheApGiO3zSdkN+ikC20Y+WscGBmlzuLBfU3u3XEWdSW9clP
+bOX8iYm5ENCqIGwDuNNMZjoZOMjyiEd52tELEaM6tA6DhNvEGa+f7KgUqh3BJjxMKIGApaGcjLAj
+6iNRM4hAnKz4jlQG51LlmiGp10bp3k8861/yyK/voiXMXgvh5q86Ywg+dNIFX+Hx48M8z+6hthPv
+lKdmeavSe46thtRz4T6o0emaR6a90bWMBeBI2nuJpEWD8tjozsbozPm2WNwBo5zRie9eVTiP4cB+
+JoCgSx30zdGs3lwIjc9OFTXi1MZp80SwkLFpZttYnkeEGz4qNIixxsGAya3IzSTtZQxsy+2UEkq6
+9UYtou8rcmUgLaoOAwMPePKRcgtPgmKKTOubnHqZnyMgguwewsDztq10OCzLrmHFFxIGh142T4t7
+zButcfaNvmS8a8kPovqkgEG4sWMzoU0eeD45RGhSyJhJYk/PHmiItyltG5yQmIyYcA0j7O2HEjLy
+vIRxc55UIdPBdZYUN74eW+W+E+XnUE9wiFRWpmvbKgOV2xk19uldRrEFZgxfE/aHboTpe0Z4OtFY
+tXltBvSfjRRSL3iPJOLcj5EogNELB+KzFC157KEsSnJafN4QeRd5Pn28i7hPSbVk0sHRyQlHAihQ
+TE7zeNLYDlMF3N8GY4RI70THzZufKPDI1hsmfH2Db/RUNk7dQ8UY5R3bKoyybdksbKeKvBbnge6Q
+JZA5e3Q6OFrzta7tknQrHmgjaV82StdgRtU/B3dWNMGvL1vXtw54Yfw176y+/Od9y//NwTxGhQTN
+SbaKO+TG8xNgQEjhqsPaAY/q70ax/5ZffHon+FEAbxkwDOu25Hf1xaUOF+sZ2BZ+EropyKL8G/ct
+QaDHX3BnlVypbG+maQBM4K5nYfOv6ktiJD13Kmsnk6TbMtOY73Qlls+jnbT3tez8C593PntkjJDD
+PGhs5rdz1U04ELhyGCRSUut10ICF6flEO2Y+gqzkcBFOCOY69rNxaqIWSwH+Hlc/O34evcrWKU9u
+3cEsex31ZrSkUHN0Gvze9W9KwNtmm6+ukdJ1cZCYJp+vTjZafxiUx0RGi/d1GWiKCTKrxoOy2lGI
+ocGa0lfc9LaK9cUai2DtbZfUpcRHo6SjO5HEkzz2FTb93WS7kkE1L8iYqzk6tnBI0a5tregYS7SX
+kvRvmt0cUNiQeLcdnn59X9RG9N0eTNIC8tnLdwO7lS9+PZlf2jZ0Axl7/ZX/vJ0T3Zzj5Iz7zJSB
+zvl+V+h6fSEvedz15iCuwpbddTTsfGd6lXFgBOd+QwvgDdBDSMhzmkS3lS8rbg1Jy/O70Gr+DSla
++g4wnOzsOB+vVl+X7m5eCI66cWN8T1jsRXzNzaV9JxfFBBMux3nk7OCBX4XcoQJLWsZlStFBnElg
+4Dd8iKhd1s0FoeoZ/RkbrZy9r5FetU+xPjTFISk8wmi9NZi2XUNqOxCzH5B6mNjZ70QZzuNujIJp
+jbeFl8nlsZ5lQ0RCYpslT2mXTFzB618Fsas7foBbDxlZTiToWnQUbvAgyWhHuw2LH2QSbdYfnFYa
+yY1LRdOAe519O0YvMdjvNTmGybOWxPbYbAgpRQW0QuUMhn6U1xBpj4CjvkjJfl+7OOy1l0OgPt7h
+dSy+4WqbNYhd1eHRuqmrbvd68m4tnOl4sQ3KStbuj8yVrThISHfezJnHRn+LApmkb3Em1NZvbRGZ
+jLQlY7n0s2HvG5H/wDs69a6DIbXx3u39xL0J+2YQn7TB9bt9Lfz09Z8zzf6PcNg1ib63vxS3VfPr
+z9PV/c2kioC9sSrg8P7VTWL+huqtzl2lULsmoaR/iNs4fnlGUxcAuKXSe70/x1lC5TgGhfqfyV+p
+8/BvHK+WrsTrv7hJOPR1rMPQa/wfiQx/PV6HudYJKos4bnQKWmievp1CmVI7pwpcIk+mR6z3lLq0
+3ngy4ZuO0ULlS9SG07XsffMpVYUwUecP9wWJcNWO5IYGez3VMXRTD/eDpE7GYQ482ypdd5Nr1uzN
+t/7gZOmPGXrxXmuahAa1pi2lxwCwNGon3VuAaRgZ6ku7BmJ3Khu77A1isj1RIx7hRsvdvZe6SMNe
+4ojbcA3YbjMVtp0btiQYnT/0xlZp3EUhwz1mmnDn2F0XQI9lXyaTWr1E72p5jyw3fyytNakGbC2+
+q1q3eBZr+LeV9ujora5CwXVe1s8NJuU9+1l8nXqkAsRnMjh33horPrJofDPwHwxBsuaOW+SgV1rW
+3/dD7raBxmnJtTNJ7gcVX07sBConORjTMbIt67FYk87ZOZN67nkxCehChaF7KcjHUVM56csamd63
+LvKWITK021GlqmuYZmDUVNY6P2TnouKKuc5FWnga1mx2YZveAy2sZUIS6GAfqKslyx3ktreCfpyd
+h2WmjGbTrsnvtkmJ2SxTOuAaN/K+D7RIvKOgx28UpM+3zWiZ+hZCUNiHKXJA3GBwSKcYdIJWW6ca
+4y22aiLpozrrIIJVWv3UEVyPE8KE7O+Nl7DylbsN48SrUwk1havg+zbDz7vnKQ9WTLppWm7tNSwf
+b278VvLNHgVSyoumkvWjeIKBy1eanxxDyH4J42+utH/6k/xfXQCpGqOLWZsvTgbbeIFFmknCDdlG
+7i0WzgTdhqPzYJWywDZuOQXZhJNeVMeeMptxS38Co7yjCubY9qg5P+207uu4Tv/uWFcyMFZ5gBWR
+cWBKzm5zluxUxvt+FjNg6/wcxlVi6ARZzxvu4XJXDm6/t4i4fyMYyrjVlUJRyM4ZaXBDt2jHxrno
+SstQAWLRIVQKhxkXxoulVI/Qsou71ODHIUfZetcRVuLTQny1yduFwGiWI0pCQZTRqNda9ZWwyIrT
+uKouNKuiwGiIKhiu+4kVsbvKNXPfzONB8PoccLl1JOIrmcdYFR+6EVF/hBKCopn3KN7bYjqEReXu
+caCVH60Sj3K9WT6gzMYZwceDTKwq6FDSt/orE7ZJIH7OB00JU0lrG1dHEFcaKdnKtwsULBoskmxD
+HQFKdb50ZhLQZYvo5awCWKS0MOKx+bg1zOJE2SbaEt26q3RWrjIaUYDDi5/V5tlhVrgzVsGtc1PE
+t17pcEWVD/Ge08J+Suqx/GCMRbfzyBJrj9k6XUTs/8eA3iaa84QaQIZ1FhnXuQTTrTgDaZAC3K2T
+S5XhRDp6i9c9NPlk9WTndqz4Kquf+XzROEhcgVfPPhgBAxLWwZBKsHVuytYZKlXjFO2Krs8I3TBl
+FevERSVord966yQm16nMIGHjTPgbsxq9yMxtDlGfH3h8nSHoqjFixqMTytF3ESJji5ynBsGwiEqG
+wpljkBuDcqBWlravQcc/0Y2WfDLy2Pc3AA7fWVcnyYZuqO7J6IvmwfCagmoND/5021C0Fp1587PH
+m3UUhK3Tpg38D26bHB8uPmoqmeyjMObyszeF7lefjgx/32aJz9CrfqetkPUdJVNWti10OzrOK8NJ
+n1h6ilay01eQ57Dyng427KBXEKiHaPPOy9fexAoRLUyZXL2VG+WVTveLaLMdCli6z4Q+XLxh1E+o
+ZOYXofBTg2SIB2dlUj0rT66aY/QgzCCr5kqvliUU6qyQVuXUeJQKc+VS3iBttrp9ob4BDlZncfNu
+T/ly0ylMljgL+1JkoLNYr5zXXOG0owJrof0bfx+u0K2xAriYtYBx2WgC5ooV0uX84bAiY2/40EaF
+8SL2gfQ6iu6NeJ2xIi01SyQF/8L9+q+4E+i8nGmiJDYGM1p+EAORLagNAMSuYomxo0Hh5CtinK+4
+sbOix3LFkH1FJEurJKuUW/rE6oUt74HwjemNXCukHMY5oOZhBZz9FXb2Ffesrwi0s9LQiosmtw9E
+OlG0tGcRZXXUChhqmudT0vUUWd3H5vRjWXFrTB7LjbFC2GMdAmSncYSjg7+kpM1ZC9usaBbFTYbv
+23xtVLEbG0g63txU9b2FqvotW1vgSF3gErJ2w6VcIbQ90Ik8pJ5+/OdcTRnRfz37n5Pof5z8+eLf
+kUf9N7JZdKh7/yejiCbwc/Lnlgn0gM/YMoTAOODyNb+DFzidabyySaPhhioYz/lHv4/+rFp8mpS5
+mtKXYqEn/J2rKXrCv19NITGhHon55G7ssOz769U0rRRBMKanBmB2T3Edhie3JnAEMmKbesSwb52o
+Ipko9LwhIBzdzMjq8IdvC8BfFYTp4P9gIUzjUzc6VzGW1bZC2zzR4lQGLHnCk9oLPKf96F+l3pEQ
+bE++vskWseAciq5V42EJGttw7G48tyjvo0jv80NLKsm8QTW2PBLIPO0ld/TZY70+ctqTOVDscVoT
+SDkYmf6VYMvnVvhRtW3brnlrijp5Rars8UPEoQm71nc30ncXCMehuro8Y8tdqQMab2Aqp3uer8Oj
+zEaPB3qXDpLjNElPtqAsbauV9MMAKmJu2i1Ixc9yUlsMz6y9b0gP2hGRtH5MyJJE6xtEtGdzXb1k
+omn1FzGYU7ef+smzPs1pWb0xhJdE0jWxsTdb/MfGVOmQK6J1rN00ykgllk8aHLZt5zPW0GnACkfV
+wHvozi9uuQwbn1iCl9ZFJtwkbpNQcJib4Ygl3KQWFCUp2daWKCgWaofqDM1NGdPseF5DpkTNChs3
+cmLf1oNp3dvWXO48hbr5aZ0/Fwp/C1cSzlJQHNO+v3cmoqqDwoPK8RQ+Z3Nen1HbjQ9HwXU4RSge
+zqcC5s5c+buojac3+lOd47TyebFC9aSVtffITyw2bB+QTyF95Qr3KcyvVsAf8rKlNhySVpIEPDZK
+ePptGoUJEuBhPbFjgB1sFUbogDCeC4UWIh9UpDOHOcShk83lB73Aw1mze65MXcznbjfJGlIR0w3U
+YqoARmtlGXuFNToKcLTShrRuKcSnusH2weV8BgvftrkMjccobvv5oqsS5pE9fhX0Q5m9GE7bim3u
+9gStAtPyzetU+WAHVqXOkP3xj2ptem474AyUcOI9VBG0pSqhM1UO3auaaMlrZ24zbqFjYKgi6djj
+LroZCH35qFXbNKYFycTTt5RQl/lk04sQNe0tyavgMB2OmJ1e5+GO1ZCTHTLluuE9q3qtabiW0m0u
+4KWEw4X5RD25qsLmFqd6oNeGbFYt0ZdZ1WYnqkCbc4gubY8HxZ5EwuwYCTncFDgQeFOGDES0aRB6
+Th4MCZFdHaYXmNz5dR5D75m0PvOZ96lFGWjq1eGm6Htuz9R3ukFaYOLDOl8nD7KM8MVZNEKahWd/
+s/3MP9hRNz2jxmefnVGkz7GRp5D5Sd+9qaKyfpOkjrybs8Y+9q5VPGhicPYun5Q7wEPjiv3ROrcV
+vRtDFoVHSqOLe5Rr7476u/SOGrLylKWkV/tjV/9A49eDLA8tcuic8IubWsNn2UXWvhVEN2yGegwf
+JHEiCIkD7PANDo+v3ALHQ2zSnIvRMIEloZVy2AgcAZcJnorpGx7oc819/6NM62UvWXxyQjTTxYgB
+hzckX2bPWtykhLhEpUFN1RLZ36bJMnaORRTRprDs8tjSBSf2dqw7D3mUapyyvPZboiVG8oPp8XrI
+KCZglzp69XetSp0ffuaab0s254FO6NODlYbGlVUHVIzmzGrcFY68F1XFbxtDA58XSae4DjtyqBiB
+r1nk0UWWcH8l1ySp862JMnbrdbNH4DuE0oEPNvpcKRfAozFl/RrLMabEzoyYjsPGv7Gd3OZ6XNDO
+3Q+dcehQ93jdFoCpe7IHyNzNCTF4HJME5HlGZLmPSdsxNgXxeS99adkqd6wvbwQfC/6Fyo0IbMKd
+UwVtYvE5oufebFmUyfEqZscgepF585MWmuNO85f2Pm+s5GGalaw6mVIzd37EGBtUqIvf+t42N0sK
+fX3pKXRl2025hEPXKl8Sz73+DdLPz/45yw3VK/XrC86hKt6//1J7U1/7+/1G/OZxdcEw4UKO4NRA
+3Pp5v+GmQowetxfDJWBFZ43x5/0G7U3AdfjE+Nr0D3In+v164/+GDMPf9aBBuZJgkvs79xu6If56
+vyE3j34Oh1FKkawwL/+22Uh5kmXtoB3d1HR3cd/w7qYb+MYQE9EqA/WRm6lgDTqSFhd0pvwmpgzD
+heGW11AU5smdTWs/uEOUoyvMLfzDYn+uY7O/lkNfnEyLX7qdS5em0AQkN+0jmxK/wIG3YXbTM+6d
+WnKwmo1rDPXLghW12wjRsWgTWo9HWh/3iNAjMV50ax1qrOfbDlT/sPh8ZVfbwztROTFwC8fFrh9q
+nehXv3n3M0fmW/p0MZKO1T1A/zuU6nmW+cWKMSWI4Rjb1vI+12X6kjOkBASN9RvBphKAZGhvlooI
+KqKP3E2GhXprz9pbpxXevtSl3DVjpfAJUMdKK42Nm/UkF1eGv4vTctxYVNwHdumfBwuOHe1gay0j
+gXlLON3l9vgUWsunmd2+CEldKaN0RGjTZnybfsLqEa/1Yo3NDWErL0i3Or91PHFhSXAkDnnFwRn3
+2E88tjJR4x+kOc7HwhzSo4YuuS24du7lMtgbnLUJCRWztjcq67/IO6/luLEsa7/KxNyjAt5czER0
+esekp0jeIOgE7z2efr6TFEumRLVUWRf6/+ZNRTfFBAECOPvsvda3IMfp4dnQ6RI0G+L8pOgUp90c
+T/bGRj04Czr8/gpvZtC9WctLwu2jm8zJ84dApuwDUU1EsZPjS5f9jGEpIB37ynDUZIfJgkE1+GI0
+gUK6nvW5tiSJKZ1LWoaQ3tXUl9itqi1IvQhmR+0Ig8/wpMq9M3eJUVgFGKIQBTY5YAAcNGdDlT4B
+nHPprtbaVA57pDNCRV/ZjTMPKvqjQ9E6a49+xbLyRgOpRznSEBoOeA4hwGebGF+CTKQHHKiav5V0
+KSY5PUjlcy9Ey5ilmiEQdRdSWaZXGrz7TSpE/b0WSsZMHUwotEOn3gyMe/YpHRUEqQcvAFoD9Vw6
+OARiXNgnibANsEG57GMA+XWcbDC6xDvybLH81RguAq+kMzKa0OXbtl7GITX1GLTGMGlUiuMxHO0a
+4ECq3WHoaVRMSFZ0PTqdsrBBJVHipaq/UJkMruvYrVclF39axJV7GY92s5ebTr8Qosllbg75KqWe
+ILXb9PVnsoTkeKqg1VjVXdOsHB1rlmo11UUGCmZjDv64TB05PI9Tnwcu8YqOcPTQFVRAZ+/iAFkH
+8TAsm4A8FKK3xkVMlOPUKMpy3rU6Pe9ICBMT9Rm2Z14t+1yh64N8ErtXQ1kxjFCZto4haoSWU5v0
+rnChmmnznDrac1tFDOuotZ1dFwbVQtNDMGn0YrMzYXBPCIhM06sgDWvUH72LKQwLKtHwCG0fRGTH
+OtIk4P8e5G4DBDi9kT72IP+h5qDgNgsDDZBWrN0qw31Lz23e+insyhFdetxI3in5rNay1EAEl5Wv
+z0wDsRsxs0N6JRNBuVaR04G77gd/XulurE0zLWnpz7hop+gonA+40m/Sxqg2mUJfdBLnfnlNgdQ/
+wvOn01BWQU7gmKxQWhQGLWyNhvNExpUiTMQ9DOncZ5K2DAMHHXIJJLFq8nyXpnmwNQU+UaMJdlHE
+ShfwCnb0+whED7VrbOxxASgfdLMgDzY1+ovCpus1rVhZgr9hGvl/1A6i/3Bktnh5fikf4v+aPuRB
+zX+vXsoyqLNyYL3+1pcpPultgMYSTY+C6Rk6BJWN+dsibv5hsbhj2IRxoKnKYUr2qUnh/AGGjamb
+zoKNFMGy+bhPq7j9B9JNgZXRmfjQwPilRVwXa/QX4zO0EYQ44fDkWCJ7yRTjtS+gMhCHdM8J03lJ
+aDX8p6A3bQToGvNeu1LacEF2RxQvEUpY9cbKNOnZ1sLRnfZyZIyrYXCNR4utdj1DU2+vMt8Phmt2
+7AT8KYz/d41j5PUKYQEDZ8rbamH0iJeJuWzqlpFdLJ+Uh8RXrY/9GzSTw7YRYbCs3xmldq+/QJ72
+oWEHoaUy6/f067AombSDxC1po6ofZXvYNb5q+kzR0AOK7NgB5mDH6D0qoSoxn3MPo7pW8pR0q7uV
+w5Z76PCqh39D9/z/tVdKBNi/X9POU7oo79e0/Ozb4+CghUEdTQiZTNno0DX7rNZRTPpyIO1M0zS+
+SCKzkEBrYEbQ8uAlIcSMZ+jT4wCAiQpYw9es2DxFGJx+qagVB/nmgcAxYTqaZuPmol7+5oFIUeoS
+eVrOClTI3K6puk99ZTyzIaRM0IxKaw9qB1g2lMrnWR8Gm07hSbCVoN1JlcNN3ar9SaqhFkUrUgtZ
+Gri6HXP08trTKXCsUO3A7CTMcUdPV9Z0tuhla5HmfkAYbk68QtLjCYo070pNVPRnbdw7JN0PYb2l
+2BWgUL3WLiQajqhEGWwRb21d4PmhPCr08aGOyRlj0kzysx+Sw7BgWlk6k0rLwwsg2Ai2ifSaej2W
+hrYuMVWBc2PlQ1Q0s9EUrwdXf8mIzMFHpQQXTVPgKYlTl/Wqz+ZeGYQXeJuhULuKf4nJMYUYkchP
+Xqx16CLl7pwM9kCC4OO5l1KIkBLto2Nd251pX+Wgnta2XBsvPoyQZWpqVFYGj2lSYGOgIaPNeUix
+F3lGmS2lRBueC0w4V51mkbfTOtWK2TPEvc4d1pVjB7fsLLQTeCLWjR342Wljyc3AMDa0T2yGAAuz
+KLVFoBXaorD9Yprh9USJNyrXZZEaW/S36aK3gmxJBBDoulgvzmDlIu0rnIpqjJSGRLWkFWnAPshk
+4KZMqw1/lQ5lPbNd+qQp86WZEqnhnNzPauXyep0pPQOSMcxh7ssD4WaFx2VHlzxLy96cNQEfSNpv
+ewrjq1qNpKStR9lpTlAs1bNBaqkcJd9/ypRSW9Yeo3otCowHRRuq64D1YluYiXYTya2xsYzWWiVe
+066B1aQYvmx2Fp2dMKGvsnLnUz4sVCdyZx1sjXmMI+g2j8lNDbKGPjLXfdFkvbEwkeEzVi6NxdhG
+FXrLgGJ6aBFn2yWKYM2p4hVDR/hPWX6aACd8CvM0u/QlZp80kdPq1Mp8pvdj6ggesFayGTBo9BYh
+fYeqLvRblZ7LtV75yqoiI3leRGbFBQoyavZhANoVgPrKo6if1/hnppXhhPAKG+BVWlztUAxoi97x
+vHUVmvKWMKR+Z3syIz/Cmuj3ENFxxVgsXUhNNb7UdiE/j7ziCVVTzo24b/AQtr6zoE0fzS3sWWeV
+GYgpVQl+tCSYg7avl08h3vYbD9/Ceaq07aPu1fLMdhIp3KI3MufMQbvFf8zsRpQQP1gGnt9H7Ymf
+fF0EqHxY/0UgAHmUsCdkpEOviwBeWkKDcNsrIpBSV79obIgoNmAUIlmcNxF+qy8XAf7QcPjovNoW
+phbe2r8iKhL0qm8WAfwxJF6yUFGGgbH6uiqqh9xNs66dxqWabOjNjyel0XndJOjo/8qgn69j8ny2
+RfckkXu27y0iwworQNvGjAWmhRqdODF7TUhvJSa3wg7yhTpUwvA11ndDZrbRnCyZ64Yxa0tnVwq8
+SdCCmCTkO3BggzqJsgjSCAQkKWXDsjSZXM911e64YwNf6iZ52TVbUD8Q7Sy1umzA4FsTSOXh2u2g
+Vs1sRiZzL2uGVTbayV2mGbhmWD2dGbohiHwy4UkQhKJ8VnqDdap5abotEuyFSTmAFnLzdoYHAeWy
+b9A9z0L50sVuu+XFjKDaG72dqdS5jB00RiTOS25lASNc+JhG0GVkytq1O7JrS1ovH7DqWUIWWW91
+CelND/DdJxopUF4cfSSZOXD7eqcFpTXOYrkpbn003ZMoVJxL3zTi+rIYMoSQTRU4c6Oy3Q375JDu
+RWLptxIqCGmSFJFz1rY9TfBWSqLotFd66T615SGclJoZldOsT719imdrCUaB1XvUlX7p+9bcGo10
+b0iywgFiC4IIGUXOeUMY0DZmudikmUFsDMi5itSckjBPIO50uLA9l9OR0DQY7J1WDjPiivpHRR6D
+a4YhjjbxaFy5uFwGt1pUI5M/OVSatcLocas4GAjdYMincFcxUWZ6heqBXhDrGOREoy9ufGg889bI
+wmkc56owKA9LoxrUvVsTABO43BZJ369SOX2uIytluDEmiClycxk0lkrkQGpv9cqN96ahxxFdJUta
+A8EYTztVvraKcGeMRQIKUje3BT3naVEn0MgAF3KqYwBSKEAfE9G/axXnLBt8mZvTphDKG3+V0bg4
+TSmHHtyAmp08gqVf6ecFuPZVBXkM1woBq0mS3isV71fJjwR1ol65mZw/xB4hzxASwPmBb3r0bdgF
+clgs9KGmwXbZhJV5GeTuRhuYcwqwLLYFwFtm4eBPj10oCHWrKxeFhHCvaUbtosURuRSIuouUtvgZ
+vhNnNyaxn6Oejv0dVHv/Rm9TPNeN2dors6+Nk16J0iXRRi8I/rUahFpwVTqVSjCnrCOiCom8qhho
+9B0ZCSVYMXqBUbFJqsGd2WaD8rprjRNSN8g8pFqcG2ZyonrojMnlyad9pctYWnz1TO2iYaXJJNqW
+E99L8i2wM2oDduXaWg3jdgYHI3iREiddeFahXaK8UW8TvbCe4Do4V2ldDZN+HPRTVR/ukRqtGx34
+oZkTB2jpVb+P8cD4E6ct7DsJcePSw51K8TO2BCvqc8+vVgQS3SMr0SZ+/2hl1dxyJG8mU1bcV2U+
+LHjWZnE+XNcSoQSd+0zEwRRr2Yi+LI29CdJJDPxZH82GRjsrybOcDFZ2i0YXfkpVJ3PqsHiimSUE
+/XLUzhol/agMNQ5qajFqT6lde3HLprHdtu6Q7cq6s2eNTp4gwuIsqrNNr8k2PSHtDNXpRg/8lxyk
+CXZVOjNxZXrExVbRmWMzj4DdvK+iWlr4kUZ6SmBvUXem89aKL4faXedQ7eUqvomJqoQNTFoTbuzK
+oVcmKyVs4qy8w7aSEwhrY8jLGQsRHymHYKji4RyJCRGuyIyVEX+JnKZT3xfGY9sCMeZJDEyIH1Ji
+RszFRMO1P9HHmq4UYtGpI9NSTAJnAYb9ykqvrb6+JIXbQEE4lPjM7cuGkNkm7haGXowbMx3PaAAt
+SEbYaIz8m8i7ZrBKTpTLoz7iIJmxP3aEVjJYIt7yPqiJQZBmZz1LFvorx2EvnMqokqJcRxAQZvPS
+a617yexg4nX+fYt9zkDg1WfJJLZ7Mr+sztvoIAjn6NalJS53l6ZpoZ94RKWj4reREbKtWkhJEjzU
+gNGneM8JRMrKeO52jr7IDddmNXDSWSj59t7qoHOqaQGhyVNGNLcqIL3cAGzdoFKHWNec4NM2sFNm
+1ry32WMb4XiZuMkiIjZqmlA6791YGWaaTroIGWdqIqm8vux65sWuPy812n4KWh5M7+0mLQdIqgjs
+l3ClMayWtXqhSWm4wldEdGfZRM6UEVo4G4tOfhiCobvwGtuoJsDQXAnpfDtq1KCtvDYqpOLoo+hL
+ZD4P296jK3gnuSDGvcokxyF2orUJVvk01JuZxOx22pSDTpCGEywHLKvL/5zyj1LtB+XfY5YO75uk
+BVL5tQIUXSygZLJCNSf286I2fK0AKfM0gN9s9KkEGVV9NklTNQJU/mp+9bkLYGJRFZZrRYGc4gBP
+/oUC8NB5+6YARGlMo4FGgCLTUxAF4hdtMdOqB/ZJ5YwZxceOQcm0TOPgxld9eUEWin9DR6qbsgr6
+O0s1n6QsuDZL8wRyxyohzlbDNOKkOgkrRvxh0Io8gnpQN9gY4/QSxFW6ghTfnyYprWQfY7Xk14jw
+fLubq0UiT7HS3GOJaWY0kz+g+/BmiWBGlqN90hGqM4+M3N/htE54OBIZYYLKGg+1UOcxnpHkra9G
+jfUlkdHUBoPvLwxigEg9651imddobKgFnojwuR7kQl4MPZRBw/XJCEeRvc8Av+ypNL3pGCD/5mE/
+SyqK3GkIznDBsqnNldBvEMTipZEdCfm2rEBMGvhN0AwC87fVftZYOpSQIu5YKoYHFzkpBCkD7mWc
+B4tWDpTLuMZ8iLic9kJzaPi7aHz1nOxxSxuX6GirRdagWnSbfHwy2jx8ZDyuASCNdRt5sWPcUyT1
+PN6SNCNRx4CR71jgxboUPLzRnuOQpUFjQAQZzSy9oMJCLB1kyhI96qzW1dsicM7x3xC2ThUFHQPD
+dXSW2FIBaYkdJHioYiIFNBOLqJLJESQ7j3OqfO0xEoXgqOnVjAYSHxZr0kojN5PoikDjjVeqEzOF
+2yCnYB/sBP6ZRKa8FoCoyBBLnTTD+EgO8qOPIHOilOoa+DNTwaI3+GFiqFiRyin0B15+pnYapkYw
+KbuoJ6IOvlRY0D81ckzwgRXKWKqtTennQK7SIZmWdWBMwlYKF2Zuv5iRchPGyeU4Gi+QypSF1FmM
+vHoEPzY42xmziJ2L9otFXHrCXrdu6m6PPKyd0za+b5X2Nlc7Z4sJG/KXj03IxWA/oguDJFQ0K6PM
+85u+9k4tdGhTV9MeO92/M2rtTtKSiwTsFVQw/MSRrjcryvB8EqsKRgmruzVInh8zJOZDlkSLOhlQ
+MKnGbWZVMmZ4x514xAFx1exFbdSPIH8AkDjkr4KdlbcBd+02b9rgmdxGZaF1irsaIdLAjiawXgtz
+ygStzKaF2iAVJYliMZqNzcgpCQlpLJyLzkqqRQFtlNtl6O/M0FQnqmEoU2KRqJbIv2g2amK6w8xu
+VXtX6pm0MDnUMMXH2oXYVH2yfnRGWyrh0GeuESFwlwhXjINO3Y+HVlwuunIjgRdTV3TqCtGzQ+lF
++46dY02bWzT1lEODzxe9Pt2pafvxwJskE+Xuh7DpUMEPokNYHpqFJGx0E4zV2tIQvcQWEiypPRay
+6hCMFMq2pupPSk3z5lVoNDvdEltD0Z+kgxeeS7poWhJ+IK15FzsgVehpOkSP7ofEMBeO6HCAoTXn
+qO9pexiiA8KEiqCeWC1XNVK+TC3DLS6gIZoqPB8rLwj6ObuFYJ+kNpQmUIxzow8/lkUHVC/KfaJT
+PLxnLricqLvkHdFd2oUzrgrZ1W80NDpbQ0c80OhNNUtIlJ3XmO83We35t2FT6zeAEp7+Y1Zdgzb0
++6vuv54fmF6+75UVP/267CJ+pd/M6qqpjJWge7+tusKxpSMmkWWNBVQMlj4LSoQqFoktLXvGTYwe
+WZE/Nd8xh8E3UdGZoMNlfqT+0rJLd+WbvgtJjAhTWP5t3ZZpC31j5sK5wsYk0ZbaGEbZVPIHHKBV
+IW+0sLcvbcXqVtI4jqgjbH1LrpT7UkqWvU8bJT8vQOTiE6hrDCpJ395mRtduM3a3exmqArHmYWAu
+htbSp8TZ5Zex4bTz2qwiBB1KzLS2bK2ZZxTJFY1EfRWlhXRPzmwbzWS3g6ZNZ8KBjanLlLLpAM2p
+UMCHeaRYe/UQn46K38nL3m6N+wSxwEUj95I1K4wg1j66Y5wgxLTicpm5Sggev5L6DZJK9WKsPVbN
+JMjY4uJh4OnT+3WlkIuDStFbMznP5iKuaDtiTpOnqMnVR0fOy5cBG+Ytblb7umokLO3sCrJkXtH7
+mVnEvOxV8ioDct41G81LUO3skYwBFL4sh6lmdR91FthtzQoCnh8t6wuxb95LlxcmZTXayye07utM
+7oOPoxP0z5gPWEv9UF8NOnnNRtxojywecA58zyelqQcSTH+LACNELoa3IFuI9D40IBvbG2CoZZqy
+16MEkeVgqSvkxMolYTIk5QY0r9wZjeZqLuPpuUMZo9Ky1XrfEAt9sncayb2u2zG8gJY3h1XWFVOV
+mpFIZK2YGVAzooktMz2wTCkixc0sOLpZdmveyTreEdvbqRU3yczSMwaCVq33S6CVZBzEbZgvyfv1
+boouj/Zsk/3LIa66eUlAKMtylRVzp0/ohjemJX2IUklCpDi2d41VOc8GRcudGgSQHFmfMSoUuiw9
+5VasLvXICDdjXipgENK0Yz1mQSDDQG+udLkMRGRbJG3RoRjnktOwK23isZz0JSa3GS678s6BO0D6
+gYNoNos0644FM51FUtze2Y4rXbKVQR2e2c1478SlMjFH3bnMMwuBXmezCgBfSK+oeGOZjVvZXMY9
+gNz1YEntnSRb2Z0yGsEu1q3sxGEm1E6IXSowQqn9jVPl5so0im5Xkz05Itkl1QlITHffZSkJodgg
+dqand2xktW6H6ESa91m7CziNbZETKo13mNTEKC4qCGopp6Pk0VLr1eLZDNn0a2b/QEQHhFPF2hOR
+6pziPEJnSpAw1jT0ot6DJAXFc09WhZb45YjGdAx7tD0thC6mclmz6CWIMUUuhCOBrFlr0fKfMc8p
+0lVELB5QUU+mULAkX74wh9HIdkFbSqvCcYsFRhbTfaK3KSlTlwV0K2M3R08KxWM86ToCxDaK35SX
+bR1b0WmNfALnNEayc1q3HiVu0lYnktLnV1aNcw0PPJGFekUztiZS62YslLMaEz2vLd/Yl7hItAUy
+E7Ofub4zxutB6XDTNSNYuGnbSNBV9HCwBAK8A9/tk5+R6G0vbWCweMCKfKfYqwc1W2JEyp3RYTCd
+arlV2+e9kKkZFn/gUsuQbyCpEtlXQuWmHARvEDW6hUvbC2e3kQhZ3DjabjFR7TrEMcnJZDvFJ+u2
+6SHhioZMtRxRvNCi8rBYjWioEKcT3ykgOI8B9pWPgE6ImoJLStAnYVRggbFOEVV/iAK1DrGg2HSJ
+CM15vbLLEMGhciNCRBuMsdKyZIq71nj9GldSWnsYD7WaoI9DEKmehoSSjlAEeLlapNNOCieE01+r
+tlgFOnxeOJhCSz7rB/FaTYkIbbsJoNbsqRZZqLpIRU3Cqv1AWkCg7HkJSftE5KcWhyhV3eMdjjsv
+VC5oXBKsaxfGSQtCZh6Uer7rRTgrnyaAlyjMfVwKIr81OmS5wpBHTD3Ixh0xkcQiuh7BO6Rpkv5K
+Ey/4gLFYucc56y5iEROrvCbGlp1NZhOWedqDIlMWRAiFvQyF/0FmDzdDJNffK5nmzjURSeuKcNpE
+JqZWPyTWlgRjTTpNLrctTNFZI6Jt/2NqIVDkP6iFJg/Nk/+DDgQ//KkUUvABISYA22qSZEIA3lst
+ZP+B8FNVUMbAUUez43xuQQjIOnJXCifkCDrqnS/VtdDZAInjwcCMJES5v9SCEAf5ugWBrx6AnEx7
+hBUHOcLXLYg4GHRGZ93S1lJUhN4op7fkeurXXmXBAcP5c0FL1tBWWt766x63zUgAlFK6M9KqmnsE
+lZWxSSLbAkczEBS7HjpMEeSR9LW6zKNSzla9R2jI0i4rvhvg1XbJg9LVZt42STNFO9NgBjBlnCFs
+e9x2Ux0SdqtRhS/O3NmpcBM7wzwEJOqyvopsXl/E9DJckdl8OWT3YqQsyfoRijUMd4q60oWcTTko
+20wX6ehswPvkMrzRcFxqIJqkZeF4pjcHWKtC37TJL6Gv6HT3TenwDh7jjjFSWra8VkYwT6Ez+Nq8
+yoveXgks6xpJ/NhNpYPyzynAv19hHzHzle6PBS4Qq8N2Ghx0ha6QGAI5crETJVYJvcwvq2VRG8PS
+7MAETUHG1jTfjRJ6Ogvlps7RMKJfjfINoyEQWbmU76wyGNhg+m6vzxWj6D8MKj6huc7idBkmXWiS
+SVFT3oS1ot05OkTzeeq27HDbRna3RqgYZ3JkgpWO8HTfDV5EG8ECtAfwTm8QVDtwTyaBIFMbfsHw
+p+LKg4sveD/JqsBaskUEae0KurUkONedC/E6O8CvnQMIO9Mq93lUoWMnr6BswcyugWcPjQ/zsj4g
+tRVB14bLAWib13rH8F3gtwkRAcUN3tJixAmfWzKtij4pg6pilhDqxzWqcEMVB2PUeDBJxYQNTQlT
+Z9kODzaqtmtUxkrmOEoYWJ1GnqCQiIat6K1jVMb8jpn84NNC7zsyXRH2rV7YLObmYDrnlDfpgxNU
+pn5p4PGuFnLq5fINkO/sRo1ab4EPDYeYR1bXmQZWdhPlpvUMzY/FdhC2MtMTDrOwV/Jgrh+cZ3lX
+hGvygJEpNFwjvGnCpsYbHbS7ZTDhScX6PFeFpc2sguE2NE0cb6kqehIORBPCEoPb4mCIo5jNpnlm
+NNgpDra5LBCyEkptthymMNaRMyTd1Ilv2vPiYL2TJJjdS6LO0rP2YM5LC2HUI+OlXurCwadmYw01
+2YqdvXDYX1tl664z4frrMt9c407JphEemX2rF+WFJHyCqeS42UzW6/Y5YUrAlFh4Co2DvTA4WA2N
+MXRPQpFaUkPlQDfu5bwShhJKIPYNWxg5mCh15pqUafwd8sHr0QjbB7Wl/uwevCA1UYf6fDh4RIrO
+zzdYfZ79PtmXgaZtPSbGc1WYShBC4y+xhdXEIi61nKVEX+PkKvOMgcHBmaIeXCqZjWGFQSTelQTz
+4A0vZYVJqFqx1h98LomwvICRwP0SyYkknSLFDcapRwxKeKl1hv8hckpZ1NeqvuCpEPgGInqMtcHf
+/oMc1MyR1Kp29m1ZkZ8W6Rj0m26ImafGjK+wsb/kXWmUSzmQ5Y900qQLFPfpTsISQ9BUjMNmBm4p
+v3XH0ONNEJspMVCIb6aFP5i8T/0OnbVmDXKwJC8HZVUVVyup91c5D5I5lRwpL5ixI1mZ4jhyVpnn
+Sy92OZbSxEP7f22ofjGPo8D9MNQ8+FcSH9BwzQNElU7YmM2WYKhGn5i+xxRTTww00t7gbHop5S4G
+fqhm8wS7PAAzqwF/qEZD0S26ImFSo2sZ9LZAsjp56sRVUaAhVjwwsoSnbvwxa659WS+kOUiTjiFl
+58vh5PcpMwSO3nvJZg/1w/wgvz1vXsrh4qVqwI++df/Fd8+yIK2vsr/3j378QZ+Ev1dD/vI///2U
+NWktfgMPkTllxmdNsPXt0OTwKx1+3x99QoyfvW6e+WgYZzKtGTp5/Ed88YFxlnqfvm39QXcG4aT9
+9u1Xjc4XV+i9a/Dj03u9mD/+N1+dwMMz7Y1ZUNVl8FR/eQnoNjHroYb5qov1zmX45lM+Xway6rA9
+KkRHifPliw/84jLAe8PWZOsI9l6/frvLoNDAVVVdO/ZCiDoU2bjNlOr1i3bdFxfCAokHDclEdv76
+RXHJhf+N7odPF0J//cU+P8m/ekeIDiTpC7j1P53p13cEpbxl0RASFOTf8gIIBvRRjwSNW/YpNtZv
+djZf3AI2Y1STJ0HsSA5ftHp/rysgxrWYDo49fxWgGM0t5+sngEY3jwevTJ1Z1eHr9zt9fmvr2NO3
+eSMamEAE9PKLvz5sNpMhLdXS73babw/+sW9Ag404k/7Pr7ivL4D5B0N7TKn8k990KSBX1XBoEhz5
++MtEuGFtxT701Q1g4RwGOcqN8en2fz3Q77cCiEico16AJjeC6TC2OoTpiLP96kLwJNBAwS319u3f
+biWgvyTWqKMvg2MRuCvSel+/vn4eyB5AH03fignf4Yvb5fdaDj69GBghHnc/6H+I554m/6cTlSkC
+v3gzmn8wq8RcZ719/7e9EMc+GNSIOAcdxrzfXgFE9PTNsF69fv1CcfgT748/t15TP4ifD5uu4KX6
+3t7svX/wtt/46/e/2VN99Q/FHuz12K8bL/G///erncSh/v3im2/18OE4n3780wn+9dBfHevtrN7+
+z1WAMbR88ofDN4ZPv+b+IWHrdjp8xxHBM/+6+H/+df7nv7/6Zb94Cn746fBW/uq6+/OVcuzH/9sI
+8cMe93X7+3d+/e3Dc5N+R7jw5+J47AlMMSRU/3URtN+D3YoKFH/H2z7175/GBIvRd//KnyrcY8/i
+X+lD8lh+5zr9ua0+9gj3D8nH76bFv72WeRsde4wfRdgeeR9d8bs/fuf6vP32Qnd65CEus4h8578+
+a2+H+Aduo8NtWr1/CF7Ux57FGc2Ul4f3jbqiDjn2GP8+NvHIP8Vp+gOXmSbwOUce4Cfg2Mce4afy
+DY48yO7By96/nUTlfeyF2mbe+7NWAQQ6+gD/PnTryIu0xdgQfG8N+vRgi17d0Wfx8L3l4e0A/8Bj
+/TPIzCOv0zp5/+UnhHzHXqOfgGIdeQa/zO848ng/gUQ49ghRUL///InkuWP/KvMfvGmFZ+Poz/8J
+w8iRF2n2Etfvlwb6P/B4T17S5gc8t3/g+Z48DC9x9YOz+AeW7Z9Rzhz5p/hXhEp5/Zgl79Y4xj+w
+ev+UHPrYM3kM3v9rCFXQjx+M720z/5zP/HXz+TaH+96Pfb2zFv/iKX55KP/3/wAAAP//</cx:binary>
               </cx:geoCache>
             </cx:geography>
           </cx:layoutPr>
@@ -20679,6 +20676,209 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39310B45-EBEE-48C7-BCE9-B7B36758F033}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A24:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="9">
+    <chartFormat chart="2" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="31"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2CF1B383-DC3A-430D-8403-C112D50B642C}" name="PivotTable6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="D24:I30" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
@@ -20914,7 +21114,936 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFBB8FAA-77E6-4C3B-B12F-BDB7BF17E0A4}" name="PivotTable20" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="E52:I54" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Victims_Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="30"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24D40726-3C6D-4A05-AD2E-119F8548D637}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A1:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item h="1" x="13"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Count of Incident_ID" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="6" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="9" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09F515BF-FB2D-4251-AA18-55F51DD3987A}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="21"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F90AD5A-9B2A-4644-85DC-FA8DE4BD73EC}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="D33:G47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="2">
+        <item x="0"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="0"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="7" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="7" format="9" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="19"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="20"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6CF8C2AB-E0DE-42EF-A73D-53985BFE2762}" name="PivotTable19" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+  <location ref="A52:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="8">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="10" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="23"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA75CDE3-3222-443A-B160-2C37DF44CBCB}" name="PivotTable21" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+  <location ref="E57:I65" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="1"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Victims_Count" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="8" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="13" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="8" format="14" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="22"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="30"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A32ED14D-C4B7-4A0A-B09B-9A1DE75A1CE8}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="D3:E10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
@@ -21115,7 +22244,105 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C6CF286-2650-49F7-B140-A90F21B0F49D}" name="PivotTable22" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="J52:J53" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="2">
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="9"/>
+        <item x="2"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Victims_Count" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="48">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
+        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B062D374-7A13-4D9B-9989-7EB12C1EF355}" name="PivotTable23" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="J55:J56" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="2">
@@ -21213,688 +22440,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{24D40726-3C6D-4A05-AD2E-119F8548D637}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A1:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item h="1" x="13"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Count of Incident_ID" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="6" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="3" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FFBB8FAA-77E6-4C3B-B12F-BDB7BF17E0A4}" name="PivotTable20" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="E52:I54" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Victims_Count" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="30"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09F515BF-FB2D-4251-AA18-55F51DD3987A}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="13">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="14">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="21"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EA75CDE3-3222-443A-B160-2C37DF44CBCB}" name="PivotTable21" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
-  <location ref="E57:I65" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="1"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Victims_Count" fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="8" format="12" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="13" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="8" format="14" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="22"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="30"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C6CF286-2650-49F7-B140-A90F21B0F49D}" name="PivotTable22" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="J52:J53" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="2">
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Victims_Count" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Sum of Victims_Count"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Count of Victims_Count"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{78102D13-0DEA-46EB-B8E2-EA9B699D30D2}" name="PivotTable3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="D13:F20" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -22044,555 +22590,6 @@
   <colHierarchiesUsage count="1">
     <colHierarchyUsage hierarchyUsage="-2"/>
   </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{39310B45-EBEE-48C7-BCE9-B7B36758F033}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A24:B27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="2">
-        <item x="0"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="9">
-    <chartFormat chart="2" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="7" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="4" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="1" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="31"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F90AD5A-9B2A-4644-85DC-FA8DE4BD73EC}" name="PivotTable7" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="D33:G47" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="2">
-        <item x="0"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="7" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="7" format="9" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="19"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="20"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_nigeria_kidnapping_dataset grp.xlsx!Table1_3">
-        <x15:activeTabTopLevelEntity name="[Table1_3]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6CF8C2AB-E0DE-42EF-A73D-53985BFE2762}" name="PivotTable19" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
-  <location ref="A52:B60" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="9"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Incident_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="10" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="48">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="23"/>
-  </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
@@ -22957,10 +22954,10 @@
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
     <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
